--- a/data/RFG.MI.xlsx
+++ b/data/RFG.MI.xlsx
@@ -28524,6 +28524,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1225">
+      <c r="A1225" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1225" t="n">
+        <v>2168</v>
+      </c>
+      <c r="C1225" t="n">
+        <v>5.15999984741211</v>
+      </c>
+      <c r="D1225" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="E1225" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="F1225" t="n">
+        <v>5.17999982833862</v>
+      </c>
+      <c r="G1225" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RFG.MI.xlsx
+++ b/data/RFG.MI.xlsx
@@ -28532,7 +28532,7 @@
         <v>2168</v>
       </c>
       <c r="C1225" t="n">
-        <v>5.15999984741211</v>
+        <v>5.17999982833862</v>
       </c>
       <c r="D1225" t="n">
         <v>5.09999990463257</v>
@@ -28544,6 +28544,29 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1225" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1226" t="n">
+        <v>4733</v>
+      </c>
+      <c r="C1226" t="n">
+        <v>5.19999980926514</v>
+      </c>
+      <c r="D1226" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="E1226" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="F1226" t="n">
+        <v>5.19999980926514</v>
+      </c>
+      <c r="G1226" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RFG.MI.xlsx
+++ b/data/RFG.MI.xlsx
@@ -28570,6 +28570,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1227">
+      <c r="A1227" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1227" t="n">
+        <v>2604</v>
+      </c>
+      <c r="C1227" t="n">
+        <v>5.19999980926514</v>
+      </c>
+      <c r="D1227" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="E1227" t="n">
+        <v>5.1399998664856</v>
+      </c>
+      <c r="F1227" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="G1227" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RFG.MI.xlsx
+++ b/data/RFG.MI.xlsx
@@ -28593,6 +28593,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1228" t="n">
+        <v>120</v>
+      </c>
+      <c r="C1228" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="D1228" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="E1228" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="F1228" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="G1228" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RFG.MI.xlsx
+++ b/data/RFG.MI.xlsx
@@ -28434,22 +28434,22 @@
     </row>
     <row r="1221">
       <c r="A1221" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1221" t="n">
-        <v>10220</v>
+        <v>7000</v>
       </c>
       <c r="C1221" t="n">
-        <v>5.19999980926514</v>
+        <v>5.17999982833862</v>
       </c>
       <c r="D1221" t="n">
-        <v>5.01999998092651</v>
+        <v>4.96000003814697</v>
       </c>
       <c r="E1221" t="n">
-        <v>5.09999990463257</v>
+        <v>5.15999984741211</v>
       </c>
       <c r="F1221" t="n">
-        <v>5.19999980926514</v>
+        <v>5.17999982833862</v>
       </c>
       <c r="G1221" t="s">
         <v>7</v>
@@ -28457,22 +28457,22 @@
     </row>
     <row r="1222">
       <c r="A1222" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1222" t="n">
-        <v>597</v>
+        <v>10220</v>
       </c>
       <c r="C1222" t="n">
         <v>5.19999980926514</v>
       </c>
       <c r="D1222" t="n">
-        <v>5.11999988555908</v>
+        <v>5.01999998092651</v>
       </c>
       <c r="E1222" t="n">
-        <v>5.11999988555908</v>
+        <v>5.09999990463257</v>
       </c>
       <c r="F1222" t="n">
-        <v>5.11999988555908</v>
+        <v>5.19999980926514</v>
       </c>
       <c r="G1222" t="s">
         <v>7</v>
@@ -28480,22 +28480,22 @@
     </row>
     <row r="1223">
       <c r="A1223" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1223" t="n">
-        <v>7350</v>
+        <v>597</v>
       </c>
       <c r="C1223" t="n">
         <v>5.19999980926514</v>
       </c>
       <c r="D1223" t="n">
-        <v>5.15999984741211</v>
+        <v>5.11999988555908</v>
       </c>
       <c r="E1223" t="n">
-        <v>5.15999984741211</v>
+        <v>5.11999988555908</v>
       </c>
       <c r="F1223" t="n">
-        <v>5.19999980926514</v>
+        <v>5.11999988555908</v>
       </c>
       <c r="G1223" t="s">
         <v>7</v>
@@ -28503,22 +28503,22 @@
     </row>
     <row r="1224">
       <c r="A1224" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1224" t="n">
-        <v>1000</v>
+        <v>7350</v>
       </c>
       <c r="C1224" t="n">
-        <v>5.11999988555908</v>
+        <v>5.19999980926514</v>
       </c>
       <c r="D1224" t="n">
-        <v>5.09999990463257</v>
+        <v>5.15999984741211</v>
       </c>
       <c r="E1224" t="n">
-        <v>5.11999988555908</v>
+        <v>5.15999984741211</v>
       </c>
       <c r="F1224" t="n">
-        <v>5.09999990463257</v>
+        <v>5.19999980926514</v>
       </c>
       <c r="G1224" t="s">
         <v>7</v>
@@ -28526,22 +28526,22 @@
     </row>
     <row r="1225">
       <c r="A1225" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1225" t="n">
-        <v>2168</v>
+        <v>1000</v>
       </c>
       <c r="C1225" t="n">
-        <v>5.17999982833862</v>
+        <v>5.11999988555908</v>
       </c>
       <c r="D1225" t="n">
         <v>5.09999990463257</v>
       </c>
       <c r="E1225" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="F1225" t="n">
         <v>5.09999990463257</v>
-      </c>
-      <c r="F1225" t="n">
-        <v>5.17999982833862</v>
       </c>
       <c r="G1225" t="s">
         <v>7</v>
@@ -28549,13 +28549,13 @@
     </row>
     <row r="1226">
       <c r="A1226" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1226" t="n">
-        <v>4733</v>
+        <v>2168</v>
       </c>
       <c r="C1226" t="n">
-        <v>5.19999980926514</v>
+        <v>5.17999982833862</v>
       </c>
       <c r="D1226" t="n">
         <v>5.09999990463257</v>
@@ -28564,7 +28564,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="F1226" t="n">
-        <v>5.19999980926514</v>
+        <v>5.17999982833862</v>
       </c>
       <c r="G1226" t="s">
         <v>7</v>
@@ -28572,22 +28572,22 @@
     </row>
     <row r="1227">
       <c r="A1227" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1227" t="n">
-        <v>2604</v>
+        <v>4733</v>
       </c>
       <c r="C1227" t="n">
         <v>5.19999980926514</v>
       </c>
       <c r="D1227" t="n">
-        <v>5.11999988555908</v>
+        <v>5.09999990463257</v>
       </c>
       <c r="E1227" t="n">
-        <v>5.1399998664856</v>
+        <v>5.09999990463257</v>
       </c>
       <c r="F1227" t="n">
-        <v>5.11999988555908</v>
+        <v>5.19999980926514</v>
       </c>
       <c r="G1227" t="s">
         <v>7</v>
@@ -28595,24 +28595,47 @@
     </row>
     <row r="1228">
       <c r="A1228" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1228" t="n">
-        <v>120</v>
+        <v>2604</v>
       </c>
       <c r="C1228" t="n">
-        <v>5.09999990463257</v>
+        <v>5.19999980926514</v>
       </c>
       <c r="D1228" t="n">
-        <v>5.09999990463257</v>
+        <v>5.11999988555908</v>
       </c>
       <c r="E1228" t="n">
-        <v>5.09999990463257</v>
+        <v>5.1399998664856</v>
       </c>
       <c r="F1228" t="n">
-        <v>5.09999990463257</v>
+        <v>5.11999988555908</v>
       </c>
       <c r="G1228" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1229" t="n">
+        <v>1963</v>
+      </c>
+      <c r="C1229" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="D1229" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="E1229" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="F1229" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="G1229" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RFG.MI.xlsx
+++ b/data/RFG.MI.xlsx
@@ -473,7 +473,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G4" t="n">
-        <v>4.40178394317627</v>
+        <v>4.40178489685059</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>4.35640573501587</v>
+        <v>4.35640525817871</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G8" t="n">
-        <v>4.22934341430664</v>
+        <v>4.22934293746948</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G11" t="n">
-        <v>4.17488765716553</v>
+        <v>4.17488813400269</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>4.17488765716553</v>
+        <v>4.17488813400269</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>4.19304037094116</v>
+        <v>4.193039894104</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G16" t="n">
-        <v>4.29741191864014</v>
+        <v>4.29741239547729</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G19" t="n">
-        <v>4.44716358184814</v>
+        <v>4.4471640586853</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>4.41993570327759</v>
+        <v>4.41993618011475</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G21" t="n">
-        <v>4.60145282745361</v>
+        <v>4.60145330429077</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G22" t="n">
-        <v>4.746666431427</v>
+        <v>4.74666690826416</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G24" t="n">
-        <v>4.82834911346436</v>
+        <v>4.8283486366272</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>4.95541048049927</v>
+        <v>4.95541095733643</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G28" t="n">
-        <v>5.00078964233398</v>
+        <v>5.00079011917114</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>5.20045852661133</v>
+        <v>5.20045804977417</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>5.52718877792358</v>
+        <v>5.52718925476074</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G35" t="n">
-        <v>5.45458221435547</v>
+        <v>5.45458269119263</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G39" t="n">
-        <v>5.36382389068604</v>
+        <v>5.36382341384888</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G41" t="n">
-        <v>5.39105176925659</v>
+        <v>5.39105129241943</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G43" t="n">
-        <v>5.42735481262207</v>
+        <v>5.42735433578491</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G44" t="n">
-        <v>5.32751989364624</v>
+        <v>5.32751941680908</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G45" t="n">
-        <v>5.3547477722168</v>
+        <v>5.35474824905396</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G46" t="n">
-        <v>5.34567165374756</v>
+        <v>5.34567213058472</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>5.26398992538452</v>
+        <v>5.26398944854736</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G48" t="n">
-        <v>5.10970067977905</v>
+        <v>5.10969972610474</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>5.10062408447266</v>
+        <v>5.10062456130981</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>5.75</v>
       </c>
       <c r="G50" t="n">
-        <v>5.21861028671265</v>
+        <v>5.21860980987549</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G51" t="n">
-        <v>5.20045852661133</v>
+        <v>5.20045804977417</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>5.5</v>
       </c>
       <c r="G52" t="n">
-        <v>4.9917140007019</v>
+        <v>4.99171495437622</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G57" t="n">
-        <v>4.8555760383606</v>
+        <v>4.85557651519775</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G58" t="n">
-        <v>4.86465263366699</v>
+        <v>4.86465215682983</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G60" t="n">
-        <v>5.01894187927246</v>
+        <v>5.01894235610962</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G61" t="n">
-        <v>4.92818307876587</v>
+        <v>4.92818355560303</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>4.746666431427</v>
+        <v>4.74666690826416</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G64" t="n">
-        <v>4.8555760383606</v>
+        <v>4.85557651519775</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G65" t="n">
-        <v>4.68313550949097</v>
+        <v>4.68313503265381</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G68" t="n">
-        <v>4.67405986785889</v>
+        <v>4.67405939102173</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G70" t="n">
-        <v>4.93725967407227</v>
+        <v>4.93725919723511</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G71" t="n">
-        <v>4.68313550949097</v>
+        <v>4.68313503265381</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G72" t="n">
-        <v>4.77389430999756</v>
+        <v>4.7738938331604</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G74" t="n">
-        <v>4.78296995162964</v>
+        <v>4.78296947479248</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G75" t="n">
-        <v>4.746666431427</v>
+        <v>4.74666690826416</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G83" t="n">
-        <v>3.99337148666382</v>
+        <v>3.99337077140808</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G84" t="n">
-        <v>4.01152324676514</v>
+        <v>4.01152372360229</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>4.03421306610107</v>
+        <v>4.03421354293823</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>4.15673637390137</v>
+        <v>4.15673685073853</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G87" t="n">
-        <v>4.21119213104248</v>
+        <v>4.21119165420532</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G88" t="n">
-        <v>4.478928565979</v>
+        <v>4.47892904281616</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G90" t="n">
-        <v>4.68313550949097</v>
+        <v>4.68313503265381</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G91" t="n">
-        <v>4.48346710205078</v>
+        <v>4.48346662521362</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G93" t="n">
-        <v>4.54699850082397</v>
+        <v>4.54699802398682</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.95499992370605</v>
       </c>
       <c r="G97" t="n">
-        <v>4.49708032608032</v>
+        <v>4.49708080291748</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G98" t="n">
-        <v>4.41086053848267</v>
+        <v>4.41086006164551</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G101" t="n">
-        <v>4.35640573501587</v>
+        <v>4.35640525817871</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G102" t="n">
-        <v>4.35640573501587</v>
+        <v>4.35640525817871</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>4.2747220993042</v>
+        <v>4.27472257614136</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>4.44716358184814</v>
+        <v>4.4471640586853</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G114" t="n">
-        <v>4.46531534194946</v>
+        <v>4.46531581878662</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>4.2747220993042</v>
+        <v>4.27472257614136</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G117" t="n">
-        <v>4.18396472930908</v>
+        <v>4.18396377563477</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G118" t="n">
-        <v>4.24295711517334</v>
+        <v>4.2429575920105</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.75</v>
       </c>
       <c r="G119" t="n">
-        <v>4.31102609634399</v>
+        <v>4.31102561950684</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G120" t="n">
-        <v>3.88446140289307</v>
+        <v>3.88446116447449</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G121" t="n">
-        <v>3.81639266014099</v>
+        <v>3.81639242172241</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>3.89807462692261</v>
+        <v>3.89807534217834</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G123" t="n">
-        <v>3.88446140289307</v>
+        <v>3.88446116447449</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G124" t="n">
-        <v>3.88446140289307</v>
+        <v>3.88446116447449</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G125" t="n">
-        <v>3.92076468467712</v>
+        <v>3.92076516151428</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G127" t="n">
-        <v>4.21597480773926</v>
+        <v>4.21597528457642</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G128" t="n">
-        <v>4.29900312423706</v>
+        <v>4.2990026473999</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G129" t="n">
-        <v>4.27132701873779</v>
+        <v>4.27132749557495</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G131" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G134" t="n">
-        <v>4.37741804122925</v>
+        <v>4.37741851806641</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G136" t="n">
-        <v>4.42354488372803</v>
+        <v>4.42354536056519</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G137" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G139" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G140" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>4.24826335906982</v>
+        <v>4.24826431274414</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G142" t="n">
-        <v>4.22058773040771</v>
+        <v>4.22058725357056</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>3.89770150184631</v>
+        <v>3.89770102500916</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766568183899</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G149" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766568183899</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>4.1052713394165</v>
+        <v>4.10527038574219</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G152" t="n">
-        <v>4.14678573608398</v>
+        <v>4.14678525924683</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G153" t="n">
-        <v>3.98534202575684</v>
+        <v>3.98534250259399</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G154" t="n">
-        <v>3.92999005317688</v>
+        <v>3.92999029159546</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G155" t="n">
-        <v>4.04530715942383</v>
+        <v>4.04530668258667</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>4.05914449691772</v>
+        <v>4.05914402008057</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G164" t="n">
-        <v>3.83773636817932</v>
+        <v>3.83773684501648</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>3.89770150184631</v>
+        <v>3.89770102500916</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G168" t="n">
-        <v>3.98534202575684</v>
+        <v>3.98534250259399</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>3.925377368927</v>
+        <v>3.92537713050842</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G170" t="n">
-        <v>3.92999005317688</v>
+        <v>3.92999029159546</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G174" t="n">
-        <v>3.89308881759644</v>
+        <v>3.89308857917786</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G175" t="n">
-        <v>3.89308881759644</v>
+        <v>3.89308857917786</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G176" t="n">
-        <v>3.95305323600769</v>
+        <v>3.95305347442627</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>3.8838632106781</v>
+        <v>3.88386368751526</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G181" t="n">
-        <v>3.83773636817932</v>
+        <v>3.83773684501648</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G183" t="n">
-        <v>3.8838632106781</v>
+        <v>3.88386368751526</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G184" t="n">
-        <v>3.87463784217834</v>
+        <v>3.87463760375977</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G185" t="n">
-        <v>3.87463784217834</v>
+        <v>3.87463760375977</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G186" t="n">
-        <v>3.89308881759644</v>
+        <v>3.89308857917786</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G187" t="n">
-        <v>3.87463784217834</v>
+        <v>3.87463760375977</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G188" t="n">
-        <v>3.93921494483948</v>
+        <v>3.93921542167664</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>3.8838632106781</v>
+        <v>3.88386368751526</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>3.87463784217834</v>
+        <v>3.87463760375977</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766568183899</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G193" t="n">
-        <v>4.0130181312561</v>
+        <v>4.01301765441895</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G194" t="n">
-        <v>4.00379228591919</v>
+        <v>4.00379276275635</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>3.99456763267517</v>
+        <v>3.99456691741943</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G197" t="n">
-        <v>3.94844079017639</v>
+        <v>3.94844055175781</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G198" t="n">
-        <v>3.86080002784729</v>
+        <v>3.86080026626587</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G199" t="n">
-        <v>3.92999005317688</v>
+        <v>3.92999029159546</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>3.99917984008789</v>
+        <v>3.99918031692505</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G201" t="n">
-        <v>3.89308881759644</v>
+        <v>3.89308857917786</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G202" t="n">
-        <v>4.05914449691772</v>
+        <v>4.05914402008057</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G204" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766568183899</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G206" t="n">
-        <v>3.94844079017639</v>
+        <v>3.94844055175781</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>3.87463784217834</v>
+        <v>3.87463760375977</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>3.90231370925903</v>
+        <v>3.90231394767761</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G209" t="n">
-        <v>3.89308881759644</v>
+        <v>3.89308857917786</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G210" t="n">
-        <v>3.90692663192749</v>
+        <v>3.90692687034607</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G211" t="n">
-        <v>3.94844079017639</v>
+        <v>3.94844055175781</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>3.8838632106781</v>
+        <v>3.88386368751526</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G214" t="n">
-        <v>3.8838632106781</v>
+        <v>3.88386368751526</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G215" t="n">
-        <v>3.87463784217834</v>
+        <v>3.87463760375977</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>3.94382810592651</v>
+        <v>3.94382786750793</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G217" t="n">
-        <v>3.90692663192749</v>
+        <v>3.90692687034607</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G218" t="n">
-        <v>3.81928586959839</v>
+        <v>3.81928563117981</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G221" t="n">
-        <v>3.7916100025177</v>
+        <v>3.79161024093628</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G224" t="n">
-        <v>4.1052713394165</v>
+        <v>4.10527038574219</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>4.0130181312561</v>
+        <v>4.01301765441895</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G228" t="n">
-        <v>4.14217185974121</v>
+        <v>4.14217233657837</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G229" t="n">
-        <v>4.22058773040771</v>
+        <v>4.22058725357056</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G230" t="n">
-        <v>4.22058773040771</v>
+        <v>4.22058725357056</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G231" t="n">
-        <v>4.22058773040771</v>
+        <v>4.22058725357056</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G232" t="n">
-        <v>4.21597480773926</v>
+        <v>4.21597528457642</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G233" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G237" t="n">
-        <v>4.47428369522095</v>
+        <v>4.47428464889526</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G239" t="n">
-        <v>4.46505928039551</v>
+        <v>4.46505880355835</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G240" t="n">
-        <v>4.42354488372803</v>
+        <v>4.42354536056519</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G241" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>4.42354488372803</v>
+        <v>4.42354536056519</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>4.5388617515564</v>
+        <v>4.53886222839355</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G255" t="n">
-        <v>4.55731248855591</v>
+        <v>4.55731201171875</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G256" t="n">
-        <v>4.52041101455688</v>
+        <v>4.52041149139404</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G264" t="n">
-        <v>4.88019895553589</v>
+        <v>4.88019847869873</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G265" t="n">
-        <v>4.8894248008728</v>
+        <v>4.88942432403564</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G266" t="n">
-        <v>4.8894248008728</v>
+        <v>4.88942432403564</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>4.8894248008728</v>
+        <v>4.88942432403564</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G269" t="n">
-        <v>4.90787506103516</v>
+        <v>4.907874584198</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G270" t="n">
-        <v>4.93555021286011</v>
+        <v>4.93555068969727</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G272" t="n">
-        <v>4.8894248008728</v>
+        <v>4.88942432403564</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G273" t="n">
-        <v>4.99090242385864</v>
+        <v>4.9909029006958</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G274" t="n">
-        <v>4.99090242385864</v>
+        <v>4.9909029006958</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G275" t="n">
-        <v>4.99090242385864</v>
+        <v>4.9909029006958</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>5.5</v>
       </c>
       <c r="G278" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>5.5</v>
       </c>
       <c r="G279" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>5.5</v>
       </c>
       <c r="G282" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>5.5</v>
       </c>
       <c r="G283" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>5.5</v>
       </c>
       <c r="G285" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G286" t="n">
-        <v>5.09238195419312</v>
+        <v>5.0923810005188</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>5.5</v>
       </c>
       <c r="G287" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>5.5</v>
       </c>
       <c r="G288" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G290" t="n">
-        <v>5.08315563201904</v>
+        <v>5.0831561088562</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>5.5</v>
       </c>
       <c r="G291" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G296" t="n">
-        <v>4.90787506103516</v>
+        <v>4.907874584198</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G298" t="n">
-        <v>5.06470441818237</v>
+        <v>5.06470489501953</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>4.93555021286011</v>
+        <v>4.93555068969727</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G300" t="n">
-        <v>4.95400142669678</v>
+        <v>4.95400094985962</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G305" t="n">
-        <v>4.8894248008728</v>
+        <v>4.88942432403564</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G307" t="n">
-        <v>4.93555021286011</v>
+        <v>4.93555068969727</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>4.76949501037598</v>
+        <v>4.76949453353882</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G311" t="n">
-        <v>4.8156213760376</v>
+        <v>4.81562089920044</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G312" t="n">
-        <v>4.76949501037598</v>
+        <v>4.76949453353882</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G313" t="n">
-        <v>4.75104427337646</v>
+        <v>4.75104379653931</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>4.75104427337646</v>
+        <v>4.75104379653931</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G318" t="n">
-        <v>4.87097358703613</v>
+        <v>4.87097406387329</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G319" t="n">
-        <v>5.06470441818237</v>
+        <v>5.06470489501953</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>4.88019895553589</v>
+        <v>4.88019847869873</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>4.8894248008728</v>
+        <v>4.88942432403564</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G322" t="n">
-        <v>4.87097358703613</v>
+        <v>4.87097406387329</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G324" t="n">
-        <v>5.04625463485718</v>
+        <v>5.04625415802002</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G325" t="n">
-        <v>4.8894248008728</v>
+        <v>4.88942432403564</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G327" t="n">
-        <v>4.8156213760376</v>
+        <v>4.81562089920044</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G329" t="n">
-        <v>4.79717016220093</v>
+        <v>4.79717063903809</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>4.79717016220093</v>
+        <v>4.79717063903809</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G331" t="n">
-        <v>4.99090242385864</v>
+        <v>4.9909029006958</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>5.5</v>
       </c>
       <c r="G332" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G334" t="n">
-        <v>5.10160684585571</v>
+        <v>5.10160732269287</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G336" t="n">
-        <v>5.06470441818237</v>
+        <v>5.06470489501953</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G340" t="n">
-        <v>4.90787506103516</v>
+        <v>4.907874584198</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G343" t="n">
-        <v>4.93555021286011</v>
+        <v>4.93555068969727</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G345" t="n">
-        <v>4.86174821853638</v>
+        <v>4.86174774169922</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G348" t="n">
-        <v>4.52963638305664</v>
+        <v>4.52963590621948</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>4.75104427337646</v>
+        <v>4.75104379653931</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G353" t="n">
-        <v>4.88019895553589</v>
+        <v>4.88019847869873</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G359" t="n">
-        <v>4.8894248008728</v>
+        <v>4.88942432403564</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>4.8894248008728</v>
+        <v>4.88942432403564</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G361" t="n">
-        <v>4.8894248008728</v>
+        <v>4.88942432403564</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G366" t="n">
-        <v>5.05548000335693</v>
+        <v>5.05548048019409</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G369" t="n">
-        <v>5.09238195419312</v>
+        <v>5.0923810005188</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G370" t="n">
-        <v>5.20308494567871</v>
+        <v>5.20308542251587</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G372" t="n">
-        <v>5.42449378967285</v>
+        <v>5.42449331283569</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G373" t="n">
-        <v>5.3506908416748</v>
+        <v>5.35069036483765</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G374" t="n">
-        <v>5.2768874168396</v>
+        <v>5.27688789367676</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G375" t="n">
-        <v>5.42449378967285</v>
+        <v>5.42449331283569</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>5.3506908416748</v>
+        <v>5.35069036483765</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>5.3506908416748</v>
+        <v>5.35069036483765</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G378" t="n">
-        <v>5.25843715667725</v>
+        <v>5.25843667984009</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G379" t="n">
-        <v>5.25843715667725</v>
+        <v>5.25843667984009</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G380" t="n">
-        <v>5.2768874168396</v>
+        <v>5.27688789367676</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G382" t="n">
-        <v>5.37998819351196</v>
+        <v>5.37998867034912</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G384" t="n">
-        <v>5.47371673583984</v>
+        <v>5.473717212677</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G386" t="n">
-        <v>5.60493612289429</v>
+        <v>5.60493564605713</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G389" t="n">
-        <v>5.54869937896729</v>
+        <v>5.54869890213013</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G395" t="n">
-        <v>5.54869937896729</v>
+        <v>5.54869890213013</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G397" t="n">
-        <v>5.47371673583984</v>
+        <v>5.473717212677</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>5.58619070053101</v>
+        <v>5.58619022369385</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G399" t="n">
-        <v>5.51120805740356</v>
+        <v>5.51120758056641</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G403" t="n">
-        <v>5.58619070053101</v>
+        <v>5.58619022369385</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G404" t="n">
-        <v>5.51120805740356</v>
+        <v>5.51120758056641</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G418" t="n">
-        <v>5.54869937896729</v>
+        <v>5.54869890213013</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G419" t="n">
-        <v>5.47371673583984</v>
+        <v>5.473717212677</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G420" t="n">
-        <v>5.47371673583984</v>
+        <v>5.473717212677</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G426" t="n">
-        <v>5.37998819351196</v>
+        <v>5.37998867034912</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G429" t="n">
-        <v>5.37998819351196</v>
+        <v>5.37998867034912</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G434" t="n">
-        <v>5.47371673583984</v>
+        <v>5.473717212677</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G457" t="n">
-        <v>5.47371673583984</v>
+        <v>5.473717212677</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G460" t="n">
-        <v>5.37998819351196</v>
+        <v>5.37998867034912</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G462" t="n">
-        <v>5.54869937896729</v>
+        <v>5.54869890213013</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G464" t="n">
-        <v>5.54869937896729</v>
+        <v>5.54869890213013</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G465" t="n">
-        <v>5.54869937896729</v>
+        <v>5.54869890213013</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G476" t="n">
-        <v>5.02382278442383</v>
+        <v>5.02382230758667</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G477" t="n">
-        <v>4.93009471893311</v>
+        <v>4.93009424209595</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G480" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G482" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G483" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G485" t="n">
-        <v>4.70514678955078</v>
+        <v>4.70514726638794</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G487" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G493" t="n">
-        <v>4.56455421447754</v>
+        <v>4.5645546913147</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G498" t="n">
-        <v>4.67702865600586</v>
+        <v>4.6770281791687</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G503" t="n">
-        <v>4.87385654449463</v>
+        <v>4.87385702133179</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G508" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G511" t="n">
-        <v>5.02382278442383</v>
+        <v>5.02382230758667</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>5.5</v>
       </c>
       <c r="G512" t="n">
-        <v>5.15504169464111</v>
+        <v>5.15504121780396</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>5.5</v>
       </c>
       <c r="G514" t="n">
-        <v>5.15504169464111</v>
+        <v>5.15504121780396</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G517" t="n">
-        <v>5.06131362915039</v>
+        <v>5.06131315231323</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.5</v>
       </c>
       <c r="G518" t="n">
-        <v>5.15504169464111</v>
+        <v>5.15504121780396</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G520" t="n">
-        <v>5.02382278442383</v>
+        <v>5.02382230758667</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G523" t="n">
-        <v>4.96758556365967</v>
+        <v>4.96758508682251</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.5</v>
       </c>
       <c r="G525" t="n">
-        <v>5.15504169464111</v>
+        <v>5.15504121780396</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G529" t="n">
-        <v>4.87385654449463</v>
+        <v>4.87385702133179</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G534" t="n">
-        <v>4.87385654449463</v>
+        <v>4.87385702133179</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>4.87385654449463</v>
+        <v>4.87385702133179</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G538" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G541" t="n">
-        <v>4.87385654449463</v>
+        <v>4.87385702133179</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G542" t="n">
-        <v>4.93009471893311</v>
+        <v>4.93009424209595</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G543" t="n">
-        <v>4.87385654449463</v>
+        <v>4.87385702133179</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G544" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G549" t="n">
-        <v>4.7426381111145</v>
+        <v>4.74263763427734</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G550" t="n">
-        <v>4.70514678955078</v>
+        <v>4.70514726638794</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G556" t="n">
-        <v>4.70514678955078</v>
+        <v>4.70514726638794</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G559" t="n">
-        <v>4.63016414642334</v>
+        <v>4.6301646232605</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G562" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G564" t="n">
-        <v>4.98633146286011</v>
+        <v>4.98633098602295</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>5.06131362915039</v>
+        <v>5.06131315231323</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G566" t="n">
-        <v>5.06131362915039</v>
+        <v>5.06131315231323</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>4.25</v>
       </c>
       <c r="G572" t="n">
-        <v>3.9834406375885</v>
+        <v>3.98344087600708</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>3.94594979286194</v>
+        <v>3.9459502696991</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>3.82410359382629</v>
+        <v>3.82410335540771</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>3.94594979286194</v>
+        <v>3.9459502696991</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G585" t="n">
-        <v>4.00218629837036</v>
+        <v>4.00218677520752</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>4.25</v>
       </c>
       <c r="G586" t="n">
-        <v>3.9834406375885</v>
+        <v>3.98344087600708</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G587" t="n">
-        <v>3.92720413208008</v>
+        <v>3.92720437049866</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G591" t="n">
-        <v>3.63664770126343</v>
+        <v>3.63664746284485</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G594" t="n">
-        <v>4.00218629837036</v>
+        <v>4.00218677520752</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G598" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G599" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G600" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G603" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G604" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G608" t="n">
-        <v>4.12403345108032</v>
+        <v>4.12403297424316</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G609" t="n">
-        <v>4.00218629837036</v>
+        <v>4.00218677520752</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G610" t="n">
-        <v>4.00218629837036</v>
+        <v>4.00218677520752</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G611" t="n">
-        <v>4.05842399597168</v>
+        <v>4.05842351913452</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>4.09591484069824</v>
+        <v>4.09591436386108</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G613" t="n">
-        <v>4.09591484069824</v>
+        <v>4.09591436386108</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>4.25</v>
       </c>
       <c r="G614" t="n">
-        <v>3.9834406375885</v>
+        <v>3.98344087600708</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G616" t="n">
-        <v>3.92720413208008</v>
+        <v>3.92720437049866</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G617" t="n">
-        <v>3.87096762657166</v>
+        <v>3.87096738815308</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G630" t="n">
-        <v>3.68351149559021</v>
+        <v>3.68351125717163</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G631" t="n">
-        <v>3.66476607322693</v>
+        <v>3.66476583480835</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G632" t="n">
-        <v>3.64602041244507</v>
+        <v>3.64602017402649</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G633" t="n">
-        <v>3.63664770126343</v>
+        <v>3.63664746284485</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G634" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G635" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G636" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G637" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G638" t="n">
-        <v>3.71341037750244</v>
+        <v>3.71341013908386</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G639" t="n">
-        <v>3.71341037750244</v>
+        <v>3.71341013908386</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G640" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G641" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G642" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G646" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G649" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G651" t="n">
-        <v>3.65583801269531</v>
+        <v>3.65583825111389</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>3.65583801269531</v>
+        <v>3.65583825111389</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G654" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G656" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G659" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G660" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G661" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G662" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G664" t="n">
-        <v>3.72300601005554</v>
+        <v>3.72300577163696</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>4.12601184844971</v>
+        <v>4.12601137161255</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G669" t="n">
-        <v>4.12601184844971</v>
+        <v>4.12601137161255</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G670" t="n">
-        <v>4.12601184844971</v>
+        <v>4.12601137161255</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G676" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G680" t="n">
-        <v>4.02046203613281</v>
+        <v>4.02046251296997</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G681" t="n">
-        <v>3.99167609214783</v>
+        <v>3.99167633056641</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G683" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G687" t="n">
-        <v>3.99167609214783</v>
+        <v>3.99167633056641</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G688" t="n">
-        <v>3.99167609214783</v>
+        <v>3.99167633056641</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G689" t="n">
-        <v>3.98208093643188</v>
+        <v>3.98208069801331</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>4.03965282440186</v>
+        <v>4.03965330123901</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>4.03965282440186</v>
+        <v>4.03965330123901</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G693" t="n">
-        <v>4.03965282440186</v>
+        <v>4.03965330123901</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G695" t="n">
-        <v>3.98208093643188</v>
+        <v>3.98208069801331</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>3.98208093643188</v>
+        <v>3.98208069801331</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>3.98208093643188</v>
+        <v>3.98208069801331</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G698" t="n">
-        <v>4.02046203613281</v>
+        <v>4.02046251296997</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G700" t="n">
-        <v>3.9436993598938</v>
+        <v>3.94369959831238</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G701" t="n">
-        <v>3.9436993598938</v>
+        <v>3.94369959831238</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G709" t="n">
-        <v>3.87653160095215</v>
+        <v>3.87653183937073</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G712" t="n">
-        <v>3.93410396575928</v>
+        <v>3.9341037273407</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G713" t="n">
-        <v>3.84774589538574</v>
+        <v>3.84774565696716</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G714" t="n">
-        <v>3.79017353057861</v>
+        <v>3.79017329216003</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G715" t="n">
-        <v>3.77098274230957</v>
+        <v>3.77098250389099</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G716" t="n">
-        <v>3.75179195404053</v>
+        <v>3.75179171562195</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G717" t="n">
-        <v>3.75179195404053</v>
+        <v>3.75179171562195</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G718" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G720" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>3.91491341590881</v>
+        <v>3.91491317749023</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G724" t="n">
-        <v>4.21236991882324</v>
+        <v>4.21236944198608</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G726" t="n">
-        <v>4.21236991882324</v>
+        <v>4.21236944198608</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G728" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G732" t="n">
-        <v>4.18358373641968</v>
+        <v>4.18358421325684</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G737" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G738" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G739" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G740" t="n">
-        <v>3.99167609214783</v>
+        <v>3.99167633056641</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G745" t="n">
-        <v>3.93410396575928</v>
+        <v>3.9341037273407</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G746" t="n">
-        <v>3.93410396575928</v>
+        <v>3.9341037273407</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>3.91491341590881</v>
+        <v>3.91491317749023</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G750" t="n">
-        <v>4.0588436126709</v>
+        <v>4.05884408950806</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G751" t="n">
-        <v>3.98208093643188</v>
+        <v>3.98208069801331</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G753" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>4.03965282440186</v>
+        <v>4.03965330123901</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G755" t="n">
-        <v>3.91491341590881</v>
+        <v>3.91491317749023</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>3.63664722442627</v>
+        <v>3.63664746284485</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G769" t="n">
-        <v>3.61745643615723</v>
+        <v>3.61745667457581</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G773" t="n">
-        <v>3.61745643615723</v>
+        <v>3.61745667457581</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>3.63664722442627</v>
+        <v>3.63664746284485</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G778" t="n">
-        <v>3.63664722442627</v>
+        <v>3.63664746284485</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G784" t="n">
-        <v>3.40635848045349</v>
+        <v>3.40635824203491</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G788" t="n">
-        <v>3.65583801269531</v>
+        <v>3.65583825111389</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G802" t="n">
-        <v>3.53109836578369</v>
+        <v>3.53109812736511</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G807" t="n">
-        <v>3.53109836578369</v>
+        <v>3.53109812736511</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>3.55988430976868</v>
+        <v>3.55988454818726</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G810" t="n">
-        <v>3.60786104202271</v>
+        <v>3.60786128044128</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G811" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G812" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G813" t="n">
-        <v>3.71341037750244</v>
+        <v>3.71341013908386</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G814" t="n">
-        <v>3.79017353057861</v>
+        <v>3.79017329216003</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G815" t="n">
-        <v>3.75179195404053</v>
+        <v>3.75179171562195</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>3.91491341590881</v>
+        <v>3.91491317749023</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G819" t="n">
-        <v>4.25075149536133</v>
+        <v>4.25075101852417</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G823" t="n">
-        <v>4.25075149536133</v>
+        <v>4.25075101852417</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G824" t="n">
-        <v>4.29872798919678</v>
+        <v>4.29872846603394</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G827" t="n">
-        <v>4.26994228363037</v>
+        <v>4.26994180679321</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G836" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G837" t="n">
-        <v>4.12601184844971</v>
+        <v>4.12601137161255</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G845" t="n">
-        <v>4.12601184844971</v>
+        <v>4.12601137161255</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G846" t="n">
-        <v>4.12601184844971</v>
+        <v>4.12601137161255</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G856" t="n">
-        <v>4.21236991882324</v>
+        <v>4.21236944198608</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G858" t="n">
-        <v>4.02046203613281</v>
+        <v>4.02046251296997</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G860" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G861" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G872" t="n">
-        <v>3.91491341590881</v>
+        <v>3.91491317749023</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G873" t="n">
-        <v>3.91491341590881</v>
+        <v>3.91491317749023</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G878" t="n">
-        <v>3.97248554229736</v>
+        <v>3.97248530387878</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G879" t="n">
-        <v>3.9436993598938</v>
+        <v>3.94369959831238</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G880" t="n">
-        <v>3.99167609214783</v>
+        <v>3.99167633056641</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G881" t="n">
-        <v>3.97248554229736</v>
+        <v>3.97248530387878</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G884" t="n">
-        <v>3.98208093643188</v>
+        <v>3.98208069801331</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -32378,6 +32378,32 @@
         <v>5.07999992370605</v>
       </c>
       <c r="H1231" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1232" t="n">
+        <v>2750</v>
+      </c>
+      <c r="C1232" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1232" t="n">
+        <v>4.96000003814697</v>
+      </c>
+      <c r="E1232" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1232" t="n">
+        <v>4.96000003814697</v>
+      </c>
+      <c r="G1232" t="n">
+        <v>4.96000003814697</v>
+      </c>
+      <c r="H1232" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RFG.MI.xlsx
+++ b/data/RFG.MI.xlsx
@@ -421,7 +421,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2" t="n">
-        <v>4.62867975234985</v>
+        <v>4.62868022918701</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>5.0789999961853</v>
       </c>
       <c r="G3" t="n">
-        <v>4.60962104797363</v>
+        <v>4.60962152481079</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G4" t="n">
-        <v>4.40178489685059</v>
+        <v>4.40178394317627</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>4.35640525817871</v>
+        <v>4.35640573501587</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G8" t="n">
-        <v>4.22934293746948</v>
+        <v>4.22934341430664</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G9" t="n">
-        <v>4.07505369186401</v>
+        <v>4.07505416870117</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G10" t="n">
-        <v>4.17035007476807</v>
+        <v>4.17035055160522</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G11" t="n">
-        <v>4.17488813400269</v>
+        <v>4.17488765716553</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G12" t="n">
-        <v>4.18850231170654</v>
+        <v>4.18850183486938</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>4.17488813400269</v>
+        <v>4.17488765716553</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>4.193039894104</v>
+        <v>4.19304037094116</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G19" t="n">
-        <v>4.4471640586853</v>
+        <v>4.44716310501099</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>4.41993618011475</v>
+        <v>4.41993522644043</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G21" t="n">
-        <v>4.60145330429077</v>
+        <v>4.60145282745361</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G22" t="n">
-        <v>4.74666690826416</v>
+        <v>4.74666595458984</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G24" t="n">
-        <v>4.8283486366272</v>
+        <v>4.82834911346436</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>4.95541095733643</v>
+        <v>4.95541048049927</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>5.20045804977417</v>
+        <v>5.20045900344849</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G30" t="n">
-        <v>5.47273397445679</v>
+        <v>5.47273445129395</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G35" t="n">
-        <v>5.45458269119263</v>
+        <v>5.45458221435547</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G36" t="n">
-        <v>5.33659648895264</v>
+        <v>5.33659696578979</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>5.25491380691528</v>
+        <v>5.25491333007812</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G39" t="n">
-        <v>5.36382341384888</v>
+        <v>5.36382389068604</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G40" t="n">
-        <v>5.30936861038208</v>
+        <v>5.30936813354492</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>5.3819751739502</v>
+        <v>5.38197469711304</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G44" t="n">
-        <v>5.32751941680908</v>
+        <v>5.3275203704834</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G48" t="n">
-        <v>5.10969972610474</v>
+        <v>5.10970067977905</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>5.10062456130981</v>
+        <v>5.10062408447266</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>5.75</v>
       </c>
       <c r="G50" t="n">
-        <v>5.21860980987549</v>
+        <v>5.21861028671265</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G51" t="n">
-        <v>5.20045804977417</v>
+        <v>5.20045900344849</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>5.5</v>
       </c>
       <c r="G52" t="n">
-        <v>4.99171495437622</v>
+        <v>4.99171447753906</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G54" t="n">
-        <v>5.04616928100586</v>
+        <v>5.04616975784302</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G55" t="n">
-        <v>5.0552453994751</v>
+        <v>5.05524587631226</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G56" t="n">
-        <v>4.94633483886719</v>
+        <v>4.94633436203003</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G57" t="n">
-        <v>4.85557651519775</v>
+        <v>4.8555760383606</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G58" t="n">
-        <v>4.86465215682983</v>
+        <v>4.86465263366699</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G60" t="n">
-        <v>5.01894235610962</v>
+        <v>5.01894187927246</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G61" t="n">
-        <v>4.92818355560303</v>
+        <v>4.92818260192871</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>4.74666690826416</v>
+        <v>4.74666595458984</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G64" t="n">
-        <v>4.85557651519775</v>
+        <v>4.8555760383606</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G65" t="n">
-        <v>4.68313503265381</v>
+        <v>4.68313550949097</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G66" t="n">
-        <v>4.63775634765625</v>
+        <v>4.63775682449341</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G68" t="n">
-        <v>4.67405939102173</v>
+        <v>4.67405986785889</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G71" t="n">
-        <v>4.68313503265381</v>
+        <v>4.68313550949097</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G72" t="n">
-        <v>4.7738938331604</v>
+        <v>4.77389430999756</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G74" t="n">
-        <v>4.78296947479248</v>
+        <v>4.78296995162964</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G75" t="n">
-        <v>4.74666690826416</v>
+        <v>4.74666595458984</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>4.51977014541626</v>
+        <v>4.51977062225342</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G78" t="n">
-        <v>4.13404703140259</v>
+        <v>4.13404750823975</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.5</v>
       </c>
       <c r="G79" t="n">
-        <v>4.08412981033325</v>
+        <v>4.08413028717041</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G83" t="n">
-        <v>3.99337077140808</v>
+        <v>3.99337124824524</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G84" t="n">
-        <v>4.01152372360229</v>
+        <v>4.01152276992798</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>4.03421354293823</v>
+        <v>4.03421306610107</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>4.15673685073853</v>
+        <v>4.15673637390137</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G87" t="n">
-        <v>4.21119165420532</v>
+        <v>4.21119213104248</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G88" t="n">
-        <v>4.47892904281616</v>
+        <v>4.478928565979</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G90" t="n">
-        <v>4.68313503265381</v>
+        <v>4.68313550949097</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G91" t="n">
-        <v>4.48346662521362</v>
+        <v>4.48346710205078</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G92" t="n">
-        <v>4.53338432312012</v>
+        <v>4.53338384628296</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G93" t="n">
-        <v>4.54699802398682</v>
+        <v>4.54699850082397</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>4.51977014541626</v>
+        <v>4.51977062225342</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>4.51977014541626</v>
+        <v>4.51977062225342</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G98" t="n">
-        <v>4.41086006164551</v>
+        <v>4.41086053848267</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>4.50161838531494</v>
+        <v>4.5016188621521</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G100" t="n">
-        <v>4.45623922348022</v>
+        <v>4.45623874664307</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G101" t="n">
-        <v>4.35640525817871</v>
+        <v>4.35640573501587</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G102" t="n">
-        <v>4.35640525817871</v>
+        <v>4.35640573501587</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>4.27472257614136</v>
+        <v>4.2747220993042</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G106" t="n">
-        <v>4.42901182174683</v>
+        <v>4.42901134490967</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G107" t="n">
-        <v>4.33371591567993</v>
+        <v>4.33371543884277</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>4.4471640586853</v>
+        <v>4.44716310501099</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G111" t="n">
-        <v>4.43808746337891</v>
+        <v>4.43808698654175</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G114" t="n">
-        <v>4.46531581878662</v>
+        <v>4.4653148651123</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>4.27472257614136</v>
+        <v>4.2747220993042</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G117" t="n">
-        <v>4.18396377563477</v>
+        <v>4.18396425247192</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G118" t="n">
-        <v>4.2429575920105</v>
+        <v>4.24295711517334</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G120" t="n">
-        <v>3.88446116447449</v>
+        <v>3.88446164131165</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>3.89807534217834</v>
+        <v>3.89807486534119</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G123" t="n">
-        <v>3.88446116447449</v>
+        <v>3.88446164131165</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G124" t="n">
-        <v>3.88446116447449</v>
+        <v>3.88446164131165</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G128" t="n">
-        <v>4.2990026473999</v>
+        <v>4.29900312423706</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G129" t="n">
-        <v>4.27132749557495</v>
+        <v>4.27132701873779</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G130" t="n">
-        <v>4.23903799057007</v>
+        <v>4.23903846740723</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>4.24365091323853</v>
+        <v>4.24365043640137</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G135" t="n">
-        <v>4.37280559539795</v>
+        <v>4.37280511856079</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G136" t="n">
-        <v>4.42354536056519</v>
+        <v>4.42354488372803</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>4.24826431274414</v>
+        <v>4.24826335906982</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G142" t="n">
-        <v>4.22058725357056</v>
+        <v>4.22058773040771</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.5</v>
       </c>
       <c r="G144" t="n">
-        <v>4.15139770507812</v>
+        <v>4.15139818191528</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>3.89770102500916</v>
+        <v>3.89770150184631</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>4.10527038574219</v>
+        <v>4.1052713394165</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G153" t="n">
-        <v>3.98534250259399</v>
+        <v>3.98534226417542</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G155" t="n">
-        <v>4.04530668258667</v>
+        <v>4.04530715942383</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>4.05914402008057</v>
+        <v>4.05914449691772</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G164" t="n">
-        <v>3.83773684501648</v>
+        <v>3.83773636817932</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G165" t="n">
-        <v>3.85618710517883</v>
+        <v>3.85618734359741</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G166" t="n">
-        <v>3.84696221351624</v>
+        <v>3.84696197509766</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>3.89770102500916</v>
+        <v>3.89770150184631</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G168" t="n">
-        <v>3.98534250259399</v>
+        <v>3.98534226417542</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G176" t="n">
-        <v>3.95305347442627</v>
+        <v>3.95305323600769</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>3.88386368751526</v>
+        <v>3.88386297225952</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G181" t="n">
-        <v>3.83773684501648</v>
+        <v>3.83773636817932</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G183" t="n">
-        <v>3.88386368751526</v>
+        <v>3.88386297225952</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G184" t="n">
-        <v>3.87463760375977</v>
+        <v>3.87463808059692</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G185" t="n">
-        <v>3.87463760375977</v>
+        <v>3.87463808059692</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G187" t="n">
-        <v>3.87463760375977</v>
+        <v>3.87463808059692</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G188" t="n">
-        <v>3.93921542167664</v>
+        <v>3.93921494483948</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>3.88386368751526</v>
+        <v>3.88386297225952</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>3.87463760375977</v>
+        <v>3.87463808059692</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G194" t="n">
-        <v>4.00379276275635</v>
+        <v>4.00379228591919</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>3.99456691741943</v>
+        <v>3.99456787109375</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G196" t="n">
-        <v>3.86541223526001</v>
+        <v>3.86541247367859</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G197" t="n">
-        <v>3.94844055175781</v>
+        <v>3.94844102859497</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G198" t="n">
-        <v>3.86080026626587</v>
+        <v>3.86080002784729</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>3.99918031692505</v>
+        <v>3.99917984008789</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G202" t="n">
-        <v>4.05914402008057</v>
+        <v>4.05914449691772</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G206" t="n">
-        <v>3.94844055175781</v>
+        <v>3.94844102859497</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>3.87463760375977</v>
+        <v>3.87463808059692</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>3.90231394767761</v>
+        <v>3.90231370925903</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G210" t="n">
-        <v>3.90692687034607</v>
+        <v>3.90692663192749</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G211" t="n">
-        <v>3.94844055175781</v>
+        <v>3.94844102859497</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>3.88386368751526</v>
+        <v>3.88386297225952</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G214" t="n">
-        <v>3.88386368751526</v>
+        <v>3.88386297225952</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G215" t="n">
-        <v>3.87463760375977</v>
+        <v>3.87463808059692</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G217" t="n">
-        <v>3.90692687034607</v>
+        <v>3.90692663192749</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G218" t="n">
-        <v>3.81928563117981</v>
+        <v>3.81928586959839</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G221" t="n">
-        <v>3.79161024093628</v>
+        <v>3.7916100025177</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G224" t="n">
-        <v>4.10527038574219</v>
+        <v>4.1052713394165</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G226" t="n">
-        <v>4.24365091323853</v>
+        <v>4.24365043640137</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.5</v>
       </c>
       <c r="G227" t="n">
-        <v>4.15139770507812</v>
+        <v>4.15139818191528</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G229" t="n">
-        <v>4.22058725357056</v>
+        <v>4.22058773040771</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G230" t="n">
-        <v>4.22058725357056</v>
+        <v>4.22058773040771</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G231" t="n">
-        <v>4.22058725357056</v>
+        <v>4.22058773040771</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G235" t="n">
-        <v>4.37280559539795</v>
+        <v>4.37280511856079</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G237" t="n">
-        <v>4.47428464889526</v>
+        <v>4.47428417205811</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>4.42815780639648</v>
+        <v>4.42815828323364</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G239" t="n">
-        <v>4.46505880355835</v>
+        <v>4.46505928039551</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G240" t="n">
-        <v>4.42354536056519</v>
+        <v>4.42354488372803</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>4.42354536056519</v>
+        <v>4.42354488372803</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>4.42815780639648</v>
+        <v>4.42815828323364</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>4.42815780639648</v>
+        <v>4.42815828323364</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G250" t="n">
-        <v>4.37280559539795</v>
+        <v>4.37280511856079</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G252" t="n">
-        <v>4.26210165023804</v>
+        <v>4.2621021270752</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>4.53886222839355</v>
+        <v>4.5388617515564</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G255" t="n">
-        <v>4.55731201171875</v>
+        <v>4.55731248855591</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G256" t="n">
-        <v>4.52041149139404</v>
+        <v>4.52041101455688</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>4.42815780639648</v>
+        <v>4.42815828323364</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>4.42815780639648</v>
+        <v>4.42815828323364</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G262" t="n">
-        <v>4.74181890487671</v>
+        <v>4.74181842803955</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G265" t="n">
-        <v>4.88942432403564</v>
+        <v>4.8894248008728</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G266" t="n">
-        <v>4.88942432403564</v>
+        <v>4.8894248008728</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>4.88942432403564</v>
+        <v>4.8894248008728</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G268" t="n">
-        <v>5.02780389785767</v>
+        <v>5.02780342102051</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G269" t="n">
-        <v>4.907874584198</v>
+        <v>4.90787506103516</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G272" t="n">
-        <v>4.88942432403564</v>
+        <v>4.8894248008728</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G273" t="n">
-        <v>4.9909029006958</v>
+        <v>4.99090242385864</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G274" t="n">
-        <v>4.9909029006958</v>
+        <v>4.99090242385864</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G275" t="n">
-        <v>4.9909029006958</v>
+        <v>4.99090242385864</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>5.5</v>
       </c>
       <c r="G278" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>5.5</v>
       </c>
       <c r="G279" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G280" t="n">
-        <v>5.16618394851685</v>
+        <v>5.16618347167969</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>5.5</v>
       </c>
       <c r="G282" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>5.5</v>
       </c>
       <c r="G283" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>5.5</v>
       </c>
       <c r="G285" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G286" t="n">
-        <v>5.0923810005188</v>
+        <v>5.09238147735596</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>5.5</v>
       </c>
       <c r="G287" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>5.5</v>
       </c>
       <c r="G288" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>5.5</v>
       </c>
       <c r="G291" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G296" t="n">
-        <v>4.907874584198</v>
+        <v>4.90787506103516</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>4.98167753219604</v>
+        <v>4.98167705535889</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G300" t="n">
-        <v>4.95400094985962</v>
+        <v>4.95400142669678</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G302" t="n">
-        <v>4.94477605819702</v>
+        <v>4.94477653503418</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G305" t="n">
-        <v>4.88942432403564</v>
+        <v>4.8894248008728</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G306" t="n">
-        <v>4.94477605819702</v>
+        <v>4.94477653503418</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>4.76949453353882</v>
+        <v>4.76949501037598</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G311" t="n">
-        <v>4.81562089920044</v>
+        <v>4.8156213760376</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G312" t="n">
-        <v>4.76949453353882</v>
+        <v>4.76949501037598</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G313" t="n">
-        <v>4.75104379653931</v>
+        <v>4.75104427337646</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>4.75104379653931</v>
+        <v>4.75104427337646</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G318" t="n">
-        <v>4.87097406387329</v>
+        <v>4.87097358703613</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>4.88942432403564</v>
+        <v>4.8894248008728</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G322" t="n">
-        <v>4.87097406387329</v>
+        <v>4.87097358703613</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G323" t="n">
-        <v>4.94477605819702</v>
+        <v>4.94477653503418</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G325" t="n">
-        <v>4.88942432403564</v>
+        <v>4.8894248008728</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G327" t="n">
-        <v>4.81562089920044</v>
+        <v>4.8156213760376</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G331" t="n">
-        <v>4.9909029006958</v>
+        <v>4.99090242385864</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>5.5</v>
       </c>
       <c r="G332" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G333" t="n">
-        <v>4.98167753219604</v>
+        <v>4.98167705535889</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G334" t="n">
-        <v>5.10160732269287</v>
+        <v>5.10160684585571</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G335" t="n">
-        <v>4.98167753219604</v>
+        <v>4.98167705535889</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>4.98167753219604</v>
+        <v>4.98167705535889</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G339" t="n">
-        <v>4.98167753219604</v>
+        <v>4.98167705535889</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G340" t="n">
-        <v>4.907874584198</v>
+        <v>4.90787506103516</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G344" t="n">
-        <v>4.98167753219604</v>
+        <v>4.98167705535889</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G345" t="n">
-        <v>4.86174774169922</v>
+        <v>4.86174821853638</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G346" t="n">
-        <v>4.83407211303711</v>
+        <v>4.83407163619995</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>4.75104379653931</v>
+        <v>4.75104427337646</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G354" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G356" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G357" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G359" t="n">
-        <v>4.88942432403564</v>
+        <v>4.8894248008728</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>4.88942432403564</v>
+        <v>4.8894248008728</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G361" t="n">
-        <v>4.88942432403564</v>
+        <v>4.8894248008728</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G363" t="n">
-        <v>4.83407211303711</v>
+        <v>4.83407163619995</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G364" t="n">
-        <v>4.83407211303711</v>
+        <v>4.83407163619995</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G365" t="n">
-        <v>4.94477605819702</v>
+        <v>4.94477653503418</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G366" t="n">
-        <v>5.05548048019409</v>
+        <v>5.05548000335693</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G367" t="n">
-        <v>5.12928247451782</v>
+        <v>5.12928295135498</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G369" t="n">
-        <v>5.0923810005188</v>
+        <v>5.09238147735596</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G370" t="n">
-        <v>5.20308542251587</v>
+        <v>5.20308494567871</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G371" t="n">
-        <v>5.33224010467529</v>
+        <v>5.33223962783813</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G372" t="n">
-        <v>5.42449331283569</v>
+        <v>5.42449378967285</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G375" t="n">
-        <v>5.42449331283569</v>
+        <v>5.42449378967285</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G378" t="n">
-        <v>5.25843667984009</v>
+        <v>5.25843715667725</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G379" t="n">
-        <v>5.25843667984009</v>
+        <v>5.25843715667725</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G382" t="n">
-        <v>5.37998867034912</v>
+        <v>5.37998819351196</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G383" t="n">
-        <v>5.3424973487854</v>
+        <v>5.34249687194824</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G384" t="n">
-        <v>5.473717212677</v>
+        <v>5.47371673583984</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G386" t="n">
-        <v>5.60493564605713</v>
+        <v>5.60493612289429</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G388" t="n">
-        <v>5.52995347976685</v>
+        <v>5.529953956604</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G397" t="n">
-        <v>5.473717212677</v>
+        <v>5.47371673583984</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G399" t="n">
-        <v>5.51120758056641</v>
+        <v>5.51120853424072</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G401" t="n">
-        <v>5.52995347976685</v>
+        <v>5.529953956604</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>5.52995347976685</v>
+        <v>5.529953956604</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G404" t="n">
-        <v>5.51120758056641</v>
+        <v>5.51120853424072</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G419" t="n">
-        <v>5.473717212677</v>
+        <v>5.47371673583984</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G420" t="n">
-        <v>5.473717212677</v>
+        <v>5.47371673583984</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G423" t="n">
-        <v>5.52995347976685</v>
+        <v>5.529953956604</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G425" t="n">
-        <v>5.52995347976685</v>
+        <v>5.529953956604</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G426" t="n">
-        <v>5.37998867034912</v>
+        <v>5.37998819351196</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G429" t="n">
-        <v>5.37998867034912</v>
+        <v>5.37998819351196</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G430" t="n">
-        <v>5.3424973487854</v>
+        <v>5.34249687194824</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G431" t="n">
-        <v>5.3424973487854</v>
+        <v>5.34249687194824</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G434" t="n">
-        <v>5.473717212677</v>
+        <v>5.47371673583984</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>5.3424973487854</v>
+        <v>5.34249687194824</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G436" t="n">
-        <v>5.3424973487854</v>
+        <v>5.34249687194824</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>5.3424973487854</v>
+        <v>5.34249687194824</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G457" t="n">
-        <v>5.473717212677</v>
+        <v>5.47371673583984</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G460" t="n">
-        <v>5.37998867034912</v>
+        <v>5.37998819351196</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G461" t="n">
-        <v>5.52995347976685</v>
+        <v>5.529953956604</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G463" t="n">
-        <v>5.52995347976685</v>
+        <v>5.529953956604</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>5.3424973487854</v>
+        <v>5.34249687194824</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>5.17378711700439</v>
+        <v>5.17378664016724</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>5.09880495071411</v>
+        <v>5.09880447387695</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G476" t="n">
-        <v>5.02382230758667</v>
+        <v>5.02382278442383</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G482" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G483" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G485" t="n">
-        <v>4.70514726638794</v>
+        <v>4.70514678955078</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>4.66765546798706</v>
+        <v>4.66765594482422</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G487" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>5</v>
       </c>
       <c r="G488" t="n">
-        <v>4.6864013671875</v>
+        <v>4.68640089035034</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G489" t="n">
-        <v>4.66765546798706</v>
+        <v>4.66765594482422</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G493" t="n">
-        <v>4.5645546913147</v>
+        <v>4.56455421447754</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G495" t="n">
-        <v>4.65828275680542</v>
+        <v>4.65828323364258</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>5</v>
       </c>
       <c r="G496" t="n">
-        <v>4.6864013671875</v>
+        <v>4.68640089035034</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>5</v>
       </c>
       <c r="G497" t="n">
-        <v>4.6864013671875</v>
+        <v>4.68640089035034</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G505" t="n">
-        <v>4.85511159896851</v>
+        <v>4.85511112213135</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G509" t="n">
-        <v>4.85511159896851</v>
+        <v>4.85511112213135</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G510" t="n">
-        <v>4.91134834289551</v>
+        <v>4.91134881973267</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G511" t="n">
-        <v>5.02382230758667</v>
+        <v>5.02382278442383</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>5.5</v>
       </c>
       <c r="G512" t="n">
-        <v>5.15504121780396</v>
+        <v>5.15504169464111</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>5.5</v>
       </c>
       <c r="G514" t="n">
-        <v>5.15504121780396</v>
+        <v>5.15504169464111</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.5</v>
       </c>
       <c r="G518" t="n">
-        <v>5.15504121780396</v>
+        <v>5.15504169464111</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G520" t="n">
-        <v>5.02382230758667</v>
+        <v>5.02382278442383</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G522" t="n">
-        <v>4.91134834289551</v>
+        <v>4.91134881973267</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G523" t="n">
-        <v>4.96758508682251</v>
+        <v>4.96758556365967</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G524" t="n">
-        <v>5.09880495071411</v>
+        <v>5.09880447387695</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.5</v>
       </c>
       <c r="G525" t="n">
-        <v>5.15504121780396</v>
+        <v>5.15504169464111</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G526" t="n">
-        <v>5.09880495071411</v>
+        <v>5.09880447387695</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G527" t="n">
-        <v>4.91134834289551</v>
+        <v>4.91134881973267</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G528" t="n">
-        <v>4.91134834289551</v>
+        <v>4.91134881973267</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G530" t="n">
-        <v>4.85511159896851</v>
+        <v>4.85511112213135</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G531" t="n">
-        <v>4.85511159896851</v>
+        <v>4.85511112213135</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G536" t="n">
-        <v>4.85511159896851</v>
+        <v>4.85511112213135</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G539" t="n">
-        <v>4.85511159896851</v>
+        <v>4.85511112213135</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G545" t="n">
-        <v>4.85511159896851</v>
+        <v>4.85511112213135</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G549" t="n">
-        <v>4.74263763427734</v>
+        <v>4.7426381111145</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G550" t="n">
-        <v>4.70514726638794</v>
+        <v>4.70514678955078</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G551" t="n">
-        <v>4.66765546798706</v>
+        <v>4.66765594482422</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>5</v>
       </c>
       <c r="G553" t="n">
-        <v>4.6864013671875</v>
+        <v>4.68640089035034</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>5</v>
       </c>
       <c r="G554" t="n">
-        <v>4.6864013671875</v>
+        <v>4.68640089035034</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G556" t="n">
-        <v>4.70514726638794</v>
+        <v>4.70514678955078</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>5</v>
       </c>
       <c r="G557" t="n">
-        <v>4.6864013671875</v>
+        <v>4.68640089035034</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>5</v>
       </c>
       <c r="G558" t="n">
-        <v>4.6864013671875</v>
+        <v>4.68640089035034</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G564" t="n">
-        <v>4.98633098602295</v>
+        <v>4.98633146286011</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>5.09880495071411</v>
+        <v>5.09880447387695</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G573" t="n">
-        <v>3.9646954536438</v>
+        <v>3.96469521522522</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>4.04905080795288</v>
+        <v>4.04905128479004</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G577" t="n">
-        <v>4.04905080795288</v>
+        <v>4.04905128479004</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G578" t="n">
-        <v>3.9646954536438</v>
+        <v>3.96469521522522</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>3.9459502696991</v>
+        <v>3.94594955444336</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>3.82410335540771</v>
+        <v>3.82410359382629</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>3.9459502696991</v>
+        <v>3.94594955444336</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G585" t="n">
-        <v>4.00218677520752</v>
+        <v>4.00218629837036</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G587" t="n">
-        <v>3.92720437049866</v>
+        <v>3.9272038936615</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G591" t="n">
-        <v>3.63664746284485</v>
+        <v>3.63664770126343</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G594" t="n">
-        <v>4.00218677520752</v>
+        <v>4.00218629837036</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G598" t="n">
-        <v>4.10528802871704</v>
+        <v>4.10528755187988</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G599" t="n">
-        <v>4.10528802871704</v>
+        <v>4.10528755187988</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G600" t="n">
-        <v>4.10528802871704</v>
+        <v>4.10528755187988</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G602" t="n">
-        <v>4.04905080795288</v>
+        <v>4.04905128479004</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G603" t="n">
-        <v>4.10528802871704</v>
+        <v>4.10528755187988</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G604" t="n">
-        <v>4.10528802871704</v>
+        <v>4.10528755187988</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G609" t="n">
-        <v>4.00218677520752</v>
+        <v>4.00218629837036</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G610" t="n">
-        <v>4.00218677520752</v>
+        <v>4.00218629837036</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>4.09591436386108</v>
+        <v>4.09591484069824</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G613" t="n">
-        <v>4.09591436386108</v>
+        <v>4.09591484069824</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G616" t="n">
-        <v>3.92720437049866</v>
+        <v>3.9272038936615</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>4</v>
       </c>
       <c r="G626" t="n">
-        <v>3.74912118911743</v>
+        <v>3.74912095069885</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>4</v>
       </c>
       <c r="G627" t="n">
-        <v>3.74912118911743</v>
+        <v>3.74912095069885</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>4</v>
       </c>
       <c r="G629" t="n">
-        <v>3.74912118911743</v>
+        <v>3.74912095069885</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G630" t="n">
-        <v>3.68351125717163</v>
+        <v>3.68351149559021</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G633" t="n">
-        <v>3.63664746284485</v>
+        <v>3.63664770126343</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G634" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G635" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G636" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G637" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G638" t="n">
-        <v>3.71341013908386</v>
+        <v>3.71341037750244</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G639" t="n">
-        <v>3.71341013908386</v>
+        <v>3.71341037750244</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G640" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G641" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G642" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G646" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G649" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G651" t="n">
-        <v>3.65583825111389</v>
+        <v>3.65583801269531</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>3.65583825111389</v>
+        <v>3.65583801269531</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G654" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G656" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G659" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G660" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G661" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G662" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G664" t="n">
-        <v>3.72300577163696</v>
+        <v>3.72300601005554</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>4.12601137161255</v>
+        <v>4.12601184844971</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G669" t="n">
-        <v>4.12601137161255</v>
+        <v>4.12601184844971</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G670" t="n">
-        <v>4.12601137161255</v>
+        <v>4.12601184844971</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G676" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G680" t="n">
-        <v>4.02046251296997</v>
+        <v>4.02046203613281</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G681" t="n">
-        <v>3.99167633056641</v>
+        <v>3.99167609214783</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G683" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G687" t="n">
-        <v>3.99167633056641</v>
+        <v>3.99167609214783</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G688" t="n">
-        <v>3.99167633056641</v>
+        <v>3.99167609214783</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G689" t="n">
-        <v>3.98208069801331</v>
+        <v>3.98208093643188</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>4.03965330123901</v>
+        <v>4.03965282440186</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>4.03965330123901</v>
+        <v>4.03965282440186</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G693" t="n">
-        <v>4.03965330123901</v>
+        <v>4.03965282440186</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G695" t="n">
-        <v>3.98208069801331</v>
+        <v>3.98208093643188</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>3.98208069801331</v>
+        <v>3.98208093643188</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>3.98208069801331</v>
+        <v>3.98208093643188</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G698" t="n">
-        <v>4.02046251296997</v>
+        <v>4.02046203613281</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G700" t="n">
-        <v>3.94369959831238</v>
+        <v>3.9436993598938</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G701" t="n">
-        <v>3.94369959831238</v>
+        <v>3.9436993598938</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G709" t="n">
-        <v>3.87653183937073</v>
+        <v>3.87653160095215</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G712" t="n">
-        <v>3.9341037273407</v>
+        <v>3.93410396575928</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G713" t="n">
-        <v>3.84774565696716</v>
+        <v>3.84774589538574</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G714" t="n">
-        <v>3.79017329216003</v>
+        <v>3.79017353057861</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G715" t="n">
-        <v>3.77098250389099</v>
+        <v>3.77098274230957</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G716" t="n">
-        <v>3.75179171562195</v>
+        <v>3.75179195404053</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G717" t="n">
-        <v>3.75179171562195</v>
+        <v>3.75179195404053</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G718" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G720" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>3.91491317749023</v>
+        <v>3.91491341590881</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G724" t="n">
-        <v>4.21236944198608</v>
+        <v>4.21236991882324</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G726" t="n">
-        <v>4.21236944198608</v>
+        <v>4.21236991882324</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G728" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G732" t="n">
-        <v>4.18358421325684</v>
+        <v>4.18358373641968</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G737" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G738" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G739" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G740" t="n">
-        <v>3.99167633056641</v>
+        <v>3.99167609214783</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G745" t="n">
-        <v>3.9341037273407</v>
+        <v>3.93410396575928</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G746" t="n">
-        <v>3.9341037273407</v>
+        <v>3.93410396575928</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>3.91491317749023</v>
+        <v>3.91491341590881</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G750" t="n">
-        <v>4.05884408950806</v>
+        <v>4.0588436126709</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G751" t="n">
-        <v>3.98208069801331</v>
+        <v>3.98208093643188</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G753" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>4.03965330123901</v>
+        <v>4.03965282440186</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G755" t="n">
-        <v>3.91491317749023</v>
+        <v>3.91491341590881</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>3.63664746284485</v>
+        <v>3.63664722442627</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G769" t="n">
-        <v>3.61745667457581</v>
+        <v>3.61745643615723</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G773" t="n">
-        <v>3.61745667457581</v>
+        <v>3.61745643615723</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>3.63664746284485</v>
+        <v>3.63664722442627</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G778" t="n">
-        <v>3.63664746284485</v>
+        <v>3.63664722442627</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G784" t="n">
-        <v>3.40635824203491</v>
+        <v>3.40635848045349</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G788" t="n">
-        <v>3.65583825111389</v>
+        <v>3.65583801269531</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G802" t="n">
-        <v>3.53109812736511</v>
+        <v>3.53109836578369</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G807" t="n">
-        <v>3.53109812736511</v>
+        <v>3.53109836578369</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>3.55988454818726</v>
+        <v>3.55988430976868</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G810" t="n">
-        <v>3.60786128044128</v>
+        <v>3.60786104202271</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G811" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G812" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G813" t="n">
-        <v>3.71341013908386</v>
+        <v>3.71341037750244</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G814" t="n">
-        <v>3.79017329216003</v>
+        <v>3.79017353057861</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G815" t="n">
-        <v>3.75179171562195</v>
+        <v>3.75179195404053</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>3.91491317749023</v>
+        <v>3.91491341590881</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G819" t="n">
-        <v>4.25075101852417</v>
+        <v>4.25075149536133</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G823" t="n">
-        <v>4.25075101852417</v>
+        <v>4.25075149536133</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G824" t="n">
-        <v>4.29872846603394</v>
+        <v>4.29872798919678</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G827" t="n">
-        <v>4.26994180679321</v>
+        <v>4.26994228363037</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G836" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G837" t="n">
-        <v>4.12601137161255</v>
+        <v>4.12601184844971</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G845" t="n">
-        <v>4.12601137161255</v>
+        <v>4.12601184844971</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G846" t="n">
-        <v>4.12601137161255</v>
+        <v>4.12601184844971</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G856" t="n">
-        <v>4.21236944198608</v>
+        <v>4.21236991882324</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G858" t="n">
-        <v>4.02046251296997</v>
+        <v>4.02046203613281</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G860" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G861" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G872" t="n">
-        <v>3.91491317749023</v>
+        <v>3.91491341590881</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G873" t="n">
-        <v>3.91491317749023</v>
+        <v>3.91491341590881</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G878" t="n">
-        <v>3.97248530387878</v>
+        <v>3.97248554229736</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G879" t="n">
-        <v>3.94369959831238</v>
+        <v>3.9436993598938</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G880" t="n">
-        <v>3.99167633056641</v>
+        <v>3.99167609214783</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G881" t="n">
-        <v>3.97248530387878</v>
+        <v>3.97248554229736</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G884" t="n">
-        <v>3.98208069801331</v>
+        <v>3.98208093643188</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -32404,6 +32404,32 @@
         <v>4.96000003814697</v>
       </c>
       <c r="H1232" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1233" t="n">
+        <v>587</v>
+      </c>
+      <c r="C1233" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1233" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1233" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1233" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1233" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1233" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RFG.MI.xlsx
+++ b/data/RFG.MI.xlsx
@@ -421,7 +421,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2" t="n">
-        <v>4.62868022918701</v>
+        <v>4.62868118286133</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>5.0789999961853</v>
       </c>
       <c r="G3" t="n">
-        <v>4.60962104797363</v>
+        <v>4.60962152481079</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G4" t="n">
-        <v>4.40178394317627</v>
+        <v>4.40178442001343</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>4.26564645767212</v>
+        <v>4.26564693450928</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G9" t="n">
-        <v>4.07505369186401</v>
+        <v>4.07505416870117</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G15" t="n">
-        <v>4.26564645767212</v>
+        <v>4.26564693450928</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G16" t="n">
-        <v>4.29741191864014</v>
+        <v>4.29741239547729</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G17" t="n">
-        <v>4.26564645767212</v>
+        <v>4.26564693450928</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>4.41993618011475</v>
+        <v>4.41993570327759</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G22" t="n">
-        <v>4.74666690826416</v>
+        <v>4.74666595458984</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G23" t="n">
-        <v>4.75574207305908</v>
+        <v>4.75574254989624</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>4.84650135040283</v>
+        <v>4.84650039672852</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G26" t="n">
-        <v>4.84650135040283</v>
+        <v>4.84650039672852</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>5.52718925476074</v>
+        <v>5.5271897315979</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G32" t="n">
-        <v>5.43643093109131</v>
+        <v>5.43643045425415</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G33" t="n">
-        <v>5.43643093109131</v>
+        <v>5.43643045425415</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G34" t="n">
-        <v>5.48181056976318</v>
+        <v>5.48181009292603</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G36" t="n">
-        <v>5.33659601211548</v>
+        <v>5.33659648895264</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G41" t="n">
-        <v>5.39105176925659</v>
+        <v>5.39105129241943</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G44" t="n">
-        <v>5.32751989364624</v>
+        <v>5.3275203704834</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G46" t="n">
-        <v>5.34567213058472</v>
+        <v>5.34567165374756</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>5.26398992538452</v>
+        <v>5.26398944854736</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G48" t="n">
-        <v>5.10969972610474</v>
+        <v>5.10970020294189</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>5.10062456130981</v>
+        <v>5.10062408447266</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>5.75</v>
       </c>
       <c r="G50" t="n">
-        <v>5.21861028671265</v>
+        <v>5.2186107635498</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G53" t="n">
-        <v>5.03709411621094</v>
+        <v>5.03709363937378</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G54" t="n">
-        <v>5.04616928100586</v>
+        <v>5.04616975784302</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G56" t="n">
-        <v>4.94633436203003</v>
+        <v>4.94633483886719</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G59" t="n">
-        <v>4.87372779846191</v>
+        <v>4.87372732162476</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G60" t="n">
-        <v>5.01894235610962</v>
+        <v>5.01894187927246</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>4.74666690826416</v>
+        <v>4.74666595458984</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G66" t="n">
-        <v>4.63775634765625</v>
+        <v>4.63775682449341</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>4.87372779846191</v>
+        <v>4.87372732162476</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G72" t="n">
-        <v>4.7738938331604</v>
+        <v>4.77389430999756</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G73" t="n">
-        <v>4.84650135040283</v>
+        <v>4.84650039672852</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G74" t="n">
-        <v>4.78296947479248</v>
+        <v>4.78296995162964</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G75" t="n">
-        <v>4.74666690826416</v>
+        <v>4.74666595458984</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>4.51977062225342</v>
+        <v>4.51977014541626</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G77" t="n">
-        <v>4.13858461380005</v>
+        <v>4.13858509063721</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.5</v>
       </c>
       <c r="G79" t="n">
-        <v>4.08412981033325</v>
+        <v>4.08413028717041</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G81" t="n">
-        <v>4.07051658630371</v>
+        <v>4.07051610946655</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G83" t="n">
-        <v>3.99337124824524</v>
+        <v>3.9933717250824</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>4.03421306610107</v>
+        <v>4.03421354293823</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>4.15673685073853</v>
+        <v>4.15673637390137</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G87" t="n">
-        <v>4.21119165420532</v>
+        <v>4.21119117736816</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G92" t="n">
-        <v>4.53338479995728</v>
+        <v>4.53338384628296</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G93" t="n">
-        <v>4.54699850082397</v>
+        <v>4.54699802398682</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>4.51977062225342</v>
+        <v>4.51977014541626</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>4.51977062225342</v>
+        <v>4.51977014541626</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G100" t="n">
-        <v>4.45623922348022</v>
+        <v>4.45623874664307</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G103" t="n">
-        <v>4.34732913970947</v>
+        <v>4.34732961654663</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>4.2747220993042</v>
+        <v>4.27472257614136</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G105" t="n">
-        <v>4.36548042297363</v>
+        <v>4.36548089981079</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>4.34732913970947</v>
+        <v>4.34732961654663</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G114" t="n">
-        <v>4.46531534194946</v>
+        <v>4.4653148651123</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>4.2747220993042</v>
+        <v>4.27472257614136</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G118" t="n">
-        <v>4.2429575920105</v>
+        <v>4.24295711517334</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G120" t="n">
-        <v>3.88446140289307</v>
+        <v>3.88446116447449</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>3.89807534217834</v>
+        <v>3.89807486534119</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G123" t="n">
-        <v>3.88446140289307</v>
+        <v>3.88446116447449</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G124" t="n">
-        <v>3.88446140289307</v>
+        <v>3.88446116447449</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G125" t="n">
-        <v>3.92076516151428</v>
+        <v>3.92076468467712</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G129" t="n">
-        <v>4.27132749557495</v>
+        <v>4.27132701873779</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G131" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G133" t="n">
-        <v>4.32667922973633</v>
+        <v>4.32667875289917</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G137" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G139" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G140" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>4.24826431274414</v>
+        <v>4.24826383590698</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G143" t="n">
-        <v>4.2067494392395</v>
+        <v>4.20674991607666</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.5</v>
       </c>
       <c r="G144" t="n">
-        <v>4.15139770507812</v>
+        <v>4.15139818191528</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>4.10527086257935</v>
+        <v>4.1052713394165</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G152" t="n">
-        <v>4.14678525924683</v>
+        <v>4.14678478240967</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G153" t="n">
-        <v>3.98534226417542</v>
+        <v>3.98534178733826</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G154" t="n">
-        <v>3.92999076843262</v>
+        <v>3.92999029159546</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>4.05914449691772</v>
+        <v>4.05914497375488</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G158" t="n">
-        <v>4.04991865158081</v>
+        <v>4.04991912841797</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G159" t="n">
-        <v>3.82851099967957</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G163" t="n">
-        <v>3.82851099967957</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G168" t="n">
-        <v>3.98534226417542</v>
+        <v>3.98534178733826</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G170" t="n">
-        <v>3.92999076843262</v>
+        <v>3.92999029159546</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G171" t="n">
-        <v>4.04991865158081</v>
+        <v>4.04991912841797</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G172" t="n">
-        <v>4.04991865158081</v>
+        <v>4.04991912841797</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G176" t="n">
-        <v>3.95305371284485</v>
+        <v>3.95305323600769</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>3.88386368751526</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G179" t="n">
-        <v>4.04991865158081</v>
+        <v>4.04991912841797</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G180" t="n">
-        <v>3.82851099967957</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G183" t="n">
-        <v>3.88386368751526</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G188" t="n">
-        <v>3.93921542167664</v>
+        <v>3.93921494483948</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G189" t="n">
-        <v>4.00840520858765</v>
+        <v>4.00840473175049</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>3.88386368751526</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G193" t="n">
-        <v>4.01301765441895</v>
+        <v>4.0130181312561</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G196" t="n">
-        <v>3.86541247367859</v>
+        <v>3.86541295051575</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G198" t="n">
-        <v>3.86080002784729</v>
+        <v>3.86079978942871</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G199" t="n">
-        <v>3.92999076843262</v>
+        <v>3.92999029159546</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>3.99918031692505</v>
+        <v>3.99917984008789</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G202" t="n">
-        <v>4.05914449691772</v>
+        <v>4.05914497375488</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G203" t="n">
-        <v>4.04991865158081</v>
+        <v>4.04991912841797</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G210" t="n">
-        <v>3.90692710876465</v>
+        <v>3.90692663192749</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>3.88386368751526</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G214" t="n">
-        <v>3.88386368751526</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>3.94382762908936</v>
+        <v>3.94382786750793</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G217" t="n">
-        <v>3.90692710876465</v>
+        <v>3.90692663192749</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G218" t="n">
-        <v>3.81928586959839</v>
+        <v>3.81928610801697</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G219" t="n">
-        <v>3.82851099967957</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>3.82851099967957</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G222" t="n">
-        <v>3.82851099967957</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G224" t="n">
-        <v>4.10527086257935</v>
+        <v>4.1052713394165</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>4.01301765441895</v>
+        <v>4.0130181312561</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.5</v>
       </c>
       <c r="G227" t="n">
-        <v>4.15139770507812</v>
+        <v>4.15139818191528</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G233" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G241" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>4.53886222839355</v>
+        <v>4.5388617515564</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G264" t="n">
-        <v>4.88019895553589</v>
+        <v>4.88019847869873</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G270" t="n">
-        <v>4.93555116653442</v>
+        <v>4.93555068969727</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G273" t="n">
-        <v>4.99090242385864</v>
+        <v>4.9909029006958</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G274" t="n">
-        <v>4.99090242385864</v>
+        <v>4.9909029006958</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G275" t="n">
-        <v>4.99090242385864</v>
+        <v>4.9909029006958</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>4.93555116653442</v>
+        <v>4.93555068969727</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G303" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G304" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G307" t="n">
-        <v>4.93555116653442</v>
+        <v>4.93555068969727</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G310" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G311" t="n">
-        <v>4.81562089920044</v>
+        <v>4.8156213760376</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G317" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>4.88019895553589</v>
+        <v>4.88019847869873</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G324" t="n">
-        <v>5.04625415802002</v>
+        <v>5.04625463485718</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G327" t="n">
-        <v>4.81562089920044</v>
+        <v>4.8156213760376</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G331" t="n">
-        <v>4.99090242385864</v>
+        <v>4.9909029006958</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G341" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G342" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G343" t="n">
-        <v>4.93555116653442</v>
+        <v>4.93555068969727</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G345" t="n">
-        <v>4.86174774169922</v>
+        <v>4.86174821853638</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G347" t="n">
-        <v>4.70491743087769</v>
+        <v>4.70491790771484</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G353" t="n">
-        <v>4.88019895553589</v>
+        <v>4.88019847869873</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G354" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G356" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G357" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G371" t="n">
-        <v>5.33223962783813</v>
+        <v>5.33224010467529</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -32534,6 +32534,32 @@
         <v>5.05999994277954</v>
       </c>
       <c r="H1237" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1238" t="n">
+        <v>37181</v>
+      </c>
+      <c r="C1238" t="n">
+        <v>5.46000003814697</v>
+      </c>
+      <c r="D1238" t="n">
+        <v>5.1399998664856</v>
+      </c>
+      <c r="E1238" t="n">
+        <v>5.19999980926514</v>
+      </c>
+      <c r="F1238" t="n">
+        <v>5.1399998664856</v>
+      </c>
+      <c r="G1238" t="n">
+        <v>5.1399998664856</v>
+      </c>
+      <c r="H1238" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RFG.MI.xlsx
+++ b/data/RFG.MI.xlsx
@@ -28908,8 +28908,31 @@
       <c r="E1241" t="n">
         <v>5.05999994277954</v>
       </c>
-      <c r="F1241"/>
+      <c r="F1241" t="n">
+        <v>5.11999988555908</v>
+      </c>
       <c r="G1241" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1242" t="n">
+        <v>3050</v>
+      </c>
+      <c r="C1242" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="D1242" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1242" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="F1242"/>
+      <c r="G1242" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RFG.MI.xlsx
+++ b/data/RFG.MI.xlsx
@@ -28931,8 +28931,31 @@
       <c r="E1242" t="n">
         <v>5.03999996185303</v>
       </c>
-      <c r="F1242"/>
+      <c r="F1242" t="n">
+        <v>5.07999992370605</v>
+      </c>
       <c r="G1242" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1243" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1243" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="D1243" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1243" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="F1243"/>
+      <c r="G1243" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RFG.MI.xlsx
+++ b/data/RFG.MI.xlsx
@@ -28946,16 +28946,39 @@
         <v>16</v>
       </c>
       <c r="C1243" t="n">
-        <v>5.07999992370605</v>
+        <v>5</v>
       </c>
       <c r="D1243" t="n">
         <v>5</v>
       </c>
       <c r="E1243" t="n">
-        <v>5.03999996185303</v>
-      </c>
-      <c r="F1243"/>
+        <v>5</v>
+      </c>
+      <c r="F1243" t="n">
+        <v>5</v>
+      </c>
       <c r="G1243" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1244" t="n">
+        <v>833</v>
+      </c>
+      <c r="C1244" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1244" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1244" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1244"/>
+      <c r="G1244" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RFG.MI.xlsx
+++ b/data/RFG.MI.xlsx
@@ -28977,8 +28977,31 @@
       <c r="E1244" t="n">
         <v>5</v>
       </c>
-      <c r="F1244"/>
+      <c r="F1244" t="n">
+        <v>5</v>
+      </c>
       <c r="G1244" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1245" t="n">
+        <v>240</v>
+      </c>
+      <c r="C1245" t="n">
+        <v>4.92999982833862</v>
+      </c>
+      <c r="D1245" t="n">
+        <v>4.92999982833862</v>
+      </c>
+      <c r="E1245" t="n">
+        <v>4.92999982833862</v>
+      </c>
+      <c r="F1245"/>
+      <c r="G1245" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RFG.MI.xlsx
+++ b/data/RFG.MI.xlsx
@@ -29007,6 +29007,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1246">
+      <c r="A1246" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1246" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1246" t="n">
+        <v>4.92999982833862</v>
+      </c>
+      <c r="D1246" t="n">
+        <v>4.92999982833862</v>
+      </c>
+      <c r="E1246" t="n">
+        <v>4.92999982833862</v>
+      </c>
+      <c r="F1246" t="n">
+        <v>4.92999982833862</v>
+      </c>
+      <c r="G1246" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RFG.MI.xlsx
+++ b/data/RFG.MI.xlsx
@@ -447,7 +447,7 @@
         <v>5.0789999961853</v>
       </c>
       <c r="G3" t="n">
-        <v>4.60962057113647</v>
+        <v>4.60962104797363</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G4" t="n">
-        <v>4.40178394317627</v>
+        <v>4.40178442001343</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G5" t="n">
-        <v>4.30648803710938</v>
+        <v>4.30648756027222</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>4.26564645767212</v>
+        <v>4.26564598083496</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G8" t="n">
-        <v>4.22934341430664</v>
+        <v>4.2293438911438</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G9" t="n">
-        <v>4.07505369186401</v>
+        <v>4.07505416870117</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G11" t="n">
-        <v>4.17488813400269</v>
+        <v>4.17488861083984</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G12" t="n">
-        <v>4.18850135803223</v>
+        <v>4.18850183486938</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>4.17488813400269</v>
+        <v>4.17488861083984</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G15" t="n">
-        <v>4.26564645767212</v>
+        <v>4.26564598083496</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G17" t="n">
-        <v>4.26564645767212</v>
+        <v>4.26564598083496</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>4.84650087356567</v>
+        <v>4.84650039672852</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G26" t="n">
-        <v>4.84650087356567</v>
+        <v>4.84650039672852</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G28" t="n">
-        <v>5.00078964233398</v>
+        <v>5.00079011917114</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>5.20045852661133</v>
+        <v>5.20045804977417</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>5.52718925476074</v>
+        <v>5.5271897315979</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G36" t="n">
-        <v>5.33659696578979</v>
+        <v>5.33659648895264</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G38" t="n">
-        <v>5.31844472885132</v>
+        <v>5.31844520568848</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G48" t="n">
-        <v>5.10970020294189</v>
+        <v>5.10970067977905</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G51" t="n">
-        <v>5.20045852661133</v>
+        <v>5.20045804977417</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>5.5</v>
       </c>
       <c r="G52" t="n">
-        <v>4.99171447753906</v>
+        <v>4.9917140007019</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G56" t="n">
-        <v>4.94633483886719</v>
+        <v>4.94633436203003</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G65" t="n">
-        <v>4.68313598632812</v>
+        <v>4.68313503265381</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G66" t="n">
-        <v>4.63775634765625</v>
+        <v>4.63775587081909</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G67" t="n">
-        <v>4.57422542572021</v>
+        <v>4.57422494888306</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G71" t="n">
-        <v>4.68313598632812</v>
+        <v>4.68313503265381</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G73" t="n">
-        <v>4.84650087356567</v>
+        <v>4.84650039672852</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>4.51977014541626</v>
+        <v>4.51977062225342</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G77" t="n">
-        <v>4.13858509063721</v>
+        <v>4.13858461380005</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G78" t="n">
-        <v>4.13404750823975</v>
+        <v>4.13404703140259</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>4.5</v>
       </c>
       <c r="G79" t="n">
-        <v>4.08412981033325</v>
+        <v>4.08413028717041</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G83" t="n">
-        <v>3.99337148666382</v>
+        <v>3.9933717250824</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>4.03421306610107</v>
+        <v>4.03421258926392</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>4.15673637390137</v>
+        <v>4.15673589706421</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G87" t="n">
-        <v>4.21119117736816</v>
+        <v>4.21119165420532</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G89" t="n">
-        <v>4.57422542572021</v>
+        <v>4.57422494888306</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G90" t="n">
-        <v>4.68313598632812</v>
+        <v>4.68313503265381</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>4.51977014541626</v>
+        <v>4.51977062225342</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>4.51977014541626</v>
+        <v>4.51977062225342</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G98" t="n">
-        <v>4.41086053848267</v>
+        <v>4.41086006164551</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G103" t="n">
-        <v>4.34732866287231</v>
+        <v>4.34732913970947</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G105" t="n">
-        <v>4.36548089981079</v>
+        <v>4.36548042297363</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>4.34732866287231</v>
+        <v>4.34732913970947</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G109" t="n">
-        <v>4.40632200241089</v>
+        <v>4.40632247924805</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G112" t="n">
-        <v>4.33825349807739</v>
+        <v>4.33825397491455</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G113" t="n">
-        <v>4.37455749511719</v>
+        <v>4.37455701828003</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G114" t="n">
-        <v>4.46531534194946</v>
+        <v>4.4653148651123</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G117" t="n">
-        <v>4.18396425247192</v>
+        <v>4.18396472930908</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G118" t="n">
-        <v>4.24295711517334</v>
+        <v>4.24295663833618</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.75</v>
       </c>
       <c r="G119" t="n">
-        <v>4.31102609634399</v>
+        <v>4.31102561950684</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G120" t="n">
-        <v>3.88446187973022</v>
+        <v>3.88446164131165</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G121" t="n">
-        <v>3.81639242172241</v>
+        <v>3.81639218330383</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G123" t="n">
-        <v>3.88446187973022</v>
+        <v>3.88446164131165</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G124" t="n">
-        <v>3.88446187973022</v>
+        <v>3.88446164131165</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G125" t="n">
-        <v>3.92076444625854</v>
+        <v>3.92076468467712</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G129" t="n">
-        <v>4.27132701873779</v>
+        <v>4.27132749557495</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G135" t="n">
-        <v>4.37280511856079</v>
+        <v>4.37280559539795</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G136" t="n">
-        <v>4.42354488372803</v>
+        <v>4.42354536056519</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G138" t="n">
-        <v>4.28516530990601</v>
+        <v>4.28516483306885</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>4.25</v>
       </c>
       <c r="G146" t="n">
-        <v>3.92076444625854</v>
+        <v>3.92076468467712</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>3.89770078659058</v>
+        <v>3.89770102500916</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766568183899</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G149" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766568183899</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>4.10527086257935</v>
+        <v>4.10527038574219</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G154" t="n">
-        <v>3.92999005317688</v>
+        <v>3.92999029159546</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G155" t="n">
-        <v>4.04530715942383</v>
+        <v>4.04530668258667</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>4.05914449691772</v>
+        <v>4.05914402008057</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>3.96689105033875</v>
+        <v>3.96689128875732</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G158" t="n">
-        <v>4.04991865158081</v>
+        <v>4.04991912841797</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G159" t="n">
-        <v>3.82851099967957</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G160" t="n">
-        <v>3.91153907775879</v>
+        <v>3.91153883934021</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G161" t="n">
-        <v>3.96689105033875</v>
+        <v>3.96689128875732</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G163" t="n">
-        <v>3.82851099967957</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G166" t="n">
-        <v>3.84696197509766</v>
+        <v>3.84696221351624</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>3.89770078659058</v>
+        <v>3.89770102500916</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>3.925377368927</v>
+        <v>3.92537713050842</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G170" t="n">
-        <v>3.92999005317688</v>
+        <v>3.92999029159546</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G171" t="n">
-        <v>4.04991865158081</v>
+        <v>4.04991912841797</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G172" t="n">
-        <v>4.04991865158081</v>
+        <v>4.04991912841797</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G174" t="n">
-        <v>3.89308834075928</v>
+        <v>3.89308857917786</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G175" t="n">
-        <v>3.89308834075928</v>
+        <v>3.89308857917786</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G176" t="n">
-        <v>3.95305323600769</v>
+        <v>3.95305347442627</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>4.25</v>
       </c>
       <c r="G177" t="n">
-        <v>3.92076444625854</v>
+        <v>3.92076468467712</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>3.88386344909668</v>
+        <v>3.88386368751526</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G179" t="n">
-        <v>4.04991865158081</v>
+        <v>4.04991912841797</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G180" t="n">
-        <v>3.82851099967957</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>4.25</v>
       </c>
       <c r="G182" t="n">
-        <v>3.92076444625854</v>
+        <v>3.92076468467712</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G183" t="n">
-        <v>3.88386344909668</v>
+        <v>3.88386368751526</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G184" t="n">
-        <v>3.87463784217834</v>
+        <v>3.87463760375977</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G185" t="n">
-        <v>3.87463784217834</v>
+        <v>3.87463760375977</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G186" t="n">
-        <v>3.89308834075928</v>
+        <v>3.89308857917786</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G187" t="n">
-        <v>3.87463784217834</v>
+        <v>3.87463760375977</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>3.88386344909668</v>
+        <v>3.88386368751526</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>3.87463784217834</v>
+        <v>3.87463760375977</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766568183899</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G194" t="n">
-        <v>4.00379228591919</v>
+        <v>4.00379276275635</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>3.99456715583801</v>
+        <v>3.99456691741943</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G196" t="n">
-        <v>3.86541271209717</v>
+        <v>3.86541223526001</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G197" t="n">
-        <v>3.94844102859497</v>
+        <v>3.94844055175781</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G198" t="n">
-        <v>3.86079978942871</v>
+        <v>3.86080026626587</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G199" t="n">
-        <v>3.92999005317688</v>
+        <v>3.92999029159546</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>3.99917984008789</v>
+        <v>3.99918031692505</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G201" t="n">
-        <v>3.89308834075928</v>
+        <v>3.89308857917786</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G202" t="n">
-        <v>4.05914449691772</v>
+        <v>4.05914402008057</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G203" t="n">
-        <v>4.04991865158081</v>
+        <v>4.04991912841797</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G204" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766568183899</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G206" t="n">
-        <v>3.94844102859497</v>
+        <v>3.94844055175781</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>3.87463784217834</v>
+        <v>3.87463760375977</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>3.90231418609619</v>
+        <v>3.90231394767761</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G209" t="n">
-        <v>3.89308834075928</v>
+        <v>3.89308857917786</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G210" t="n">
-        <v>3.90692710876465</v>
+        <v>3.90692687034607</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G211" t="n">
-        <v>3.94844102859497</v>
+        <v>3.94844055175781</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>3.88386344909668</v>
+        <v>3.88386368751526</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G214" t="n">
-        <v>3.88386344909668</v>
+        <v>3.88386368751526</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G215" t="n">
-        <v>3.87463784217834</v>
+        <v>3.87463760375977</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G217" t="n">
-        <v>3.90692710876465</v>
+        <v>3.90692687034607</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G218" t="n">
-        <v>3.81928586959839</v>
+        <v>3.81928563117981</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G219" t="n">
-        <v>3.82851099967957</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>3.82851099967957</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G222" t="n">
-        <v>3.82851099967957</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G224" t="n">
-        <v>4.10527086257935</v>
+        <v>4.10527038574219</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G235" t="n">
-        <v>4.37280511856079</v>
+        <v>4.37280559539795</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>4.45583343505859</v>
+        <v>4.45583391189575</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G237" t="n">
-        <v>4.47428417205811</v>
+        <v>4.47428464889526</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>4.42815828323364</v>
+        <v>4.42815780639648</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G239" t="n">
-        <v>4.46505928039551</v>
+        <v>4.46505880355835</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G240" t="n">
-        <v>4.42354488372803</v>
+        <v>4.42354536056519</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>4.42354488372803</v>
+        <v>4.42354536056519</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G243" t="n">
-        <v>4.50196075439453</v>
+        <v>4.50196027755737</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G244" t="n">
-        <v>4.50196075439453</v>
+        <v>4.50196027755737</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G245" t="n">
-        <v>4.50196075439453</v>
+        <v>4.50196027755737</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G246" t="n">
-        <v>4.3543553352356</v>
+        <v>4.35435485839844</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>4.42815828323364</v>
+        <v>4.42815780639648</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>4.42815828323364</v>
+        <v>4.42815780639648</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G249" t="n">
-        <v>4.40970706939697</v>
+        <v>4.40970754623413</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G250" t="n">
-        <v>4.37280511856079</v>
+        <v>4.37280559539795</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G251" t="n">
-        <v>4.3543553352356</v>
+        <v>4.35435485839844</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G252" t="n">
-        <v>4.2621021270752</v>
+        <v>4.26210165023804</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G253" t="n">
-        <v>4.50196075439453</v>
+        <v>4.50196027755737</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>4.53886127471924</v>
+        <v>4.53886222839355</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G255" t="n">
-        <v>4.55731248855591</v>
+        <v>4.55731201171875</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G256" t="n">
-        <v>4.52041101455688</v>
+        <v>4.52041149139404</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>5</v>
       </c>
       <c r="G257" t="n">
-        <v>4.61266374588013</v>
+        <v>4.61266422271729</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G258" t="n">
-        <v>4.51118564605713</v>
+        <v>4.51118516921997</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>4.42815828323364</v>
+        <v>4.42815780639648</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>4.42815828323364</v>
+        <v>4.42815780639648</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G261" t="n">
-        <v>4.59882593154907</v>
+        <v>4.59882640838623</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G264" t="n">
-        <v>4.88019895553589</v>
+        <v>4.88019847869873</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G273" t="n">
-        <v>4.99090242385864</v>
+        <v>4.9909029006958</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G274" t="n">
-        <v>4.99090242385864</v>
+        <v>4.9909029006958</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G275" t="n">
-        <v>4.99090242385864</v>
+        <v>4.9909029006958</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G277" t="n">
-        <v>5.03702974319458</v>
+        <v>5.03702926635742</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>5.5</v>
       </c>
       <c r="G278" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>5.5</v>
       </c>
       <c r="G279" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G281" t="n">
-        <v>5.15695905685425</v>
+        <v>5.15695858001709</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>5.5</v>
       </c>
       <c r="G282" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>5.5</v>
       </c>
       <c r="G283" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G284" t="n">
-        <v>5.13850784301758</v>
+        <v>5.13850831985474</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>5.5</v>
       </c>
       <c r="G285" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>5.5</v>
       </c>
       <c r="G287" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>5.5</v>
       </c>
       <c r="G288" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>5.14773368835449</v>
+        <v>5.14773321151733</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>5.5</v>
       </c>
       <c r="G291" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G292" t="n">
-        <v>5.14773368835449</v>
+        <v>5.14773321151733</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G293" t="n">
-        <v>5.15695905685425</v>
+        <v>5.15695858001709</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G294" t="n">
-        <v>5.11083221435547</v>
+        <v>5.11083173751831</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>4.98167705535889</v>
+        <v>4.98167753219604</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G298" t="n">
-        <v>5.06470537185669</v>
+        <v>5.06470489501953</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>4.76949501037598</v>
+        <v>4.76949453353882</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G312" t="n">
-        <v>4.76949501037598</v>
+        <v>4.76949453353882</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G313" t="n">
-        <v>4.75104427337646</v>
+        <v>4.75104379653931</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>4.75104427337646</v>
+        <v>4.75104379653931</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G319" t="n">
-        <v>5.06470537185669</v>
+        <v>5.06470489501953</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>4.88019895553589</v>
+        <v>4.88019847869873</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G331" t="n">
-        <v>4.99090242385864</v>
+        <v>4.9909029006958</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>5.5</v>
       </c>
       <c r="G332" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G333" t="n">
-        <v>4.98167705535889</v>
+        <v>4.98167753219604</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G334" t="n">
-        <v>5.10160684585571</v>
+        <v>5.10160732269287</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G335" t="n">
-        <v>4.98167705535889</v>
+        <v>4.98167753219604</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G336" t="n">
-        <v>5.06470537185669</v>
+        <v>5.06470489501953</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>4.98167705535889</v>
+        <v>4.98167753219604</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G339" t="n">
-        <v>4.98167705535889</v>
+        <v>4.98167753219604</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G344" t="n">
-        <v>4.98167705535889</v>
+        <v>4.98167753219604</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G345" t="n">
-        <v>4.86174821853638</v>
+        <v>4.86174774169922</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G347" t="n">
-        <v>4.70491743087769</v>
+        <v>4.70491695404053</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>5</v>
       </c>
       <c r="G349" t="n">
-        <v>4.61266374588013</v>
+        <v>4.61266422271729</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>5</v>
       </c>
       <c r="G350" t="n">
-        <v>4.61266374588013</v>
+        <v>4.61266422271729</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>4.75104427337646</v>
+        <v>4.75104379653931</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G353" t="n">
-        <v>4.88019895553589</v>
+        <v>4.88019847869873</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>5.03702974319458</v>
+        <v>5.03702926635742</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G366" t="n">
-        <v>5.05548000335693</v>
+        <v>5.05548048019409</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G368" t="n">
-        <v>5.14773368835449</v>
+        <v>5.14773321151733</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G371" t="n">
-        <v>5.33223962783813</v>
+        <v>5.33224010467529</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G373" t="n">
-        <v>5.3506908416748</v>
+        <v>5.35069036483765</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G374" t="n">
-        <v>5.2768874168396</v>
+        <v>5.27688789367676</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>5.3506908416748</v>
+        <v>5.35069036483765</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>5.3506908416748</v>
+        <v>5.35069036483765</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G378" t="n">
-        <v>5.25843715667725</v>
+        <v>5.25843667984009</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G379" t="n">
-        <v>5.25843715667725</v>
+        <v>5.25843667984009</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G380" t="n">
-        <v>5.2768874168396</v>
+        <v>5.27688789367676</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G385" t="n">
-        <v>5.49246215820312</v>
+        <v>5.49246263504028</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G399" t="n">
-        <v>5.51120805740356</v>
+        <v>5.51120758056641</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G400" t="n">
-        <v>5.49246215820312</v>
+        <v>5.49246263504028</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G404" t="n">
-        <v>5.51120805740356</v>
+        <v>5.51120758056641</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G406" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G407" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G408" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G409" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G410" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G412" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G413" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G414" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G416" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G417" t="n">
-        <v>5.49246215820312</v>
+        <v>5.49246263504028</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G421" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G422" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G427" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G428" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G432" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G433" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G443" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G447" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G448" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G449" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G456" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G466" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G468" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>5.23002433776855</v>
+        <v>5.2300238609314</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>5.17378664016724</v>
+        <v>5.17378711700439</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>5.09880447387695</v>
+        <v>5.09880495071411</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G480" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G482" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G483" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>4.66765594482422</v>
+        <v>4.66765546798706</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G487" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>5</v>
       </c>
       <c r="G488" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G489" t="n">
-        <v>4.66765594482422</v>
+        <v>4.66765546798706</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>4.64890956878662</v>
+        <v>4.64891004562378</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G494" t="n">
-        <v>4.64890956878662</v>
+        <v>4.64891004562378</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G495" t="n">
-        <v>4.65828323364258</v>
+        <v>4.65828275680542</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>5</v>
       </c>
       <c r="G496" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>5</v>
       </c>
       <c r="G497" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G508" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>5.5</v>
       </c>
       <c r="G512" t="n">
-        <v>5.15504169464111</v>
+        <v>5.15504121780396</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>5.5</v>
       </c>
       <c r="G514" t="n">
-        <v>5.15504169464111</v>
+        <v>5.15504121780396</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.5</v>
       </c>
       <c r="G518" t="n">
-        <v>5.15504169464111</v>
+        <v>5.15504121780396</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G523" t="n">
-        <v>4.96758556365967</v>
+        <v>4.96758508682251</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G524" t="n">
-        <v>5.09880447387695</v>
+        <v>5.09880495071411</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.5</v>
       </c>
       <c r="G525" t="n">
-        <v>5.15504169464111</v>
+        <v>5.15504121780396</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G526" t="n">
-        <v>5.09880447387695</v>
+        <v>5.09880495071411</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G538" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G544" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G549" t="n">
-        <v>4.7426381111145</v>
+        <v>4.74263763427734</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G551" t="n">
-        <v>4.66765594482422</v>
+        <v>4.66765546798706</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>5</v>
       </c>
       <c r="G553" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>5</v>
       </c>
       <c r="G554" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>5</v>
       </c>
       <c r="G557" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>5</v>
       </c>
       <c r="G558" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G562" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>5.09880447387695</v>
+        <v>5.09880495071411</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G573" t="n">
-        <v>3.96469569206238</v>
+        <v>3.9646954536438</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G575" t="n">
-        <v>4.08654260635376</v>
+        <v>4.0865421295166</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>4.04905128479004</v>
+        <v>4.04905080795288</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G577" t="n">
-        <v>4.04905128479004</v>
+        <v>4.04905080795288</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G578" t="n">
-        <v>3.96469569206238</v>
+        <v>3.9646954536438</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>3.94595003128052</v>
+        <v>3.9459502696991</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G583" t="n">
-        <v>3.88971281051636</v>
+        <v>3.88971304893494</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>3.94595003128052</v>
+        <v>3.9459502696991</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G588" t="n">
-        <v>3.88971281051636</v>
+        <v>3.88971304893494</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G592" t="n">
-        <v>3.88971281051636</v>
+        <v>3.88971304893494</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G598" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G599" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G600" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G601" t="n">
-        <v>4.03030490875244</v>
+        <v>4.0303053855896</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G602" t="n">
-        <v>4.04905128479004</v>
+        <v>4.04905080795288</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G603" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G604" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G605" t="n">
-        <v>4.08654260635376</v>
+        <v>4.0865421295166</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G606" t="n">
-        <v>4.08654260635376</v>
+        <v>4.0865421295166</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>4.09591484069824</v>
+        <v>4.09591436386108</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G613" t="n">
-        <v>4.09591484069824</v>
+        <v>4.09591436386108</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G618" t="n">
-        <v>3.88971281051636</v>
+        <v>3.88971304893494</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G619" t="n">
-        <v>3.88971281051636</v>
+        <v>3.88971304893494</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G620" t="n">
-        <v>3.88971281051636</v>
+        <v>3.88971304893494</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G621" t="n">
-        <v>3.88971281051636</v>
+        <v>3.88971304893494</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G625" t="n">
-        <v>3.70225691795349</v>
+        <v>3.70225715637207</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>4</v>
       </c>
       <c r="G626" t="n">
-        <v>3.74912095069885</v>
+        <v>3.74912118911743</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>4</v>
       </c>
       <c r="G627" t="n">
-        <v>3.74912095069885</v>
+        <v>3.74912118911743</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G628" t="n">
-        <v>3.70225691795349</v>
+        <v>3.70225715637207</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>4</v>
       </c>
       <c r="G629" t="n">
-        <v>3.74912095069885</v>
+        <v>3.74912118911743</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G631" t="n">
-        <v>3.66476559638977</v>
+        <v>3.66476583480835</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -32820,6 +32820,32 @@
         <v>5.09999990463257</v>
       </c>
       <c r="H1248" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1249" t="n">
+        <v>1230</v>
+      </c>
+      <c r="C1249" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="D1249" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="E1249" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="F1249" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="G1249" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="H1249" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RFG.MI.xlsx
+++ b/data/RFG.MI.xlsx
@@ -447,7 +447,7 @@
         <v>5.0789999961853</v>
       </c>
       <c r="G3" t="n">
-        <v>4.60962104797363</v>
+        <v>4.60962152481079</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G5" t="n">
-        <v>4.30648756027222</v>
+        <v>4.30648803710938</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>4.26564598083496</v>
+        <v>4.26564645767212</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>4.35640525817871</v>
+        <v>4.35640573501587</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G8" t="n">
-        <v>4.2293438911438</v>
+        <v>4.22934293746948</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G9" t="n">
-        <v>4.07505416870117</v>
+        <v>4.07505369186401</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G12" t="n">
-        <v>4.18850183486938</v>
+        <v>4.18850135803223</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G15" t="n">
-        <v>4.26564598083496</v>
+        <v>4.26564645767212</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G17" t="n">
-        <v>4.26564598083496</v>
+        <v>4.26564645767212</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G18" t="n">
-        <v>4.32463979721069</v>
+        <v>4.32463932037354</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G24" t="n">
-        <v>4.82834911346436</v>
+        <v>4.8283486366272</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>4.95541095733643</v>
+        <v>4.95541143417358</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G30" t="n">
-        <v>5.47273445129395</v>
+        <v>5.47273397445679</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G34" t="n">
-        <v>5.48181009292603</v>
+        <v>5.48180961608887</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>5.3819751739502</v>
+        <v>5.38197565078735</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G43" t="n">
-        <v>5.42735481262207</v>
+        <v>5.42735433578491</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>5.10062408447266</v>
+        <v>5.1006236076355</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G53" t="n">
-        <v>5.03709363937378</v>
+        <v>5.03709316253662</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G56" t="n">
-        <v>4.94633436203003</v>
+        <v>4.94633483886719</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G59" t="n">
-        <v>4.87372827529907</v>
+        <v>4.87372779846191</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G60" t="n">
-        <v>5.01894235610962</v>
+        <v>5.01894187927246</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G65" t="n">
-        <v>4.68313503265381</v>
+        <v>4.68313550949097</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G66" t="n">
-        <v>4.63775587081909</v>
+        <v>4.63775634765625</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G67" t="n">
-        <v>4.57422494888306</v>
+        <v>4.5742244720459</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>4.87372827529907</v>
+        <v>4.87372779846191</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G70" t="n">
-        <v>4.93725919723511</v>
+        <v>4.93725967407227</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G71" t="n">
-        <v>4.68313503265381</v>
+        <v>4.68313550949097</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G72" t="n">
-        <v>4.77389478683472</v>
+        <v>4.77389430999756</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>4.51977062225342</v>
+        <v>4.51977014541626</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G78" t="n">
-        <v>4.13404703140259</v>
+        <v>4.13404655456543</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G87" t="n">
-        <v>4.21119165420532</v>
+        <v>4.21119117736816</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G88" t="n">
-        <v>4.47892904281616</v>
+        <v>4.478928565979</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G89" t="n">
-        <v>4.57422494888306</v>
+        <v>4.5742244720459</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G90" t="n">
-        <v>4.68313503265381</v>
+        <v>4.68313550949097</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G92" t="n">
-        <v>4.53338432312012</v>
+        <v>4.5333833694458</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>4.51977062225342</v>
+        <v>4.51977014541626</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>4.51977062225342</v>
+        <v>4.51977014541626</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>4.5016188621521</v>
+        <v>4.50161838531494</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G100" t="n">
-        <v>4.45623922348022</v>
+        <v>4.45623874664307</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G101" t="n">
-        <v>4.35640525817871</v>
+        <v>4.35640573501587</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G102" t="n">
-        <v>4.35640525817871</v>
+        <v>4.35640573501587</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G107" t="n">
-        <v>4.33371543884277</v>
+        <v>4.33371591567993</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G111" t="n">
-        <v>4.43808794021606</v>
+        <v>4.43808746337891</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G112" t="n">
-        <v>4.33825397491455</v>
+        <v>4.33825445175171</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G114" t="n">
-        <v>4.4653148651123</v>
+        <v>4.46531534194946</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G117" t="n">
-        <v>4.18396472930908</v>
+        <v>4.18396425247192</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G118" t="n">
-        <v>4.24295663833618</v>
+        <v>4.24295711517334</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>4.75</v>
       </c>
       <c r="G119" t="n">
-        <v>4.31102561950684</v>
+        <v>4.31102609634399</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G120" t="n">
-        <v>3.88446164131165</v>
+        <v>3.88446116447449</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G121" t="n">
-        <v>3.81639218330383</v>
+        <v>3.81639242172241</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G123" t="n">
-        <v>3.88446164131165</v>
+        <v>3.88446116447449</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G124" t="n">
-        <v>3.88446164131165</v>
+        <v>3.88446116447449</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G129" t="n">
-        <v>4.27132749557495</v>
+        <v>4.27132701873779</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G131" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G133" t="n">
-        <v>4.32667922973633</v>
+        <v>4.32667875289917</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G137" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G139" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G140" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>4.24826431274414</v>
+        <v>4.24826383590698</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G143" t="n">
-        <v>4.2067494392395</v>
+        <v>4.20674991607666</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.5</v>
       </c>
       <c r="G144" t="n">
-        <v>4.15139770507812</v>
+        <v>4.15139818191528</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>4.10527038574219</v>
+        <v>4.10527086257935</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G152" t="n">
-        <v>4.14678525924683</v>
+        <v>4.14678478240967</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G153" t="n">
-        <v>3.98534250259399</v>
+        <v>3.98534202575684</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G154" t="n">
-        <v>3.92999029159546</v>
+        <v>3.9299898147583</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>4.05914402008057</v>
+        <v>4.05914449691772</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G158" t="n">
-        <v>4.04991912841797</v>
+        <v>4.04991960525513</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G159" t="n">
-        <v>3.82851123809814</v>
+        <v>3.82851147651672</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G163" t="n">
-        <v>3.82851123809814</v>
+        <v>3.82851147651672</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G168" t="n">
-        <v>3.98534250259399</v>
+        <v>3.98534202575684</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G170" t="n">
-        <v>3.92999029159546</v>
+        <v>3.9299898147583</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G171" t="n">
-        <v>4.04991912841797</v>
+        <v>4.04991960525513</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G172" t="n">
-        <v>4.04991912841797</v>
+        <v>4.04991960525513</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G176" t="n">
-        <v>3.95305347442627</v>
+        <v>3.95305299758911</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>3.88386368751526</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G179" t="n">
-        <v>4.04991912841797</v>
+        <v>4.04991960525513</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G180" t="n">
-        <v>3.82851123809814</v>
+        <v>3.82851147651672</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G183" t="n">
-        <v>3.88386368751526</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G188" t="n">
-        <v>3.93921542167664</v>
+        <v>3.93921494483948</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G189" t="n">
-        <v>4.00840520858765</v>
+        <v>4.00840473175049</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>3.88386368751526</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G196" t="n">
-        <v>3.86541223526001</v>
+        <v>3.86541271209717</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G198" t="n">
-        <v>3.86080026626587</v>
+        <v>3.86079978942871</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G199" t="n">
-        <v>3.92999029159546</v>
+        <v>3.9299898147583</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>3.99918031692505</v>
+        <v>3.99917984008789</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G202" t="n">
-        <v>4.05914402008057</v>
+        <v>4.05914449691772</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G203" t="n">
-        <v>4.04991912841797</v>
+        <v>4.04991960525513</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G210" t="n">
-        <v>3.90692687034607</v>
+        <v>3.90692663192749</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>3.88386368751526</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G214" t="n">
-        <v>3.88386368751526</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>3.94382786750793</v>
+        <v>3.94382834434509</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G217" t="n">
-        <v>3.90692687034607</v>
+        <v>3.90692663192749</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G218" t="n">
-        <v>3.81928563117981</v>
+        <v>3.81928586959839</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G219" t="n">
-        <v>3.82851123809814</v>
+        <v>3.82851147651672</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>3.82851123809814</v>
+        <v>3.82851147651672</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G222" t="n">
-        <v>3.82851123809814</v>
+        <v>3.82851147651672</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G224" t="n">
-        <v>4.10527038574219</v>
+        <v>4.10527086257935</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>4.5</v>
       </c>
       <c r="G227" t="n">
-        <v>4.15139770507812</v>
+        <v>4.15139818191528</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G233" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G241" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>4.53886222839355</v>
+        <v>4.5388617515564</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G270" t="n">
-        <v>4.93555068969727</v>
+        <v>4.93555021286011</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G295" t="n">
-        <v>4.80639600753784</v>
+        <v>4.806396484375</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>4.93555068969727</v>
+        <v>4.93555021286011</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G303" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G304" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G307" t="n">
-        <v>4.93555068969727</v>
+        <v>4.93555021286011</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G310" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G317" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G318" t="n">
-        <v>4.87097406387329</v>
+        <v>4.87097358703613</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G322" t="n">
-        <v>4.87097406387329</v>
+        <v>4.87097358703613</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G324" t="n">
-        <v>5.04625415802002</v>
+        <v>5.04625463485718</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>4.80639600753784</v>
+        <v>4.806396484375</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G341" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G342" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G343" t="n">
-        <v>4.93555068969727</v>
+        <v>4.93555021286011</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G345" t="n">
-        <v>4.86174774169922</v>
+        <v>4.86174821853638</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G347" t="n">
-        <v>4.70491695404053</v>
+        <v>4.70491743087769</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G354" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G356" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G357" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G371" t="n">
-        <v>5.33224010467529</v>
+        <v>5.33224058151245</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -32846,6 +32846,32 @@
         <v>5.07999992370605</v>
       </c>
       <c r="H1249" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1250" t="n">
+        <v>3106</v>
+      </c>
+      <c r="C1250" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="D1250" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="E1250" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="F1250" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="G1250" t="n">
+        <v>5.07999992370605</v>
+      </c>
+      <c r="H1250" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RFG.MI.xlsx
+++ b/data/RFG.MI.xlsx
@@ -427,7 +427,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2" t="n">
-        <v>4.62868022918701</v>
+        <v>4.62868070602417</v>
       </c>
       <c r="H2" t="n">
         <v>355635</v>
@@ -456,7 +456,7 @@
         <v>5.0789999961853</v>
       </c>
       <c r="G3" t="n">
-        <v>4.60962152481079</v>
+        <v>4.60962104797363</v>
       </c>
       <c r="H3" t="n">
         <v>253124</v>
@@ -543,7 +543,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>4.26564645767212</v>
+        <v>4.26564598083496</v>
       </c>
       <c r="H6" t="n">
         <v>157332</v>
@@ -572,7 +572,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>4.35640573501587</v>
+        <v>4.35640525817871</v>
       </c>
       <c r="H7" t="n">
         <v>53988</v>
@@ -601,7 +601,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G8" t="n">
-        <v>4.22934293746948</v>
+        <v>4.22934341430664</v>
       </c>
       <c r="H8" t="n">
         <v>147200</v>
@@ -630,7 +630,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G9" t="n">
-        <v>4.07505369186401</v>
+        <v>4.07505416870117</v>
       </c>
       <c r="H9" t="n">
         <v>88738</v>
@@ -688,7 +688,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G11" t="n">
-        <v>4.17488813400269</v>
+        <v>4.174889087677</v>
       </c>
       <c r="H11" t="n">
         <v>49843</v>
@@ -746,7 +746,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>4.17488813400269</v>
+        <v>4.174889087677</v>
       </c>
       <c r="H13" t="n">
         <v>29293</v>
@@ -775,7 +775,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>4.19304037094116</v>
+        <v>4.193039894104</v>
       </c>
       <c r="H14" t="n">
         <v>6960</v>
@@ -804,7 +804,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G15" t="n">
-        <v>4.26564645767212</v>
+        <v>4.26564598083496</v>
       </c>
       <c r="H15" t="n">
         <v>56165</v>
@@ -833,7 +833,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G16" t="n">
-        <v>4.29741239547729</v>
+        <v>4.29741191864014</v>
       </c>
       <c r="H16" t="n">
         <v>16165</v>
@@ -862,7 +862,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G17" t="n">
-        <v>4.26564645767212</v>
+        <v>4.26564598083496</v>
       </c>
       <c r="H17" t="n">
         <v>15689</v>
@@ -949,7 +949,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>4.41993618011475</v>
+        <v>4.41993570327759</v>
       </c>
       <c r="H20" t="n">
         <v>14288</v>
@@ -1007,7 +1007,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G22" t="n">
-        <v>4.74666690826416</v>
+        <v>4.746666431427</v>
       </c>
       <c r="H22" t="n">
         <v>84587</v>
@@ -1065,7 +1065,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G24" t="n">
-        <v>4.8283486366272</v>
+        <v>4.82834911346436</v>
       </c>
       <c r="H24" t="n">
         <v>64828</v>
@@ -1094,7 +1094,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>4.84650087356567</v>
+        <v>4.84650039672852</v>
       </c>
       <c r="H25" t="n">
         <v>24608</v>
@@ -1123,7 +1123,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G26" t="n">
-        <v>4.84650087356567</v>
+        <v>4.84650039672852</v>
       </c>
       <c r="H26" t="n">
         <v>84199</v>
@@ -1152,7 +1152,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>4.95541143417358</v>
+        <v>4.95541095733643</v>
       </c>
       <c r="H27" t="n">
         <v>26232</v>
@@ -1239,7 +1239,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G30" t="n">
-        <v>5.47273445129395</v>
+        <v>5.47273397445679</v>
       </c>
       <c r="H30" t="n">
         <v>193631</v>
@@ -1268,7 +1268,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>5.52718925476074</v>
+        <v>5.5271897315979</v>
       </c>
       <c r="H31" t="n">
         <v>27209</v>
@@ -1384,7 +1384,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G35" t="n">
-        <v>5.45458269119263</v>
+        <v>5.45458221435547</v>
       </c>
       <c r="H35" t="n">
         <v>24789</v>
@@ -1471,7 +1471,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G38" t="n">
-        <v>5.31844472885132</v>
+        <v>5.31844520568848</v>
       </c>
       <c r="H38" t="n">
         <v>24272</v>
@@ -1529,7 +1529,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G40" t="n">
-        <v>5.30936861038208</v>
+        <v>5.30936813354492</v>
       </c>
       <c r="H40" t="n">
         <v>10863</v>
@@ -1587,7 +1587,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>5.3819751739502</v>
+        <v>5.38197565078735</v>
       </c>
       <c r="H42" t="n">
         <v>10599</v>
@@ -1616,7 +1616,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G43" t="n">
-        <v>5.42735433578491</v>
+        <v>5.42735481262207</v>
       </c>
       <c r="H43" t="n">
         <v>24833</v>
@@ -1645,7 +1645,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G44" t="n">
-        <v>5.32751989364624</v>
+        <v>5.3275203704834</v>
       </c>
       <c r="H44" t="n">
         <v>29103</v>
@@ -1703,7 +1703,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G46" t="n">
-        <v>5.34567213058472</v>
+        <v>5.34567165374756</v>
       </c>
       <c r="H46" t="n">
         <v>21861</v>
@@ -1790,7 +1790,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>5.10062456130981</v>
+        <v>5.1006236076355</v>
       </c>
       <c r="H49" t="n">
         <v>37488</v>
@@ -1819,7 +1819,7 @@
         <v>5.75</v>
       </c>
       <c r="G50" t="n">
-        <v>5.2186107635498</v>
+        <v>5.21861028671265</v>
       </c>
       <c r="H50" t="n">
         <v>53296</v>
@@ -1877,7 +1877,7 @@
         <v>5.5</v>
       </c>
       <c r="G52" t="n">
-        <v>4.99171447753906</v>
+        <v>4.9917140007019</v>
       </c>
       <c r="H52" t="n">
         <v>31337</v>
@@ -1906,7 +1906,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G53" t="n">
-        <v>5.03709363937378</v>
+        <v>5.03709316253662</v>
       </c>
       <c r="H53" t="n">
         <v>29429</v>
@@ -2080,7 +2080,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G59" t="n">
-        <v>4.87372779846191</v>
+        <v>4.87372827529907</v>
       </c>
       <c r="H59" t="n">
         <v>60004</v>
@@ -2109,7 +2109,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G60" t="n">
-        <v>5.01894187927246</v>
+        <v>5.01894235610962</v>
       </c>
       <c r="H60" t="n">
         <v>23167</v>
@@ -2196,7 +2196,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>4.74666690826416</v>
+        <v>4.746666431427</v>
       </c>
       <c r="H63" t="n">
         <v>54083</v>
@@ -2254,7 +2254,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G65" t="n">
-        <v>4.68313503265381</v>
+        <v>4.68313550949097</v>
       </c>
       <c r="H65" t="n">
         <v>14192</v>
@@ -2370,7 +2370,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>4.87372779846191</v>
+        <v>4.87372827529907</v>
       </c>
       <c r="H69" t="n">
         <v>20469</v>
@@ -2428,7 +2428,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G71" t="n">
-        <v>4.68313503265381</v>
+        <v>4.68313550949097</v>
       </c>
       <c r="H71" t="n">
         <v>21164</v>
@@ -2457,7 +2457,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G72" t="n">
-        <v>4.7738938331604</v>
+        <v>4.77389478683472</v>
       </c>
       <c r="H72" t="n">
         <v>8024</v>
@@ -2486,7 +2486,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G73" t="n">
-        <v>4.84650087356567</v>
+        <v>4.84650039672852</v>
       </c>
       <c r="H73" t="n">
         <v>6837</v>
@@ -2515,7 +2515,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G74" t="n">
-        <v>4.78296995162964</v>
+        <v>4.78296947479248</v>
       </c>
       <c r="H74" t="n">
         <v>4082</v>
@@ -2544,7 +2544,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G75" t="n">
-        <v>4.74666690826416</v>
+        <v>4.746666431427</v>
       </c>
       <c r="H75" t="n">
         <v>12871</v>
@@ -2631,7 +2631,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G78" t="n">
-        <v>4.13404750823975</v>
+        <v>4.13404703140259</v>
       </c>
       <c r="H78" t="n">
         <v>12171</v>
@@ -2660,7 +2660,7 @@
         <v>4.5</v>
       </c>
       <c r="G79" t="n">
-        <v>4.08412981033325</v>
+        <v>4.08413028717041</v>
       </c>
       <c r="H79" t="n">
         <v>23806</v>
@@ -2718,7 +2718,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G81" t="n">
-        <v>4.07051658630371</v>
+        <v>4.07051610946655</v>
       </c>
       <c r="H81" t="n">
         <v>26271</v>
@@ -2776,7 +2776,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G83" t="n">
-        <v>3.99337124824524</v>
+        <v>3.9933717250824</v>
       </c>
       <c r="H83" t="n">
         <v>14139</v>
@@ -2805,7 +2805,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G84" t="n">
-        <v>4.01152324676514</v>
+        <v>4.01152276992798</v>
       </c>
       <c r="H84" t="n">
         <v>13008</v>
@@ -2834,7 +2834,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>4.03421306610107</v>
+        <v>4.03421258926392</v>
       </c>
       <c r="H85" t="n">
         <v>9318</v>
@@ -2863,7 +2863,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>4.15673685073853</v>
+        <v>4.15673589706421</v>
       </c>
       <c r="H86" t="n">
         <v>20105</v>
@@ -2892,7 +2892,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G87" t="n">
-        <v>4.21119165420532</v>
+        <v>4.21119117736816</v>
       </c>
       <c r="H87" t="n">
         <v>12593</v>
@@ -2979,7 +2979,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G90" t="n">
-        <v>4.68313503265381</v>
+        <v>4.68313550949097</v>
       </c>
       <c r="H90" t="n">
         <v>7231</v>
@@ -3037,7 +3037,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G92" t="n">
-        <v>4.53338432312012</v>
+        <v>4.53338384628296</v>
       </c>
       <c r="H92" t="n">
         <v>1969</v>
@@ -3095,7 +3095,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G94" t="n">
-        <v>4.50615692138672</v>
+        <v>4.50615644454956</v>
       </c>
       <c r="H94" t="n">
         <v>2116</v>
@@ -3211,7 +3211,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G98" t="n">
-        <v>4.41086006164551</v>
+        <v>4.41085958480835</v>
       </c>
       <c r="H98" t="n">
         <v>2735</v>
@@ -3240,7 +3240,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>4.50161790847778</v>
+        <v>4.50161838531494</v>
       </c>
       <c r="H99" t="n">
         <v>18031</v>
@@ -3269,7 +3269,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G100" t="n">
-        <v>4.45623922348022</v>
+        <v>4.45623874664307</v>
       </c>
       <c r="H100" t="n">
         <v>1700</v>
@@ -3298,7 +3298,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G101" t="n">
-        <v>4.35640573501587</v>
+        <v>4.35640525817871</v>
       </c>
       <c r="H101" t="n">
         <v>2000</v>
@@ -3327,7 +3327,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G102" t="n">
-        <v>4.35640573501587</v>
+        <v>4.35640525817871</v>
       </c>
       <c r="H102" t="n">
         <v>1155</v>
@@ -3385,7 +3385,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>4.2747220993042</v>
+        <v>4.27472257614136</v>
       </c>
       <c r="H104" t="n">
         <v>501</v>
@@ -3414,7 +3414,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G105" t="n">
-        <v>4.36548089981079</v>
+        <v>4.36548042297363</v>
       </c>
       <c r="H105" t="n">
         <v>618</v>
@@ -3443,7 +3443,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G106" t="n">
-        <v>4.42901229858398</v>
+        <v>4.42901182174683</v>
       </c>
       <c r="H106" t="n">
         <v>317</v>
@@ -3617,7 +3617,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G112" t="n">
-        <v>4.33825349807739</v>
+        <v>4.33825397491455</v>
       </c>
       <c r="H112" t="n">
         <v>5545</v>
@@ -3675,7 +3675,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G114" t="n">
-        <v>4.4653148651123</v>
+        <v>4.46531534194946</v>
       </c>
       <c r="H114" t="n">
         <v>2900</v>
@@ -3704,7 +3704,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>4.2747220993042</v>
+        <v>4.27472257614136</v>
       </c>
       <c r="H115" t="n">
         <v>3033</v>
@@ -3733,7 +3733,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G116" t="n">
-        <v>4.29287433624268</v>
+        <v>4.29287481307983</v>
       </c>
       <c r="H116" t="n">
         <v>5190</v>
@@ -3762,7 +3762,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G117" t="n">
-        <v>4.18396377563477</v>
+        <v>4.18396425247192</v>
       </c>
       <c r="H117" t="n">
         <v>3181</v>
@@ -3878,7 +3878,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G121" t="n">
-        <v>3.81639242172241</v>
+        <v>3.81639218330383</v>
       </c>
       <c r="H121" t="n">
         <v>9794</v>
@@ -3994,7 +3994,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G125" t="n">
-        <v>3.92076516151428</v>
+        <v>3.92076468467712</v>
       </c>
       <c r="H125" t="n">
         <v>16385</v>
@@ -4168,7 +4168,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G131" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H131" t="n">
         <v>15380</v>
@@ -4226,7 +4226,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G133" t="n">
-        <v>4.32667922973633</v>
+        <v>4.32667875289917</v>
       </c>
       <c r="H133" t="n">
         <v>10570</v>
@@ -4284,7 +4284,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G135" t="n">
-        <v>4.37280511856079</v>
+        <v>4.37280559539795</v>
       </c>
       <c r="H135" t="n">
         <v>4000</v>
@@ -4313,7 +4313,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G136" t="n">
-        <v>4.42354488372803</v>
+        <v>4.42354536056519</v>
       </c>
       <c r="H136" t="n">
         <v>520</v>
@@ -4342,7 +4342,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G137" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H137" t="n">
         <v>3650</v>
@@ -4371,7 +4371,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G138" t="n">
-        <v>4.28516530990601</v>
+        <v>4.28516483306885</v>
       </c>
       <c r="H138" t="n">
         <v>7384</v>
@@ -4400,7 +4400,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G139" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H139" t="n">
         <v>2000</v>
@@ -4429,7 +4429,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G140" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>4.24826431274414</v>
+        <v>4.24826383590698</v>
       </c>
       <c r="H141" t="n">
         <v>1470</v>
@@ -4516,7 +4516,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G143" t="n">
-        <v>4.2067494392395</v>
+        <v>4.20674991607666</v>
       </c>
       <c r="H143" t="n">
         <v>17151</v>
@@ -4545,7 +4545,7 @@
         <v>4.5</v>
       </c>
       <c r="G144" t="n">
-        <v>4.15139770507812</v>
+        <v>4.15139818191528</v>
       </c>
       <c r="H144" t="n">
         <v>12389</v>
@@ -4603,7 +4603,7 @@
         <v>4.25</v>
       </c>
       <c r="G146" t="n">
-        <v>3.92076444625854</v>
+        <v>3.92076468467712</v>
       </c>
       <c r="H146" t="n">
         <v>15623</v>
@@ -4632,7 +4632,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>3.89770078659058</v>
+        <v>3.89770102500916</v>
       </c>
       <c r="H147" t="n">
         <v>8340</v>
@@ -4661,7 +4661,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766568183899</v>
       </c>
       <c r="H148" t="n">
         <v>2849</v>
@@ -4690,7 +4690,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G149" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766568183899</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G152" t="n">
-        <v>4.14678525924683</v>
+        <v>4.14678478240967</v>
       </c>
       <c r="H152" t="n">
         <v>2449</v>
@@ -4806,7 +4806,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G153" t="n">
-        <v>3.98534250259399</v>
+        <v>3.98534202575684</v>
       </c>
       <c r="H153" t="n">
         <v>8687</v>
@@ -4835,7 +4835,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G154" t="n">
-        <v>3.92999005317688</v>
+        <v>3.9299898147583</v>
       </c>
       <c r="H154" t="n">
         <v>5428</v>
@@ -4864,7 +4864,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G155" t="n">
-        <v>4.04530715942383</v>
+        <v>4.04530668258667</v>
       </c>
       <c r="H155" t="n">
         <v>3576</v>
@@ -4922,7 +4922,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>3.96689105033875</v>
+        <v>3.96689128875732</v>
       </c>
       <c r="H157" t="n">
         <v>90</v>
@@ -4951,7 +4951,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G158" t="n">
-        <v>4.04991865158081</v>
+        <v>4.04991960525513</v>
       </c>
       <c r="H158" t="n">
         <v>5</v>
@@ -4980,7 +4980,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G159" t="n">
-        <v>3.82851099967957</v>
+        <v>3.82851147651672</v>
       </c>
       <c r="H159" t="n">
         <v>11901</v>
@@ -5009,7 +5009,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G160" t="n">
-        <v>3.91153907775879</v>
+        <v>3.91153883934021</v>
       </c>
       <c r="H160" t="n">
         <v>4000</v>
@@ -5038,7 +5038,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G161" t="n">
-        <v>3.96689105033875</v>
+        <v>3.96689128875732</v>
       </c>
       <c r="H161" t="n">
         <v>1000</v>
@@ -5096,7 +5096,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G163" t="n">
-        <v>3.82851099967957</v>
+        <v>3.82851147651672</v>
       </c>
       <c r="H163" t="n">
         <v>5720</v>
@@ -5183,7 +5183,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G166" t="n">
-        <v>3.84696197509766</v>
+        <v>3.84696221351624</v>
       </c>
       <c r="H166" t="n">
         <v>612</v>
@@ -5212,7 +5212,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>3.89770078659058</v>
+        <v>3.89770102500916</v>
       </c>
       <c r="H167" t="n">
         <v>205</v>
@@ -5241,7 +5241,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G168" t="n">
-        <v>3.98534250259399</v>
+        <v>3.98534202575684</v>
       </c>
       <c r="H168" t="n">
         <v>5404</v>
@@ -5270,7 +5270,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>3.925377368927</v>
+        <v>3.92537713050842</v>
       </c>
       <c r="H169" t="n">
         <v>2375</v>
@@ -5299,7 +5299,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G170" t="n">
-        <v>3.92999005317688</v>
+        <v>3.9299898147583</v>
       </c>
       <c r="H170" t="n">
         <v>10150</v>
@@ -5328,7 +5328,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G171" t="n">
-        <v>4.04991865158081</v>
+        <v>4.04991960525513</v>
       </c>
       <c r="H171" t="n">
         <v>2250</v>
@@ -5357,7 +5357,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G172" t="n">
-        <v>4.04991865158081</v>
+        <v>4.04991960525513</v>
       </c>
       <c r="H172" t="n">
         <v>520</v>
@@ -5415,7 +5415,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G174" t="n">
-        <v>3.89308834075928</v>
+        <v>3.89308857917786</v>
       </c>
       <c r="H174" t="n">
         <v>3424</v>
@@ -5444,7 +5444,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G175" t="n">
-        <v>3.89308834075928</v>
+        <v>3.89308857917786</v>
       </c>
       <c r="H175" t="n">
         <v>470</v>
@@ -5473,7 +5473,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G176" t="n">
-        <v>3.95305323600769</v>
+        <v>3.95305299758911</v>
       </c>
       <c r="H176" t="n">
         <v>1056</v>
@@ -5502,7 +5502,7 @@
         <v>4.25</v>
       </c>
       <c r="G177" t="n">
-        <v>3.92076444625854</v>
+        <v>3.92076468467712</v>
       </c>
       <c r="H177" t="n">
         <v>3092</v>
@@ -5531,7 +5531,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>3.88386344909668</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H178" t="n">
         <v>5254</v>
@@ -5560,7 +5560,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G179" t="n">
-        <v>4.04991865158081</v>
+        <v>4.04991960525513</v>
       </c>
       <c r="H179" t="n">
         <v>3005</v>
@@ -5589,7 +5589,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G180" t="n">
-        <v>3.82851099967957</v>
+        <v>3.82851147651672</v>
       </c>
       <c r="H180" t="n">
         <v>6092</v>
@@ -5647,7 +5647,7 @@
         <v>4.25</v>
       </c>
       <c r="G182" t="n">
-        <v>3.92076444625854</v>
+        <v>3.92076468467712</v>
       </c>
       <c r="H182" t="n">
         <v>4226</v>
@@ -5676,7 +5676,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G183" t="n">
-        <v>3.88386344909668</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H183" t="n">
         <v>11079</v>
@@ -5705,7 +5705,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G184" t="n">
-        <v>3.87463784217834</v>
+        <v>3.87463760375977</v>
       </c>
       <c r="H184" t="n">
         <v>508</v>
@@ -5734,7 +5734,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G185" t="n">
-        <v>3.87463784217834</v>
+        <v>3.87463760375977</v>
       </c>
       <c r="H185" t="n">
         <v>4806</v>
@@ -5763,7 +5763,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G186" t="n">
-        <v>3.89308834075928</v>
+        <v>3.89308857917786</v>
       </c>
       <c r="H186" t="n">
         <v>13086</v>
@@ -5792,7 +5792,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G187" t="n">
-        <v>3.87463784217834</v>
+        <v>3.87463760375977</v>
       </c>
       <c r="H187" t="n">
         <v>1555</v>
@@ -5821,7 +5821,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G188" t="n">
-        <v>3.93921542167664</v>
+        <v>3.93921494483948</v>
       </c>
       <c r="H188" t="n">
         <v>2507</v>
@@ -5850,7 +5850,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G189" t="n">
-        <v>4.00840520858765</v>
+        <v>4.00840473175049</v>
       </c>
       <c r="H189" t="n">
         <v>3667</v>
@@ -5879,7 +5879,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>3.88386344909668</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H190" t="n">
         <v>1237</v>
@@ -5908,7 +5908,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>3.87463784217834</v>
+        <v>3.87463760375977</v>
       </c>
       <c r="H191" t="n">
         <v>3347</v>
@@ -5937,7 +5937,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766568183899</v>
       </c>
       <c r="H192" t="n">
         <v>3183</v>
@@ -5995,7 +5995,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G194" t="n">
-        <v>4.00379228591919</v>
+        <v>4.00379276275635</v>
       </c>
       <c r="H194" t="n">
         <v>1199</v>
@@ -6024,7 +6024,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>3.99456715583801</v>
+        <v>3.99456691741943</v>
       </c>
       <c r="H195" t="n">
         <v>131</v>
@@ -6082,7 +6082,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G197" t="n">
-        <v>3.94844102859497</v>
+        <v>3.94844055175781</v>
       </c>
       <c r="H197" t="n">
         <v>2149</v>
@@ -6140,7 +6140,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G199" t="n">
-        <v>3.92999005317688</v>
+        <v>3.9299898147583</v>
       </c>
       <c r="H199" t="n">
         <v>2982</v>
@@ -6198,7 +6198,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G201" t="n">
-        <v>3.89308834075928</v>
+        <v>3.89308857917786</v>
       </c>
       <c r="H201" t="n">
         <v>1122</v>
@@ -6256,7 +6256,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G203" t="n">
-        <v>4.04991865158081</v>
+        <v>4.04991960525513</v>
       </c>
       <c r="H203" t="n">
         <v>24810</v>
@@ -6285,7 +6285,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G204" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766568183899</v>
       </c>
       <c r="H204" t="n">
         <v>5370</v>
@@ -6343,7 +6343,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G206" t="n">
-        <v>3.94844102859497</v>
+        <v>3.94844055175781</v>
       </c>
       <c r="H206" t="n">
         <v>5295</v>
@@ -6372,7 +6372,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>3.87463784217834</v>
+        <v>3.87463760375977</v>
       </c>
       <c r="H207" t="n">
         <v>6451</v>
@@ -6401,7 +6401,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>3.90231418609619</v>
+        <v>3.90231394767761</v>
       </c>
       <c r="H208" t="n">
         <v>1430</v>
@@ -6430,7 +6430,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G209" t="n">
-        <v>3.89308834075928</v>
+        <v>3.89308857917786</v>
       </c>
       <c r="H209" t="n">
         <v>7711</v>
@@ -6459,7 +6459,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G210" t="n">
-        <v>3.90692710876465</v>
+        <v>3.90692663192749</v>
       </c>
       <c r="H210" t="n">
         <v>2126</v>
@@ -6488,7 +6488,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G211" t="n">
-        <v>3.94844102859497</v>
+        <v>3.94844055175781</v>
       </c>
       <c r="H211" t="n">
         <v>5037</v>
@@ -6546,7 +6546,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>3.88386344909668</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H213" t="n">
         <v>1793</v>
@@ -6575,7 +6575,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G214" t="n">
-        <v>3.88386344909668</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H214" t="n">
         <v>63</v>
@@ -6604,7 +6604,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G215" t="n">
-        <v>3.87463784217834</v>
+        <v>3.87463760375977</v>
       </c>
       <c r="H215" t="n">
         <v>5793</v>
@@ -6633,7 +6633,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>3.94382786750793</v>
+        <v>3.94382834434509</v>
       </c>
       <c r="H216" t="n">
         <v>1</v>
@@ -6662,7 +6662,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G217" t="n">
-        <v>3.90692710876465</v>
+        <v>3.90692663192749</v>
       </c>
       <c r="H217" t="n">
         <v>601</v>
@@ -6720,7 +6720,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G219" t="n">
-        <v>3.82851099967957</v>
+        <v>3.82851147651672</v>
       </c>
       <c r="H219" t="n">
         <v>650</v>
@@ -6749,7 +6749,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>3.82851099967957</v>
+        <v>3.82851147651672</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G222" t="n">
-        <v>3.82851099967957</v>
+        <v>3.82851147651672</v>
       </c>
       <c r="H222" t="n">
         <v>400</v>
@@ -6952,7 +6952,7 @@
         <v>4.5</v>
       </c>
       <c r="G227" t="n">
-        <v>4.15139770507812</v>
+        <v>4.15139818191528</v>
       </c>
       <c r="H227" t="n">
         <v>5590</v>
@@ -7126,7 +7126,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G233" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H233" t="n">
         <v>12462</v>
@@ -7155,7 +7155,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H234" t="n">
         <v>15005</v>
@@ -7184,7 +7184,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G235" t="n">
-        <v>4.37280511856079</v>
+        <v>4.37280559539795</v>
       </c>
       <c r="H235" t="n">
         <v>17132</v>
@@ -7213,7 +7213,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>4.45583343505859</v>
+        <v>4.45583391189575</v>
       </c>
       <c r="H236" t="n">
         <v>4300</v>
@@ -7242,7 +7242,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G237" t="n">
-        <v>4.47428417205811</v>
+        <v>4.47428464889526</v>
       </c>
       <c r="H237" t="n">
         <v>567</v>
@@ -7271,7 +7271,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>4.42815828323364</v>
+        <v>4.42815780639648</v>
       </c>
       <c r="H238" t="n">
         <v>2197</v>
@@ -7300,7 +7300,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G239" t="n">
-        <v>4.46505928039551</v>
+        <v>4.46505880355835</v>
       </c>
       <c r="H239" t="n">
         <v>1590</v>
@@ -7329,7 +7329,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G240" t="n">
-        <v>4.42354488372803</v>
+        <v>4.42354536056519</v>
       </c>
       <c r="H240" t="n">
         <v>3500</v>
@@ -7358,7 +7358,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G241" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H241" t="n">
         <v>1200</v>
@@ -7387,7 +7387,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>4.42354488372803</v>
+        <v>4.42354536056519</v>
       </c>
       <c r="H242" t="n">
         <v>9000</v>
@@ -7416,7 +7416,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G243" t="n">
-        <v>4.50196075439453</v>
+        <v>4.50196027755737</v>
       </c>
       <c r="H243" t="n">
         <v>668</v>
@@ -7445,7 +7445,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G244" t="n">
-        <v>4.50196075439453</v>
+        <v>4.50196027755737</v>
       </c>
       <c r="H244" t="n">
         <v>32</v>
@@ -7474,7 +7474,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G245" t="n">
-        <v>4.50196075439453</v>
+        <v>4.50196027755737</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -7503,7 +7503,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G246" t="n">
-        <v>4.3543553352356</v>
+        <v>4.35435485839844</v>
       </c>
       <c r="H246" t="n">
         <v>2400</v>
@@ -7532,7 +7532,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>4.42815828323364</v>
+        <v>4.42815780639648</v>
       </c>
       <c r="H247" t="n">
         <v>1851</v>
@@ -7561,7 +7561,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>4.42815828323364</v>
+        <v>4.42815780639648</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G249" t="n">
-        <v>4.40970706939697</v>
+        <v>4.40970754623413</v>
       </c>
       <c r="H249" t="n">
         <v>6200</v>
@@ -7619,7 +7619,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G250" t="n">
-        <v>4.37280511856079</v>
+        <v>4.37280559539795</v>
       </c>
       <c r="H250" t="n">
         <v>241</v>
@@ -7648,7 +7648,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G251" t="n">
-        <v>4.3543553352356</v>
+        <v>4.35435485839844</v>
       </c>
       <c r="H251" t="n">
         <v>1595</v>
@@ -7677,7 +7677,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G252" t="n">
-        <v>4.2621021270752</v>
+        <v>4.26210165023804</v>
       </c>
       <c r="H252" t="n">
         <v>330</v>
@@ -7706,7 +7706,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G253" t="n">
-        <v>4.50196075439453</v>
+        <v>4.50196027755737</v>
       </c>
       <c r="H253" t="n">
         <v>1449</v>
@@ -7735,7 +7735,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>4.53886127471924</v>
+        <v>4.5388617515564</v>
       </c>
       <c r="H254" t="n">
         <v>12150</v>
@@ -7764,7 +7764,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G255" t="n">
-        <v>4.55731248855591</v>
+        <v>4.55731201171875</v>
       </c>
       <c r="H255" t="n">
         <v>4318</v>
@@ -7793,7 +7793,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G256" t="n">
-        <v>4.52041101455688</v>
+        <v>4.52041149139404</v>
       </c>
       <c r="H256" t="n">
         <v>9927</v>
@@ -7822,7 +7822,7 @@
         <v>5</v>
       </c>
       <c r="G257" t="n">
-        <v>4.61266374588013</v>
+        <v>4.61266422271729</v>
       </c>
       <c r="H257" t="n">
         <v>5177</v>
@@ -7851,7 +7851,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G258" t="n">
-        <v>4.51118564605713</v>
+        <v>4.51118516921997</v>
       </c>
       <c r="H258" t="n">
         <v>22611</v>
@@ -7880,7 +7880,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>4.42815828323364</v>
+        <v>4.42815780639648</v>
       </c>
       <c r="H259" t="n">
         <v>350</v>
@@ -7909,7 +7909,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>4.42815828323364</v>
+        <v>4.42815780639648</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G261" t="n">
-        <v>4.59882593154907</v>
+        <v>4.59882640838623</v>
       </c>
       <c r="H261" t="n">
         <v>4514</v>
@@ -8025,7 +8025,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G264" t="n">
-        <v>4.88019895553589</v>
+        <v>4.88019847869873</v>
       </c>
       <c r="H264" t="n">
         <v>69249</v>
@@ -8199,7 +8199,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G270" t="n">
-        <v>4.93555068969727</v>
+        <v>4.93555021286011</v>
       </c>
       <c r="H270" t="n">
         <v>78819</v>
@@ -8286,7 +8286,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G273" t="n">
-        <v>4.99090242385864</v>
+        <v>4.9909029006958</v>
       </c>
       <c r="H273" t="n">
         <v>2440</v>
@@ -8315,7 +8315,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G274" t="n">
-        <v>4.99090242385864</v>
+        <v>4.9909029006958</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -8344,7 +8344,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G275" t="n">
-        <v>4.99090242385864</v>
+        <v>4.9909029006958</v>
       </c>
       <c r="H275" t="n">
         <v>6023</v>
@@ -8373,7 +8373,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H276" t="n">
         <v>5852</v>
@@ -8402,7 +8402,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G277" t="n">
-        <v>5.03702974319458</v>
+        <v>5.03702926635742</v>
       </c>
       <c r="H277" t="n">
         <v>22783</v>
@@ -8431,7 +8431,7 @@
         <v>5.5</v>
       </c>
       <c r="G278" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H278" t="n">
         <v>3731</v>
@@ -8460,7 +8460,7 @@
         <v>5.5</v>
       </c>
       <c r="G279" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H279" t="n">
         <v>5517</v>
@@ -8518,7 +8518,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G281" t="n">
-        <v>5.15695905685425</v>
+        <v>5.15695858001709</v>
       </c>
       <c r="H281" t="n">
         <v>13832</v>
@@ -8547,7 +8547,7 @@
         <v>5.5</v>
       </c>
       <c r="G282" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H282" t="n">
         <v>6695</v>
@@ -8576,7 +8576,7 @@
         <v>5.5</v>
       </c>
       <c r="G283" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H283" t="n">
         <v>5105</v>
@@ -8605,7 +8605,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G284" t="n">
-        <v>5.13850784301758</v>
+        <v>5.13850831985474</v>
       </c>
       <c r="H284" t="n">
         <v>3550</v>
@@ -8634,7 +8634,7 @@
         <v>5.5</v>
       </c>
       <c r="G285" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H285" t="n">
         <v>3111</v>
@@ -8692,7 +8692,7 @@
         <v>5.5</v>
       </c>
       <c r="G287" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H287" t="n">
         <v>5370</v>
@@ -8721,7 +8721,7 @@
         <v>5.5</v>
       </c>
       <c r="G288" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H288" t="n">
         <v>1000</v>
@@ -8750,7 +8750,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>5.14773368835449</v>
+        <v>5.14773321151733</v>
       </c>
       <c r="H289" t="n">
         <v>160</v>
@@ -8808,7 +8808,7 @@
         <v>5.5</v>
       </c>
       <c r="G291" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H291" t="n">
         <v>4850</v>
@@ -8837,7 +8837,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G292" t="n">
-        <v>5.14773368835449</v>
+        <v>5.14773321151733</v>
       </c>
       <c r="H292" t="n">
         <v>14959</v>
@@ -8866,7 +8866,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G293" t="n">
-        <v>5.15695905685425</v>
+        <v>5.15695858001709</v>
       </c>
       <c r="H293" t="n">
         <v>10</v>
@@ -8895,7 +8895,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G294" t="n">
-        <v>5.11083221435547</v>
+        <v>5.11083173751831</v>
       </c>
       <c r="H294" t="n">
         <v>27739</v>
@@ -8924,7 +8924,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G295" t="n">
-        <v>4.80639600753784</v>
+        <v>4.806396484375</v>
       </c>
       <c r="H295" t="n">
         <v>11013</v>
@@ -8982,7 +8982,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>4.98167705535889</v>
+        <v>4.98167753219604</v>
       </c>
       <c r="H297" t="n">
         <v>83453</v>
@@ -9011,7 +9011,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G298" t="n">
-        <v>5.06470537185669</v>
+        <v>5.06470489501953</v>
       </c>
       <c r="H298" t="n">
         <v>39937</v>
@@ -9040,7 +9040,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>4.93555068969727</v>
+        <v>4.93555021286011</v>
       </c>
       <c r="H299" t="n">
         <v>1763</v>
@@ -9156,7 +9156,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G303" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H303" t="n">
         <v>700</v>
@@ -9185,7 +9185,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G304" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H304" t="n">
         <v>3145</v>
@@ -9272,7 +9272,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G307" t="n">
-        <v>4.93555068969727</v>
+        <v>4.93555021286011</v>
       </c>
       <c r="H307" t="n">
         <v>1214</v>
@@ -9301,7 +9301,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>4.76949501037598</v>
+        <v>4.76949453353882</v>
       </c>
       <c r="H308" t="n">
         <v>7904</v>
@@ -9359,7 +9359,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G310" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H310" t="n">
         <v>1967</v>
@@ -9417,7 +9417,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G312" t="n">
-        <v>4.76949501037598</v>
+        <v>4.76949453353882</v>
       </c>
       <c r="H312" t="n">
         <v>4994</v>
@@ -9446,7 +9446,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G313" t="n">
-        <v>4.75104427337646</v>
+        <v>4.75104379653931</v>
       </c>
       <c r="H313" t="n">
         <v>3070</v>
@@ -9504,7 +9504,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>4.75104427337646</v>
+        <v>4.75104379653931</v>
       </c>
       <c r="H315" t="n">
         <v>278649</v>
@@ -9562,7 +9562,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G317" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H317" t="n">
         <v>31544</v>
@@ -9591,7 +9591,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G318" t="n">
-        <v>4.87097406387329</v>
+        <v>4.87097358703613</v>
       </c>
       <c r="H318" t="n">
         <v>7990</v>
@@ -9620,7 +9620,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G319" t="n">
-        <v>5.06470537185669</v>
+        <v>5.06470489501953</v>
       </c>
       <c r="H319" t="n">
         <v>4244</v>
@@ -9649,7 +9649,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>4.88019895553589</v>
+        <v>4.88019847869873</v>
       </c>
       <c r="H320" t="n">
         <v>6441</v>
@@ -9707,7 +9707,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G322" t="n">
-        <v>4.87097406387329</v>
+        <v>4.87097358703613</v>
       </c>
       <c r="H322" t="n">
         <v>10071</v>
@@ -9765,7 +9765,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G324" t="n">
-        <v>5.04625415802002</v>
+        <v>5.04625463485718</v>
       </c>
       <c r="H324" t="n">
         <v>3919</v>
@@ -9823,7 +9823,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>4.80639600753784</v>
+        <v>4.806396484375</v>
       </c>
       <c r="H326" t="n">
         <v>9846</v>
@@ -9968,7 +9968,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G331" t="n">
-        <v>4.99090242385864</v>
+        <v>4.9909029006958</v>
       </c>
       <c r="H331" t="n">
         <v>1655</v>
@@ -9997,7 +9997,7 @@
         <v>5.5</v>
       </c>
       <c r="G332" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H332" t="n">
         <v>10755</v>
@@ -10026,7 +10026,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G333" t="n">
-        <v>4.98167705535889</v>
+        <v>4.98167753219604</v>
       </c>
       <c r="H333" t="n">
         <v>54722</v>
@@ -10055,7 +10055,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G334" t="n">
-        <v>5.10160684585571</v>
+        <v>5.10160732269287</v>
       </c>
       <c r="H334" t="n">
         <v>10899</v>
@@ -10084,7 +10084,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G335" t="n">
-        <v>4.98167705535889</v>
+        <v>4.98167753219604</v>
       </c>
       <c r="H335" t="n">
         <v>34644</v>
@@ -10113,7 +10113,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G336" t="n">
-        <v>5.06470537185669</v>
+        <v>5.06470489501953</v>
       </c>
       <c r="H336" t="n">
         <v>610</v>
@@ -10171,7 +10171,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>4.98167705535889</v>
+        <v>4.98167753219604</v>
       </c>
       <c r="H338" t="n">
         <v>3600</v>
@@ -10200,7 +10200,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G339" t="n">
-        <v>4.98167705535889</v>
+        <v>4.98167753219604</v>
       </c>
       <c r="H339" t="n">
         <v>700</v>
@@ -10258,7 +10258,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G341" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H341" t="n">
         <v>6351</v>
@@ -10287,7 +10287,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G342" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H342" t="n">
         <v>1223</v>
@@ -10316,7 +10316,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G343" t="n">
-        <v>4.93555068969727</v>
+        <v>4.93555021286011</v>
       </c>
       <c r="H343" t="n">
         <v>1750</v>
@@ -10345,7 +10345,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G344" t="n">
-        <v>4.98167705535889</v>
+        <v>4.98167753219604</v>
       </c>
       <c r="H344" t="n">
         <v>8710</v>
@@ -10490,7 +10490,7 @@
         <v>5</v>
       </c>
       <c r="G349" t="n">
-        <v>4.61266374588013</v>
+        <v>4.61266422271729</v>
       </c>
       <c r="H349" t="n">
         <v>8051</v>
@@ -10519,7 +10519,7 @@
         <v>5</v>
       </c>
       <c r="G350" t="n">
-        <v>4.61266374588013</v>
+        <v>4.61266422271729</v>
       </c>
       <c r="H350" t="n">
         <v>5297</v>
@@ -10548,7 +10548,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>4.75104427337646</v>
+        <v>4.75104379653931</v>
       </c>
       <c r="H351" t="n">
         <v>9088</v>
@@ -10606,7 +10606,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G353" t="n">
-        <v>4.88019895553589</v>
+        <v>4.88019847869873</v>
       </c>
       <c r="H353" t="n">
         <v>1026</v>
@@ -10635,7 +10635,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G354" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H354" t="n">
         <v>1901</v>
@@ -10664,7 +10664,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H355" t="n">
         <v>7480</v>
@@ -10693,7 +10693,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G356" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H356" t="n">
         <v>7610</v>
@@ -10722,7 +10722,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G357" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H357" t="n">
         <v>1202</v>
@@ -10751,7 +10751,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>5.03702974319458</v>
+        <v>5.03702926635742</v>
       </c>
       <c r="H358" t="n">
         <v>1175</v>
@@ -10983,7 +10983,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G366" t="n">
-        <v>5.05548000335693</v>
+        <v>5.05548048019409</v>
       </c>
       <c r="H366" t="n">
         <v>26294</v>
@@ -11041,7 +11041,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G368" t="n">
-        <v>5.14773368835449</v>
+        <v>5.14773321151733</v>
       </c>
       <c r="H368" t="n">
         <v>5393</v>
@@ -11128,7 +11128,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G371" t="n">
-        <v>5.33223962783813</v>
+        <v>5.33224058151245</v>
       </c>
       <c r="H371" t="n">
         <v>27751</v>
@@ -11186,7 +11186,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G373" t="n">
-        <v>5.3506908416748</v>
+        <v>5.35069036483765</v>
       </c>
       <c r="H373" t="n">
         <v>5008</v>
@@ -11215,7 +11215,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G374" t="n">
-        <v>5.2768874168396</v>
+        <v>5.27688789367676</v>
       </c>
       <c r="H374" t="n">
         <v>2643</v>
@@ -11273,7 +11273,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>5.3506908416748</v>
+        <v>5.35069036483765</v>
       </c>
       <c r="H376" t="n">
         <v>1774</v>
@@ -11302,7 +11302,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>5.3506908416748</v>
+        <v>5.35069036483765</v>
       </c>
       <c r="H377" t="n">
         <v>2594</v>
@@ -11331,7 +11331,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G378" t="n">
-        <v>5.25843715667725</v>
+        <v>5.25843667984009</v>
       </c>
       <c r="H378" t="n">
         <v>4491</v>
@@ -11360,7 +11360,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G379" t="n">
-        <v>5.25843715667725</v>
+        <v>5.25843667984009</v>
       </c>
       <c r="H379" t="n">
         <v>270</v>
@@ -11389,7 +11389,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G380" t="n">
-        <v>5.2768874168396</v>
+        <v>5.27688789367676</v>
       </c>
       <c r="H380" t="n">
         <v>43761</v>
@@ -11534,7 +11534,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G385" t="n">
-        <v>5.49246215820312</v>
+        <v>5.49246263504028</v>
       </c>
       <c r="H385" t="n">
         <v>5319</v>
@@ -11679,7 +11679,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H390" t="n">
         <v>24702</v>
@@ -11940,7 +11940,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G399" t="n">
-        <v>5.51120805740356</v>
+        <v>5.51120758056641</v>
       </c>
       <c r="H399" t="n">
         <v>550</v>
@@ -11969,7 +11969,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G400" t="n">
-        <v>5.49246215820312</v>
+        <v>5.49246263504028</v>
       </c>
       <c r="H400" t="n">
         <v>800</v>
@@ -12085,7 +12085,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G404" t="n">
-        <v>5.51120805740356</v>
+        <v>5.51120758056641</v>
       </c>
       <c r="H404" t="n">
         <v>1070</v>
@@ -12114,7 +12114,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H405" t="n">
         <v>1418</v>
@@ -12143,7 +12143,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G406" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H406" t="n">
         <v>1138</v>
@@ -12172,7 +12172,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G407" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H407" t="n">
         <v>9530</v>
@@ -12201,7 +12201,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G408" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H408" t="n">
         <v>200</v>
@@ -12230,7 +12230,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G409" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H409" t="n">
         <v>620</v>
@@ -12259,7 +12259,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G410" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H410" t="n">
         <v>8991</v>
@@ -12288,7 +12288,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H411" t="n">
         <v>200</v>
@@ -12317,7 +12317,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G412" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H412" t="n">
         <v>1439</v>
@@ -12346,7 +12346,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G413" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H413" t="n">
         <v>1000</v>
@@ -12375,7 +12375,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G414" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H414" t="n">
         <v>500</v>
@@ -12404,7 +12404,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H415" t="n">
         <v>100</v>
@@ -12433,7 +12433,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G416" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H416" t="n">
         <v>45</v>
@@ -12462,7 +12462,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G417" t="n">
-        <v>5.49246215820312</v>
+        <v>5.49246263504028</v>
       </c>
       <c r="H417" t="n">
         <v>210</v>
@@ -12578,7 +12578,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G421" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H421" t="n">
         <v>2490</v>
@@ -12607,7 +12607,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G422" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H422" t="n">
         <v>18970</v>
@@ -12752,7 +12752,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G427" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H427" t="n">
         <v>4203</v>
@@ -12781,7 +12781,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G428" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H428" t="n">
         <v>760</v>
@@ -12897,7 +12897,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G432" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H432" t="n">
         <v>1171</v>
@@ -12926,7 +12926,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G433" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H433" t="n">
         <v>0</v>
@@ -13042,7 +13042,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H437" t="n">
         <v>7332</v>
@@ -13071,7 +13071,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H438" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G443" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H443" t="n">
         <v>52</v>
@@ -13245,7 +13245,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H444" t="n">
         <v>10</v>
@@ -13332,7 +13332,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G447" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H447" t="n">
         <v>20</v>
@@ -13361,7 +13361,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G448" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H448" t="n">
         <v>2255</v>
@@ -13390,7 +13390,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G449" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H449" t="n">
         <v>300</v>
@@ -13593,7 +13593,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G456" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H456" t="n">
         <v>20122</v>
@@ -13883,7 +13883,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G466" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H466" t="n">
         <v>6381</v>
@@ -13941,7 +13941,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G468" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H468" t="n">
         <v>1239</v>
@@ -14028,7 +14028,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>5.23002433776855</v>
+        <v>5.2300238609314</v>
       </c>
       <c r="H471" t="n">
         <v>5247</v>
@@ -14115,7 +14115,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>5.17378664016724</v>
+        <v>5.17378711700439</v>
       </c>
       <c r="H474" t="n">
         <v>3332</v>
@@ -14144,7 +14144,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>5.09880447387695</v>
+        <v>5.09880495071411</v>
       </c>
       <c r="H475" t="n">
         <v>5512</v>
@@ -14289,7 +14289,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G480" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H480" t="n">
         <v>900</v>
@@ -14318,7 +14318,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H481" t="n">
         <v>16552</v>
@@ -14347,7 +14347,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G482" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H482" t="n">
         <v>1000</v>
@@ -14376,7 +14376,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G483" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14463,7 +14463,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>4.66765594482422</v>
+        <v>4.66765546798706</v>
       </c>
       <c r="H486" t="n">
         <v>8004</v>
@@ -14492,7 +14492,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G487" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H487" t="n">
         <v>1050</v>
@@ -14521,7 +14521,7 @@
         <v>5</v>
       </c>
       <c r="G488" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H488" t="n">
         <v>400</v>
@@ -14550,7 +14550,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G489" t="n">
-        <v>4.66765594482422</v>
+        <v>4.66765546798706</v>
       </c>
       <c r="H489" t="n">
         <v>49</v>
@@ -14579,7 +14579,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>4.64890956878662</v>
+        <v>4.64891004562378</v>
       </c>
       <c r="H490" t="n">
         <v>2650</v>
@@ -14695,7 +14695,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G494" t="n">
-        <v>4.64890956878662</v>
+        <v>4.64891004562378</v>
       </c>
       <c r="H494" t="n">
         <v>21434</v>
@@ -14724,7 +14724,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G495" t="n">
-        <v>4.65828323364258</v>
+        <v>4.65828275680542</v>
       </c>
       <c r="H495" t="n">
         <v>32639</v>
@@ -14753,7 +14753,7 @@
         <v>5</v>
       </c>
       <c r="G496" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H496" t="n">
         <v>7653</v>
@@ -14782,7 +14782,7 @@
         <v>5</v>
       </c>
       <c r="G497" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H497" t="n">
         <v>37466</v>
@@ -15101,7 +15101,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G508" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H508" t="n">
         <v>80250</v>
@@ -15217,7 +15217,7 @@
         <v>5.5</v>
       </c>
       <c r="G512" t="n">
-        <v>5.15504169464111</v>
+        <v>5.15504121780396</v>
       </c>
       <c r="H512" t="n">
         <v>4203</v>
@@ -15275,7 +15275,7 @@
         <v>5.5</v>
       </c>
       <c r="G514" t="n">
-        <v>5.15504169464111</v>
+        <v>5.15504121780396</v>
       </c>
       <c r="H514" t="n">
         <v>1884</v>
@@ -15391,7 +15391,7 @@
         <v>5.5</v>
       </c>
       <c r="G518" t="n">
-        <v>5.15504169464111</v>
+        <v>5.15504121780396</v>
       </c>
       <c r="H518" t="n">
         <v>6482</v>
@@ -15536,7 +15536,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G523" t="n">
-        <v>4.96758556365967</v>
+        <v>4.96758508682251</v>
       </c>
       <c r="H523" t="n">
         <v>560</v>
@@ -15565,7 +15565,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G524" t="n">
-        <v>5.09880447387695</v>
+        <v>5.09880495071411</v>
       </c>
       <c r="H524" t="n">
         <v>1651</v>
@@ -15594,7 +15594,7 @@
         <v>5.5</v>
       </c>
       <c r="G525" t="n">
-        <v>5.15504169464111</v>
+        <v>5.15504121780396</v>
       </c>
       <c r="H525" t="n">
         <v>3840</v>
@@ -15623,7 +15623,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G526" t="n">
-        <v>5.09880447387695</v>
+        <v>5.09880495071411</v>
       </c>
       <c r="H526" t="n">
         <v>2500</v>
@@ -15971,7 +15971,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G538" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H538" t="n">
         <v>11050</v>
@@ -16145,7 +16145,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G544" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H544" t="n">
         <v>1500</v>
@@ -16290,7 +16290,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G549" t="n">
-        <v>4.7426381111145</v>
+        <v>4.74263763427734</v>
       </c>
       <c r="H549" t="n">
         <v>400</v>
@@ -16348,7 +16348,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G551" t="n">
-        <v>4.66765594482422</v>
+        <v>4.66765546798706</v>
       </c>
       <c r="H551" t="n">
         <v>33872</v>
@@ -16377,7 +16377,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H552" t="n">
         <v>2770</v>
@@ -16406,7 +16406,7 @@
         <v>5</v>
       </c>
       <c r="G553" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H553" t="n">
         <v>200</v>
@@ -16435,7 +16435,7 @@
         <v>5</v>
       </c>
       <c r="G554" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H554" t="n">
         <v>1284</v>
@@ -16464,7 +16464,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H555" t="n">
         <v>1730</v>
@@ -16522,7 +16522,7 @@
         <v>5</v>
       </c>
       <c r="G557" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H557" t="n">
         <v>5070</v>
@@ -16551,7 +16551,7 @@
         <v>5</v>
       </c>
       <c r="G558" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H558" t="n">
         <v>497</v>
@@ -16667,7 +16667,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G562" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H562" t="n">
         <v>5341</v>
@@ -16812,7 +16812,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>5.09880447387695</v>
+        <v>5.09880495071411</v>
       </c>
       <c r="H567" t="n">
         <v>17491</v>
@@ -16986,7 +16986,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G573" t="n">
-        <v>3.96469569206238</v>
+        <v>3.9646954536438</v>
       </c>
       <c r="H573" t="n">
         <v>1226</v>
@@ -17044,7 +17044,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G575" t="n">
-        <v>4.08654260635376</v>
+        <v>4.0865421295166</v>
       </c>
       <c r="H575" t="n">
         <v>16683</v>
@@ -17073,7 +17073,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>4.04905128479004</v>
+        <v>4.04905080795288</v>
       </c>
       <c r="H576" t="n">
         <v>6405</v>
@@ -17102,7 +17102,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G577" t="n">
-        <v>4.04905128479004</v>
+        <v>4.04905080795288</v>
       </c>
       <c r="H577" t="n">
         <v>5942</v>
@@ -17131,7 +17131,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G578" t="n">
-        <v>3.96469569206238</v>
+        <v>3.9646954536438</v>
       </c>
       <c r="H578" t="n">
         <v>2445</v>
@@ -17189,7 +17189,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>3.94595003128052</v>
+        <v>3.9459502696991</v>
       </c>
       <c r="H580" t="n">
         <v>8147</v>
@@ -17276,7 +17276,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G583" t="n">
-        <v>3.88971281051636</v>
+        <v>3.88971304893494</v>
       </c>
       <c r="H583" t="n">
         <v>2610</v>
@@ -17305,7 +17305,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>3.94595003128052</v>
+        <v>3.9459502696991</v>
       </c>
       <c r="H584" t="n">
         <v>3049</v>
@@ -17421,7 +17421,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G588" t="n">
-        <v>3.88971281051636</v>
+        <v>3.88971304893494</v>
       </c>
       <c r="H588" t="n">
         <v>3999</v>
@@ -17537,7 +17537,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G592" t="n">
-        <v>3.88971281051636</v>
+        <v>3.88971304893494</v>
       </c>
       <c r="H592" t="n">
         <v>30337</v>
@@ -17711,7 +17711,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G598" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H598" t="n">
         <v>5102</v>
@@ -17740,7 +17740,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G599" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H599" t="n">
         <v>4178</v>
@@ -17769,7 +17769,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G600" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H600" t="n">
         <v>2406</v>
@@ -17798,7 +17798,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G601" t="n">
-        <v>4.03030490875244</v>
+        <v>4.0303053855896</v>
       </c>
       <c r="H601" t="n">
         <v>1764</v>
@@ -17827,7 +17827,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G602" t="n">
-        <v>4.04905128479004</v>
+        <v>4.04905080795288</v>
       </c>
       <c r="H602" t="n">
         <v>150</v>
@@ -17856,7 +17856,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G603" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H603" t="n">
         <v>5008</v>
@@ -17885,7 +17885,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G604" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H604" t="n">
         <v>7230</v>
@@ -17914,7 +17914,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G605" t="n">
-        <v>4.08654260635376</v>
+        <v>4.0865421295166</v>
       </c>
       <c r="H605" t="n">
         <v>4030</v>
@@ -17943,7 +17943,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G606" t="n">
-        <v>4.08654260635376</v>
+        <v>4.0865421295166</v>
       </c>
       <c r="H606" t="n">
         <v>1150</v>
@@ -18117,7 +18117,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>4.09591484069824</v>
+        <v>4.09591436386108</v>
       </c>
       <c r="H612" t="n">
         <v>401</v>
@@ -18146,7 +18146,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G613" t="n">
-        <v>4.09591484069824</v>
+        <v>4.09591436386108</v>
       </c>
       <c r="H613" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G618" t="n">
-        <v>3.88971281051636</v>
+        <v>3.88971304893494</v>
       </c>
       <c r="H618" t="n">
         <v>450</v>
@@ -18320,7 +18320,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G619" t="n">
-        <v>3.88971281051636</v>
+        <v>3.88971304893494</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -18349,7 +18349,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G620" t="n">
-        <v>3.88971281051636</v>
+        <v>3.88971304893494</v>
       </c>
       <c r="H620" t="n">
         <v>200</v>
@@ -18378,7 +18378,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G621" t="n">
-        <v>3.88971281051636</v>
+        <v>3.88971304893494</v>
       </c>
       <c r="H621" t="n">
         <v>1810</v>
@@ -18494,7 +18494,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G625" t="n">
-        <v>3.70225691795349</v>
+        <v>3.70225715637207</v>
       </c>
       <c r="H625" t="n">
         <v>2781</v>
@@ -18523,7 +18523,7 @@
         <v>4</v>
       </c>
       <c r="G626" t="n">
-        <v>3.74912095069885</v>
+        <v>3.74912118911743</v>
       </c>
       <c r="H626" t="n">
         <v>4138</v>
@@ -18552,7 +18552,7 @@
         <v>4</v>
       </c>
       <c r="G627" t="n">
-        <v>3.74912095069885</v>
+        <v>3.74912118911743</v>
       </c>
       <c r="H627" t="n">
         <v>3430</v>
@@ -18581,7 +18581,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G628" t="n">
-        <v>3.70225691795349</v>
+        <v>3.70225715637207</v>
       </c>
       <c r="H628" t="n">
         <v>432</v>
@@ -18610,7 +18610,7 @@
         <v>4</v>
       </c>
       <c r="G629" t="n">
-        <v>3.74912095069885</v>
+        <v>3.74912118911743</v>
       </c>
       <c r="H629" t="n">
         <v>1000</v>
@@ -18668,7 +18668,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G631" t="n">
-        <v>3.66476559638977</v>
+        <v>3.66476583480835</v>
       </c>
       <c r="H631" t="n">
         <v>2461</v>
@@ -36625,6 +36625,64 @@
         <v>3106</v>
       </c>
       <c r="I1250" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1251" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1251" t="n">
+        <v>5.1399998664856</v>
+      </c>
+      <c r="D1251" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="E1251" t="n">
+        <v>4.94000005722046</v>
+      </c>
+      <c r="F1251" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1251" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1251" t="n">
+        <v>4268</v>
+      </c>
+      <c r="I1251" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1252" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1252" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="D1252" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="E1252" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="F1252" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="G1252" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="H1252" t="n">
+        <v>3194</v>
+      </c>
+      <c r="I1252" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RFG.MI.xlsx
+++ b/data/RFG.MI.xlsx
@@ -427,7 +427,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2" t="n">
-        <v>4.62868070602417</v>
+        <v>4.62868022918701</v>
       </c>
       <c r="H2" t="n">
         <v>355635</v>
@@ -543,7 +543,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>4.26564598083496</v>
+        <v>4.26564645767212</v>
       </c>
       <c r="H6" t="n">
         <v>157332</v>
@@ -572,7 +572,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>4.35640525817871</v>
+        <v>4.35640573501587</v>
       </c>
       <c r="H7" t="n">
         <v>53988</v>
@@ -601,7 +601,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G8" t="n">
-        <v>4.22934341430664</v>
+        <v>4.22934293746948</v>
       </c>
       <c r="H8" t="n">
         <v>147200</v>
@@ -630,7 +630,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G9" t="n">
-        <v>4.07505416870117</v>
+        <v>4.07505369186401</v>
       </c>
       <c r="H9" t="n">
         <v>88738</v>
@@ -688,7 +688,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G11" t="n">
-        <v>4.174889087677</v>
+        <v>4.17488813400269</v>
       </c>
       <c r="H11" t="n">
         <v>49843</v>
@@ -746,7 +746,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>4.174889087677</v>
+        <v>4.17488813400269</v>
       </c>
       <c r="H13" t="n">
         <v>29293</v>
@@ -775,7 +775,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>4.193039894104</v>
+        <v>4.19304037094116</v>
       </c>
       <c r="H14" t="n">
         <v>6960</v>
@@ -804,7 +804,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G15" t="n">
-        <v>4.26564598083496</v>
+        <v>4.26564645767212</v>
       </c>
       <c r="H15" t="n">
         <v>56165</v>
@@ -833,7 +833,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G16" t="n">
-        <v>4.29741191864014</v>
+        <v>4.29741239547729</v>
       </c>
       <c r="H16" t="n">
         <v>16165</v>
@@ -862,7 +862,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G17" t="n">
-        <v>4.26564598083496</v>
+        <v>4.26564645767212</v>
       </c>
       <c r="H17" t="n">
         <v>15689</v>
@@ -1007,7 +1007,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G22" t="n">
-        <v>4.746666431427</v>
+        <v>4.74666690826416</v>
       </c>
       <c r="H22" t="n">
         <v>84587</v>
@@ -1065,7 +1065,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G24" t="n">
-        <v>4.82834911346436</v>
+        <v>4.8283486366272</v>
       </c>
       <c r="H24" t="n">
         <v>64828</v>
@@ -1094,7 +1094,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>4.84650039672852</v>
+        <v>4.84650087356567</v>
       </c>
       <c r="H25" t="n">
         <v>24608</v>
@@ -1123,7 +1123,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G26" t="n">
-        <v>4.84650039672852</v>
+        <v>4.84650087356567</v>
       </c>
       <c r="H26" t="n">
         <v>84199</v>
@@ -1210,7 +1210,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>5.20045804977417</v>
+        <v>5.20045852661133</v>
       </c>
       <c r="H29" t="n">
         <v>89716</v>
@@ -1239,7 +1239,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G30" t="n">
-        <v>5.47273397445679</v>
+        <v>5.47273445129395</v>
       </c>
       <c r="H30" t="n">
         <v>193631</v>
@@ -1268,7 +1268,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>5.5271897315979</v>
+        <v>5.52718925476074</v>
       </c>
       <c r="H31" t="n">
         <v>27209</v>
@@ -1297,7 +1297,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G32" t="n">
-        <v>5.43643045425415</v>
+        <v>5.43643093109131</v>
       </c>
       <c r="H32" t="n">
         <v>36811</v>
@@ -1326,7 +1326,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G33" t="n">
-        <v>5.43643045425415</v>
+        <v>5.43643093109131</v>
       </c>
       <c r="H33" t="n">
         <v>30706</v>
@@ -1355,7 +1355,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G34" t="n">
-        <v>5.48181009292603</v>
+        <v>5.48180961608887</v>
       </c>
       <c r="H34" t="n">
         <v>30948</v>
@@ -1384,7 +1384,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G35" t="n">
-        <v>5.45458221435547</v>
+        <v>5.45458269119263</v>
       </c>
       <c r="H35" t="n">
         <v>24789</v>
@@ -1442,7 +1442,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>5.25491333007812</v>
+        <v>5.25491380691528</v>
       </c>
       <c r="H37" t="n">
         <v>23662</v>
@@ -1471,7 +1471,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G38" t="n">
-        <v>5.31844520568848</v>
+        <v>5.31844425201416</v>
       </c>
       <c r="H38" t="n">
         <v>24272</v>
@@ -1500,7 +1500,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G39" t="n">
-        <v>5.36382341384888</v>
+        <v>5.36382389068604</v>
       </c>
       <c r="H39" t="n">
         <v>8885</v>
@@ -1529,7 +1529,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G40" t="n">
-        <v>5.30936813354492</v>
+        <v>5.30936861038208</v>
       </c>
       <c r="H40" t="n">
         <v>10863</v>
@@ -1587,7 +1587,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>5.38197565078735</v>
+        <v>5.3819751739502</v>
       </c>
       <c r="H42" t="n">
         <v>10599</v>
@@ -1616,7 +1616,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G43" t="n">
-        <v>5.42735481262207</v>
+        <v>5.42735433578491</v>
       </c>
       <c r="H43" t="n">
         <v>24833</v>
@@ -1703,7 +1703,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G46" t="n">
-        <v>5.34567165374756</v>
+        <v>5.34567213058472</v>
       </c>
       <c r="H46" t="n">
         <v>21861</v>
@@ -1790,7 +1790,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>5.1006236076355</v>
+        <v>5.10062456130981</v>
       </c>
       <c r="H49" t="n">
         <v>37488</v>
@@ -1819,7 +1819,7 @@
         <v>5.75</v>
       </c>
       <c r="G50" t="n">
-        <v>5.21861028671265</v>
+        <v>5.2186107635498</v>
       </c>
       <c r="H50" t="n">
         <v>53296</v>
@@ -1848,7 +1848,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G51" t="n">
-        <v>5.20045804977417</v>
+        <v>5.20045852661133</v>
       </c>
       <c r="H51" t="n">
         <v>11633</v>
@@ -1877,7 +1877,7 @@
         <v>5.5</v>
       </c>
       <c r="G52" t="n">
-        <v>4.9917140007019</v>
+        <v>4.99171447753906</v>
       </c>
       <c r="H52" t="n">
         <v>31337</v>
@@ -1906,7 +1906,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G53" t="n">
-        <v>5.03709316253662</v>
+        <v>5.03709363937378</v>
       </c>
       <c r="H53" t="n">
         <v>29429</v>
@@ -1935,7 +1935,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G54" t="n">
-        <v>5.04616928100586</v>
+        <v>5.0461688041687</v>
       </c>
       <c r="H54" t="n">
         <v>17032</v>
@@ -2080,7 +2080,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G59" t="n">
-        <v>4.87372827529907</v>
+        <v>4.87372779846191</v>
       </c>
       <c r="H59" t="n">
         <v>60004</v>
@@ -2109,7 +2109,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G60" t="n">
-        <v>5.01894235610962</v>
+        <v>5.01894187927246</v>
       </c>
       <c r="H60" t="n">
         <v>23167</v>
@@ -2138,7 +2138,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G61" t="n">
-        <v>4.92818307876587</v>
+        <v>4.92818355560303</v>
       </c>
       <c r="H61" t="n">
         <v>10150</v>
@@ -2196,7 +2196,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>4.746666431427</v>
+        <v>4.74666690826416</v>
       </c>
       <c r="H63" t="n">
         <v>54083</v>
@@ -2254,7 +2254,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G65" t="n">
-        <v>4.68313550949097</v>
+        <v>4.68313503265381</v>
       </c>
       <c r="H65" t="n">
         <v>14192</v>
@@ -2370,7 +2370,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>4.87372827529907</v>
+        <v>4.87372779846191</v>
       </c>
       <c r="H69" t="n">
         <v>20469</v>
@@ -2399,7 +2399,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G70" t="n">
-        <v>4.93725919723511</v>
+        <v>4.93725872039795</v>
       </c>
       <c r="H70" t="n">
         <v>2829</v>
@@ -2428,7 +2428,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G71" t="n">
-        <v>4.68313550949097</v>
+        <v>4.68313503265381</v>
       </c>
       <c r="H71" t="n">
         <v>21164</v>
@@ -2457,7 +2457,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G72" t="n">
-        <v>4.77389478683472</v>
+        <v>4.7738938331604</v>
       </c>
       <c r="H72" t="n">
         <v>8024</v>
@@ -2486,7 +2486,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G73" t="n">
-        <v>4.84650039672852</v>
+        <v>4.84650087356567</v>
       </c>
       <c r="H73" t="n">
         <v>6837</v>
@@ -2515,7 +2515,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G74" t="n">
-        <v>4.78296947479248</v>
+        <v>4.78296995162964</v>
       </c>
       <c r="H74" t="n">
         <v>4082</v>
@@ -2544,7 +2544,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G75" t="n">
-        <v>4.746666431427</v>
+        <v>4.74666690826416</v>
       </c>
       <c r="H75" t="n">
         <v>12871</v>
@@ -2573,7 +2573,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>4.51977062225342</v>
+        <v>4.51977014541626</v>
       </c>
       <c r="H76" t="n">
         <v>20769</v>
@@ -2602,7 +2602,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G77" t="n">
-        <v>4.13858461380005</v>
+        <v>4.13858509063721</v>
       </c>
       <c r="H77" t="n">
         <v>29751</v>
@@ -2631,7 +2631,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G78" t="n">
-        <v>4.13404703140259</v>
+        <v>4.13404750823975</v>
       </c>
       <c r="H78" t="n">
         <v>12171</v>
@@ -2660,7 +2660,7 @@
         <v>4.5</v>
       </c>
       <c r="G79" t="n">
-        <v>4.08413028717041</v>
+        <v>4.08412981033325</v>
       </c>
       <c r="H79" t="n">
         <v>23806</v>
@@ -2718,7 +2718,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G81" t="n">
-        <v>4.07051610946655</v>
+        <v>4.07051658630371</v>
       </c>
       <c r="H81" t="n">
         <v>26271</v>
@@ -2776,7 +2776,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G83" t="n">
-        <v>3.9933717250824</v>
+        <v>3.99337148666382</v>
       </c>
       <c r="H83" t="n">
         <v>14139</v>
@@ -2805,7 +2805,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G84" t="n">
-        <v>4.01152276992798</v>
+        <v>4.01152324676514</v>
       </c>
       <c r="H84" t="n">
         <v>13008</v>
@@ -2834,7 +2834,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>4.03421258926392</v>
+        <v>4.03421306610107</v>
       </c>
       <c r="H85" t="n">
         <v>9318</v>
@@ -2863,7 +2863,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>4.15673589706421</v>
+        <v>4.15673685073853</v>
       </c>
       <c r="H86" t="n">
         <v>20105</v>
@@ -2892,7 +2892,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G87" t="n">
-        <v>4.21119117736816</v>
+        <v>4.21119165420532</v>
       </c>
       <c r="H87" t="n">
         <v>12593</v>
@@ -2979,7 +2979,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G90" t="n">
-        <v>4.68313550949097</v>
+        <v>4.68313503265381</v>
       </c>
       <c r="H90" t="n">
         <v>7231</v>
@@ -3037,7 +3037,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G92" t="n">
-        <v>4.53338384628296</v>
+        <v>4.53338432312012</v>
       </c>
       <c r="H92" t="n">
         <v>1969</v>
@@ -3095,7 +3095,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G94" t="n">
-        <v>4.50615644454956</v>
+        <v>4.50615692138672</v>
       </c>
       <c r="H94" t="n">
         <v>2116</v>
@@ -3124,7 +3124,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>4.51977062225342</v>
+        <v>4.51977014541626</v>
       </c>
       <c r="H95" t="n">
         <v>243259</v>
@@ -3153,7 +3153,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>4.51977062225342</v>
+        <v>4.51977014541626</v>
       </c>
       <c r="H96" t="n">
         <v>4515</v>
@@ -3211,7 +3211,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G98" t="n">
-        <v>4.41085958480835</v>
+        <v>4.41086053848267</v>
       </c>
       <c r="H98" t="n">
         <v>2735</v>
@@ -3240,7 +3240,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>4.50161838531494</v>
+        <v>4.50161790847778</v>
       </c>
       <c r="H99" t="n">
         <v>18031</v>
@@ -3298,7 +3298,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G101" t="n">
-        <v>4.35640525817871</v>
+        <v>4.35640573501587</v>
       </c>
       <c r="H101" t="n">
         <v>2000</v>
@@ -3327,7 +3327,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G102" t="n">
-        <v>4.35640525817871</v>
+        <v>4.35640573501587</v>
       </c>
       <c r="H102" t="n">
         <v>1155</v>
@@ -3356,7 +3356,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G103" t="n">
-        <v>4.34732913970947</v>
+        <v>4.34732866287231</v>
       </c>
       <c r="H103" t="n">
         <v>12517</v>
@@ -3414,7 +3414,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G105" t="n">
-        <v>4.36548042297363</v>
+        <v>4.36548089981079</v>
       </c>
       <c r="H105" t="n">
         <v>618</v>
@@ -3501,7 +3501,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>4.34732913970947</v>
+        <v>4.34732866287231</v>
       </c>
       <c r="H108" t="n">
         <v>5476</v>
@@ -3646,7 +3646,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G113" t="n">
-        <v>4.37455701828003</v>
+        <v>4.37455749511719</v>
       </c>
       <c r="H113" t="n">
         <v>38</v>
@@ -3675,7 +3675,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G114" t="n">
-        <v>4.46531534194946</v>
+        <v>4.4653148651123</v>
       </c>
       <c r="H114" t="n">
         <v>2900</v>
@@ -3733,7 +3733,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G116" t="n">
-        <v>4.29287481307983</v>
+        <v>4.29287433624268</v>
       </c>
       <c r="H116" t="n">
         <v>5190</v>
@@ -3762,7 +3762,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G117" t="n">
-        <v>4.18396425247192</v>
+        <v>4.18396377563477</v>
       </c>
       <c r="H117" t="n">
         <v>3181</v>
@@ -3820,7 +3820,7 @@
         <v>4.75</v>
       </c>
       <c r="G119" t="n">
-        <v>4.31102561950684</v>
+        <v>4.31102609634399</v>
       </c>
       <c r="H119" t="n">
         <v>635</v>
@@ -3878,7 +3878,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G121" t="n">
-        <v>3.81639218330383</v>
+        <v>3.81639242172241</v>
       </c>
       <c r="H121" t="n">
         <v>9794</v>
@@ -3994,7 +3994,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G125" t="n">
-        <v>3.92076468467712</v>
+        <v>3.92076516151428</v>
       </c>
       <c r="H125" t="n">
         <v>16385</v>
@@ -4168,7 +4168,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G131" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H131" t="n">
         <v>15380</v>
@@ -4226,7 +4226,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G133" t="n">
-        <v>4.32667875289917</v>
+        <v>4.32667922973633</v>
       </c>
       <c r="H133" t="n">
         <v>10570</v>
@@ -4284,7 +4284,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G135" t="n">
-        <v>4.37280559539795</v>
+        <v>4.37280511856079</v>
       </c>
       <c r="H135" t="n">
         <v>4000</v>
@@ -4313,7 +4313,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G136" t="n">
-        <v>4.42354536056519</v>
+        <v>4.42354488372803</v>
       </c>
       <c r="H136" t="n">
         <v>520</v>
@@ -4342,7 +4342,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G137" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H137" t="n">
         <v>3650</v>
@@ -4371,7 +4371,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G138" t="n">
-        <v>4.28516483306885</v>
+        <v>4.28516530990601</v>
       </c>
       <c r="H138" t="n">
         <v>7384</v>
@@ -4400,7 +4400,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G139" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H139" t="n">
         <v>2000</v>
@@ -4429,7 +4429,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G140" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>4.24826383590698</v>
+        <v>4.24826431274414</v>
       </c>
       <c r="H141" t="n">
         <v>1470</v>
@@ -4516,7 +4516,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G143" t="n">
-        <v>4.20674991607666</v>
+        <v>4.2067494392395</v>
       </c>
       <c r="H143" t="n">
         <v>17151</v>
@@ -4545,7 +4545,7 @@
         <v>4.5</v>
       </c>
       <c r="G144" t="n">
-        <v>4.15139818191528</v>
+        <v>4.15139770507812</v>
       </c>
       <c r="H144" t="n">
         <v>12389</v>
@@ -4603,7 +4603,7 @@
         <v>4.25</v>
       </c>
       <c r="G146" t="n">
-        <v>3.92076468467712</v>
+        <v>3.92076444625854</v>
       </c>
       <c r="H146" t="n">
         <v>15623</v>
@@ -4632,7 +4632,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>3.89770102500916</v>
+        <v>3.89770078659058</v>
       </c>
       <c r="H147" t="n">
         <v>8340</v>
@@ -4661,7 +4661,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95766568183899</v>
+        <v>3.95766592025757</v>
       </c>
       <c r="H148" t="n">
         <v>2849</v>
@@ -4690,7 +4690,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G149" t="n">
-        <v>3.95766568183899</v>
+        <v>3.95766592025757</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G152" t="n">
-        <v>4.14678478240967</v>
+        <v>4.14678525924683</v>
       </c>
       <c r="H152" t="n">
         <v>2449</v>
@@ -4806,7 +4806,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G153" t="n">
-        <v>3.98534202575684</v>
+        <v>3.98534250259399</v>
       </c>
       <c r="H153" t="n">
         <v>8687</v>
@@ -4835,7 +4835,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G154" t="n">
-        <v>3.9299898147583</v>
+        <v>3.92999005317688</v>
       </c>
       <c r="H154" t="n">
         <v>5428</v>
@@ -4864,7 +4864,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G155" t="n">
-        <v>4.04530668258667</v>
+        <v>4.04530715942383</v>
       </c>
       <c r="H155" t="n">
         <v>3576</v>
@@ -4922,7 +4922,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>3.96689128875732</v>
+        <v>3.96689105033875</v>
       </c>
       <c r="H157" t="n">
         <v>90</v>
@@ -4951,7 +4951,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G158" t="n">
-        <v>4.04991960525513</v>
+        <v>4.04991865158081</v>
       </c>
       <c r="H158" t="n">
         <v>5</v>
@@ -4980,7 +4980,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G159" t="n">
-        <v>3.82851147651672</v>
+        <v>3.82851099967957</v>
       </c>
       <c r="H159" t="n">
         <v>11901</v>
@@ -5009,7 +5009,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G160" t="n">
-        <v>3.91153883934021</v>
+        <v>3.91153907775879</v>
       </c>
       <c r="H160" t="n">
         <v>4000</v>
@@ -5038,7 +5038,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G161" t="n">
-        <v>3.96689128875732</v>
+        <v>3.96689105033875</v>
       </c>
       <c r="H161" t="n">
         <v>1000</v>
@@ -5096,7 +5096,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G163" t="n">
-        <v>3.82851147651672</v>
+        <v>3.82851099967957</v>
       </c>
       <c r="H163" t="n">
         <v>5720</v>
@@ -5183,7 +5183,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G166" t="n">
-        <v>3.84696221351624</v>
+        <v>3.84696197509766</v>
       </c>
       <c r="H166" t="n">
         <v>612</v>
@@ -5212,7 +5212,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>3.89770102500916</v>
+        <v>3.89770078659058</v>
       </c>
       <c r="H167" t="n">
         <v>205</v>
@@ -5241,7 +5241,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G168" t="n">
-        <v>3.98534202575684</v>
+        <v>3.98534250259399</v>
       </c>
       <c r="H168" t="n">
         <v>5404</v>
@@ -5270,7 +5270,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>3.92537713050842</v>
+        <v>3.925377368927</v>
       </c>
       <c r="H169" t="n">
         <v>2375</v>
@@ -5299,7 +5299,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G170" t="n">
-        <v>3.9299898147583</v>
+        <v>3.92999005317688</v>
       </c>
       <c r="H170" t="n">
         <v>10150</v>
@@ -5328,7 +5328,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G171" t="n">
-        <v>4.04991960525513</v>
+        <v>4.04991865158081</v>
       </c>
       <c r="H171" t="n">
         <v>2250</v>
@@ -5357,7 +5357,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G172" t="n">
-        <v>4.04991960525513</v>
+        <v>4.04991865158081</v>
       </c>
       <c r="H172" t="n">
         <v>520</v>
@@ -5415,7 +5415,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G174" t="n">
-        <v>3.89308857917786</v>
+        <v>3.89308834075928</v>
       </c>
       <c r="H174" t="n">
         <v>3424</v>
@@ -5444,7 +5444,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G175" t="n">
-        <v>3.89308857917786</v>
+        <v>3.89308834075928</v>
       </c>
       <c r="H175" t="n">
         <v>470</v>
@@ -5473,7 +5473,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G176" t="n">
-        <v>3.95305299758911</v>
+        <v>3.95305323600769</v>
       </c>
       <c r="H176" t="n">
         <v>1056</v>
@@ -5502,7 +5502,7 @@
         <v>4.25</v>
       </c>
       <c r="G177" t="n">
-        <v>3.92076468467712</v>
+        <v>3.92076444625854</v>
       </c>
       <c r="H177" t="n">
         <v>3092</v>
@@ -5531,7 +5531,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>3.8838632106781</v>
+        <v>3.88386344909668</v>
       </c>
       <c r="H178" t="n">
         <v>5254</v>
@@ -5560,7 +5560,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G179" t="n">
-        <v>4.04991960525513</v>
+        <v>4.04991865158081</v>
       </c>
       <c r="H179" t="n">
         <v>3005</v>
@@ -5589,7 +5589,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G180" t="n">
-        <v>3.82851147651672</v>
+        <v>3.82851099967957</v>
       </c>
       <c r="H180" t="n">
         <v>6092</v>
@@ -5647,7 +5647,7 @@
         <v>4.25</v>
       </c>
       <c r="G182" t="n">
-        <v>3.92076468467712</v>
+        <v>3.92076444625854</v>
       </c>
       <c r="H182" t="n">
         <v>4226</v>
@@ -5676,7 +5676,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G183" t="n">
-        <v>3.8838632106781</v>
+        <v>3.88386344909668</v>
       </c>
       <c r="H183" t="n">
         <v>11079</v>
@@ -5705,7 +5705,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G184" t="n">
-        <v>3.87463760375977</v>
+        <v>3.87463784217834</v>
       </c>
       <c r="H184" t="n">
         <v>508</v>
@@ -5734,7 +5734,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G185" t="n">
-        <v>3.87463760375977</v>
+        <v>3.87463784217834</v>
       </c>
       <c r="H185" t="n">
         <v>4806</v>
@@ -5763,7 +5763,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G186" t="n">
-        <v>3.89308857917786</v>
+        <v>3.89308834075928</v>
       </c>
       <c r="H186" t="n">
         <v>13086</v>
@@ -5792,7 +5792,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G187" t="n">
-        <v>3.87463760375977</v>
+        <v>3.87463784217834</v>
       </c>
       <c r="H187" t="n">
         <v>1555</v>
@@ -5821,7 +5821,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G188" t="n">
-        <v>3.93921494483948</v>
+        <v>3.93921542167664</v>
       </c>
       <c r="H188" t="n">
         <v>2507</v>
@@ -5850,7 +5850,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G189" t="n">
-        <v>4.00840473175049</v>
+        <v>4.00840520858765</v>
       </c>
       <c r="H189" t="n">
         <v>3667</v>
@@ -5879,7 +5879,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>3.8838632106781</v>
+        <v>3.88386344909668</v>
       </c>
       <c r="H190" t="n">
         <v>1237</v>
@@ -5908,7 +5908,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>3.87463760375977</v>
+        <v>3.87463784217834</v>
       </c>
       <c r="H191" t="n">
         <v>3347</v>
@@ -5937,7 +5937,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>3.95766568183899</v>
+        <v>3.95766592025757</v>
       </c>
       <c r="H192" t="n">
         <v>3183</v>
@@ -5995,7 +5995,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G194" t="n">
-        <v>4.00379276275635</v>
+        <v>4.00379228591919</v>
       </c>
       <c r="H194" t="n">
         <v>1199</v>
@@ -6024,7 +6024,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>3.99456691741943</v>
+        <v>3.99456715583801</v>
       </c>
       <c r="H195" t="n">
         <v>131</v>
@@ -6082,7 +6082,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G197" t="n">
-        <v>3.94844055175781</v>
+        <v>3.94844102859497</v>
       </c>
       <c r="H197" t="n">
         <v>2149</v>
@@ -6140,7 +6140,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G199" t="n">
-        <v>3.9299898147583</v>
+        <v>3.92999005317688</v>
       </c>
       <c r="H199" t="n">
         <v>2982</v>
@@ -6198,7 +6198,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G201" t="n">
-        <v>3.89308857917786</v>
+        <v>3.89308834075928</v>
       </c>
       <c r="H201" t="n">
         <v>1122</v>
@@ -6256,7 +6256,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G203" t="n">
-        <v>4.04991960525513</v>
+        <v>4.04991865158081</v>
       </c>
       <c r="H203" t="n">
         <v>24810</v>
@@ -6285,7 +6285,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G204" t="n">
-        <v>3.95766568183899</v>
+        <v>3.95766592025757</v>
       </c>
       <c r="H204" t="n">
         <v>5370</v>
@@ -6343,7 +6343,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G206" t="n">
-        <v>3.94844055175781</v>
+        <v>3.94844102859497</v>
       </c>
       <c r="H206" t="n">
         <v>5295</v>
@@ -6372,7 +6372,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>3.87463760375977</v>
+        <v>3.87463784217834</v>
       </c>
       <c r="H207" t="n">
         <v>6451</v>
@@ -6401,7 +6401,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>3.90231394767761</v>
+        <v>3.90231418609619</v>
       </c>
       <c r="H208" t="n">
         <v>1430</v>
@@ -6430,7 +6430,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G209" t="n">
-        <v>3.89308857917786</v>
+        <v>3.89308834075928</v>
       </c>
       <c r="H209" t="n">
         <v>7711</v>
@@ -6459,7 +6459,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G210" t="n">
-        <v>3.90692663192749</v>
+        <v>3.90692710876465</v>
       </c>
       <c r="H210" t="n">
         <v>2126</v>
@@ -6488,7 +6488,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G211" t="n">
-        <v>3.94844055175781</v>
+        <v>3.94844102859497</v>
       </c>
       <c r="H211" t="n">
         <v>5037</v>
@@ -6546,7 +6546,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>3.8838632106781</v>
+        <v>3.88386344909668</v>
       </c>
       <c r="H213" t="n">
         <v>1793</v>
@@ -6575,7 +6575,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G214" t="n">
-        <v>3.8838632106781</v>
+        <v>3.88386344909668</v>
       </c>
       <c r="H214" t="n">
         <v>63</v>
@@ -6604,7 +6604,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G215" t="n">
-        <v>3.87463760375977</v>
+        <v>3.87463784217834</v>
       </c>
       <c r="H215" t="n">
         <v>5793</v>
@@ -6633,7 +6633,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>3.94382834434509</v>
+        <v>3.94382786750793</v>
       </c>
       <c r="H216" t="n">
         <v>1</v>
@@ -6662,7 +6662,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G217" t="n">
-        <v>3.90692663192749</v>
+        <v>3.90692710876465</v>
       </c>
       <c r="H217" t="n">
         <v>601</v>
@@ -6720,7 +6720,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G219" t="n">
-        <v>3.82851147651672</v>
+        <v>3.82851099967957</v>
       </c>
       <c r="H219" t="n">
         <v>650</v>
@@ -6749,7 +6749,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>3.82851147651672</v>
+        <v>3.82851099967957</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G222" t="n">
-        <v>3.82851147651672</v>
+        <v>3.82851099967957</v>
       </c>
       <c r="H222" t="n">
         <v>400</v>
@@ -6952,7 +6952,7 @@
         <v>4.5</v>
       </c>
       <c r="G227" t="n">
-        <v>4.15139818191528</v>
+        <v>4.15139770507812</v>
       </c>
       <c r="H227" t="n">
         <v>5590</v>
@@ -7126,7 +7126,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G233" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H233" t="n">
         <v>12462</v>
@@ -7155,7 +7155,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H234" t="n">
         <v>15005</v>
@@ -7184,7 +7184,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G235" t="n">
-        <v>4.37280559539795</v>
+        <v>4.37280511856079</v>
       </c>
       <c r="H235" t="n">
         <v>17132</v>
@@ -7213,7 +7213,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>4.45583391189575</v>
+        <v>4.45583343505859</v>
       </c>
       <c r="H236" t="n">
         <v>4300</v>
@@ -7242,7 +7242,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G237" t="n">
-        <v>4.47428464889526</v>
+        <v>4.47428417205811</v>
       </c>
       <c r="H237" t="n">
         <v>567</v>
@@ -7271,7 +7271,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>4.42815780639648</v>
+        <v>4.42815828323364</v>
       </c>
       <c r="H238" t="n">
         <v>2197</v>
@@ -7300,7 +7300,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G239" t="n">
-        <v>4.46505880355835</v>
+        <v>4.46505928039551</v>
       </c>
       <c r="H239" t="n">
         <v>1590</v>
@@ -7329,7 +7329,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G240" t="n">
-        <v>4.42354536056519</v>
+        <v>4.42354488372803</v>
       </c>
       <c r="H240" t="n">
         <v>3500</v>
@@ -7358,7 +7358,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G241" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H241" t="n">
         <v>1200</v>
@@ -7387,7 +7387,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>4.42354536056519</v>
+        <v>4.42354488372803</v>
       </c>
       <c r="H242" t="n">
         <v>9000</v>
@@ -7416,7 +7416,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G243" t="n">
-        <v>4.50196027755737</v>
+        <v>4.50196075439453</v>
       </c>
       <c r="H243" t="n">
         <v>668</v>
@@ -7445,7 +7445,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G244" t="n">
-        <v>4.50196027755737</v>
+        <v>4.50196075439453</v>
       </c>
       <c r="H244" t="n">
         <v>32</v>
@@ -7474,7 +7474,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G245" t="n">
-        <v>4.50196027755737</v>
+        <v>4.50196075439453</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -7503,7 +7503,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G246" t="n">
-        <v>4.35435485839844</v>
+        <v>4.3543553352356</v>
       </c>
       <c r="H246" t="n">
         <v>2400</v>
@@ -7532,7 +7532,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>4.42815780639648</v>
+        <v>4.42815828323364</v>
       </c>
       <c r="H247" t="n">
         <v>1851</v>
@@ -7561,7 +7561,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>4.42815780639648</v>
+        <v>4.42815828323364</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G249" t="n">
-        <v>4.40970754623413</v>
+        <v>4.40970706939697</v>
       </c>
       <c r="H249" t="n">
         <v>6200</v>
@@ -7619,7 +7619,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G250" t="n">
-        <v>4.37280559539795</v>
+        <v>4.37280511856079</v>
       </c>
       <c r="H250" t="n">
         <v>241</v>
@@ -7648,7 +7648,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G251" t="n">
-        <v>4.35435485839844</v>
+        <v>4.3543553352356</v>
       </c>
       <c r="H251" t="n">
         <v>1595</v>
@@ -7677,7 +7677,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G252" t="n">
-        <v>4.26210165023804</v>
+        <v>4.2621021270752</v>
       </c>
       <c r="H252" t="n">
         <v>330</v>
@@ -7706,7 +7706,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G253" t="n">
-        <v>4.50196027755737</v>
+        <v>4.50196075439453</v>
       </c>
       <c r="H253" t="n">
         <v>1449</v>
@@ -7735,7 +7735,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>4.5388617515564</v>
+        <v>4.53886127471924</v>
       </c>
       <c r="H254" t="n">
         <v>12150</v>
@@ -7764,7 +7764,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G255" t="n">
-        <v>4.55731201171875</v>
+        <v>4.55731248855591</v>
       </c>
       <c r="H255" t="n">
         <v>4318</v>
@@ -7793,7 +7793,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G256" t="n">
-        <v>4.52041149139404</v>
+        <v>4.52041101455688</v>
       </c>
       <c r="H256" t="n">
         <v>9927</v>
@@ -7822,7 +7822,7 @@
         <v>5</v>
       </c>
       <c r="G257" t="n">
-        <v>4.61266422271729</v>
+        <v>4.61266374588013</v>
       </c>
       <c r="H257" t="n">
         <v>5177</v>
@@ -7851,7 +7851,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G258" t="n">
-        <v>4.51118516921997</v>
+        <v>4.51118564605713</v>
       </c>
       <c r="H258" t="n">
         <v>22611</v>
@@ -7880,7 +7880,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>4.42815780639648</v>
+        <v>4.42815828323364</v>
       </c>
       <c r="H259" t="n">
         <v>350</v>
@@ -7909,7 +7909,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>4.42815780639648</v>
+        <v>4.42815828323364</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G261" t="n">
-        <v>4.59882640838623</v>
+        <v>4.59882593154907</v>
       </c>
       <c r="H261" t="n">
         <v>4514</v>
@@ -8025,7 +8025,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G264" t="n">
-        <v>4.88019847869873</v>
+        <v>4.88019895553589</v>
       </c>
       <c r="H264" t="n">
         <v>69249</v>
@@ -8199,7 +8199,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G270" t="n">
-        <v>4.93555021286011</v>
+        <v>4.93555068969727</v>
       </c>
       <c r="H270" t="n">
         <v>78819</v>
@@ -8286,7 +8286,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G273" t="n">
-        <v>4.9909029006958</v>
+        <v>4.99090242385864</v>
       </c>
       <c r="H273" t="n">
         <v>2440</v>
@@ -8315,7 +8315,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G274" t="n">
-        <v>4.9909029006958</v>
+        <v>4.99090242385864</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -8344,7 +8344,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G275" t="n">
-        <v>4.9909029006958</v>
+        <v>4.99090242385864</v>
       </c>
       <c r="H275" t="n">
         <v>6023</v>
@@ -8373,7 +8373,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>5.01857900619507</v>
+        <v>5.01857852935791</v>
       </c>
       <c r="H276" t="n">
         <v>5852</v>
@@ -8402,7 +8402,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G277" t="n">
-        <v>5.03702926635742</v>
+        <v>5.03702974319458</v>
       </c>
       <c r="H277" t="n">
         <v>22783</v>
@@ -8431,7 +8431,7 @@
         <v>5.5</v>
       </c>
       <c r="G278" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H278" t="n">
         <v>3731</v>
@@ -8460,7 +8460,7 @@
         <v>5.5</v>
       </c>
       <c r="G279" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H279" t="n">
         <v>5517</v>
@@ -8518,7 +8518,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G281" t="n">
-        <v>5.15695858001709</v>
+        <v>5.15695905685425</v>
       </c>
       <c r="H281" t="n">
         <v>13832</v>
@@ -8547,7 +8547,7 @@
         <v>5.5</v>
       </c>
       <c r="G282" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H282" t="n">
         <v>6695</v>
@@ -8576,7 +8576,7 @@
         <v>5.5</v>
       </c>
       <c r="G283" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H283" t="n">
         <v>5105</v>
@@ -8605,7 +8605,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G284" t="n">
-        <v>5.13850831985474</v>
+        <v>5.13850784301758</v>
       </c>
       <c r="H284" t="n">
         <v>3550</v>
@@ -8634,7 +8634,7 @@
         <v>5.5</v>
       </c>
       <c r="G285" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H285" t="n">
         <v>3111</v>
@@ -8692,7 +8692,7 @@
         <v>5.5</v>
       </c>
       <c r="G287" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H287" t="n">
         <v>5370</v>
@@ -8721,7 +8721,7 @@
         <v>5.5</v>
       </c>
       <c r="G288" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H288" t="n">
         <v>1000</v>
@@ -8750,7 +8750,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>5.14773321151733</v>
+        <v>5.14773368835449</v>
       </c>
       <c r="H289" t="n">
         <v>160</v>
@@ -8808,7 +8808,7 @@
         <v>5.5</v>
       </c>
       <c r="G291" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H291" t="n">
         <v>4850</v>
@@ -8837,7 +8837,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G292" t="n">
-        <v>5.14773321151733</v>
+        <v>5.14773368835449</v>
       </c>
       <c r="H292" t="n">
         <v>14959</v>
@@ -8866,7 +8866,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G293" t="n">
-        <v>5.15695858001709</v>
+        <v>5.15695905685425</v>
       </c>
       <c r="H293" t="n">
         <v>10</v>
@@ -8895,7 +8895,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G294" t="n">
-        <v>5.11083173751831</v>
+        <v>5.11083221435547</v>
       </c>
       <c r="H294" t="n">
         <v>27739</v>
@@ -8924,7 +8924,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G295" t="n">
-        <v>4.806396484375</v>
+        <v>4.80639600753784</v>
       </c>
       <c r="H295" t="n">
         <v>11013</v>
@@ -8982,7 +8982,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>4.98167753219604</v>
+        <v>4.98167705535889</v>
       </c>
       <c r="H297" t="n">
         <v>83453</v>
@@ -9011,7 +9011,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G298" t="n">
-        <v>5.06470489501953</v>
+        <v>5.06470537185669</v>
       </c>
       <c r="H298" t="n">
         <v>39937</v>
@@ -9040,7 +9040,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>4.93555021286011</v>
+        <v>4.93555068969727</v>
       </c>
       <c r="H299" t="n">
         <v>1763</v>
@@ -9156,7 +9156,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G303" t="n">
-        <v>4.92632532119751</v>
+        <v>4.92632579803467</v>
       </c>
       <c r="H303" t="n">
         <v>700</v>
@@ -9185,7 +9185,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G304" t="n">
-        <v>4.92632532119751</v>
+        <v>4.92632579803467</v>
       </c>
       <c r="H304" t="n">
         <v>3145</v>
@@ -9272,7 +9272,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G307" t="n">
-        <v>4.93555021286011</v>
+        <v>4.93555068969727</v>
       </c>
       <c r="H307" t="n">
         <v>1214</v>
@@ -9301,7 +9301,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>4.76949453353882</v>
+        <v>4.76949501037598</v>
       </c>
       <c r="H308" t="n">
         <v>7904</v>
@@ -9359,7 +9359,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G310" t="n">
-        <v>4.92632532119751</v>
+        <v>4.92632579803467</v>
       </c>
       <c r="H310" t="n">
         <v>1967</v>
@@ -9417,7 +9417,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G312" t="n">
-        <v>4.76949453353882</v>
+        <v>4.76949501037598</v>
       </c>
       <c r="H312" t="n">
         <v>4994</v>
@@ -9446,7 +9446,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G313" t="n">
-        <v>4.75104379653931</v>
+        <v>4.75104427337646</v>
       </c>
       <c r="H313" t="n">
         <v>3070</v>
@@ -9504,7 +9504,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>4.75104379653931</v>
+        <v>4.75104427337646</v>
       </c>
       <c r="H315" t="n">
         <v>278649</v>
@@ -9562,7 +9562,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G317" t="n">
-        <v>4.92632532119751</v>
+        <v>4.92632579803467</v>
       </c>
       <c r="H317" t="n">
         <v>31544</v>
@@ -9591,7 +9591,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G318" t="n">
-        <v>4.87097358703613</v>
+        <v>4.87097406387329</v>
       </c>
       <c r="H318" t="n">
         <v>7990</v>
@@ -9620,7 +9620,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G319" t="n">
-        <v>5.06470489501953</v>
+        <v>5.06470537185669</v>
       </c>
       <c r="H319" t="n">
         <v>4244</v>
@@ -9649,7 +9649,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>4.88019847869873</v>
+        <v>4.88019895553589</v>
       </c>
       <c r="H320" t="n">
         <v>6441</v>
@@ -9707,7 +9707,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G322" t="n">
-        <v>4.87097358703613</v>
+        <v>4.87097406387329</v>
       </c>
       <c r="H322" t="n">
         <v>10071</v>
@@ -9765,7 +9765,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G324" t="n">
-        <v>5.04625463485718</v>
+        <v>5.04625415802002</v>
       </c>
       <c r="H324" t="n">
         <v>3919</v>
@@ -9823,7 +9823,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>4.806396484375</v>
+        <v>4.80639600753784</v>
       </c>
       <c r="H326" t="n">
         <v>9846</v>
@@ -9968,7 +9968,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G331" t="n">
-        <v>4.9909029006958</v>
+        <v>4.99090242385864</v>
       </c>
       <c r="H331" t="n">
         <v>1655</v>
@@ -9997,7 +9997,7 @@
         <v>5.5</v>
       </c>
       <c r="G332" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H332" t="n">
         <v>10755</v>
@@ -10026,7 +10026,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G333" t="n">
-        <v>4.98167753219604</v>
+        <v>4.98167705535889</v>
       </c>
       <c r="H333" t="n">
         <v>54722</v>
@@ -10055,7 +10055,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G334" t="n">
-        <v>5.10160732269287</v>
+        <v>5.10160684585571</v>
       </c>
       <c r="H334" t="n">
         <v>10899</v>
@@ -10084,7 +10084,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G335" t="n">
-        <v>4.98167753219604</v>
+        <v>4.98167705535889</v>
       </c>
       <c r="H335" t="n">
         <v>34644</v>
@@ -10113,7 +10113,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G336" t="n">
-        <v>5.06470489501953</v>
+        <v>5.06470537185669</v>
       </c>
       <c r="H336" t="n">
         <v>610</v>
@@ -10171,7 +10171,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>4.98167753219604</v>
+        <v>4.98167705535889</v>
       </c>
       <c r="H338" t="n">
         <v>3600</v>
@@ -10200,7 +10200,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G339" t="n">
-        <v>4.98167753219604</v>
+        <v>4.98167705535889</v>
       </c>
       <c r="H339" t="n">
         <v>700</v>
@@ -10258,7 +10258,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G341" t="n">
-        <v>4.92632532119751</v>
+        <v>4.92632579803467</v>
       </c>
       <c r="H341" t="n">
         <v>6351</v>
@@ -10287,7 +10287,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G342" t="n">
-        <v>4.92632532119751</v>
+        <v>4.92632579803467</v>
       </c>
       <c r="H342" t="n">
         <v>1223</v>
@@ -10316,7 +10316,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G343" t="n">
-        <v>4.93555021286011</v>
+        <v>4.93555068969727</v>
       </c>
       <c r="H343" t="n">
         <v>1750</v>
@@ -10345,7 +10345,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G344" t="n">
-        <v>4.98167753219604</v>
+        <v>4.98167705535889</v>
       </c>
       <c r="H344" t="n">
         <v>8710</v>
@@ -10490,7 +10490,7 @@
         <v>5</v>
       </c>
       <c r="G349" t="n">
-        <v>4.61266422271729</v>
+        <v>4.61266374588013</v>
       </c>
       <c r="H349" t="n">
         <v>8051</v>
@@ -10519,7 +10519,7 @@
         <v>5</v>
       </c>
       <c r="G350" t="n">
-        <v>4.61266422271729</v>
+        <v>4.61266374588013</v>
       </c>
       <c r="H350" t="n">
         <v>5297</v>
@@ -10548,7 +10548,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>4.75104379653931</v>
+        <v>4.75104427337646</v>
       </c>
       <c r="H351" t="n">
         <v>9088</v>
@@ -10606,7 +10606,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G353" t="n">
-        <v>4.88019847869873</v>
+        <v>4.88019895553589</v>
       </c>
       <c r="H353" t="n">
         <v>1026</v>
@@ -10635,7 +10635,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G354" t="n">
-        <v>5.01857900619507</v>
+        <v>5.01857852935791</v>
       </c>
       <c r="H354" t="n">
         <v>1901</v>
@@ -10664,7 +10664,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>5.01857900619507</v>
+        <v>5.01857852935791</v>
       </c>
       <c r="H355" t="n">
         <v>7480</v>
@@ -10693,7 +10693,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G356" t="n">
-        <v>5.01857900619507</v>
+        <v>5.01857852935791</v>
       </c>
       <c r="H356" t="n">
         <v>7610</v>
@@ -10722,7 +10722,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G357" t="n">
-        <v>5.01857900619507</v>
+        <v>5.01857852935791</v>
       </c>
       <c r="H357" t="n">
         <v>1202</v>
@@ -10751,7 +10751,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>5.03702926635742</v>
+        <v>5.03702974319458</v>
       </c>
       <c r="H358" t="n">
         <v>1175</v>
@@ -10983,7 +10983,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G366" t="n">
-        <v>5.05548048019409</v>
+        <v>5.05548000335693</v>
       </c>
       <c r="H366" t="n">
         <v>26294</v>
@@ -11041,7 +11041,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G368" t="n">
-        <v>5.14773321151733</v>
+        <v>5.14773368835449</v>
       </c>
       <c r="H368" t="n">
         <v>5393</v>
@@ -11128,7 +11128,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G371" t="n">
-        <v>5.33224058151245</v>
+        <v>5.33223962783813</v>
       </c>
       <c r="H371" t="n">
         <v>27751</v>
@@ -11186,7 +11186,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G373" t="n">
-        <v>5.35069036483765</v>
+        <v>5.3506908416748</v>
       </c>
       <c r="H373" t="n">
         <v>5008</v>
@@ -11215,7 +11215,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G374" t="n">
-        <v>5.27688789367676</v>
+        <v>5.2768874168396</v>
       </c>
       <c r="H374" t="n">
         <v>2643</v>
@@ -11273,7 +11273,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>5.35069036483765</v>
+        <v>5.3506908416748</v>
       </c>
       <c r="H376" t="n">
         <v>1774</v>
@@ -11302,7 +11302,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>5.35069036483765</v>
+        <v>5.3506908416748</v>
       </c>
       <c r="H377" t="n">
         <v>2594</v>
@@ -11331,7 +11331,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G378" t="n">
-        <v>5.25843667984009</v>
+        <v>5.25843715667725</v>
       </c>
       <c r="H378" t="n">
         <v>4491</v>
@@ -11360,7 +11360,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G379" t="n">
-        <v>5.25843667984009</v>
+        <v>5.25843715667725</v>
       </c>
       <c r="H379" t="n">
         <v>270</v>
@@ -11389,7 +11389,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G380" t="n">
-        <v>5.27688789367676</v>
+        <v>5.2768874168396</v>
       </c>
       <c r="H380" t="n">
         <v>43761</v>
@@ -11534,7 +11534,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G385" t="n">
-        <v>5.49246263504028</v>
+        <v>5.49246215820312</v>
       </c>
       <c r="H385" t="n">
         <v>5319</v>
@@ -11679,7 +11679,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H390" t="n">
         <v>24702</v>
@@ -11940,7 +11940,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G399" t="n">
-        <v>5.51120758056641</v>
+        <v>5.51120805740356</v>
       </c>
       <c r="H399" t="n">
         <v>550</v>
@@ -11969,7 +11969,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G400" t="n">
-        <v>5.49246263504028</v>
+        <v>5.49246215820312</v>
       </c>
       <c r="H400" t="n">
         <v>800</v>
@@ -12085,7 +12085,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G404" t="n">
-        <v>5.51120758056641</v>
+        <v>5.51120805740356</v>
       </c>
       <c r="H404" t="n">
         <v>1070</v>
@@ -12114,7 +12114,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H405" t="n">
         <v>1418</v>
@@ -12143,7 +12143,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G406" t="n">
-        <v>5.41747999191284</v>
+        <v>5.41747951507568</v>
       </c>
       <c r="H406" t="n">
         <v>1138</v>
@@ -12172,7 +12172,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G407" t="n">
-        <v>5.41747999191284</v>
+        <v>5.41747951507568</v>
       </c>
       <c r="H407" t="n">
         <v>9530</v>
@@ -12201,7 +12201,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G408" t="n">
-        <v>5.41747999191284</v>
+        <v>5.41747951507568</v>
       </c>
       <c r="H408" t="n">
         <v>200</v>
@@ -12230,7 +12230,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G409" t="n">
-        <v>5.41747999191284</v>
+        <v>5.41747951507568</v>
       </c>
       <c r="H409" t="n">
         <v>620</v>
@@ -12259,7 +12259,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G410" t="n">
-        <v>5.41747999191284</v>
+        <v>5.41747951507568</v>
       </c>
       <c r="H410" t="n">
         <v>8991</v>
@@ -12288,7 +12288,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H411" t="n">
         <v>200</v>
@@ -12317,7 +12317,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G412" t="n">
-        <v>5.41747999191284</v>
+        <v>5.41747951507568</v>
       </c>
       <c r="H412" t="n">
         <v>1439</v>
@@ -12346,7 +12346,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G413" t="n">
-        <v>5.41747999191284</v>
+        <v>5.41747951507568</v>
       </c>
       <c r="H413" t="n">
         <v>1000</v>
@@ -12375,7 +12375,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G414" t="n">
-        <v>5.41747999191284</v>
+        <v>5.41747951507568</v>
       </c>
       <c r="H414" t="n">
         <v>500</v>
@@ -12404,7 +12404,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H415" t="n">
         <v>100</v>
@@ -12433,7 +12433,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G416" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H416" t="n">
         <v>45</v>
@@ -12462,7 +12462,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G417" t="n">
-        <v>5.49246263504028</v>
+        <v>5.49246215820312</v>
       </c>
       <c r="H417" t="n">
         <v>210</v>
@@ -12578,7 +12578,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G421" t="n">
-        <v>5.41747999191284</v>
+        <v>5.41747951507568</v>
       </c>
       <c r="H421" t="n">
         <v>2490</v>
@@ -12607,7 +12607,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G422" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H422" t="n">
         <v>18970</v>
@@ -12752,7 +12752,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G427" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H427" t="n">
         <v>4203</v>
@@ -12781,7 +12781,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G428" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H428" t="n">
         <v>760</v>
@@ -12897,7 +12897,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G432" t="n">
-        <v>5.41747999191284</v>
+        <v>5.41747951507568</v>
       </c>
       <c r="H432" t="n">
         <v>1171</v>
@@ -12926,7 +12926,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G433" t="n">
-        <v>5.41747999191284</v>
+        <v>5.41747951507568</v>
       </c>
       <c r="H433" t="n">
         <v>0</v>
@@ -13042,7 +13042,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H437" t="n">
         <v>7332</v>
@@ -13071,7 +13071,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H438" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G443" t="n">
-        <v>5.41747999191284</v>
+        <v>5.41747951507568</v>
       </c>
       <c r="H443" t="n">
         <v>52</v>
@@ -13245,7 +13245,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H444" t="n">
         <v>10</v>
@@ -13332,7 +13332,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G447" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H447" t="n">
         <v>20</v>
@@ -13361,7 +13361,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G448" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H448" t="n">
         <v>2255</v>
@@ -13390,7 +13390,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G449" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H449" t="n">
         <v>300</v>
@@ -13593,7 +13593,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G456" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H456" t="n">
         <v>20122</v>
@@ -13883,7 +13883,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G466" t="n">
-        <v>5.41747999191284</v>
+        <v>5.41747951507568</v>
       </c>
       <c r="H466" t="n">
         <v>6381</v>
@@ -13941,7 +13941,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G468" t="n">
-        <v>5.41747999191284</v>
+        <v>5.41747951507568</v>
       </c>
       <c r="H468" t="n">
         <v>1239</v>
@@ -14028,7 +14028,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>5.2300238609314</v>
+        <v>5.23002433776855</v>
       </c>
       <c r="H471" t="n">
         <v>5247</v>
@@ -14115,7 +14115,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>5.17378711700439</v>
+        <v>5.17378664016724</v>
       </c>
       <c r="H474" t="n">
         <v>3332</v>
@@ -14144,7 +14144,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>5.09880495071411</v>
+        <v>5.09880447387695</v>
       </c>
       <c r="H475" t="n">
         <v>5512</v>
@@ -14289,7 +14289,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G480" t="n">
-        <v>4.7988748550415</v>
+        <v>4.79887437820435</v>
       </c>
       <c r="H480" t="n">
         <v>900</v>
@@ -14318,7 +14318,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H481" t="n">
         <v>16552</v>
@@ -14347,7 +14347,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G482" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H482" t="n">
         <v>1000</v>
@@ -14376,7 +14376,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G483" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14463,7 +14463,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>4.66765546798706</v>
+        <v>4.66765594482422</v>
       </c>
       <c r="H486" t="n">
         <v>8004</v>
@@ -14492,7 +14492,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G487" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H487" t="n">
         <v>1050</v>
@@ -14521,7 +14521,7 @@
         <v>5</v>
       </c>
       <c r="G488" t="n">
-        <v>4.6864013671875</v>
+        <v>4.68640089035034</v>
       </c>
       <c r="H488" t="n">
         <v>400</v>
@@ -14550,7 +14550,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G489" t="n">
-        <v>4.66765546798706</v>
+        <v>4.66765594482422</v>
       </c>
       <c r="H489" t="n">
         <v>49</v>
@@ -14579,7 +14579,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>4.64891004562378</v>
+        <v>4.64890956878662</v>
       </c>
       <c r="H490" t="n">
         <v>2650</v>
@@ -14695,7 +14695,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G494" t="n">
-        <v>4.64891004562378</v>
+        <v>4.64890956878662</v>
       </c>
       <c r="H494" t="n">
         <v>21434</v>
@@ -14724,7 +14724,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G495" t="n">
-        <v>4.65828275680542</v>
+        <v>4.65828323364258</v>
       </c>
       <c r="H495" t="n">
         <v>32639</v>
@@ -14753,7 +14753,7 @@
         <v>5</v>
       </c>
       <c r="G496" t="n">
-        <v>4.6864013671875</v>
+        <v>4.68640089035034</v>
       </c>
       <c r="H496" t="n">
         <v>7653</v>
@@ -14782,7 +14782,7 @@
         <v>5</v>
       </c>
       <c r="G497" t="n">
-        <v>4.6864013671875</v>
+        <v>4.68640089035034</v>
       </c>
       <c r="H497" t="n">
         <v>37466</v>
@@ -15101,7 +15101,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G508" t="n">
-        <v>4.7988748550415</v>
+        <v>4.79887437820435</v>
       </c>
       <c r="H508" t="n">
         <v>80250</v>
@@ -15217,7 +15217,7 @@
         <v>5.5</v>
       </c>
       <c r="G512" t="n">
-        <v>5.15504121780396</v>
+        <v>5.15504169464111</v>
       </c>
       <c r="H512" t="n">
         <v>4203</v>
@@ -15275,7 +15275,7 @@
         <v>5.5</v>
       </c>
       <c r="G514" t="n">
-        <v>5.15504121780396</v>
+        <v>5.15504169464111</v>
       </c>
       <c r="H514" t="n">
         <v>1884</v>
@@ -15391,7 +15391,7 @@
         <v>5.5</v>
       </c>
       <c r="G518" t="n">
-        <v>5.15504121780396</v>
+        <v>5.15504169464111</v>
       </c>
       <c r="H518" t="n">
         <v>6482</v>
@@ -15536,7 +15536,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G523" t="n">
-        <v>4.96758508682251</v>
+        <v>4.96758556365967</v>
       </c>
       <c r="H523" t="n">
         <v>560</v>
@@ -15565,7 +15565,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G524" t="n">
-        <v>5.09880495071411</v>
+        <v>5.09880447387695</v>
       </c>
       <c r="H524" t="n">
         <v>1651</v>
@@ -15594,7 +15594,7 @@
         <v>5.5</v>
       </c>
       <c r="G525" t="n">
-        <v>5.15504121780396</v>
+        <v>5.15504169464111</v>
       </c>
       <c r="H525" t="n">
         <v>3840</v>
@@ -15623,7 +15623,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G526" t="n">
-        <v>5.09880495071411</v>
+        <v>5.09880447387695</v>
       </c>
       <c r="H526" t="n">
         <v>2500</v>
@@ -15971,7 +15971,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G538" t="n">
-        <v>4.7988748550415</v>
+        <v>4.79887437820435</v>
       </c>
       <c r="H538" t="n">
         <v>11050</v>
@@ -16145,7 +16145,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G544" t="n">
-        <v>4.7988748550415</v>
+        <v>4.79887437820435</v>
       </c>
       <c r="H544" t="n">
         <v>1500</v>
@@ -16290,7 +16290,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G549" t="n">
-        <v>4.74263763427734</v>
+        <v>4.7426381111145</v>
       </c>
       <c r="H549" t="n">
         <v>400</v>
@@ -16348,7 +16348,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G551" t="n">
-        <v>4.66765546798706</v>
+        <v>4.66765594482422</v>
       </c>
       <c r="H551" t="n">
         <v>33872</v>
@@ -16377,7 +16377,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H552" t="n">
         <v>2770</v>
@@ -16406,7 +16406,7 @@
         <v>5</v>
       </c>
       <c r="G553" t="n">
-        <v>4.6864013671875</v>
+        <v>4.68640089035034</v>
       </c>
       <c r="H553" t="n">
         <v>200</v>
@@ -16435,7 +16435,7 @@
         <v>5</v>
       </c>
       <c r="G554" t="n">
-        <v>4.6864013671875</v>
+        <v>4.68640089035034</v>
       </c>
       <c r="H554" t="n">
         <v>1284</v>
@@ -16464,7 +16464,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H555" t="n">
         <v>1730</v>
@@ -16522,7 +16522,7 @@
         <v>5</v>
       </c>
       <c r="G557" t="n">
-        <v>4.6864013671875</v>
+        <v>4.68640089035034</v>
       </c>
       <c r="H557" t="n">
         <v>5070</v>
@@ -16551,7 +16551,7 @@
         <v>5</v>
       </c>
       <c r="G558" t="n">
-        <v>4.6864013671875</v>
+        <v>4.68640089035034</v>
       </c>
       <c r="H558" t="n">
         <v>497</v>
@@ -16667,7 +16667,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G562" t="n">
-        <v>4.7988748550415</v>
+        <v>4.79887437820435</v>
       </c>
       <c r="H562" t="n">
         <v>5341</v>
@@ -16812,7 +16812,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>5.09880495071411</v>
+        <v>5.09880447387695</v>
       </c>
       <c r="H567" t="n">
         <v>17491</v>
@@ -16986,7 +16986,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G573" t="n">
-        <v>3.9646954536438</v>
+        <v>3.96469569206238</v>
       </c>
       <c r="H573" t="n">
         <v>1226</v>
@@ -17044,7 +17044,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G575" t="n">
-        <v>4.0865421295166</v>
+        <v>4.08654260635376</v>
       </c>
       <c r="H575" t="n">
         <v>16683</v>
@@ -17073,7 +17073,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>4.04905080795288</v>
+        <v>4.04905128479004</v>
       </c>
       <c r="H576" t="n">
         <v>6405</v>
@@ -17102,7 +17102,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G577" t="n">
-        <v>4.04905080795288</v>
+        <v>4.04905128479004</v>
       </c>
       <c r="H577" t="n">
         <v>5942</v>
@@ -17131,7 +17131,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G578" t="n">
-        <v>3.9646954536438</v>
+        <v>3.96469569206238</v>
       </c>
       <c r="H578" t="n">
         <v>2445</v>
@@ -17189,7 +17189,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>3.9459502696991</v>
+        <v>3.94595003128052</v>
       </c>
       <c r="H580" t="n">
         <v>8147</v>
@@ -17276,7 +17276,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G583" t="n">
-        <v>3.88971304893494</v>
+        <v>3.88971281051636</v>
       </c>
       <c r="H583" t="n">
         <v>2610</v>
@@ -17305,7 +17305,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>3.9459502696991</v>
+        <v>3.94595003128052</v>
       </c>
       <c r="H584" t="n">
         <v>3049</v>
@@ -17421,7 +17421,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G588" t="n">
-        <v>3.88971304893494</v>
+        <v>3.88971281051636</v>
       </c>
       <c r="H588" t="n">
         <v>3999</v>
@@ -17537,7 +17537,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G592" t="n">
-        <v>3.88971304893494</v>
+        <v>3.88971281051636</v>
       </c>
       <c r="H592" t="n">
         <v>30337</v>
@@ -17711,7 +17711,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G598" t="n">
-        <v>4.10528802871704</v>
+        <v>4.10528755187988</v>
       </c>
       <c r="H598" t="n">
         <v>5102</v>
@@ -17740,7 +17740,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G599" t="n">
-        <v>4.10528802871704</v>
+        <v>4.10528755187988</v>
       </c>
       <c r="H599" t="n">
         <v>4178</v>
@@ -17769,7 +17769,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G600" t="n">
-        <v>4.10528802871704</v>
+        <v>4.10528755187988</v>
       </c>
       <c r="H600" t="n">
         <v>2406</v>
@@ -17798,7 +17798,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G601" t="n">
-        <v>4.0303053855896</v>
+        <v>4.03030490875244</v>
       </c>
       <c r="H601" t="n">
         <v>1764</v>
@@ -17827,7 +17827,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G602" t="n">
-        <v>4.04905080795288</v>
+        <v>4.04905128479004</v>
       </c>
       <c r="H602" t="n">
         <v>150</v>
@@ -17856,7 +17856,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G603" t="n">
-        <v>4.10528802871704</v>
+        <v>4.10528755187988</v>
       </c>
       <c r="H603" t="n">
         <v>5008</v>
@@ -17885,7 +17885,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G604" t="n">
-        <v>4.10528802871704</v>
+        <v>4.10528755187988</v>
       </c>
       <c r="H604" t="n">
         <v>7230</v>
@@ -17914,7 +17914,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G605" t="n">
-        <v>4.0865421295166</v>
+        <v>4.08654260635376</v>
       </c>
       <c r="H605" t="n">
         <v>4030</v>
@@ -17943,7 +17943,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G606" t="n">
-        <v>4.0865421295166</v>
+        <v>4.08654260635376</v>
       </c>
       <c r="H606" t="n">
         <v>1150</v>
@@ -18117,7 +18117,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>4.09591436386108</v>
+        <v>4.09591484069824</v>
       </c>
       <c r="H612" t="n">
         <v>401</v>
@@ -18146,7 +18146,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G613" t="n">
-        <v>4.09591436386108</v>
+        <v>4.09591484069824</v>
       </c>
       <c r="H613" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G618" t="n">
-        <v>3.88971304893494</v>
+        <v>3.88971281051636</v>
       </c>
       <c r="H618" t="n">
         <v>450</v>
@@ -18320,7 +18320,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G619" t="n">
-        <v>3.88971304893494</v>
+        <v>3.88971281051636</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -18349,7 +18349,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G620" t="n">
-        <v>3.88971304893494</v>
+        <v>3.88971281051636</v>
       </c>
       <c r="H620" t="n">
         <v>200</v>
@@ -18378,7 +18378,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G621" t="n">
-        <v>3.88971304893494</v>
+        <v>3.88971281051636</v>
       </c>
       <c r="H621" t="n">
         <v>1810</v>
@@ -18494,7 +18494,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G625" t="n">
-        <v>3.70225715637207</v>
+        <v>3.70225691795349</v>
       </c>
       <c r="H625" t="n">
         <v>2781</v>
@@ -18523,7 +18523,7 @@
         <v>4</v>
       </c>
       <c r="G626" t="n">
-        <v>3.74912118911743</v>
+        <v>3.74912095069885</v>
       </c>
       <c r="H626" t="n">
         <v>4138</v>
@@ -18552,7 +18552,7 @@
         <v>4</v>
       </c>
       <c r="G627" t="n">
-        <v>3.74912118911743</v>
+        <v>3.74912095069885</v>
       </c>
       <c r="H627" t="n">
         <v>3430</v>
@@ -18581,7 +18581,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G628" t="n">
-        <v>3.70225715637207</v>
+        <v>3.70225691795349</v>
       </c>
       <c r="H628" t="n">
         <v>432</v>
@@ -18610,7 +18610,7 @@
         <v>4</v>
       </c>
       <c r="G629" t="n">
-        <v>3.74912118911743</v>
+        <v>3.74912095069885</v>
       </c>
       <c r="H629" t="n">
         <v>1000</v>
@@ -18668,7 +18668,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G631" t="n">
-        <v>3.66476583480835</v>
+        <v>3.66476559638977</v>
       </c>
       <c r="H631" t="n">
         <v>2461</v>
@@ -36683,6 +36683,35 @@
         <v>3194</v>
       </c>
       <c r="I1252" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1253" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1253" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="D1253" t="n">
+        <v>5.15999984741211</v>
+      </c>
+      <c r="E1253" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="F1253" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="G1253" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="H1253" t="n">
+        <v>4395</v>
+      </c>
+      <c r="I1253" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RFG.MI.xlsx
+++ b/data/RFG.MI.xlsx
@@ -456,7 +456,7 @@
         <v>5.0789999961853</v>
       </c>
       <c r="G3" t="n">
-        <v>4.60962104797363</v>
+        <v>4.60962152481079</v>
       </c>
       <c r="H3" t="n">
         <v>253124</v>
@@ -514,7 +514,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G5" t="n">
-        <v>4.30648803710938</v>
+        <v>4.30648756027222</v>
       </c>
       <c r="H5" t="n">
         <v>223483</v>
@@ -572,7 +572,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>4.35640573501587</v>
+        <v>4.35640525817871</v>
       </c>
       <c r="H7" t="n">
         <v>53988</v>
@@ -601,7 +601,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G8" t="n">
-        <v>4.22934293746948</v>
+        <v>4.22934341430664</v>
       </c>
       <c r="H8" t="n">
         <v>147200</v>
@@ -1007,7 +1007,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G22" t="n">
-        <v>4.74666690826416</v>
+        <v>4.746666431427</v>
       </c>
       <c r="H22" t="n">
         <v>84587</v>
@@ -1036,7 +1036,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G23" t="n">
-        <v>4.75574207305908</v>
+        <v>4.75574254989624</v>
       </c>
       <c r="H23" t="n">
         <v>42090</v>
@@ -1094,7 +1094,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>4.84650087356567</v>
+        <v>4.84650039672852</v>
       </c>
       <c r="H25" t="n">
         <v>24608</v>
@@ -1123,7 +1123,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G26" t="n">
-        <v>4.84650087356567</v>
+        <v>4.84650039672852</v>
       </c>
       <c r="H26" t="n">
         <v>84199</v>
@@ -1210,7 +1210,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>5.20045852661133</v>
+        <v>5.20045900344849</v>
       </c>
       <c r="H29" t="n">
         <v>89716</v>
@@ -1239,7 +1239,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G30" t="n">
-        <v>5.47273445129395</v>
+        <v>5.47273397445679</v>
       </c>
       <c r="H30" t="n">
         <v>193631</v>
@@ -1268,7 +1268,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>5.52718925476074</v>
+        <v>5.52718877792358</v>
       </c>
       <c r="H31" t="n">
         <v>27209</v>
@@ -1297,7 +1297,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G32" t="n">
-        <v>5.43643093109131</v>
+        <v>5.43643045425415</v>
       </c>
       <c r="H32" t="n">
         <v>36811</v>
@@ -1326,7 +1326,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G33" t="n">
-        <v>5.43643093109131</v>
+        <v>5.43643045425415</v>
       </c>
       <c r="H33" t="n">
         <v>30706</v>
@@ -1442,7 +1442,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>5.25491380691528</v>
+        <v>5.25491333007812</v>
       </c>
       <c r="H37" t="n">
         <v>23662</v>
@@ -1471,7 +1471,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G38" t="n">
-        <v>5.31844425201416</v>
+        <v>5.31844472885132</v>
       </c>
       <c r="H38" t="n">
         <v>24272</v>
@@ -1529,7 +1529,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G40" t="n">
-        <v>5.30936861038208</v>
+        <v>5.30936813354492</v>
       </c>
       <c r="H40" t="n">
         <v>10863</v>
@@ -1558,7 +1558,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G41" t="n">
-        <v>5.39105129241943</v>
+        <v>5.39105081558228</v>
       </c>
       <c r="H41" t="n">
         <v>11791</v>
@@ -1616,7 +1616,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G43" t="n">
-        <v>5.42735433578491</v>
+        <v>5.42735481262207</v>
       </c>
       <c r="H43" t="n">
         <v>24833</v>
@@ -1703,7 +1703,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G46" t="n">
-        <v>5.34567213058472</v>
+        <v>5.34567165374756</v>
       </c>
       <c r="H46" t="n">
         <v>21861</v>
@@ -1761,7 +1761,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G48" t="n">
-        <v>5.10970020294189</v>
+        <v>5.10969972610474</v>
       </c>
       <c r="H48" t="n">
         <v>75369</v>
@@ -1819,7 +1819,7 @@
         <v>5.75</v>
       </c>
       <c r="G50" t="n">
-        <v>5.2186107635498</v>
+        <v>5.21861028671265</v>
       </c>
       <c r="H50" t="n">
         <v>53296</v>
@@ -1848,7 +1848,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G51" t="n">
-        <v>5.20045852661133</v>
+        <v>5.20045900344849</v>
       </c>
       <c r="H51" t="n">
         <v>11633</v>
@@ -1877,7 +1877,7 @@
         <v>5.5</v>
       </c>
       <c r="G52" t="n">
-        <v>4.99171447753906</v>
+        <v>4.9917140007019</v>
       </c>
       <c r="H52" t="n">
         <v>31337</v>
@@ -1935,7 +1935,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G54" t="n">
-        <v>5.0461688041687</v>
+        <v>5.04616928100586</v>
       </c>
       <c r="H54" t="n">
         <v>17032</v>
@@ -1964,7 +1964,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G55" t="n">
-        <v>5.05524492263794</v>
+        <v>5.0552453994751</v>
       </c>
       <c r="H55" t="n">
         <v>23049</v>
@@ -1993,7 +1993,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G56" t="n">
-        <v>4.94633483886719</v>
+        <v>4.94633436203003</v>
       </c>
       <c r="H56" t="n">
         <v>4077</v>
@@ -2051,7 +2051,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G58" t="n">
-        <v>4.86465215682983</v>
+        <v>4.86465167999268</v>
       </c>
       <c r="H58" t="n">
         <v>10871</v>
@@ -2109,7 +2109,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G60" t="n">
-        <v>5.01894187927246</v>
+        <v>5.01894235610962</v>
       </c>
       <c r="H60" t="n">
         <v>23167</v>
@@ -2138,7 +2138,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G61" t="n">
-        <v>4.92818355560303</v>
+        <v>4.92818307876587</v>
       </c>
       <c r="H61" t="n">
         <v>10150</v>
@@ -2196,7 +2196,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>4.74666690826416</v>
+        <v>4.746666431427</v>
       </c>
       <c r="H63" t="n">
         <v>54083</v>
@@ -2254,7 +2254,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G65" t="n">
-        <v>4.68313503265381</v>
+        <v>4.68313550949097</v>
       </c>
       <c r="H65" t="n">
         <v>14192</v>
@@ -2283,7 +2283,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G66" t="n">
-        <v>4.63775634765625</v>
+        <v>4.63775682449341</v>
       </c>
       <c r="H66" t="n">
         <v>9021</v>
@@ -2399,7 +2399,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G70" t="n">
-        <v>4.93725872039795</v>
+        <v>4.93725919723511</v>
       </c>
       <c r="H70" t="n">
         <v>2829</v>
@@ -2428,7 +2428,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G71" t="n">
-        <v>4.68313503265381</v>
+        <v>4.68313550949097</v>
       </c>
       <c r="H71" t="n">
         <v>21164</v>
@@ -2457,7 +2457,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G72" t="n">
-        <v>4.7738938331604</v>
+        <v>4.77389430999756</v>
       </c>
       <c r="H72" t="n">
         <v>8024</v>
@@ -2486,7 +2486,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G73" t="n">
-        <v>4.84650087356567</v>
+        <v>4.84650039672852</v>
       </c>
       <c r="H73" t="n">
         <v>6837</v>
@@ -2544,7 +2544,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G75" t="n">
-        <v>4.74666690826416</v>
+        <v>4.746666431427</v>
       </c>
       <c r="H75" t="n">
         <v>12871</v>
@@ -2602,7 +2602,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G77" t="n">
-        <v>4.13858509063721</v>
+        <v>4.13858556747437</v>
       </c>
       <c r="H77" t="n">
         <v>29751</v>
@@ -2631,7 +2631,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G78" t="n">
-        <v>4.13404750823975</v>
+        <v>4.13404703140259</v>
       </c>
       <c r="H78" t="n">
         <v>12171</v>
@@ -2747,7 +2747,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G82" t="n">
-        <v>4.02059841156006</v>
+        <v>4.02059888839722</v>
       </c>
       <c r="H82" t="n">
         <v>47987</v>
@@ -2805,7 +2805,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G84" t="n">
-        <v>4.01152324676514</v>
+        <v>4.01152276992798</v>
       </c>
       <c r="H84" t="n">
         <v>13008</v>
@@ -2834,7 +2834,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>4.03421306610107</v>
+        <v>4.03421258926392</v>
       </c>
       <c r="H85" t="n">
         <v>9318</v>
@@ -2863,7 +2863,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>4.15673685073853</v>
+        <v>4.15673637390137</v>
       </c>
       <c r="H86" t="n">
         <v>20105</v>
@@ -2892,7 +2892,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G87" t="n">
-        <v>4.21119165420532</v>
+        <v>4.21119117736816</v>
       </c>
       <c r="H87" t="n">
         <v>12593</v>
@@ -2979,7 +2979,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G90" t="n">
-        <v>4.68313503265381</v>
+        <v>4.68313550949097</v>
       </c>
       <c r="H90" t="n">
         <v>7231</v>
@@ -3037,7 +3037,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G92" t="n">
-        <v>4.53338432312012</v>
+        <v>4.53338384628296</v>
       </c>
       <c r="H92" t="n">
         <v>1969</v>
@@ -3095,7 +3095,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G94" t="n">
-        <v>4.50615692138672</v>
+        <v>4.50615644454956</v>
       </c>
       <c r="H94" t="n">
         <v>2116</v>
@@ -3240,7 +3240,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>4.50161790847778</v>
+        <v>4.5016188621521</v>
       </c>
       <c r="H99" t="n">
         <v>18031</v>
@@ -3298,7 +3298,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G101" t="n">
-        <v>4.35640573501587</v>
+        <v>4.35640525817871</v>
       </c>
       <c r="H101" t="n">
         <v>2000</v>
@@ -3327,7 +3327,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G102" t="n">
-        <v>4.35640573501587</v>
+        <v>4.35640525817871</v>
       </c>
       <c r="H102" t="n">
         <v>1155</v>
@@ -3356,7 +3356,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G103" t="n">
-        <v>4.34732866287231</v>
+        <v>4.34732913970947</v>
       </c>
       <c r="H103" t="n">
         <v>12517</v>
@@ -3385,7 +3385,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>4.27472257614136</v>
+        <v>4.27472305297852</v>
       </c>
       <c r="H104" t="n">
         <v>501</v>
@@ -3501,7 +3501,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>4.34732866287231</v>
+        <v>4.34732913970947</v>
       </c>
       <c r="H108" t="n">
         <v>5476</v>
@@ -3646,7 +3646,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G113" t="n">
-        <v>4.37455749511719</v>
+        <v>4.37455701828003</v>
       </c>
       <c r="H113" t="n">
         <v>38</v>
@@ -3675,7 +3675,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G114" t="n">
-        <v>4.4653148651123</v>
+        <v>4.46531534194946</v>
       </c>
       <c r="H114" t="n">
         <v>2900</v>
@@ -3704,7 +3704,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>4.27472257614136</v>
+        <v>4.27472305297852</v>
       </c>
       <c r="H115" t="n">
         <v>3033</v>
@@ -3733,7 +3733,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G116" t="n">
-        <v>4.29287433624268</v>
+        <v>4.29287385940552</v>
       </c>
       <c r="H116" t="n">
         <v>5190</v>
@@ -3791,7 +3791,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G118" t="n">
-        <v>4.24295711517334</v>
+        <v>4.2429575920105</v>
       </c>
       <c r="H118" t="n">
         <v>50</v>
@@ -3849,7 +3849,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G120" t="n">
-        <v>3.88446164131165</v>
+        <v>3.88446092605591</v>
       </c>
       <c r="H120" t="n">
         <v>37503</v>
@@ -3907,7 +3907,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>3.89807534217834</v>
+        <v>3.89807486534119</v>
       </c>
       <c r="H122" t="n">
         <v>1318</v>
@@ -3936,7 +3936,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G123" t="n">
-        <v>3.88446164131165</v>
+        <v>3.88446092605591</v>
       </c>
       <c r="H123" t="n">
         <v>3695</v>
@@ -3965,7 +3965,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G124" t="n">
-        <v>3.88446164131165</v>
+        <v>3.88446092605591</v>
       </c>
       <c r="H124" t="n">
         <v>7707</v>
@@ -4052,7 +4052,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G127" t="n">
-        <v>4.21597528457642</v>
+        <v>4.21597480773926</v>
       </c>
       <c r="H127" t="n">
         <v>26910</v>
@@ -4081,7 +4081,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G128" t="n">
-        <v>4.2990026473999</v>
+        <v>4.29900312423706</v>
       </c>
       <c r="H128" t="n">
         <v>9321</v>
@@ -4139,7 +4139,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G130" t="n">
-        <v>4.23903799057007</v>
+        <v>4.23903846740723</v>
       </c>
       <c r="H130" t="n">
         <v>6758</v>
@@ -4226,7 +4226,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G133" t="n">
-        <v>4.32667922973633</v>
+        <v>4.32667970657349</v>
       </c>
       <c r="H133" t="n">
         <v>10570</v>
@@ -4255,7 +4255,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G134" t="n">
-        <v>4.37741851806641</v>
+        <v>4.37741804122925</v>
       </c>
       <c r="H134" t="n">
         <v>1511</v>
@@ -4284,7 +4284,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G135" t="n">
-        <v>4.37280511856079</v>
+        <v>4.37280559539795</v>
       </c>
       <c r="H135" t="n">
         <v>4000</v>
@@ -4458,7 +4458,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>4.24826431274414</v>
+        <v>4.24826383590698</v>
       </c>
       <c r="H141" t="n">
         <v>1470</v>
@@ -4516,7 +4516,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G143" t="n">
-        <v>4.2067494392395</v>
+        <v>4.20674991607666</v>
       </c>
       <c r="H143" t="n">
         <v>17151</v>
@@ -4574,7 +4574,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G145" t="n">
-        <v>4.05453205108643</v>
+        <v>4.05453157424927</v>
       </c>
       <c r="H145" t="n">
         <v>90396</v>
@@ -4603,7 +4603,7 @@
         <v>4.25</v>
       </c>
       <c r="G146" t="n">
-        <v>3.92076444625854</v>
+        <v>3.92076468467712</v>
       </c>
       <c r="H146" t="n">
         <v>15623</v>
@@ -4632,7 +4632,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>3.89770078659058</v>
+        <v>3.89770126342773</v>
       </c>
       <c r="H147" t="n">
         <v>8340</v>
@@ -4661,7 +4661,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766639709473</v>
       </c>
       <c r="H148" t="n">
         <v>2849</v>
@@ -4690,7 +4690,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G149" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766639709473</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G153" t="n">
-        <v>3.98534250259399</v>
+        <v>3.98534202575684</v>
       </c>
       <c r="H153" t="n">
         <v>8687</v>
@@ -4893,7 +4893,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>4.05914449691772</v>
+        <v>4.05914497375488</v>
       </c>
       <c r="H156" t="n">
         <v>120</v>
@@ -4980,7 +4980,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G159" t="n">
-        <v>3.82851099967957</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H159" t="n">
         <v>11901</v>
@@ -5009,7 +5009,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G160" t="n">
-        <v>3.91153907775879</v>
+        <v>3.91153883934021</v>
       </c>
       <c r="H160" t="n">
         <v>4000</v>
@@ -5096,7 +5096,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G163" t="n">
-        <v>3.82851099967957</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H163" t="n">
         <v>5720</v>
@@ -5125,7 +5125,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G164" t="n">
-        <v>3.83773684501648</v>
+        <v>3.8377366065979</v>
       </c>
       <c r="H164" t="n">
         <v>2438</v>
@@ -5212,7 +5212,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>3.89770078659058</v>
+        <v>3.89770126342773</v>
       </c>
       <c r="H167" t="n">
         <v>205</v>
@@ -5241,7 +5241,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G168" t="n">
-        <v>3.98534250259399</v>
+        <v>3.98534202575684</v>
       </c>
       <c r="H168" t="n">
         <v>5404</v>
@@ -5386,7 +5386,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G173" t="n">
-        <v>4.05453205108643</v>
+        <v>4.05453157424927</v>
       </c>
       <c r="H173" t="n">
         <v>6047</v>
@@ -5502,7 +5502,7 @@
         <v>4.25</v>
       </c>
       <c r="G177" t="n">
-        <v>3.92076444625854</v>
+        <v>3.92076468467712</v>
       </c>
       <c r="H177" t="n">
         <v>3092</v>
@@ -5531,7 +5531,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>3.88386344909668</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H178" t="n">
         <v>5254</v>
@@ -5589,7 +5589,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G180" t="n">
-        <v>3.82851099967957</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H180" t="n">
         <v>6092</v>
@@ -5618,7 +5618,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G181" t="n">
-        <v>3.83773684501648</v>
+        <v>3.8377366065979</v>
       </c>
       <c r="H181" t="n">
         <v>5582</v>
@@ -5647,7 +5647,7 @@
         <v>4.25</v>
       </c>
       <c r="G182" t="n">
-        <v>3.92076444625854</v>
+        <v>3.92076468467712</v>
       </c>
       <c r="H182" t="n">
         <v>4226</v>
@@ -5676,7 +5676,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G183" t="n">
-        <v>3.88386344909668</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H183" t="n">
         <v>11079</v>
@@ -5850,7 +5850,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G189" t="n">
-        <v>4.00840520858765</v>
+        <v>4.00840473175049</v>
       </c>
       <c r="H189" t="n">
         <v>3667</v>
@@ -5879,7 +5879,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>3.88386344909668</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H190" t="n">
         <v>1237</v>
@@ -5937,7 +5937,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766639709473</v>
       </c>
       <c r="H192" t="n">
         <v>3183</v>
@@ -5995,7 +5995,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G194" t="n">
-        <v>4.00379228591919</v>
+        <v>4.00379276275635</v>
       </c>
       <c r="H194" t="n">
         <v>1199</v>
@@ -6053,7 +6053,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G196" t="n">
-        <v>3.86541271209717</v>
+        <v>3.86541247367859</v>
       </c>
       <c r="H196" t="n">
         <v>5890</v>
@@ -6082,7 +6082,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G197" t="n">
-        <v>3.94844102859497</v>
+        <v>3.94844055175781</v>
       </c>
       <c r="H197" t="n">
         <v>2149</v>
@@ -6111,7 +6111,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G198" t="n">
-        <v>3.86079978942871</v>
+        <v>3.86080026626587</v>
       </c>
       <c r="H198" t="n">
         <v>3433</v>
@@ -6227,7 +6227,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G202" t="n">
-        <v>4.05914449691772</v>
+        <v>4.05914497375488</v>
       </c>
       <c r="H202" t="n">
         <v>7141</v>
@@ -6285,7 +6285,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G204" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766639709473</v>
       </c>
       <c r="H204" t="n">
         <v>5370</v>
@@ -6343,7 +6343,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G206" t="n">
-        <v>3.94844102859497</v>
+        <v>3.94844055175781</v>
       </c>
       <c r="H206" t="n">
         <v>5295</v>
@@ -6401,7 +6401,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>3.90231418609619</v>
+        <v>3.90231394767761</v>
       </c>
       <c r="H208" t="n">
         <v>1430</v>
@@ -6459,7 +6459,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G210" t="n">
-        <v>3.90692710876465</v>
+        <v>3.90692663192749</v>
       </c>
       <c r="H210" t="n">
         <v>2126</v>
@@ -6488,7 +6488,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G211" t="n">
-        <v>3.94844102859497</v>
+        <v>3.94844055175781</v>
       </c>
       <c r="H211" t="n">
         <v>5037</v>
@@ -6517,7 +6517,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G212" t="n">
-        <v>3.87002563476562</v>
+        <v>3.87002515792847</v>
       </c>
       <c r="H212" t="n">
         <v>3149</v>
@@ -6546,7 +6546,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>3.88386344909668</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H213" t="n">
         <v>1793</v>
@@ -6575,7 +6575,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G214" t="n">
-        <v>3.88386344909668</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H214" t="n">
         <v>63</v>
@@ -6662,7 +6662,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G217" t="n">
-        <v>3.90692710876465</v>
+        <v>3.90692663192749</v>
       </c>
       <c r="H217" t="n">
         <v>601</v>
@@ -6691,7 +6691,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G218" t="n">
-        <v>3.81928586959839</v>
+        <v>3.81928610801697</v>
       </c>
       <c r="H218" t="n">
         <v>120</v>
@@ -6720,7 +6720,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G219" t="n">
-        <v>3.82851099967957</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H219" t="n">
         <v>650</v>
@@ -6749,7 +6749,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>3.82851099967957</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G222" t="n">
-        <v>3.82851099967957</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H222" t="n">
         <v>400</v>
@@ -7097,7 +7097,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G232" t="n">
-        <v>4.21597528457642</v>
+        <v>4.21597480773926</v>
       </c>
       <c r="H232" t="n">
         <v>7962</v>
@@ -7184,7 +7184,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G235" t="n">
-        <v>4.37280511856079</v>
+        <v>4.37280559539795</v>
       </c>
       <c r="H235" t="n">
         <v>17132</v>
@@ -7503,7 +7503,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G246" t="n">
-        <v>4.3543553352356</v>
+        <v>4.35435438156128</v>
       </c>
       <c r="H246" t="n">
         <v>2400</v>
@@ -7619,7 +7619,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G250" t="n">
-        <v>4.37280511856079</v>
+        <v>4.37280559539795</v>
       </c>
       <c r="H250" t="n">
         <v>241</v>
@@ -7648,7 +7648,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G251" t="n">
-        <v>4.3543553352356</v>
+        <v>4.35435438156128</v>
       </c>
       <c r="H251" t="n">
         <v>1595</v>
@@ -7764,7 +7764,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G255" t="n">
-        <v>4.55731248855591</v>
+        <v>4.55731201171875</v>
       </c>
       <c r="H255" t="n">
         <v>4318</v>
@@ -7822,7 +7822,7 @@
         <v>5</v>
       </c>
       <c r="G257" t="n">
-        <v>4.61266374588013</v>
+        <v>4.61266422271729</v>
       </c>
       <c r="H257" t="n">
         <v>5177</v>
@@ -7938,7 +7938,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G261" t="n">
-        <v>4.59882593154907</v>
+        <v>4.59882640838623</v>
       </c>
       <c r="H261" t="n">
         <v>4514</v>
@@ -7967,7 +7967,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G262" t="n">
-        <v>4.74181890487671</v>
+        <v>4.74181842803955</v>
       </c>
       <c r="H262" t="n">
         <v>8453</v>
@@ -7996,7 +7996,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G263" t="n">
-        <v>4.89864921569824</v>
+        <v>4.8986496925354</v>
       </c>
       <c r="H263" t="n">
         <v>29512</v>
@@ -8141,7 +8141,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G268" t="n">
-        <v>5.02780389785767</v>
+        <v>5.02780342102051</v>
       </c>
       <c r="H268" t="n">
         <v>4916</v>
@@ -8228,7 +8228,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G271" t="n">
-        <v>4.89864921569824</v>
+        <v>4.8986496925354</v>
       </c>
       <c r="H271" t="n">
         <v>10062</v>
@@ -8373,7 +8373,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H276" t="n">
         <v>5852</v>
@@ -8402,7 +8402,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G277" t="n">
-        <v>5.03702974319458</v>
+        <v>5.03702926635742</v>
       </c>
       <c r="H277" t="n">
         <v>22783</v>
@@ -8518,7 +8518,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G281" t="n">
-        <v>5.15695905685425</v>
+        <v>5.15695858001709</v>
       </c>
       <c r="H281" t="n">
         <v>13832</v>
@@ -8605,7 +8605,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G284" t="n">
-        <v>5.13850784301758</v>
+        <v>5.13850831985474</v>
       </c>
       <c r="H284" t="n">
         <v>3550</v>
@@ -8779,7 +8779,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G290" t="n">
-        <v>5.0831561088562</v>
+        <v>5.08315658569336</v>
       </c>
       <c r="H290" t="n">
         <v>100</v>
@@ -8866,7 +8866,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G293" t="n">
-        <v>5.15695905685425</v>
+        <v>5.15695858001709</v>
       </c>
       <c r="H293" t="n">
         <v>10</v>
@@ -8895,7 +8895,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G294" t="n">
-        <v>5.11083221435547</v>
+        <v>5.11083173751831</v>
       </c>
       <c r="H294" t="n">
         <v>27739</v>
@@ -8982,7 +8982,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>4.98167705535889</v>
+        <v>4.98167753219604</v>
       </c>
       <c r="H297" t="n">
         <v>83453</v>
@@ -9069,7 +9069,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G300" t="n">
-        <v>4.95400094985962</v>
+        <v>4.95400142669678</v>
       </c>
       <c r="H300" t="n">
         <v>25268</v>
@@ -9098,7 +9098,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G301" t="n">
-        <v>4.89864921569824</v>
+        <v>4.8986496925354</v>
       </c>
       <c r="H301" t="n">
         <v>49432</v>
@@ -9156,7 +9156,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G303" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H303" t="n">
         <v>700</v>
@@ -9185,7 +9185,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G304" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H304" t="n">
         <v>3145</v>
@@ -9301,7 +9301,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>4.76949501037598</v>
+        <v>4.76949548721313</v>
       </c>
       <c r="H308" t="n">
         <v>7904</v>
@@ -9330,7 +9330,7 @@
         <v>5.25</v>
       </c>
       <c r="G309" t="n">
-        <v>4.84329748153687</v>
+        <v>4.84329700469971</v>
       </c>
       <c r="H309" t="n">
         <v>995</v>
@@ -9359,7 +9359,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G310" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H310" t="n">
         <v>1967</v>
@@ -9388,7 +9388,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G311" t="n">
-        <v>4.81562089920044</v>
+        <v>4.8156213760376</v>
       </c>
       <c r="H311" t="n">
         <v>3343</v>
@@ -9417,7 +9417,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G312" t="n">
-        <v>4.76949501037598</v>
+        <v>4.76949548721313</v>
       </c>
       <c r="H312" t="n">
         <v>4994</v>
@@ -9533,7 +9533,7 @@
         <v>5.25</v>
       </c>
       <c r="G316" t="n">
-        <v>4.84329748153687</v>
+        <v>4.84329700469971</v>
       </c>
       <c r="H316" t="n">
         <v>16</v>
@@ -9562,7 +9562,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G317" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H317" t="n">
         <v>31544</v>
@@ -9852,7 +9852,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G327" t="n">
-        <v>4.81562089920044</v>
+        <v>4.8156213760376</v>
       </c>
       <c r="H327" t="n">
         <v>123</v>
@@ -10026,7 +10026,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G333" t="n">
-        <v>4.98167705535889</v>
+        <v>4.98167753219604</v>
       </c>
       <c r="H333" t="n">
         <v>54722</v>
@@ -10084,7 +10084,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G335" t="n">
-        <v>4.98167705535889</v>
+        <v>4.98167753219604</v>
       </c>
       <c r="H335" t="n">
         <v>34644</v>
@@ -10171,7 +10171,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>4.98167705535889</v>
+        <v>4.98167753219604</v>
       </c>
       <c r="H338" t="n">
         <v>3600</v>
@@ -10200,7 +10200,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G339" t="n">
-        <v>4.98167705535889</v>
+        <v>4.98167753219604</v>
       </c>
       <c r="H339" t="n">
         <v>700</v>
@@ -10258,7 +10258,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G341" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H341" t="n">
         <v>6351</v>
@@ -10287,7 +10287,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G342" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H342" t="n">
         <v>1223</v>
@@ -10345,7 +10345,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G344" t="n">
-        <v>4.98167705535889</v>
+        <v>4.98167753219604</v>
       </c>
       <c r="H344" t="n">
         <v>8710</v>
@@ -10461,7 +10461,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G348" t="n">
-        <v>4.52963590621948</v>
+        <v>4.52963638305664</v>
       </c>
       <c r="H348" t="n">
         <v>9810</v>
@@ -10490,7 +10490,7 @@
         <v>5</v>
       </c>
       <c r="G349" t="n">
-        <v>4.61266374588013</v>
+        <v>4.61266422271729</v>
       </c>
       <c r="H349" t="n">
         <v>8051</v>
@@ -10519,7 +10519,7 @@
         <v>5</v>
       </c>
       <c r="G350" t="n">
-        <v>4.61266374588013</v>
+        <v>4.61266422271729</v>
       </c>
       <c r="H350" t="n">
         <v>5297</v>
@@ -10577,7 +10577,7 @@
         <v>5.25</v>
       </c>
       <c r="G352" t="n">
-        <v>4.84329748153687</v>
+        <v>4.84329700469971</v>
       </c>
       <c r="H352" t="n">
         <v>15431</v>
@@ -10635,7 +10635,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G354" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H354" t="n">
         <v>1901</v>
@@ -10664,7 +10664,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H355" t="n">
         <v>7480</v>
@@ -10693,7 +10693,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G356" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H356" t="n">
         <v>7610</v>
@@ -10722,7 +10722,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G357" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H357" t="n">
         <v>1202</v>
@@ -10751,7 +10751,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>5.03702974319458</v>
+        <v>5.03702926635742</v>
       </c>
       <c r="H358" t="n">
         <v>1175</v>
@@ -11128,7 +11128,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G371" t="n">
-        <v>5.33223962783813</v>
+        <v>5.33224010467529</v>
       </c>
       <c r="H371" t="n">
         <v>27751</v>
@@ -11447,7 +11447,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G382" t="n">
-        <v>5.37998867034912</v>
+        <v>5.37998819351196</v>
       </c>
       <c r="H382" t="n">
         <v>14325</v>
@@ -11563,7 +11563,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G386" t="n">
-        <v>5.60493564605713</v>
+        <v>5.60493612289429</v>
       </c>
       <c r="H386" t="n">
         <v>24572</v>
@@ -11650,7 +11650,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G389" t="n">
-        <v>5.54869890213013</v>
+        <v>5.54869937896729</v>
       </c>
       <c r="H389" t="n">
         <v>8766</v>
@@ -11824,7 +11824,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G395" t="n">
-        <v>5.54869890213013</v>
+        <v>5.54869937896729</v>
       </c>
       <c r="H395" t="n">
         <v>4979</v>
@@ -12143,7 +12143,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G406" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H406" t="n">
         <v>1138</v>
@@ -12172,7 +12172,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G407" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H407" t="n">
         <v>9530</v>
@@ -12201,7 +12201,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G408" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H408" t="n">
         <v>200</v>
@@ -12230,7 +12230,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G409" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H409" t="n">
         <v>620</v>
@@ -12259,7 +12259,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G410" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H410" t="n">
         <v>8991</v>
@@ -12317,7 +12317,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G412" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H412" t="n">
         <v>1439</v>
@@ -12346,7 +12346,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G413" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H413" t="n">
         <v>1000</v>
@@ -12375,7 +12375,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G414" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H414" t="n">
         <v>500</v>
@@ -12491,7 +12491,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G418" t="n">
-        <v>5.54869890213013</v>
+        <v>5.54869937896729</v>
       </c>
       <c r="H418" t="n">
         <v>1000</v>
@@ -12578,7 +12578,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G421" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H421" t="n">
         <v>2490</v>
@@ -12665,7 +12665,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G424" t="n">
-        <v>5.4549708366394</v>
+        <v>5.45497131347656</v>
       </c>
       <c r="H424" t="n">
         <v>8384</v>
@@ -12723,7 +12723,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G426" t="n">
-        <v>5.37998867034912</v>
+        <v>5.37998819351196</v>
       </c>
       <c r="H426" t="n">
         <v>6509</v>
@@ -12810,7 +12810,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G429" t="n">
-        <v>5.37998867034912</v>
+        <v>5.37998819351196</v>
       </c>
       <c r="H429" t="n">
         <v>1050</v>
@@ -12897,7 +12897,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G432" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H432" t="n">
         <v>1171</v>
@@ -12926,7 +12926,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G433" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H433" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G443" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H443" t="n">
         <v>52</v>
@@ -13709,7 +13709,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G460" t="n">
-        <v>5.37998867034912</v>
+        <v>5.37998819351196</v>
       </c>
       <c r="H460" t="n">
         <v>11165</v>
@@ -13767,7 +13767,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G462" t="n">
-        <v>5.54869890213013</v>
+        <v>5.54869937896729</v>
       </c>
       <c r="H462" t="n">
         <v>3576</v>
@@ -13825,7 +13825,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G464" t="n">
-        <v>5.54869890213013</v>
+        <v>5.54869937896729</v>
       </c>
       <c r="H464" t="n">
         <v>1167</v>
@@ -13854,7 +13854,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G465" t="n">
-        <v>5.54869890213013</v>
+        <v>5.54869937896729</v>
       </c>
       <c r="H465" t="n">
         <v>2604</v>
@@ -13883,7 +13883,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G466" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H466" t="n">
         <v>6381</v>
@@ -13941,7 +13941,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G468" t="n">
-        <v>5.41747951507568</v>
+        <v>5.41747999191284</v>
       </c>
       <c r="H468" t="n">
         <v>1239</v>
@@ -14144,7 +14144,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>5.09880447387695</v>
+        <v>5.09880495071411</v>
       </c>
       <c r="H475" t="n">
         <v>5512</v>
@@ -14231,7 +14231,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G478" t="n">
-        <v>4.89260244369507</v>
+        <v>4.89260292053223</v>
       </c>
       <c r="H478" t="n">
         <v>1880</v>
@@ -14318,7 +14318,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H481" t="n">
         <v>16552</v>
@@ -14347,7 +14347,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G482" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H482" t="n">
         <v>1000</v>
@@ -14376,7 +14376,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G483" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14434,7 +14434,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G485" t="n">
-        <v>4.70514726638794</v>
+        <v>4.70514678955078</v>
       </c>
       <c r="H485" t="n">
         <v>2550</v>
@@ -14463,7 +14463,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>4.66765594482422</v>
+        <v>4.66765546798706</v>
       </c>
       <c r="H486" t="n">
         <v>8004</v>
@@ -14492,7 +14492,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G487" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H487" t="n">
         <v>1050</v>
@@ -14521,7 +14521,7 @@
         <v>5</v>
       </c>
       <c r="G488" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H488" t="n">
         <v>400</v>
@@ -14550,7 +14550,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G489" t="n">
-        <v>4.66765594482422</v>
+        <v>4.66765546798706</v>
       </c>
       <c r="H489" t="n">
         <v>49</v>
@@ -14579,7 +14579,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>4.64890956878662</v>
+        <v>4.64891052246094</v>
       </c>
       <c r="H490" t="n">
         <v>2650</v>
@@ -14695,7 +14695,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G494" t="n">
-        <v>4.64890956878662</v>
+        <v>4.64891052246094</v>
       </c>
       <c r="H494" t="n">
         <v>21434</v>
@@ -14724,7 +14724,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G495" t="n">
-        <v>4.65828323364258</v>
+        <v>4.65828275680542</v>
       </c>
       <c r="H495" t="n">
         <v>32639</v>
@@ -14753,7 +14753,7 @@
         <v>5</v>
       </c>
       <c r="G496" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H496" t="n">
         <v>7653</v>
@@ -14782,7 +14782,7 @@
         <v>5</v>
       </c>
       <c r="G497" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H497" t="n">
         <v>37466</v>
@@ -14898,7 +14898,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>4.83636569976807</v>
+        <v>4.83636617660522</v>
       </c>
       <c r="H501" t="n">
         <v>9387</v>
@@ -14927,7 +14927,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G502" t="n">
-        <v>4.89260244369507</v>
+        <v>4.89260292053223</v>
       </c>
       <c r="H502" t="n">
         <v>5569</v>
@@ -15304,7 +15304,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G515" t="n">
-        <v>5.00507688522339</v>
+        <v>5.00507640838623</v>
       </c>
       <c r="H515" t="n">
         <v>632</v>
@@ -15333,7 +15333,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G516" t="n">
-        <v>5.00507688522339</v>
+        <v>5.00507640838623</v>
       </c>
       <c r="H516" t="n">
         <v>0</v>
@@ -15362,7 +15362,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G517" t="n">
-        <v>5.06131315231323</v>
+        <v>5.06131362915039</v>
       </c>
       <c r="H517" t="n">
         <v>3072</v>
@@ -15565,7 +15565,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G524" t="n">
-        <v>5.09880447387695</v>
+        <v>5.09880495071411</v>
       </c>
       <c r="H524" t="n">
         <v>1651</v>
@@ -15623,7 +15623,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G526" t="n">
-        <v>5.09880447387695</v>
+        <v>5.09880495071411</v>
       </c>
       <c r="H526" t="n">
         <v>2500</v>
@@ -15826,7 +15826,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G533" t="n">
-        <v>4.89260244369507</v>
+        <v>4.89260292053223</v>
       </c>
       <c r="H533" t="n">
         <v>2400</v>
@@ -16319,7 +16319,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G550" t="n">
-        <v>4.70514726638794</v>
+        <v>4.70514678955078</v>
       </c>
       <c r="H550" t="n">
         <v>16370</v>
@@ -16348,7 +16348,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G551" t="n">
-        <v>4.66765594482422</v>
+        <v>4.66765546798706</v>
       </c>
       <c r="H551" t="n">
         <v>33872</v>
@@ -16377,7 +16377,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H552" t="n">
         <v>2770</v>
@@ -16406,7 +16406,7 @@
         <v>5</v>
       </c>
       <c r="G553" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H553" t="n">
         <v>200</v>
@@ -16435,7 +16435,7 @@
         <v>5</v>
       </c>
       <c r="G554" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H554" t="n">
         <v>1284</v>
@@ -16464,7 +16464,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H555" t="n">
         <v>1730</v>
@@ -16493,7 +16493,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G556" t="n">
-        <v>4.70514726638794</v>
+        <v>4.70514678955078</v>
       </c>
       <c r="H556" t="n">
         <v>2313</v>
@@ -16522,7 +16522,7 @@
         <v>5</v>
       </c>
       <c r="G557" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H557" t="n">
         <v>5070</v>
@@ -16551,7 +16551,7 @@
         <v>5</v>
       </c>
       <c r="G558" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H558" t="n">
         <v>497</v>
@@ -16580,7 +16580,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G559" t="n">
-        <v>4.6301646232605</v>
+        <v>4.63016414642334</v>
       </c>
       <c r="H559" t="n">
         <v>465</v>
@@ -16696,7 +16696,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G563" t="n">
-        <v>4.83636569976807</v>
+        <v>4.83636617660522</v>
       </c>
       <c r="H563" t="n">
         <v>5514</v>
@@ -16754,7 +16754,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>5.06131315231323</v>
+        <v>5.06131362915039</v>
       </c>
       <c r="H565" t="n">
         <v>5184</v>
@@ -16783,7 +16783,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G566" t="n">
-        <v>5.06131315231323</v>
+        <v>5.06131362915039</v>
       </c>
       <c r="H566" t="n">
         <v>7208</v>
@@ -16812,7 +16812,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>5.09880447387695</v>
+        <v>5.09880495071411</v>
       </c>
       <c r="H567" t="n">
         <v>17491</v>
@@ -16957,7 +16957,7 @@
         <v>4.25</v>
       </c>
       <c r="G572" t="n">
-        <v>3.98344087600708</v>
+        <v>3.98344111442566</v>
       </c>
       <c r="H572" t="n">
         <v>9140</v>
@@ -16986,7 +16986,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G573" t="n">
-        <v>3.96469569206238</v>
+        <v>3.9646954536438</v>
       </c>
       <c r="H573" t="n">
         <v>1226</v>
@@ -17015,7 +17015,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G574" t="n">
-        <v>4.0209321975708</v>
+        <v>4.02093267440796</v>
       </c>
       <c r="H574" t="n">
         <v>6577</v>
@@ -17073,7 +17073,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>4.04905128479004</v>
+        <v>4.04905080795288</v>
       </c>
       <c r="H576" t="n">
         <v>6405</v>
@@ -17102,7 +17102,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G577" t="n">
-        <v>4.04905128479004</v>
+        <v>4.04905080795288</v>
       </c>
       <c r="H577" t="n">
         <v>5942</v>
@@ -17131,7 +17131,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G578" t="n">
-        <v>3.96469569206238</v>
+        <v>3.9646954536438</v>
       </c>
       <c r="H578" t="n">
         <v>2445</v>
@@ -17189,7 +17189,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>3.94595003128052</v>
+        <v>3.94594979286194</v>
       </c>
       <c r="H580" t="n">
         <v>8147</v>
@@ -17276,7 +17276,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G583" t="n">
-        <v>3.88971281051636</v>
+        <v>3.88971304893494</v>
       </c>
       <c r="H583" t="n">
         <v>2610</v>
@@ -17305,7 +17305,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>3.94595003128052</v>
+        <v>3.94594979286194</v>
       </c>
       <c r="H584" t="n">
         <v>3049</v>
@@ -17363,7 +17363,7 @@
         <v>4.25</v>
       </c>
       <c r="G586" t="n">
-        <v>3.98344087600708</v>
+        <v>3.98344111442566</v>
       </c>
       <c r="H586" t="n">
         <v>2353</v>
@@ -17392,7 +17392,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G587" t="n">
-        <v>3.92720437049866</v>
+        <v>3.92720413208008</v>
       </c>
       <c r="H587" t="n">
         <v>1105</v>
@@ -17421,7 +17421,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G588" t="n">
-        <v>3.88971281051636</v>
+        <v>3.88971304893494</v>
       </c>
       <c r="H588" t="n">
         <v>3999</v>
@@ -17537,7 +17537,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G592" t="n">
-        <v>3.88971281051636</v>
+        <v>3.88971304893494</v>
       </c>
       <c r="H592" t="n">
         <v>30337</v>
@@ -17566,7 +17566,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G593" t="n">
-        <v>4.03967809677124</v>
+        <v>4.03967761993408</v>
       </c>
       <c r="H593" t="n">
         <v>12527</v>
@@ -17653,7 +17653,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>4.0209321975708</v>
+        <v>4.02093267440796</v>
       </c>
       <c r="H596" t="n">
         <v>6142</v>
@@ -17682,7 +17682,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G597" t="n">
-        <v>4.06779623031616</v>
+        <v>4.06779670715332</v>
       </c>
       <c r="H597" t="n">
         <v>2200</v>
@@ -17827,7 +17827,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G602" t="n">
-        <v>4.04905128479004</v>
+        <v>4.04905080795288</v>
       </c>
       <c r="H602" t="n">
         <v>150</v>
@@ -17972,7 +17972,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G607" t="n">
-        <v>4.13340616226196</v>
+        <v>4.1334056854248</v>
       </c>
       <c r="H607" t="n">
         <v>55370</v>
@@ -18001,7 +18001,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G608" t="n">
-        <v>4.12403297424316</v>
+        <v>4.12403345108032</v>
       </c>
       <c r="H608" t="n">
         <v>2894</v>
@@ -18117,7 +18117,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>4.09591484069824</v>
+        <v>4.09591436386108</v>
       </c>
       <c r="H612" t="n">
         <v>401</v>
@@ -18146,7 +18146,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G613" t="n">
-        <v>4.09591484069824</v>
+        <v>4.09591436386108</v>
       </c>
       <c r="H613" t="n">
         <v>0</v>
@@ -18175,7 +18175,7 @@
         <v>4.25</v>
       </c>
       <c r="G614" t="n">
-        <v>3.98344087600708</v>
+        <v>3.98344111442566</v>
       </c>
       <c r="H614" t="n">
         <v>2924</v>
@@ -18204,7 +18204,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G615" t="n">
-        <v>4.03967809677124</v>
+        <v>4.03967761993408</v>
       </c>
       <c r="H615" t="n">
         <v>320</v>
@@ -18233,7 +18233,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G616" t="n">
-        <v>3.92720437049866</v>
+        <v>3.92720413208008</v>
       </c>
       <c r="H616" t="n">
         <v>3977</v>
@@ -18262,7 +18262,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G617" t="n">
-        <v>3.87096738815308</v>
+        <v>3.87096762657166</v>
       </c>
       <c r="H617" t="n">
         <v>5257</v>
@@ -18291,7 +18291,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G618" t="n">
-        <v>3.88971281051636</v>
+        <v>3.88971304893494</v>
       </c>
       <c r="H618" t="n">
         <v>450</v>
@@ -18320,7 +18320,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G619" t="n">
-        <v>3.88971281051636</v>
+        <v>3.88971304893494</v>
       </c>
       <c r="H619" t="n">
         <v>0</v>
@@ -18349,7 +18349,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G620" t="n">
-        <v>3.88971281051636</v>
+        <v>3.88971304893494</v>
       </c>
       <c r="H620" t="n">
         <v>200</v>
@@ -18378,7 +18378,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G621" t="n">
-        <v>3.88971281051636</v>
+        <v>3.88971304893494</v>
       </c>
       <c r="H621" t="n">
         <v>1810</v>
@@ -18436,7 +18436,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G623" t="n">
-        <v>3.72100257873535</v>
+        <v>3.72100281715393</v>
       </c>
       <c r="H623" t="n">
         <v>572</v>
@@ -18465,7 +18465,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G624" t="n">
-        <v>3.72100257873535</v>
+        <v>3.72100281715393</v>
       </c>
       <c r="H624" t="n">
         <v>148</v>
@@ -18494,7 +18494,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G625" t="n">
-        <v>3.70225691795349</v>
+        <v>3.70225715637207</v>
       </c>
       <c r="H625" t="n">
         <v>2781</v>
@@ -18523,7 +18523,7 @@
         <v>4</v>
       </c>
       <c r="G626" t="n">
-        <v>3.74912095069885</v>
+        <v>3.74912118911743</v>
       </c>
       <c r="H626" t="n">
         <v>4138</v>
@@ -18552,7 +18552,7 @@
         <v>4</v>
       </c>
       <c r="G627" t="n">
-        <v>3.74912095069885</v>
+        <v>3.74912118911743</v>
       </c>
       <c r="H627" t="n">
         <v>3430</v>
@@ -18581,7 +18581,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G628" t="n">
-        <v>3.70225691795349</v>
+        <v>3.70225715637207</v>
       </c>
       <c r="H628" t="n">
         <v>432</v>
@@ -18610,7 +18610,7 @@
         <v>4</v>
       </c>
       <c r="G629" t="n">
-        <v>3.74912095069885</v>
+        <v>3.74912118911743</v>
       </c>
       <c r="H629" t="n">
         <v>1000</v>
@@ -18639,7 +18639,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G630" t="n">
-        <v>3.68351125717163</v>
+        <v>3.68351149559021</v>
       </c>
       <c r="H630" t="n">
         <v>9933</v>
@@ -18668,7 +18668,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G631" t="n">
-        <v>3.66476559638977</v>
+        <v>3.66476583480835</v>
       </c>
       <c r="H631" t="n">
         <v>2461</v>
@@ -18697,7 +18697,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G632" t="n">
-        <v>3.64602017402649</v>
+        <v>3.64602041244507</v>
       </c>
       <c r="H632" t="n">
         <v>3650</v>
@@ -18755,7 +18755,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G634" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H634" t="n">
         <v>3900</v>
@@ -18784,7 +18784,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G635" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H635" t="n">
         <v>6237</v>
@@ -18813,7 +18813,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G636" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H636" t="n">
         <v>7752</v>
@@ -18842,7 +18842,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G637" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H637" t="n">
         <v>1500</v>
@@ -18871,7 +18871,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G638" t="n">
-        <v>3.71341013908386</v>
+        <v>3.71341037750244</v>
       </c>
       <c r="H638" t="n">
         <v>8760</v>
@@ -18900,7 +18900,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G639" t="n">
-        <v>3.71341013908386</v>
+        <v>3.71341037750244</v>
       </c>
       <c r="H639" t="n">
         <v>0</v>
@@ -18929,7 +18929,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G640" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H640" t="n">
         <v>1052</v>
@@ -18958,7 +18958,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G641" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H641" t="n">
         <v>10</v>
@@ -18987,7 +18987,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G642" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H642" t="n">
         <v>90</v>
@@ -19103,7 +19103,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G646" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H646" t="n">
         <v>13400</v>
@@ -19190,7 +19190,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G649" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H649" t="n">
         <v>4153</v>
@@ -19248,7 +19248,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G651" t="n">
-        <v>3.65583825111389</v>
+        <v>3.65583801269531</v>
       </c>
       <c r="H651" t="n">
         <v>900</v>
@@ -19277,7 +19277,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>3.65583825111389</v>
+        <v>3.65583801269531</v>
       </c>
       <c r="H652" t="n">
         <v>10</v>
@@ -19335,7 +19335,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G654" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H654" t="n">
         <v>3015</v>
@@ -19393,7 +19393,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G656" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H656" t="n">
         <v>3182</v>
@@ -19422,7 +19422,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H657" t="n">
         <v>1517</v>
@@ -19480,7 +19480,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G659" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H659" t="n">
         <v>100</v>
@@ -19509,7 +19509,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G660" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H660" t="n">
         <v>299</v>
@@ -19538,7 +19538,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G661" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H661" t="n">
         <v>1404</v>
@@ -19567,7 +19567,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G662" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H662" t="n">
         <v>0</v>
@@ -19625,7 +19625,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G664" t="n">
-        <v>3.72300577163696</v>
+        <v>3.72300601005554</v>
       </c>
       <c r="H664" t="n">
         <v>800</v>
@@ -19712,7 +19712,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>4.12601137161255</v>
+        <v>4.12601184844971</v>
       </c>
       <c r="H667" t="n">
         <v>45390</v>
@@ -19770,7 +19770,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G669" t="n">
-        <v>4.12601137161255</v>
+        <v>4.12601184844971</v>
       </c>
       <c r="H669" t="n">
         <v>8487</v>
@@ -19799,7 +19799,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G670" t="n">
-        <v>4.12601137161255</v>
+        <v>4.12601184844971</v>
       </c>
       <c r="H670" t="n">
         <v>2970</v>
@@ -19973,7 +19973,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G676" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H676" t="n">
         <v>1500</v>
@@ -20089,7 +20089,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G680" t="n">
-        <v>4.02046251296997</v>
+        <v>4.02046203613281</v>
       </c>
       <c r="H680" t="n">
         <v>1420</v>
@@ -20118,7 +20118,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G681" t="n">
-        <v>3.99167633056641</v>
+        <v>3.99167609214783</v>
       </c>
       <c r="H681" t="n">
         <v>1555</v>
@@ -20176,7 +20176,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G683" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H683" t="n">
         <v>10</v>
@@ -20205,7 +20205,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H684" t="n">
         <v>9595</v>
@@ -20292,7 +20292,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G687" t="n">
-        <v>3.99167633056641</v>
+        <v>3.99167609214783</v>
       </c>
       <c r="H687" t="n">
         <v>750</v>
@@ -20321,7 +20321,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G688" t="n">
-        <v>3.99167633056641</v>
+        <v>3.99167609214783</v>
       </c>
       <c r="H688" t="n">
         <v>0</v>
@@ -20350,7 +20350,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G689" t="n">
-        <v>3.98208069801331</v>
+        <v>3.98208093643188</v>
       </c>
       <c r="H689" t="n">
         <v>150</v>
@@ -20379,7 +20379,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>4.03965330123901</v>
+        <v>4.03965282440186</v>
       </c>
       <c r="H690" t="n">
         <v>1160</v>
@@ -20408,7 +20408,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>4.03965330123901</v>
+        <v>4.03965282440186</v>
       </c>
       <c r="H691" t="n">
         <v>10</v>
@@ -20437,7 +20437,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H692" t="n">
         <v>11</v>
@@ -20466,7 +20466,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G693" t="n">
-        <v>4.03965330123901</v>
+        <v>4.03965282440186</v>
       </c>
       <c r="H693" t="n">
         <v>1069</v>
@@ -20524,7 +20524,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G695" t="n">
-        <v>3.98208069801331</v>
+        <v>3.98208093643188</v>
       </c>
       <c r="H695" t="n">
         <v>1981</v>
@@ -20553,7 +20553,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>3.98208069801331</v>
+        <v>3.98208093643188</v>
       </c>
       <c r="H696" t="n">
         <v>0</v>
@@ -20582,7 +20582,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>3.98208069801331</v>
+        <v>3.98208093643188</v>
       </c>
       <c r="H697" t="n">
         <v>120</v>
@@ -20611,7 +20611,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G698" t="n">
-        <v>4.02046251296997</v>
+        <v>4.02046203613281</v>
       </c>
       <c r="H698" t="n">
         <v>245</v>
@@ -20669,7 +20669,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G700" t="n">
-        <v>3.94369959831238</v>
+        <v>3.9436993598938</v>
       </c>
       <c r="H700" t="n">
         <v>210</v>
@@ -20698,7 +20698,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G701" t="n">
-        <v>3.94369959831238</v>
+        <v>3.9436993598938</v>
       </c>
       <c r="H701" t="n">
         <v>280</v>
@@ -20930,7 +20930,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G709" t="n">
-        <v>3.87653183937073</v>
+        <v>3.87653160095215</v>
       </c>
       <c r="H709" t="n">
         <v>1788</v>
@@ -21017,7 +21017,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G712" t="n">
-        <v>3.9341037273407</v>
+        <v>3.93410396575928</v>
       </c>
       <c r="H712" t="n">
         <v>3931</v>
@@ -21046,7 +21046,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G713" t="n">
-        <v>3.84774565696716</v>
+        <v>3.84774589538574</v>
       </c>
       <c r="H713" t="n">
         <v>5760</v>
@@ -21075,7 +21075,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G714" t="n">
-        <v>3.79017329216003</v>
+        <v>3.79017353057861</v>
       </c>
       <c r="H714" t="n">
         <v>185</v>
@@ -21104,7 +21104,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G715" t="n">
-        <v>3.77098250389099</v>
+        <v>3.77098274230957</v>
       </c>
       <c r="H715" t="n">
         <v>540</v>
@@ -21133,7 +21133,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G716" t="n">
-        <v>3.75179171562195</v>
+        <v>3.75179195404053</v>
       </c>
       <c r="H716" t="n">
         <v>330</v>
@@ -21162,7 +21162,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G717" t="n">
-        <v>3.75179171562195</v>
+        <v>3.75179195404053</v>
       </c>
       <c r="H717" t="n">
         <v>0</v>
@@ -21191,7 +21191,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G718" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H718" t="n">
         <v>20488</v>
@@ -21249,7 +21249,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G720" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H720" t="n">
         <v>1602</v>
@@ -21336,7 +21336,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>3.91491317749023</v>
+        <v>3.91491341590881</v>
       </c>
       <c r="H723" t="n">
         <v>750</v>
@@ -21365,7 +21365,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G724" t="n">
-        <v>4.21236944198608</v>
+        <v>4.21236991882324</v>
       </c>
       <c r="H724" t="n">
         <v>46988</v>
@@ -21423,7 +21423,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G726" t="n">
-        <v>4.21236944198608</v>
+        <v>4.21236991882324</v>
       </c>
       <c r="H726" t="n">
         <v>70435</v>
@@ -21481,7 +21481,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G728" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H728" t="n">
         <v>172</v>
@@ -21597,7 +21597,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G732" t="n">
-        <v>4.18358421325684</v>
+        <v>4.18358373641968</v>
       </c>
       <c r="H732" t="n">
         <v>1320</v>
@@ -21742,7 +21742,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G737" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H737" t="n">
         <v>1637</v>
@@ -21771,7 +21771,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G738" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H738" t="n">
         <v>75279</v>
@@ -21800,7 +21800,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G739" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H739" t="n">
         <v>0</v>
@@ -21829,7 +21829,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G740" t="n">
-        <v>3.99167633056641</v>
+        <v>3.99167609214783</v>
       </c>
       <c r="H740" t="n">
         <v>7953</v>
@@ -21974,7 +21974,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G745" t="n">
-        <v>3.9341037273407</v>
+        <v>3.93410396575928</v>
       </c>
       <c r="H745" t="n">
         <v>81270</v>
@@ -22003,7 +22003,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G746" t="n">
-        <v>3.9341037273407</v>
+        <v>3.93410396575928</v>
       </c>
       <c r="H746" t="n">
         <v>3945</v>
@@ -22032,7 +22032,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>3.91491317749023</v>
+        <v>3.91491341590881</v>
       </c>
       <c r="H747" t="n">
         <v>196255</v>
@@ -22119,7 +22119,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G750" t="n">
-        <v>4.05884408950806</v>
+        <v>4.0588436126709</v>
       </c>
       <c r="H750" t="n">
         <v>1996</v>
@@ -22148,7 +22148,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G751" t="n">
-        <v>3.98208069801331</v>
+        <v>3.98208093643188</v>
       </c>
       <c r="H751" t="n">
         <v>7044</v>
@@ -22206,7 +22206,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G753" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H753" t="n">
         <v>7875</v>
@@ -22235,7 +22235,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>4.03965330123901</v>
+        <v>4.03965282440186</v>
       </c>
       <c r="H754" t="n">
         <v>498</v>
@@ -22264,7 +22264,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G755" t="n">
-        <v>3.91491317749023</v>
+        <v>3.91491341590881</v>
       </c>
       <c r="H755" t="n">
         <v>21081</v>
@@ -22641,7 +22641,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>3.63664746284485</v>
+        <v>3.63664722442627</v>
       </c>
       <c r="H768" t="n">
         <v>8155</v>
@@ -22670,7 +22670,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G769" t="n">
-        <v>3.61745667457581</v>
+        <v>3.61745643615723</v>
       </c>
       <c r="H769" t="n">
         <v>19701</v>
@@ -22786,7 +22786,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G773" t="n">
-        <v>3.61745667457581</v>
+        <v>3.61745643615723</v>
       </c>
       <c r="H773" t="n">
         <v>16809</v>
@@ -22902,7 +22902,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>3.63664746284485</v>
+        <v>3.63664722442627</v>
       </c>
       <c r="H777" t="n">
         <v>23488</v>
@@ -22931,7 +22931,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G778" t="n">
-        <v>3.63664746284485</v>
+        <v>3.63664722442627</v>
       </c>
       <c r="H778" t="n">
         <v>5020</v>
@@ -23105,7 +23105,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G784" t="n">
-        <v>3.40635824203491</v>
+        <v>3.40635848045349</v>
       </c>
       <c r="H784" t="n">
         <v>13684</v>
@@ -23192,7 +23192,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H787" t="n">
         <v>1420</v>
@@ -23221,7 +23221,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G788" t="n">
-        <v>3.65583825111389</v>
+        <v>3.65583801269531</v>
       </c>
       <c r="H788" t="n">
         <v>1250</v>
@@ -23627,7 +23627,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G802" t="n">
-        <v>3.53109812736511</v>
+        <v>3.53109836578369</v>
       </c>
       <c r="H802" t="n">
         <v>18225</v>
@@ -23772,7 +23772,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G807" t="n">
-        <v>3.53109812736511</v>
+        <v>3.53109836578369</v>
       </c>
       <c r="H807" t="n">
         <v>6020</v>
@@ -23801,7 +23801,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>3.55988454818726</v>
+        <v>3.55988430976868</v>
       </c>
       <c r="H808" t="n">
         <v>5589</v>
@@ -23859,7 +23859,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G810" t="n">
-        <v>3.60786128044128</v>
+        <v>3.60786104202271</v>
       </c>
       <c r="H810" t="n">
         <v>35932</v>
@@ -23888,7 +23888,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G811" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H811" t="n">
         <v>3848</v>
@@ -23917,7 +23917,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G812" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H812" t="n">
         <v>10695</v>
@@ -23946,7 +23946,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G813" t="n">
-        <v>3.71341013908386</v>
+        <v>3.71341037750244</v>
       </c>
       <c r="H813" t="n">
         <v>3973</v>
@@ -23975,7 +23975,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G814" t="n">
-        <v>3.79017329216003</v>
+        <v>3.79017353057861</v>
       </c>
       <c r="H814" t="n">
         <v>8700</v>
@@ -24004,7 +24004,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G815" t="n">
-        <v>3.75179171562195</v>
+        <v>3.75179195404053</v>
       </c>
       <c r="H815" t="n">
         <v>4141</v>
@@ -24091,7 +24091,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>3.91491317749023</v>
+        <v>3.91491341590881</v>
       </c>
       <c r="H818" t="n">
         <v>4284</v>
@@ -24120,7 +24120,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G819" t="n">
-        <v>4.25075101852417</v>
+        <v>4.25075149536133</v>
       </c>
       <c r="H819" t="n">
         <v>51273</v>
@@ -24236,7 +24236,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G823" t="n">
-        <v>4.25075101852417</v>
+        <v>4.25075149536133</v>
       </c>
       <c r="H823" t="n">
         <v>21761</v>
@@ -24265,7 +24265,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G824" t="n">
-        <v>4.29872846603394</v>
+        <v>4.29872798919678</v>
       </c>
       <c r="H824" t="n">
         <v>12287</v>
@@ -24352,7 +24352,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G827" t="n">
-        <v>4.26994180679321</v>
+        <v>4.26994228363037</v>
       </c>
       <c r="H827" t="n">
         <v>3147</v>
@@ -24613,7 +24613,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G836" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H836" t="n">
         <v>440</v>
@@ -24642,7 +24642,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G837" t="n">
-        <v>4.12601137161255</v>
+        <v>4.12601184844971</v>
       </c>
       <c r="H837" t="n">
         <v>1700</v>
@@ -24874,7 +24874,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G845" t="n">
-        <v>4.12601137161255</v>
+        <v>4.12601184844971</v>
       </c>
       <c r="H845" t="n">
         <v>1616</v>
@@ -24903,7 +24903,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G846" t="n">
-        <v>4.12601137161255</v>
+        <v>4.12601184844971</v>
       </c>
       <c r="H846" t="n">
         <v>0</v>
@@ -25193,7 +25193,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G856" t="n">
-        <v>4.21236944198608</v>
+        <v>4.21236991882324</v>
       </c>
       <c r="H856" t="n">
         <v>12800</v>
@@ -25251,7 +25251,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G858" t="n">
-        <v>4.02046251296997</v>
+        <v>4.02046203613281</v>
       </c>
       <c r="H858" t="n">
         <v>3537</v>
@@ -25309,7 +25309,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G860" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H860" t="n">
         <v>2994</v>
@@ -25338,7 +25338,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G861" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H861" t="n">
         <v>280</v>
@@ -25657,7 +25657,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G872" t="n">
-        <v>3.91491317749023</v>
+        <v>3.91491341590881</v>
       </c>
       <c r="H872" t="n">
         <v>1409</v>
@@ -25686,7 +25686,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G873" t="n">
-        <v>3.91491317749023</v>
+        <v>3.91491341590881</v>
       </c>
       <c r="H873" t="n">
         <v>4382</v>
@@ -25831,7 +25831,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G878" t="n">
-        <v>3.97248530387878</v>
+        <v>3.97248554229736</v>
       </c>
       <c r="H878" t="n">
         <v>850</v>
@@ -25860,7 +25860,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G879" t="n">
-        <v>3.94369959831238</v>
+        <v>3.9436993598938</v>
       </c>
       <c r="H879" t="n">
         <v>3403</v>
@@ -25889,7 +25889,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G880" t="n">
-        <v>3.99167633056641</v>
+        <v>3.99167609214783</v>
       </c>
       <c r="H880" t="n">
         <v>17094</v>
@@ -25918,7 +25918,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G881" t="n">
-        <v>3.97248530387878</v>
+        <v>3.97248554229736</v>
       </c>
       <c r="H881" t="n">
         <v>7211</v>
@@ -26005,7 +26005,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G884" t="n">
-        <v>3.98208069801331</v>
+        <v>3.98208093643188</v>
       </c>
       <c r="H884" t="n">
         <v>2973</v>
@@ -36712,6 +36712,35 @@
         <v>4395</v>
       </c>
       <c r="I1253" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1254" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1254" t="n">
+        <v>5.15999984741211</v>
+      </c>
+      <c r="D1254" t="n">
+        <v>5.15999984741211</v>
+      </c>
+      <c r="E1254" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="F1254" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="G1254" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="H1254" t="n">
+        <v>7839</v>
+      </c>
+      <c r="I1254" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RFG.MI.xlsx
+++ b/data/RFG.MI.xlsx
@@ -485,7 +485,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G4" t="n">
-        <v>4.40178442001343</v>
+        <v>4.40178394317627</v>
       </c>
       <c r="H4" t="n">
         <v>167566</v>
@@ -514,7 +514,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G5" t="n">
-        <v>4.30648756027222</v>
+        <v>4.30648803710938</v>
       </c>
       <c r="H5" t="n">
         <v>223483</v>
@@ -543,7 +543,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>4.26564645767212</v>
+        <v>4.26564693450928</v>
       </c>
       <c r="H6" t="n">
         <v>157332</v>
@@ -659,7 +659,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G10" t="n">
-        <v>4.17035007476807</v>
+        <v>4.17035055160522</v>
       </c>
       <c r="H10" t="n">
         <v>39798</v>
@@ -804,7 +804,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G15" t="n">
-        <v>4.26564645767212</v>
+        <v>4.26564693450928</v>
       </c>
       <c r="H15" t="n">
         <v>56165</v>
@@ -862,7 +862,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G17" t="n">
-        <v>4.26564645767212</v>
+        <v>4.26564693450928</v>
       </c>
       <c r="H17" t="n">
         <v>15689</v>
@@ -891,7 +891,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G18" t="n">
-        <v>4.32463932037354</v>
+        <v>4.32463884353638</v>
       </c>
       <c r="H18" t="n">
         <v>32335</v>
@@ -920,7 +920,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G19" t="n">
-        <v>4.44716358184814</v>
+        <v>4.4471640586853</v>
       </c>
       <c r="H19" t="n">
         <v>155415</v>
@@ -978,7 +978,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G21" t="n">
-        <v>4.60145282745361</v>
+        <v>4.60145330429077</v>
       </c>
       <c r="H21" t="n">
         <v>46761</v>
@@ -1094,7 +1094,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>4.84650039672852</v>
+        <v>4.84650135040283</v>
       </c>
       <c r="H25" t="n">
         <v>24608</v>
@@ -1123,7 +1123,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G26" t="n">
-        <v>4.84650039672852</v>
+        <v>4.84650135040283</v>
       </c>
       <c r="H26" t="n">
         <v>84199</v>
@@ -1181,7 +1181,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G28" t="n">
-        <v>5.00079011917114</v>
+        <v>5.00078964233398</v>
       </c>
       <c r="H28" t="n">
         <v>40759</v>
@@ -1268,7 +1268,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>5.52718877792358</v>
+        <v>5.52718925476074</v>
       </c>
       <c r="H31" t="n">
         <v>27209</v>
@@ -1297,7 +1297,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G32" t="n">
-        <v>5.43643045425415</v>
+        <v>5.43643093109131</v>
       </c>
       <c r="H32" t="n">
         <v>36811</v>
@@ -1326,7 +1326,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G33" t="n">
-        <v>5.43643045425415</v>
+        <v>5.43643093109131</v>
       </c>
       <c r="H33" t="n">
         <v>30706</v>
@@ -1384,7 +1384,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G35" t="n">
-        <v>5.45458269119263</v>
+        <v>5.45458221435547</v>
       </c>
       <c r="H35" t="n">
         <v>24789</v>
@@ -1413,7 +1413,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G36" t="n">
-        <v>5.33659648895264</v>
+        <v>5.33659696578979</v>
       </c>
       <c r="H36" t="n">
         <v>16617</v>
@@ -1442,7 +1442,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>5.25491333007812</v>
+        <v>5.25491380691528</v>
       </c>
       <c r="H37" t="n">
         <v>23662</v>
@@ -1500,7 +1500,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G39" t="n">
-        <v>5.36382389068604</v>
+        <v>5.36382341384888</v>
       </c>
       <c r="H39" t="n">
         <v>8885</v>
@@ -1558,7 +1558,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G41" t="n">
-        <v>5.39105081558228</v>
+        <v>5.39105176925659</v>
       </c>
       <c r="H41" t="n">
         <v>11791</v>
@@ -1703,7 +1703,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G46" t="n">
-        <v>5.34567165374756</v>
+        <v>5.34567213058472</v>
       </c>
       <c r="H46" t="n">
         <v>21861</v>
@@ -1732,7 +1732,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>5.26398992538452</v>
+        <v>5.26398944854736</v>
       </c>
       <c r="H47" t="n">
         <v>26913</v>
@@ -1761,7 +1761,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G48" t="n">
-        <v>5.10969972610474</v>
+        <v>5.10970020294189</v>
       </c>
       <c r="H48" t="n">
         <v>75369</v>
@@ -1790,7 +1790,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>5.10062456130981</v>
+        <v>5.10062408447266</v>
       </c>
       <c r="H49" t="n">
         <v>37488</v>
@@ -1819,7 +1819,7 @@
         <v>5.75</v>
       </c>
       <c r="G50" t="n">
-        <v>5.21861028671265</v>
+        <v>5.2186107635498</v>
       </c>
       <c r="H50" t="n">
         <v>53296</v>
@@ -1877,7 +1877,7 @@
         <v>5.5</v>
       </c>
       <c r="G52" t="n">
-        <v>4.9917140007019</v>
+        <v>4.99171447753906</v>
       </c>
       <c r="H52" t="n">
         <v>31337</v>
@@ -1906,7 +1906,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G53" t="n">
-        <v>5.03709363937378</v>
+        <v>5.03709411621094</v>
       </c>
       <c r="H53" t="n">
         <v>29429</v>
@@ -1935,7 +1935,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G54" t="n">
-        <v>5.04616928100586</v>
+        <v>5.0461688041687</v>
       </c>
       <c r="H54" t="n">
         <v>17032</v>
@@ -2051,7 +2051,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G58" t="n">
-        <v>4.86465167999268</v>
+        <v>4.86465263366699</v>
       </c>
       <c r="H58" t="n">
         <v>10871</v>
@@ -2109,7 +2109,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G60" t="n">
-        <v>5.01894235610962</v>
+        <v>5.01894187927246</v>
       </c>
       <c r="H60" t="n">
         <v>23167</v>
@@ -2167,7 +2167,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G62" t="n">
-        <v>4.83742475509644</v>
+        <v>4.83742427825928</v>
       </c>
       <c r="H62" t="n">
         <v>13006</v>
@@ -2283,7 +2283,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G66" t="n">
-        <v>4.63775682449341</v>
+        <v>4.63775634765625</v>
       </c>
       <c r="H66" t="n">
         <v>9021</v>
@@ -2312,7 +2312,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G67" t="n">
-        <v>4.57422494888306</v>
+        <v>4.57422542572021</v>
       </c>
       <c r="H67" t="n">
         <v>28927</v>
@@ -2486,7 +2486,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G73" t="n">
-        <v>4.84650039672852</v>
+        <v>4.84650135040283</v>
       </c>
       <c r="H73" t="n">
         <v>6837</v>
@@ -2573,7 +2573,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>4.51977014541626</v>
+        <v>4.5197696685791</v>
       </c>
       <c r="H76" t="n">
         <v>20769</v>
@@ -2602,7 +2602,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G77" t="n">
-        <v>4.13858556747437</v>
+        <v>4.13858509063721</v>
       </c>
       <c r="H77" t="n">
         <v>29751</v>
@@ -2660,7 +2660,7 @@
         <v>4.5</v>
       </c>
       <c r="G79" t="n">
-        <v>4.08412981033325</v>
+        <v>4.08412933349609</v>
       </c>
       <c r="H79" t="n">
         <v>23806</v>
@@ -2718,7 +2718,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G81" t="n">
-        <v>4.07051658630371</v>
+        <v>4.07051610946655</v>
       </c>
       <c r="H81" t="n">
         <v>26271</v>
@@ -2747,7 +2747,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G82" t="n">
-        <v>4.02059888839722</v>
+        <v>4.02059936523438</v>
       </c>
       <c r="H82" t="n">
         <v>47987</v>
@@ -2776,7 +2776,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G83" t="n">
-        <v>3.99337148666382</v>
+        <v>3.99337100982666</v>
       </c>
       <c r="H83" t="n">
         <v>14139</v>
@@ -2805,7 +2805,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G84" t="n">
-        <v>4.01152276992798</v>
+        <v>4.01152324676514</v>
       </c>
       <c r="H84" t="n">
         <v>13008</v>
@@ -2834,7 +2834,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>4.03421258926392</v>
+        <v>4.03421306610107</v>
       </c>
       <c r="H85" t="n">
         <v>9318</v>
@@ -2950,7 +2950,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G89" t="n">
-        <v>4.57422494888306</v>
+        <v>4.57422542572021</v>
       </c>
       <c r="H89" t="n">
         <v>5442</v>
@@ -3008,7 +3008,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G91" t="n">
-        <v>4.48346710205078</v>
+        <v>4.48346757888794</v>
       </c>
       <c r="H91" t="n">
         <v>5261</v>
@@ -3066,7 +3066,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G93" t="n">
-        <v>4.54699802398682</v>
+        <v>4.54699850082397</v>
       </c>
       <c r="H93" t="n">
         <v>105195</v>
@@ -3124,7 +3124,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>4.51977014541626</v>
+        <v>4.5197696685791</v>
       </c>
       <c r="H95" t="n">
         <v>243259</v>
@@ -3153,7 +3153,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>4.51977014541626</v>
+        <v>4.5197696685791</v>
       </c>
       <c r="H96" t="n">
         <v>4515</v>
@@ -3182,7 +3182,7 @@
         <v>4.95499992370605</v>
       </c>
       <c r="G97" t="n">
-        <v>4.49708080291748</v>
+        <v>4.49708032608032</v>
       </c>
       <c r="H97" t="n">
         <v>8314</v>
@@ -3356,7 +3356,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G103" t="n">
-        <v>4.34732913970947</v>
+        <v>4.34732866287231</v>
       </c>
       <c r="H103" t="n">
         <v>12517</v>
@@ -3385,7 +3385,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>4.27472305297852</v>
+        <v>4.27472257614136</v>
       </c>
       <c r="H104" t="n">
         <v>501</v>
@@ -3472,7 +3472,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G107" t="n">
-        <v>4.33371591567993</v>
+        <v>4.33371543884277</v>
       </c>
       <c r="H107" t="n">
         <v>1592</v>
@@ -3501,7 +3501,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>4.34732913970947</v>
+        <v>4.34732866287231</v>
       </c>
       <c r="H108" t="n">
         <v>5476</v>
@@ -3559,7 +3559,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>4.44716358184814</v>
+        <v>4.4471640586853</v>
       </c>
       <c r="H110" t="n">
         <v>197</v>
@@ -3588,7 +3588,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G111" t="n">
-        <v>4.43808794021606</v>
+        <v>4.43808746337891</v>
       </c>
       <c r="H111" t="n">
         <v>941</v>
@@ -3617,7 +3617,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G112" t="n">
-        <v>4.33825397491455</v>
+        <v>4.33825349807739</v>
       </c>
       <c r="H112" t="n">
         <v>5545</v>
@@ -3646,7 +3646,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G113" t="n">
-        <v>4.37455701828003</v>
+        <v>4.37455749511719</v>
       </c>
       <c r="H113" t="n">
         <v>38</v>
@@ -3704,7 +3704,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>4.27472305297852</v>
+        <v>4.27472257614136</v>
       </c>
       <c r="H115" t="n">
         <v>3033</v>
@@ -3733,7 +3733,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G116" t="n">
-        <v>4.29287385940552</v>
+        <v>4.29287433624268</v>
       </c>
       <c r="H116" t="n">
         <v>5190</v>
@@ -3849,7 +3849,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G120" t="n">
-        <v>3.88446092605591</v>
+        <v>3.88446140289307</v>
       </c>
       <c r="H120" t="n">
         <v>37503</v>
@@ -3878,7 +3878,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G121" t="n">
-        <v>3.81639242172241</v>
+        <v>3.81639289855957</v>
       </c>
       <c r="H121" t="n">
         <v>9794</v>
@@ -3936,7 +3936,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G123" t="n">
-        <v>3.88446092605591</v>
+        <v>3.88446140289307</v>
       </c>
       <c r="H123" t="n">
         <v>3695</v>
@@ -3965,7 +3965,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G124" t="n">
-        <v>3.88446092605591</v>
+        <v>3.88446140289307</v>
       </c>
       <c r="H124" t="n">
         <v>7707</v>
@@ -3994,7 +3994,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G125" t="n">
-        <v>3.92076516151428</v>
+        <v>3.9207649230957</v>
       </c>
       <c r="H125" t="n">
         <v>16385</v>
@@ -4052,7 +4052,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G127" t="n">
-        <v>4.21597480773926</v>
+        <v>4.21597528457642</v>
       </c>
       <c r="H127" t="n">
         <v>26910</v>
@@ -4139,7 +4139,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G130" t="n">
-        <v>4.23903846740723</v>
+        <v>4.23903799057007</v>
       </c>
       <c r="H130" t="n">
         <v>6758</v>
@@ -4197,7 +4197,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>4.24365091323853</v>
+        <v>4.24365043640137</v>
       </c>
       <c r="H132" t="n">
         <v>3060</v>
@@ -4226,7 +4226,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G133" t="n">
-        <v>4.32667970657349</v>
+        <v>4.32667922973633</v>
       </c>
       <c r="H133" t="n">
         <v>10570</v>
@@ -4284,7 +4284,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G135" t="n">
-        <v>4.37280559539795</v>
+        <v>4.37280511856079</v>
       </c>
       <c r="H135" t="n">
         <v>4000</v>
@@ -4487,7 +4487,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G142" t="n">
-        <v>4.22058725357056</v>
+        <v>4.22058773040771</v>
       </c>
       <c r="H142" t="n">
         <v>70519</v>
@@ -4516,7 +4516,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G143" t="n">
-        <v>4.20674991607666</v>
+        <v>4.2067494392395</v>
       </c>
       <c r="H143" t="n">
         <v>17151</v>
@@ -4603,7 +4603,7 @@
         <v>4.25</v>
       </c>
       <c r="G146" t="n">
-        <v>3.92076468467712</v>
+        <v>3.92076444625854</v>
       </c>
       <c r="H146" t="n">
         <v>15623</v>
@@ -4661,7 +4661,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95766639709473</v>
+        <v>3.95766592025757</v>
       </c>
       <c r="H148" t="n">
         <v>2849</v>
@@ -4690,7 +4690,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G149" t="n">
-        <v>3.95766639709473</v>
+        <v>3.95766592025757</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>4.10527086257935</v>
+        <v>4.1052713394165</v>
       </c>
       <c r="H151" t="n">
         <v>124</v>
@@ -4806,7 +4806,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G153" t="n">
-        <v>3.98534202575684</v>
+        <v>3.98534250259399</v>
       </c>
       <c r="H153" t="n">
         <v>8687</v>
@@ -4893,7 +4893,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>4.05914497375488</v>
+        <v>4.05914449691772</v>
       </c>
       <c r="H156" t="n">
         <v>120</v>
@@ -4922,7 +4922,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>3.96689105033875</v>
+        <v>3.9668915271759</v>
       </c>
       <c r="H157" t="n">
         <v>90</v>
@@ -4951,7 +4951,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G158" t="n">
-        <v>4.04991865158081</v>
+        <v>4.04991912841797</v>
       </c>
       <c r="H158" t="n">
         <v>5</v>
@@ -5009,7 +5009,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G160" t="n">
-        <v>3.91153883934021</v>
+        <v>3.91153907775879</v>
       </c>
       <c r="H160" t="n">
         <v>4000</v>
@@ -5038,7 +5038,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G161" t="n">
-        <v>3.96689105033875</v>
+        <v>3.9668915271759</v>
       </c>
       <c r="H161" t="n">
         <v>1000</v>
@@ -5154,7 +5154,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G165" t="n">
-        <v>3.85618710517883</v>
+        <v>3.85618758201599</v>
       </c>
       <c r="H165" t="n">
         <v>450</v>
@@ -5241,7 +5241,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G168" t="n">
-        <v>3.98534202575684</v>
+        <v>3.98534250259399</v>
       </c>
       <c r="H168" t="n">
         <v>5404</v>
@@ -5328,7 +5328,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G171" t="n">
-        <v>4.04991865158081</v>
+        <v>4.04991912841797</v>
       </c>
       <c r="H171" t="n">
         <v>2250</v>
@@ -5357,7 +5357,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G172" t="n">
-        <v>4.04991865158081</v>
+        <v>4.04991912841797</v>
       </c>
       <c r="H172" t="n">
         <v>520</v>
@@ -5502,7 +5502,7 @@
         <v>4.25</v>
       </c>
       <c r="G177" t="n">
-        <v>3.92076468467712</v>
+        <v>3.92076444625854</v>
       </c>
       <c r="H177" t="n">
         <v>3092</v>
@@ -5531,7 +5531,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>3.8838632106781</v>
+        <v>3.88386297225952</v>
       </c>
       <c r="H178" t="n">
         <v>5254</v>
@@ -5560,7 +5560,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G179" t="n">
-        <v>4.04991865158081</v>
+        <v>4.04991912841797</v>
       </c>
       <c r="H179" t="n">
         <v>3005</v>
@@ -5647,7 +5647,7 @@
         <v>4.25</v>
       </c>
       <c r="G182" t="n">
-        <v>3.92076468467712</v>
+        <v>3.92076444625854</v>
       </c>
       <c r="H182" t="n">
         <v>4226</v>
@@ -5676,7 +5676,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G183" t="n">
-        <v>3.8838632106781</v>
+        <v>3.88386297225952</v>
       </c>
       <c r="H183" t="n">
         <v>11079</v>
@@ -5821,7 +5821,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G188" t="n">
-        <v>3.93921542167664</v>
+        <v>3.93921494483948</v>
       </c>
       <c r="H188" t="n">
         <v>2507</v>
@@ -5850,7 +5850,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G189" t="n">
-        <v>4.00840473175049</v>
+        <v>4.00840520858765</v>
       </c>
       <c r="H189" t="n">
         <v>3667</v>
@@ -5879,7 +5879,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>3.8838632106781</v>
+        <v>3.88386297225952</v>
       </c>
       <c r="H190" t="n">
         <v>1237</v>
@@ -5937,7 +5937,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>3.95766639709473</v>
+        <v>3.95766592025757</v>
       </c>
       <c r="H192" t="n">
         <v>3183</v>
@@ -5995,7 +5995,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G194" t="n">
-        <v>4.00379276275635</v>
+        <v>4.00379228591919</v>
       </c>
       <c r="H194" t="n">
         <v>1199</v>
@@ -6053,7 +6053,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G196" t="n">
-        <v>3.86541247367859</v>
+        <v>3.86541223526001</v>
       </c>
       <c r="H196" t="n">
         <v>5890</v>
@@ -6082,7 +6082,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G197" t="n">
-        <v>3.94844055175781</v>
+        <v>3.94844102859497</v>
       </c>
       <c r="H197" t="n">
         <v>2149</v>
@@ -6169,7 +6169,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>3.99917984008789</v>
+        <v>3.99917936325073</v>
       </c>
       <c r="H200" t="n">
         <v>155</v>
@@ -6227,7 +6227,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G202" t="n">
-        <v>4.05914497375488</v>
+        <v>4.05914449691772</v>
       </c>
       <c r="H202" t="n">
         <v>7141</v>
@@ -6256,7 +6256,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G203" t="n">
-        <v>4.04991865158081</v>
+        <v>4.04991912841797</v>
       </c>
       <c r="H203" t="n">
         <v>24810</v>
@@ -6285,7 +6285,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G204" t="n">
-        <v>3.95766639709473</v>
+        <v>3.95766592025757</v>
       </c>
       <c r="H204" t="n">
         <v>5370</v>
@@ -6343,7 +6343,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G206" t="n">
-        <v>3.94844055175781</v>
+        <v>3.94844102859497</v>
       </c>
       <c r="H206" t="n">
         <v>5295</v>
@@ -6401,7 +6401,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>3.90231394767761</v>
+        <v>3.90231370925903</v>
       </c>
       <c r="H208" t="n">
         <v>1430</v>
@@ -6488,7 +6488,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G211" t="n">
-        <v>3.94844055175781</v>
+        <v>3.94844102859497</v>
       </c>
       <c r="H211" t="n">
         <v>5037</v>
@@ -6546,7 +6546,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>3.8838632106781</v>
+        <v>3.88386297225952</v>
       </c>
       <c r="H213" t="n">
         <v>1793</v>
@@ -6575,7 +6575,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G214" t="n">
-        <v>3.8838632106781</v>
+        <v>3.88386297225952</v>
       </c>
       <c r="H214" t="n">
         <v>63</v>
@@ -6865,7 +6865,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G224" t="n">
-        <v>4.10527086257935</v>
+        <v>4.1052713394165</v>
       </c>
       <c r="H224" t="n">
         <v>7165</v>
@@ -6923,7 +6923,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G226" t="n">
-        <v>4.24365091323853</v>
+        <v>4.24365043640137</v>
       </c>
       <c r="H226" t="n">
         <v>14277</v>
@@ -7010,7 +7010,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G229" t="n">
-        <v>4.22058725357056</v>
+        <v>4.22058773040771</v>
       </c>
       <c r="H229" t="n">
         <v>464</v>
@@ -7039,7 +7039,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G230" t="n">
-        <v>4.22058725357056</v>
+        <v>4.22058773040771</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G231" t="n">
-        <v>4.22058725357056</v>
+        <v>4.22058773040771</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G232" t="n">
-        <v>4.21597480773926</v>
+        <v>4.21597528457642</v>
       </c>
       <c r="H232" t="n">
         <v>7962</v>
@@ -7184,7 +7184,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G235" t="n">
-        <v>4.37280559539795</v>
+        <v>4.37280511856079</v>
       </c>
       <c r="H235" t="n">
         <v>17132</v>
@@ -7300,7 +7300,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G239" t="n">
-        <v>4.46505928039551</v>
+        <v>4.46505975723267</v>
       </c>
       <c r="H239" t="n">
         <v>1590</v>
@@ -7503,7 +7503,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G246" t="n">
-        <v>4.35435438156128</v>
+        <v>4.3543553352356</v>
       </c>
       <c r="H246" t="n">
         <v>2400</v>
@@ -7619,7 +7619,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G250" t="n">
-        <v>4.37280559539795</v>
+        <v>4.37280511856079</v>
       </c>
       <c r="H250" t="n">
         <v>241</v>
@@ -7648,7 +7648,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G251" t="n">
-        <v>4.35435438156128</v>
+        <v>4.3543553352356</v>
       </c>
       <c r="H251" t="n">
         <v>1595</v>
@@ -7764,7 +7764,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G255" t="n">
-        <v>4.55731201171875</v>
+        <v>4.55731248855591</v>
       </c>
       <c r="H255" t="n">
         <v>4318</v>
@@ -7822,7 +7822,7 @@
         <v>5</v>
       </c>
       <c r="G257" t="n">
-        <v>4.61266422271729</v>
+        <v>4.61266374588013</v>
       </c>
       <c r="H257" t="n">
         <v>5177</v>
@@ -7851,7 +7851,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G258" t="n">
-        <v>4.51118564605713</v>
+        <v>4.51118516921997</v>
       </c>
       <c r="H258" t="n">
         <v>22611</v>
@@ -7996,7 +7996,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G263" t="n">
-        <v>4.8986496925354</v>
+        <v>4.89864921569824</v>
       </c>
       <c r="H263" t="n">
         <v>29512</v>
@@ -8025,7 +8025,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G264" t="n">
-        <v>4.88019895553589</v>
+        <v>4.88019847869873</v>
       </c>
       <c r="H264" t="n">
         <v>69249</v>
@@ -8141,7 +8141,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G268" t="n">
-        <v>5.02780342102051</v>
+        <v>5.02780389785767</v>
       </c>
       <c r="H268" t="n">
         <v>4916</v>
@@ -8170,7 +8170,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G269" t="n">
-        <v>4.907874584198</v>
+        <v>4.90787506103516</v>
       </c>
       <c r="H269" t="n">
         <v>54096</v>
@@ -8228,7 +8228,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G271" t="n">
-        <v>4.8986496925354</v>
+        <v>4.89864921569824</v>
       </c>
       <c r="H271" t="n">
         <v>10062</v>
@@ -8373,7 +8373,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>5.01857900619507</v>
+        <v>5.01857852935791</v>
       </c>
       <c r="H276" t="n">
         <v>5852</v>
@@ -8402,7 +8402,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G277" t="n">
-        <v>5.03702926635742</v>
+        <v>5.03702974319458</v>
       </c>
       <c r="H277" t="n">
         <v>22783</v>
@@ -8518,7 +8518,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G281" t="n">
-        <v>5.15695858001709</v>
+        <v>5.15695905685425</v>
       </c>
       <c r="H281" t="n">
         <v>13832</v>
@@ -8750,7 +8750,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>5.14773368835449</v>
+        <v>5.14773321151733</v>
       </c>
       <c r="H289" t="n">
         <v>160</v>
@@ -8779,7 +8779,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G290" t="n">
-        <v>5.08315658569336</v>
+        <v>5.0831561088562</v>
       </c>
       <c r="H290" t="n">
         <v>100</v>
@@ -8837,7 +8837,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G292" t="n">
-        <v>5.14773368835449</v>
+        <v>5.14773321151733</v>
       </c>
       <c r="H292" t="n">
         <v>14959</v>
@@ -8866,7 +8866,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G293" t="n">
-        <v>5.15695858001709</v>
+        <v>5.15695905685425</v>
       </c>
       <c r="H293" t="n">
         <v>10</v>
@@ -8953,7 +8953,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G296" t="n">
-        <v>4.907874584198</v>
+        <v>4.90787506103516</v>
       </c>
       <c r="H296" t="n">
         <v>14673</v>
@@ -8982,7 +8982,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>4.98167753219604</v>
+        <v>4.98167705535889</v>
       </c>
       <c r="H297" t="n">
         <v>83453</v>
@@ -9098,7 +9098,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G301" t="n">
-        <v>4.8986496925354</v>
+        <v>4.89864921569824</v>
       </c>
       <c r="H301" t="n">
         <v>49432</v>
@@ -9127,7 +9127,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G302" t="n">
-        <v>4.94477605819702</v>
+        <v>4.94477653503418</v>
       </c>
       <c r="H302" t="n">
         <v>8210</v>
@@ -9156,7 +9156,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G303" t="n">
-        <v>4.92632532119751</v>
+        <v>4.92632579803467</v>
       </c>
       <c r="H303" t="n">
         <v>700</v>
@@ -9185,7 +9185,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G304" t="n">
-        <v>4.92632532119751</v>
+        <v>4.92632579803467</v>
       </c>
       <c r="H304" t="n">
         <v>3145</v>
@@ -9243,7 +9243,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G306" t="n">
-        <v>4.94477605819702</v>
+        <v>4.94477653503418</v>
       </c>
       <c r="H306" t="n">
         <v>69945</v>
@@ -9301,7 +9301,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>4.76949548721313</v>
+        <v>4.76949501037598</v>
       </c>
       <c r="H308" t="n">
         <v>7904</v>
@@ -9330,7 +9330,7 @@
         <v>5.25</v>
       </c>
       <c r="G309" t="n">
-        <v>4.84329700469971</v>
+        <v>4.84329748153687</v>
       </c>
       <c r="H309" t="n">
         <v>995</v>
@@ -9359,7 +9359,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G310" t="n">
-        <v>4.92632532119751</v>
+        <v>4.92632579803467</v>
       </c>
       <c r="H310" t="n">
         <v>1967</v>
@@ -9388,7 +9388,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G311" t="n">
-        <v>4.8156213760376</v>
+        <v>4.81562089920044</v>
       </c>
       <c r="H311" t="n">
         <v>3343</v>
@@ -9417,7 +9417,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G312" t="n">
-        <v>4.76949548721313</v>
+        <v>4.76949501037598</v>
       </c>
       <c r="H312" t="n">
         <v>4994</v>
@@ -9533,7 +9533,7 @@
         <v>5.25</v>
       </c>
       <c r="G316" t="n">
-        <v>4.84329700469971</v>
+        <v>4.84329748153687</v>
       </c>
       <c r="H316" t="n">
         <v>16</v>
@@ -9562,7 +9562,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G317" t="n">
-        <v>4.92632532119751</v>
+        <v>4.92632579803467</v>
       </c>
       <c r="H317" t="n">
         <v>31544</v>
@@ -9649,7 +9649,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>4.88019895553589</v>
+        <v>4.88019847869873</v>
       </c>
       <c r="H320" t="n">
         <v>6441</v>
@@ -9736,7 +9736,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G323" t="n">
-        <v>4.94477605819702</v>
+        <v>4.94477653503418</v>
       </c>
       <c r="H323" t="n">
         <v>1845</v>
@@ -9852,7 +9852,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G327" t="n">
-        <v>4.8156213760376</v>
+        <v>4.81562089920044</v>
       </c>
       <c r="H327" t="n">
         <v>123</v>
@@ -10026,7 +10026,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G333" t="n">
-        <v>4.98167753219604</v>
+        <v>4.98167705535889</v>
       </c>
       <c r="H333" t="n">
         <v>54722</v>
@@ -10084,7 +10084,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G335" t="n">
-        <v>4.98167753219604</v>
+        <v>4.98167705535889</v>
       </c>
       <c r="H335" t="n">
         <v>34644</v>
@@ -10171,7 +10171,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>4.98167753219604</v>
+        <v>4.98167705535889</v>
       </c>
       <c r="H338" t="n">
         <v>3600</v>
@@ -10200,7 +10200,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G339" t="n">
-        <v>4.98167753219604</v>
+        <v>4.98167705535889</v>
       </c>
       <c r="H339" t="n">
         <v>700</v>
@@ -10229,7 +10229,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G340" t="n">
-        <v>4.907874584198</v>
+        <v>4.90787506103516</v>
       </c>
       <c r="H340" t="n">
         <v>9032</v>
@@ -10258,7 +10258,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G341" t="n">
-        <v>4.92632532119751</v>
+        <v>4.92632579803467</v>
       </c>
       <c r="H341" t="n">
         <v>6351</v>
@@ -10287,7 +10287,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G342" t="n">
-        <v>4.92632532119751</v>
+        <v>4.92632579803467</v>
       </c>
       <c r="H342" t="n">
         <v>1223</v>
@@ -10345,7 +10345,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G344" t="n">
-        <v>4.98167753219604</v>
+        <v>4.98167705535889</v>
       </c>
       <c r="H344" t="n">
         <v>8710</v>
@@ -10403,7 +10403,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G346" t="n">
-        <v>4.83407211303711</v>
+        <v>4.83407258987427</v>
       </c>
       <c r="H346" t="n">
         <v>2525</v>
@@ -10461,7 +10461,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G348" t="n">
-        <v>4.52963638305664</v>
+        <v>4.52963590621948</v>
       </c>
       <c r="H348" t="n">
         <v>9810</v>
@@ -10490,7 +10490,7 @@
         <v>5</v>
       </c>
       <c r="G349" t="n">
-        <v>4.61266422271729</v>
+        <v>4.61266374588013</v>
       </c>
       <c r="H349" t="n">
         <v>8051</v>
@@ -10519,7 +10519,7 @@
         <v>5</v>
       </c>
       <c r="G350" t="n">
-        <v>4.61266422271729</v>
+        <v>4.61266374588013</v>
       </c>
       <c r="H350" t="n">
         <v>5297</v>
@@ -10577,7 +10577,7 @@
         <v>5.25</v>
       </c>
       <c r="G352" t="n">
-        <v>4.84329700469971</v>
+        <v>4.84329748153687</v>
       </c>
       <c r="H352" t="n">
         <v>15431</v>
@@ -10606,7 +10606,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G353" t="n">
-        <v>4.88019895553589</v>
+        <v>4.88019847869873</v>
       </c>
       <c r="H353" t="n">
         <v>1026</v>
@@ -10635,7 +10635,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G354" t="n">
-        <v>5.01857900619507</v>
+        <v>5.01857852935791</v>
       </c>
       <c r="H354" t="n">
         <v>1901</v>
@@ -10664,7 +10664,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>5.01857900619507</v>
+        <v>5.01857852935791</v>
       </c>
       <c r="H355" t="n">
         <v>7480</v>
@@ -10693,7 +10693,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G356" t="n">
-        <v>5.01857900619507</v>
+        <v>5.01857852935791</v>
       </c>
       <c r="H356" t="n">
         <v>7610</v>
@@ -10722,7 +10722,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G357" t="n">
-        <v>5.01857900619507</v>
+        <v>5.01857852935791</v>
       </c>
       <c r="H357" t="n">
         <v>1202</v>
@@ -10751,7 +10751,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>5.03702926635742</v>
+        <v>5.03702974319458</v>
       </c>
       <c r="H358" t="n">
         <v>1175</v>
@@ -10896,7 +10896,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G363" t="n">
-        <v>4.83407211303711</v>
+        <v>4.83407258987427</v>
       </c>
       <c r="H363" t="n">
         <v>1304</v>
@@ -10925,7 +10925,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G364" t="n">
-        <v>4.83407211303711</v>
+        <v>4.83407258987427</v>
       </c>
       <c r="H364" t="n">
         <v>15936</v>
@@ -10954,7 +10954,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G365" t="n">
-        <v>4.94477605819702</v>
+        <v>4.94477653503418</v>
       </c>
       <c r="H365" t="n">
         <v>3500</v>
@@ -11041,7 +11041,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G368" t="n">
-        <v>5.14773368835449</v>
+        <v>5.14773321151733</v>
       </c>
       <c r="H368" t="n">
         <v>5393</v>
@@ -11157,7 +11157,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G372" t="n">
-        <v>5.42449331283569</v>
+        <v>5.42449378967285</v>
       </c>
       <c r="H372" t="n">
         <v>16849</v>
@@ -11186,7 +11186,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G373" t="n">
-        <v>5.3506908416748</v>
+        <v>5.35069036483765</v>
       </c>
       <c r="H373" t="n">
         <v>5008</v>
@@ -11244,7 +11244,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G375" t="n">
-        <v>5.42449331283569</v>
+        <v>5.42449378967285</v>
       </c>
       <c r="H375" t="n">
         <v>7922</v>
@@ -11273,7 +11273,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>5.3506908416748</v>
+        <v>5.35069036483765</v>
       </c>
       <c r="H376" t="n">
         <v>1774</v>
@@ -11302,7 +11302,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>5.3506908416748</v>
+        <v>5.35069036483765</v>
       </c>
       <c r="H377" t="n">
         <v>2594</v>
@@ -11331,7 +11331,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G378" t="n">
-        <v>5.25843715667725</v>
+        <v>5.25843667984009</v>
       </c>
       <c r="H378" t="n">
         <v>4491</v>
@@ -11360,7 +11360,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G379" t="n">
-        <v>5.25843715667725</v>
+        <v>5.25843667984009</v>
       </c>
       <c r="H379" t="n">
         <v>270</v>
@@ -11476,7 +11476,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G383" t="n">
-        <v>5.3424973487854</v>
+        <v>5.34249687194824</v>
       </c>
       <c r="H383" t="n">
         <v>7621</v>
@@ -11505,7 +11505,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G384" t="n">
-        <v>5.473717212677</v>
+        <v>5.47371673583984</v>
       </c>
       <c r="H384" t="n">
         <v>4634</v>
@@ -11534,7 +11534,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G385" t="n">
-        <v>5.49246215820312</v>
+        <v>5.49246263504028</v>
       </c>
       <c r="H385" t="n">
         <v>5319</v>
@@ -11621,7 +11621,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G388" t="n">
-        <v>5.52995347976685</v>
+        <v>5.529953956604</v>
       </c>
       <c r="H388" t="n">
         <v>9781</v>
@@ -11650,7 +11650,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G389" t="n">
-        <v>5.54869937896729</v>
+        <v>5.54869890213013</v>
       </c>
       <c r="H389" t="n">
         <v>8766</v>
@@ -11679,7 +11679,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H390" t="n">
         <v>24702</v>
@@ -11824,7 +11824,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G395" t="n">
-        <v>5.54869937896729</v>
+        <v>5.54869890213013</v>
       </c>
       <c r="H395" t="n">
         <v>4979</v>
@@ -11882,7 +11882,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G397" t="n">
-        <v>5.473717212677</v>
+        <v>5.47371673583984</v>
       </c>
       <c r="H397" t="n">
         <v>2362</v>
@@ -11940,7 +11940,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G399" t="n">
-        <v>5.51120805740356</v>
+        <v>5.51120853424072</v>
       </c>
       <c r="H399" t="n">
         <v>550</v>
@@ -11969,7 +11969,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G400" t="n">
-        <v>5.49246215820312</v>
+        <v>5.49246263504028</v>
       </c>
       <c r="H400" t="n">
         <v>800</v>
@@ -11998,7 +11998,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G401" t="n">
-        <v>5.52995347976685</v>
+        <v>5.529953956604</v>
       </c>
       <c r="H401" t="n">
         <v>9050</v>
@@ -12027,7 +12027,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>5.52995347976685</v>
+        <v>5.529953956604</v>
       </c>
       <c r="H402" t="n">
         <v>1661</v>
@@ -12085,7 +12085,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G404" t="n">
-        <v>5.51120805740356</v>
+        <v>5.51120853424072</v>
       </c>
       <c r="H404" t="n">
         <v>1070</v>
@@ -12114,7 +12114,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H405" t="n">
         <v>1418</v>
@@ -12288,7 +12288,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H411" t="n">
         <v>200</v>
@@ -12404,7 +12404,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H415" t="n">
         <v>100</v>
@@ -12433,7 +12433,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G416" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H416" t="n">
         <v>45</v>
@@ -12462,7 +12462,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G417" t="n">
-        <v>5.49246215820312</v>
+        <v>5.49246263504028</v>
       </c>
       <c r="H417" t="n">
         <v>210</v>
@@ -12491,7 +12491,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G418" t="n">
-        <v>5.54869937896729</v>
+        <v>5.54869890213013</v>
       </c>
       <c r="H418" t="n">
         <v>1000</v>
@@ -12520,7 +12520,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G419" t="n">
-        <v>5.473717212677</v>
+        <v>5.47371673583984</v>
       </c>
       <c r="H419" t="n">
         <v>560</v>
@@ -12549,7 +12549,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G420" t="n">
-        <v>5.473717212677</v>
+        <v>5.47371673583984</v>
       </c>
       <c r="H420" t="n">
         <v>10242</v>
@@ -12607,7 +12607,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G422" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H422" t="n">
         <v>18970</v>
@@ -12636,7 +12636,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G423" t="n">
-        <v>5.52995347976685</v>
+        <v>5.529953956604</v>
       </c>
       <c r="H423" t="n">
         <v>1350</v>
@@ -12665,7 +12665,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G424" t="n">
-        <v>5.45497131347656</v>
+        <v>5.4549708366394</v>
       </c>
       <c r="H424" t="n">
         <v>8384</v>
@@ -12694,7 +12694,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G425" t="n">
-        <v>5.52995347976685</v>
+        <v>5.529953956604</v>
       </c>
       <c r="H425" t="n">
         <v>18369</v>
@@ -12752,7 +12752,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G427" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H427" t="n">
         <v>4203</v>
@@ -12781,7 +12781,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G428" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H428" t="n">
         <v>760</v>
@@ -12839,7 +12839,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G430" t="n">
-        <v>5.3424973487854</v>
+        <v>5.34249687194824</v>
       </c>
       <c r="H430" t="n">
         <v>3980</v>
@@ -12868,7 +12868,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G431" t="n">
-        <v>5.3424973487854</v>
+        <v>5.34249687194824</v>
       </c>
       <c r="H431" t="n">
         <v>2611</v>
@@ -12955,7 +12955,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G434" t="n">
-        <v>5.473717212677</v>
+        <v>5.47371673583984</v>
       </c>
       <c r="H434" t="n">
         <v>170</v>
@@ -12984,7 +12984,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>5.3424973487854</v>
+        <v>5.34249687194824</v>
       </c>
       <c r="H435" t="n">
         <v>868</v>
@@ -13013,7 +13013,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G436" t="n">
-        <v>5.3424973487854</v>
+        <v>5.34249687194824</v>
       </c>
       <c r="H436" t="n">
         <v>3947</v>
@@ -13042,7 +13042,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H437" t="n">
         <v>7332</v>
@@ -13071,7 +13071,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H438" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>5.3424973487854</v>
+        <v>5.34249687194824</v>
       </c>
       <c r="H442" t="n">
         <v>2261</v>
@@ -13245,7 +13245,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H444" t="n">
         <v>10</v>
@@ -13332,7 +13332,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G447" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H447" t="n">
         <v>20</v>
@@ -13361,7 +13361,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G448" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H448" t="n">
         <v>2255</v>
@@ -13390,7 +13390,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G449" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H449" t="n">
         <v>300</v>
@@ -13593,7 +13593,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G456" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H456" t="n">
         <v>20122</v>
@@ -13622,7 +13622,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G457" t="n">
-        <v>5.473717212677</v>
+        <v>5.47371673583984</v>
       </c>
       <c r="H457" t="n">
         <v>3375</v>
@@ -13738,7 +13738,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G461" t="n">
-        <v>5.52995347976685</v>
+        <v>5.529953956604</v>
       </c>
       <c r="H461" t="n">
         <v>10854</v>
@@ -13767,7 +13767,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G462" t="n">
-        <v>5.54869937896729</v>
+        <v>5.54869890213013</v>
       </c>
       <c r="H462" t="n">
         <v>3576</v>
@@ -13796,7 +13796,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G463" t="n">
-        <v>5.52995347976685</v>
+        <v>5.529953956604</v>
       </c>
       <c r="H463" t="n">
         <v>3785</v>
@@ -13825,7 +13825,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G464" t="n">
-        <v>5.54869937896729</v>
+        <v>5.54869890213013</v>
       </c>
       <c r="H464" t="n">
         <v>1167</v>
@@ -13854,7 +13854,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G465" t="n">
-        <v>5.54869937896729</v>
+        <v>5.54869890213013</v>
       </c>
       <c r="H465" t="n">
         <v>2604</v>
@@ -13912,7 +13912,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>5.3424973487854</v>
+        <v>5.34249687194824</v>
       </c>
       <c r="H467" t="n">
         <v>3558</v>
@@ -14028,7 +14028,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G471" t="n">
-        <v>5.23002433776855</v>
+        <v>5.2300238609314</v>
       </c>
       <c r="H471" t="n">
         <v>5247</v>
@@ -14144,7 +14144,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>5.09880495071411</v>
+        <v>5.09880447387695</v>
       </c>
       <c r="H475" t="n">
         <v>5512</v>
@@ -14173,7 +14173,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G476" t="n">
-        <v>5.02382230758667</v>
+        <v>5.02382278442383</v>
       </c>
       <c r="H476" t="n">
         <v>311</v>
@@ -14231,7 +14231,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G478" t="n">
-        <v>4.89260292053223</v>
+        <v>4.89260244369507</v>
       </c>
       <c r="H478" t="n">
         <v>1880</v>
@@ -14289,7 +14289,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G480" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H480" t="n">
         <v>900</v>
@@ -14318,7 +14318,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H481" t="n">
         <v>16552</v>
@@ -14347,7 +14347,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G482" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H482" t="n">
         <v>1000</v>
@@ -14376,7 +14376,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G483" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14463,7 +14463,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>4.66765546798706</v>
+        <v>4.66765594482422</v>
       </c>
       <c r="H486" t="n">
         <v>8004</v>
@@ -14492,7 +14492,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G487" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H487" t="n">
         <v>1050</v>
@@ -14521,7 +14521,7 @@
         <v>5</v>
       </c>
       <c r="G488" t="n">
-        <v>4.6864013671875</v>
+        <v>4.68640089035034</v>
       </c>
       <c r="H488" t="n">
         <v>400</v>
@@ -14550,7 +14550,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G489" t="n">
-        <v>4.66765546798706</v>
+        <v>4.66765594482422</v>
       </c>
       <c r="H489" t="n">
         <v>49</v>
@@ -14579,7 +14579,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>4.64891052246094</v>
+        <v>4.64891004562378</v>
       </c>
       <c r="H490" t="n">
         <v>2650</v>
@@ -14666,7 +14666,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G493" t="n">
-        <v>4.5645546913147</v>
+        <v>4.56455421447754</v>
       </c>
       <c r="H493" t="n">
         <v>1016</v>
@@ -14695,7 +14695,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G494" t="n">
-        <v>4.64891052246094</v>
+        <v>4.64891004562378</v>
       </c>
       <c r="H494" t="n">
         <v>21434</v>
@@ -14724,7 +14724,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G495" t="n">
-        <v>4.65828275680542</v>
+        <v>4.65828323364258</v>
       </c>
       <c r="H495" t="n">
         <v>32639</v>
@@ -14753,7 +14753,7 @@
         <v>5</v>
       </c>
       <c r="G496" t="n">
-        <v>4.6864013671875</v>
+        <v>4.68640089035034</v>
       </c>
       <c r="H496" t="n">
         <v>7653</v>
@@ -14782,7 +14782,7 @@
         <v>5</v>
       </c>
       <c r="G497" t="n">
-        <v>4.6864013671875</v>
+        <v>4.68640089035034</v>
       </c>
       <c r="H497" t="n">
         <v>37466</v>
@@ -14898,7 +14898,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>4.83636617660522</v>
+        <v>4.83636569976807</v>
       </c>
       <c r="H501" t="n">
         <v>9387</v>
@@ -14927,7 +14927,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G502" t="n">
-        <v>4.89260292053223</v>
+        <v>4.89260244369507</v>
       </c>
       <c r="H502" t="n">
         <v>5569</v>
@@ -15014,7 +15014,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G505" t="n">
-        <v>4.85511159896851</v>
+        <v>4.85511112213135</v>
       </c>
       <c r="H505" t="n">
         <v>1553</v>
@@ -15101,7 +15101,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G508" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H508" t="n">
         <v>80250</v>
@@ -15130,7 +15130,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G509" t="n">
-        <v>4.85511159896851</v>
+        <v>4.85511112213135</v>
       </c>
       <c r="H509" t="n">
         <v>1200</v>
@@ -15159,7 +15159,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G510" t="n">
-        <v>4.91134834289551</v>
+        <v>4.91134881973267</v>
       </c>
       <c r="H510" t="n">
         <v>2290</v>
@@ -15188,7 +15188,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G511" t="n">
-        <v>5.02382230758667</v>
+        <v>5.02382278442383</v>
       </c>
       <c r="H511" t="n">
         <v>4402</v>
@@ -15304,7 +15304,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G515" t="n">
-        <v>5.00507640838623</v>
+        <v>5.00507688522339</v>
       </c>
       <c r="H515" t="n">
         <v>632</v>
@@ -15333,7 +15333,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G516" t="n">
-        <v>5.00507640838623</v>
+        <v>5.00507688522339</v>
       </c>
       <c r="H516" t="n">
         <v>0</v>
@@ -15362,7 +15362,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G517" t="n">
-        <v>5.06131362915039</v>
+        <v>5.06131315231323</v>
       </c>
       <c r="H517" t="n">
         <v>3072</v>
@@ -15449,7 +15449,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G520" t="n">
-        <v>5.02382230758667</v>
+        <v>5.02382278442383</v>
       </c>
       <c r="H520" t="n">
         <v>1669</v>
@@ -15507,7 +15507,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G522" t="n">
-        <v>4.91134834289551</v>
+        <v>4.91134881973267</v>
       </c>
       <c r="H522" t="n">
         <v>551</v>
@@ -15565,7 +15565,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G524" t="n">
-        <v>5.09880495071411</v>
+        <v>5.09880447387695</v>
       </c>
       <c r="H524" t="n">
         <v>1651</v>
@@ -15623,7 +15623,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G526" t="n">
-        <v>5.09880495071411</v>
+        <v>5.09880447387695</v>
       </c>
       <c r="H526" t="n">
         <v>2500</v>
@@ -15652,7 +15652,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G527" t="n">
-        <v>4.91134834289551</v>
+        <v>4.91134881973267</v>
       </c>
       <c r="H527" t="n">
         <v>4746</v>
@@ -15681,7 +15681,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G528" t="n">
-        <v>4.91134834289551</v>
+        <v>4.91134881973267</v>
       </c>
       <c r="H528" t="n">
         <v>524</v>
@@ -15739,7 +15739,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G530" t="n">
-        <v>4.85511159896851</v>
+        <v>4.85511112213135</v>
       </c>
       <c r="H530" t="n">
         <v>7425</v>
@@ -15768,7 +15768,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G531" t="n">
-        <v>4.85511159896851</v>
+        <v>4.85511112213135</v>
       </c>
       <c r="H531" t="n">
         <v>1488</v>
@@ -15826,7 +15826,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G533" t="n">
-        <v>4.89260292053223</v>
+        <v>4.89260244369507</v>
       </c>
       <c r="H533" t="n">
         <v>2400</v>
@@ -15913,7 +15913,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G536" t="n">
-        <v>4.85511159896851</v>
+        <v>4.85511112213135</v>
       </c>
       <c r="H536" t="n">
         <v>23217</v>
@@ -15971,7 +15971,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G538" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H538" t="n">
         <v>11050</v>
@@ -16000,7 +16000,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G539" t="n">
-        <v>4.85511159896851</v>
+        <v>4.85511112213135</v>
       </c>
       <c r="H539" t="n">
         <v>21211</v>
@@ -16145,7 +16145,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G544" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H544" t="n">
         <v>1500</v>
@@ -16174,7 +16174,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G545" t="n">
-        <v>4.85511159896851</v>
+        <v>4.85511112213135</v>
       </c>
       <c r="H545" t="n">
         <v>550</v>
@@ -16348,7 +16348,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G551" t="n">
-        <v>4.66765546798706</v>
+        <v>4.66765594482422</v>
       </c>
       <c r="H551" t="n">
         <v>33872</v>
@@ -16377,7 +16377,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H552" t="n">
         <v>2770</v>
@@ -16406,7 +16406,7 @@
         <v>5</v>
       </c>
       <c r="G553" t="n">
-        <v>4.6864013671875</v>
+        <v>4.68640089035034</v>
       </c>
       <c r="H553" t="n">
         <v>200</v>
@@ -16435,7 +16435,7 @@
         <v>5</v>
       </c>
       <c r="G554" t="n">
-        <v>4.6864013671875</v>
+        <v>4.68640089035034</v>
       </c>
       <c r="H554" t="n">
         <v>1284</v>
@@ -16464,7 +16464,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H555" t="n">
         <v>1730</v>
@@ -16522,7 +16522,7 @@
         <v>5</v>
       </c>
       <c r="G557" t="n">
-        <v>4.6864013671875</v>
+        <v>4.68640089035034</v>
       </c>
       <c r="H557" t="n">
         <v>5070</v>
@@ -16551,7 +16551,7 @@
         <v>5</v>
       </c>
       <c r="G558" t="n">
-        <v>4.6864013671875</v>
+        <v>4.68640089035034</v>
       </c>
       <c r="H558" t="n">
         <v>497</v>
@@ -16580,7 +16580,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G559" t="n">
-        <v>4.63016414642334</v>
+        <v>4.6301646232605</v>
       </c>
       <c r="H559" t="n">
         <v>465</v>
@@ -16667,7 +16667,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G562" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H562" t="n">
         <v>5341</v>
@@ -16696,7 +16696,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G563" t="n">
-        <v>4.83636617660522</v>
+        <v>4.83636569976807</v>
       </c>
       <c r="H563" t="n">
         <v>5514</v>
@@ -16725,7 +16725,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G564" t="n">
-        <v>4.98633098602295</v>
+        <v>4.98633146286011</v>
       </c>
       <c r="H564" t="n">
         <v>4495</v>
@@ -16754,7 +16754,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>5.06131362915039</v>
+        <v>5.06131315231323</v>
       </c>
       <c r="H565" t="n">
         <v>5184</v>
@@ -16783,7 +16783,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G566" t="n">
-        <v>5.06131362915039</v>
+        <v>5.06131315231323</v>
       </c>
       <c r="H566" t="n">
         <v>7208</v>
@@ -16812,7 +16812,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>5.09880495071411</v>
+        <v>5.09880447387695</v>
       </c>
       <c r="H567" t="n">
         <v>17491</v>
@@ -16957,7 +16957,7 @@
         <v>4.25</v>
       </c>
       <c r="G572" t="n">
-        <v>3.98344111442566</v>
+        <v>3.98344087600708</v>
       </c>
       <c r="H572" t="n">
         <v>9140</v>
@@ -16986,7 +16986,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G573" t="n">
-        <v>3.9646954536438</v>
+        <v>3.96469521522522</v>
       </c>
       <c r="H573" t="n">
         <v>1226</v>
@@ -17015,7 +17015,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G574" t="n">
-        <v>4.02093267440796</v>
+        <v>4.0209321975708</v>
       </c>
       <c r="H574" t="n">
         <v>6577</v>
@@ -17044,7 +17044,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G575" t="n">
-        <v>4.08654260635376</v>
+        <v>4.0865421295166</v>
       </c>
       <c r="H575" t="n">
         <v>16683</v>
@@ -17073,7 +17073,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>4.04905080795288</v>
+        <v>4.04905128479004</v>
       </c>
       <c r="H576" t="n">
         <v>6405</v>
@@ -17102,7 +17102,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G577" t="n">
-        <v>4.04905080795288</v>
+        <v>4.04905128479004</v>
       </c>
       <c r="H577" t="n">
         <v>5942</v>
@@ -17131,7 +17131,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G578" t="n">
-        <v>3.9646954536438</v>
+        <v>3.96469521522522</v>
       </c>
       <c r="H578" t="n">
         <v>2445</v>
@@ -17189,7 +17189,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>3.94594979286194</v>
+        <v>3.94594955444336</v>
       </c>
       <c r="H580" t="n">
         <v>8147</v>
@@ -17247,7 +17247,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G582" t="n">
-        <v>3.82410335540771</v>
+        <v>3.82410359382629</v>
       </c>
       <c r="H582" t="n">
         <v>7767</v>
@@ -17305,7 +17305,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>3.94594979286194</v>
+        <v>3.94594955444336</v>
       </c>
       <c r="H584" t="n">
         <v>3049</v>
@@ -17334,7 +17334,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G585" t="n">
-        <v>4.00218677520752</v>
+        <v>4.00218629837036</v>
       </c>
       <c r="H585" t="n">
         <v>1475</v>
@@ -17363,7 +17363,7 @@
         <v>4.25</v>
       </c>
       <c r="G586" t="n">
-        <v>3.98344111442566</v>
+        <v>3.98344087600708</v>
       </c>
       <c r="H586" t="n">
         <v>2353</v>
@@ -17392,7 +17392,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G587" t="n">
-        <v>3.92720413208008</v>
+        <v>3.9272038936615</v>
       </c>
       <c r="H587" t="n">
         <v>1105</v>
@@ -17508,7 +17508,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G591" t="n">
-        <v>3.63664746284485</v>
+        <v>3.63664770126343</v>
       </c>
       <c r="H591" t="n">
         <v>1370</v>
@@ -17566,7 +17566,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G593" t="n">
-        <v>4.03967761993408</v>
+        <v>4.03967809677124</v>
       </c>
       <c r="H593" t="n">
         <v>12527</v>
@@ -17595,7 +17595,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G594" t="n">
-        <v>4.00218677520752</v>
+        <v>4.00218629837036</v>
       </c>
       <c r="H594" t="n">
         <v>22055</v>
@@ -17653,7 +17653,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>4.02093267440796</v>
+        <v>4.0209321975708</v>
       </c>
       <c r="H596" t="n">
         <v>6142</v>
@@ -17682,7 +17682,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G597" t="n">
-        <v>4.06779670715332</v>
+        <v>4.06779623031616</v>
       </c>
       <c r="H597" t="n">
         <v>2200</v>
@@ -17798,7 +17798,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G601" t="n">
-        <v>4.03030490875244</v>
+        <v>4.0303053855896</v>
       </c>
       <c r="H601" t="n">
         <v>1764</v>
@@ -17827,7 +17827,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G602" t="n">
-        <v>4.04905080795288</v>
+        <v>4.04905128479004</v>
       </c>
       <c r="H602" t="n">
         <v>150</v>
@@ -17914,7 +17914,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G605" t="n">
-        <v>4.08654260635376</v>
+        <v>4.0865421295166</v>
       </c>
       <c r="H605" t="n">
         <v>4030</v>
@@ -17943,7 +17943,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G606" t="n">
-        <v>4.08654260635376</v>
+        <v>4.0865421295166</v>
       </c>
       <c r="H606" t="n">
         <v>1150</v>
@@ -17972,7 +17972,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G607" t="n">
-        <v>4.1334056854248</v>
+        <v>4.13340616226196</v>
       </c>
       <c r="H607" t="n">
         <v>55370</v>
@@ -18001,7 +18001,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G608" t="n">
-        <v>4.12403345108032</v>
+        <v>4.12403297424316</v>
       </c>
       <c r="H608" t="n">
         <v>2894</v>
@@ -18030,7 +18030,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G609" t="n">
-        <v>4.00218677520752</v>
+        <v>4.00218629837036</v>
       </c>
       <c r="H609" t="n">
         <v>1958</v>
@@ -18059,7 +18059,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G610" t="n">
-        <v>4.00218677520752</v>
+        <v>4.00218629837036</v>
       </c>
       <c r="H610" t="n">
         <v>2262</v>
@@ -18117,7 +18117,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>4.09591436386108</v>
+        <v>4.09591484069824</v>
       </c>
       <c r="H612" t="n">
         <v>401</v>
@@ -18146,7 +18146,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G613" t="n">
-        <v>4.09591436386108</v>
+        <v>4.09591484069824</v>
       </c>
       <c r="H613" t="n">
         <v>0</v>
@@ -18175,7 +18175,7 @@
         <v>4.25</v>
       </c>
       <c r="G614" t="n">
-        <v>3.98344111442566</v>
+        <v>3.98344087600708</v>
       </c>
       <c r="H614" t="n">
         <v>2924</v>
@@ -18204,7 +18204,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G615" t="n">
-        <v>4.03967761993408</v>
+        <v>4.03967809677124</v>
       </c>
       <c r="H615" t="n">
         <v>320</v>
@@ -18233,7 +18233,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G616" t="n">
-        <v>3.92720413208008</v>
+        <v>3.9272038936615</v>
       </c>
       <c r="H616" t="n">
         <v>3977</v>
@@ -18262,7 +18262,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G617" t="n">
-        <v>3.87096762657166</v>
+        <v>3.87096738815308</v>
       </c>
       <c r="H617" t="n">
         <v>5257</v>
@@ -18436,7 +18436,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G623" t="n">
-        <v>3.72100281715393</v>
+        <v>3.72100257873535</v>
       </c>
       <c r="H623" t="n">
         <v>572</v>
@@ -18465,7 +18465,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G624" t="n">
-        <v>3.72100281715393</v>
+        <v>3.72100257873535</v>
       </c>
       <c r="H624" t="n">
         <v>148</v>
@@ -18523,7 +18523,7 @@
         <v>4</v>
       </c>
       <c r="G626" t="n">
-        <v>3.74912118911743</v>
+        <v>3.74912095069885</v>
       </c>
       <c r="H626" t="n">
         <v>4138</v>
@@ -18552,7 +18552,7 @@
         <v>4</v>
       </c>
       <c r="G627" t="n">
-        <v>3.74912118911743</v>
+        <v>3.74912095069885</v>
       </c>
       <c r="H627" t="n">
         <v>3430</v>
@@ -18610,7 +18610,7 @@
         <v>4</v>
       </c>
       <c r="G629" t="n">
-        <v>3.74912118911743</v>
+        <v>3.74912095069885</v>
       </c>
       <c r="H629" t="n">
         <v>1000</v>
@@ -18697,7 +18697,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G632" t="n">
-        <v>3.64602041244507</v>
+        <v>3.64602017402649</v>
       </c>
       <c r="H632" t="n">
         <v>3650</v>
@@ -18726,7 +18726,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G633" t="n">
-        <v>3.63664746284485</v>
+        <v>3.63664770126343</v>
       </c>
       <c r="H633" t="n">
         <v>27710</v>
@@ -36741,6 +36741,35 @@
         <v>7839</v>
       </c>
       <c r="I1254" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1255" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1255" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="D1255" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="E1255" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="F1255" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="G1255" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="H1255" t="n">
+        <v>1061</v>
+      </c>
+      <c r="I1255" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RFG.MI.xlsx
+++ b/data/RFG.MI.xlsx
@@ -485,7 +485,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G4" t="n">
-        <v>4.40178394317627</v>
+        <v>4.40178489685059</v>
       </c>
       <c r="H4" t="n">
         <v>167566</v>
@@ -601,7 +601,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G8" t="n">
-        <v>4.22934341430664</v>
+        <v>4.22934293746948</v>
       </c>
       <c r="H8" t="n">
         <v>147200</v>
@@ -630,7 +630,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G9" t="n">
-        <v>4.07505369186401</v>
+        <v>4.07505321502686</v>
       </c>
       <c r="H9" t="n">
         <v>88738</v>
@@ -659,7 +659,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G10" t="n">
-        <v>4.17035055160522</v>
+        <v>4.17035007476807</v>
       </c>
       <c r="H10" t="n">
         <v>39798</v>
@@ -775,7 +775,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>4.19304037094116</v>
+        <v>4.193039894104</v>
       </c>
       <c r="H14" t="n">
         <v>6960</v>
@@ -891,7 +891,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G18" t="n">
-        <v>4.32463884353638</v>
+        <v>4.32463932037354</v>
       </c>
       <c r="H18" t="n">
         <v>32335</v>
@@ -1036,7 +1036,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G23" t="n">
-        <v>4.75574254989624</v>
+        <v>4.75574207305908</v>
       </c>
       <c r="H23" t="n">
         <v>42090</v>
@@ -1094,7 +1094,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>4.84650135040283</v>
+        <v>4.84650087356567</v>
       </c>
       <c r="H25" t="n">
         <v>24608</v>
@@ -1123,7 +1123,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G26" t="n">
-        <v>4.84650135040283</v>
+        <v>4.84650087356567</v>
       </c>
       <c r="H26" t="n">
         <v>84199</v>
@@ -1152,7 +1152,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>4.95541095733643</v>
+        <v>4.95541143417358</v>
       </c>
       <c r="H27" t="n">
         <v>26232</v>
@@ -1181,7 +1181,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G28" t="n">
-        <v>5.00078964233398</v>
+        <v>5.00079011917114</v>
       </c>
       <c r="H28" t="n">
         <v>40759</v>
@@ -1210,7 +1210,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>5.20045900344849</v>
+        <v>5.20045804977417</v>
       </c>
       <c r="H29" t="n">
         <v>89716</v>
@@ -1268,7 +1268,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>5.52718925476074</v>
+        <v>5.5271897315979</v>
       </c>
       <c r="H31" t="n">
         <v>27209</v>
@@ -1297,7 +1297,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G32" t="n">
-        <v>5.43643093109131</v>
+        <v>5.43643045425415</v>
       </c>
       <c r="H32" t="n">
         <v>36811</v>
@@ -1326,7 +1326,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G33" t="n">
-        <v>5.43643093109131</v>
+        <v>5.43643045425415</v>
       </c>
       <c r="H33" t="n">
         <v>30706</v>
@@ -1413,7 +1413,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G36" t="n">
-        <v>5.33659696578979</v>
+        <v>5.33659648895264</v>
       </c>
       <c r="H36" t="n">
         <v>16617</v>
@@ -1529,7 +1529,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G40" t="n">
-        <v>5.30936813354492</v>
+        <v>5.30936861038208</v>
       </c>
       <c r="H40" t="n">
         <v>10863</v>
@@ -1558,7 +1558,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G41" t="n">
-        <v>5.39105176925659</v>
+        <v>5.39105129241943</v>
       </c>
       <c r="H41" t="n">
         <v>11791</v>
@@ -1587,7 +1587,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>5.3819751739502</v>
+        <v>5.38197469711304</v>
       </c>
       <c r="H42" t="n">
         <v>10599</v>
@@ -1616,7 +1616,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G43" t="n">
-        <v>5.42735481262207</v>
+        <v>5.42735433578491</v>
       </c>
       <c r="H43" t="n">
         <v>24833</v>
@@ -1645,7 +1645,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G44" t="n">
-        <v>5.3275203704834</v>
+        <v>5.32751989364624</v>
       </c>
       <c r="H44" t="n">
         <v>29103</v>
@@ -1674,7 +1674,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G45" t="n">
-        <v>5.3547477722168</v>
+        <v>5.35474824905396</v>
       </c>
       <c r="H45" t="n">
         <v>29347</v>
@@ -1703,7 +1703,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G46" t="n">
-        <v>5.34567213058472</v>
+        <v>5.34567165374756</v>
       </c>
       <c r="H46" t="n">
         <v>21861</v>
@@ -1732,7 +1732,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>5.26398944854736</v>
+        <v>5.26398992538452</v>
       </c>
       <c r="H47" t="n">
         <v>26913</v>
@@ -1761,7 +1761,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G48" t="n">
-        <v>5.10970020294189</v>
+        <v>5.10969972610474</v>
       </c>
       <c r="H48" t="n">
         <v>75369</v>
@@ -1790,7 +1790,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>5.10062408447266</v>
+        <v>5.10062456130981</v>
       </c>
       <c r="H49" t="n">
         <v>37488</v>
@@ -1819,7 +1819,7 @@
         <v>5.75</v>
       </c>
       <c r="G50" t="n">
-        <v>5.2186107635498</v>
+        <v>5.21861028671265</v>
       </c>
       <c r="H50" t="n">
         <v>53296</v>
@@ -1848,7 +1848,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G51" t="n">
-        <v>5.20045900344849</v>
+        <v>5.20045804977417</v>
       </c>
       <c r="H51" t="n">
         <v>11633</v>
@@ -1877,7 +1877,7 @@
         <v>5.5</v>
       </c>
       <c r="G52" t="n">
-        <v>4.99171447753906</v>
+        <v>4.99171495437622</v>
       </c>
       <c r="H52" t="n">
         <v>31337</v>
@@ -1906,7 +1906,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G53" t="n">
-        <v>5.03709411621094</v>
+        <v>5.03709363937378</v>
       </c>
       <c r="H53" t="n">
         <v>29429</v>
@@ -1935,7 +1935,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G54" t="n">
-        <v>5.0461688041687</v>
+        <v>5.04616928100586</v>
       </c>
       <c r="H54" t="n">
         <v>17032</v>
@@ -1993,7 +1993,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G56" t="n">
-        <v>4.94633436203003</v>
+        <v>4.94633483886719</v>
       </c>
       <c r="H56" t="n">
         <v>4077</v>
@@ -2051,7 +2051,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G58" t="n">
-        <v>4.86465263366699</v>
+        <v>4.86465215682983</v>
       </c>
       <c r="H58" t="n">
         <v>10871</v>
@@ -2138,7 +2138,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G61" t="n">
-        <v>4.92818307876587</v>
+        <v>4.92818355560303</v>
       </c>
       <c r="H61" t="n">
         <v>10150</v>
@@ -2283,7 +2283,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G66" t="n">
-        <v>4.63775634765625</v>
+        <v>4.63775682449341</v>
       </c>
       <c r="H66" t="n">
         <v>9021</v>
@@ -2399,7 +2399,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G70" t="n">
-        <v>4.93725919723511</v>
+        <v>4.93725967407227</v>
       </c>
       <c r="H70" t="n">
         <v>2829</v>
@@ -2457,7 +2457,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G72" t="n">
-        <v>4.77389430999756</v>
+        <v>4.7738938331604</v>
       </c>
       <c r="H72" t="n">
         <v>8024</v>
@@ -2486,7 +2486,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G73" t="n">
-        <v>4.84650135040283</v>
+        <v>4.84650087356567</v>
       </c>
       <c r="H73" t="n">
         <v>6837</v>
@@ -2631,7 +2631,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G78" t="n">
-        <v>4.13404703140259</v>
+        <v>4.13404655456543</v>
       </c>
       <c r="H78" t="n">
         <v>12171</v>
@@ -2660,7 +2660,7 @@
         <v>4.5</v>
       </c>
       <c r="G79" t="n">
-        <v>4.08412933349609</v>
+        <v>4.08413028717041</v>
       </c>
       <c r="H79" t="n">
         <v>23806</v>
@@ -2689,7 +2689,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G80" t="n">
-        <v>4.32917785644531</v>
+        <v>4.32917737960815</v>
       </c>
       <c r="H80" t="n">
         <v>11441</v>
@@ -2747,7 +2747,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G82" t="n">
-        <v>4.02059936523438</v>
+        <v>4.02059888839722</v>
       </c>
       <c r="H82" t="n">
         <v>47987</v>
@@ -2776,7 +2776,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G83" t="n">
-        <v>3.99337100982666</v>
+        <v>3.9933717250824</v>
       </c>
       <c r="H83" t="n">
         <v>14139</v>
@@ -3008,7 +3008,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G91" t="n">
-        <v>4.48346757888794</v>
+        <v>4.48346662521362</v>
       </c>
       <c r="H91" t="n">
         <v>5261</v>
@@ -3066,7 +3066,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G93" t="n">
-        <v>4.54699850082397</v>
+        <v>4.54699802398682</v>
       </c>
       <c r="H93" t="n">
         <v>105195</v>
@@ -3182,7 +3182,7 @@
         <v>4.95499992370605</v>
       </c>
       <c r="G97" t="n">
-        <v>4.49708032608032</v>
+        <v>4.49708080291748</v>
       </c>
       <c r="H97" t="n">
         <v>8314</v>
@@ -3240,7 +3240,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>4.5016188621521</v>
+        <v>4.50161838531494</v>
       </c>
       <c r="H99" t="n">
         <v>18031</v>
@@ -3269,7 +3269,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G100" t="n">
-        <v>4.45623874664307</v>
+        <v>4.45623922348022</v>
       </c>
       <c r="H100" t="n">
         <v>1700</v>
@@ -3356,7 +3356,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G103" t="n">
-        <v>4.34732866287231</v>
+        <v>4.34732913970947</v>
       </c>
       <c r="H103" t="n">
         <v>12517</v>
@@ -3385,7 +3385,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>4.27472257614136</v>
+        <v>4.27472305297852</v>
       </c>
       <c r="H104" t="n">
         <v>501</v>
@@ -3414,7 +3414,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G105" t="n">
-        <v>4.36548089981079</v>
+        <v>4.36548137664795</v>
       </c>
       <c r="H105" t="n">
         <v>618</v>
@@ -3472,7 +3472,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G107" t="n">
-        <v>4.33371543884277</v>
+        <v>4.33371591567993</v>
       </c>
       <c r="H107" t="n">
         <v>1592</v>
@@ -3501,7 +3501,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>4.34732866287231</v>
+        <v>4.34732913970947</v>
       </c>
       <c r="H108" t="n">
         <v>5476</v>
@@ -3530,7 +3530,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G109" t="n">
-        <v>4.40632247924805</v>
+        <v>4.40632200241089</v>
       </c>
       <c r="H109" t="n">
         <v>2660</v>
@@ -3588,7 +3588,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G111" t="n">
-        <v>4.43808746337891</v>
+        <v>4.43808794021606</v>
       </c>
       <c r="H111" t="n">
         <v>941</v>
@@ -3617,7 +3617,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G112" t="n">
-        <v>4.33825349807739</v>
+        <v>4.33825397491455</v>
       </c>
       <c r="H112" t="n">
         <v>5545</v>
@@ -3646,7 +3646,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G113" t="n">
-        <v>4.37455749511719</v>
+        <v>4.37455701828003</v>
       </c>
       <c r="H113" t="n">
         <v>38</v>
@@ -3704,7 +3704,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>4.27472257614136</v>
+        <v>4.27472305297852</v>
       </c>
       <c r="H115" t="n">
         <v>3033</v>
@@ -3733,7 +3733,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G116" t="n">
-        <v>4.29287433624268</v>
+        <v>4.29287385940552</v>
       </c>
       <c r="H116" t="n">
         <v>5190</v>
@@ -3849,7 +3849,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G120" t="n">
-        <v>3.88446140289307</v>
+        <v>3.88446116447449</v>
       </c>
       <c r="H120" t="n">
         <v>37503</v>
@@ -3878,7 +3878,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G121" t="n">
-        <v>3.81639289855957</v>
+        <v>3.81639242172241</v>
       </c>
       <c r="H121" t="n">
         <v>9794</v>
@@ -3936,7 +3936,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G123" t="n">
-        <v>3.88446140289307</v>
+        <v>3.88446116447449</v>
       </c>
       <c r="H123" t="n">
         <v>3695</v>
@@ -3965,7 +3965,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G124" t="n">
-        <v>3.88446140289307</v>
+        <v>3.88446116447449</v>
       </c>
       <c r="H124" t="n">
         <v>7707</v>
@@ -3994,7 +3994,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G125" t="n">
-        <v>3.9207649230957</v>
+        <v>3.92076468467712</v>
       </c>
       <c r="H125" t="n">
         <v>16385</v>
@@ -4081,7 +4081,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G128" t="n">
-        <v>4.29900312423706</v>
+        <v>4.2990026473999</v>
       </c>
       <c r="H128" t="n">
         <v>9321</v>
@@ -4168,7 +4168,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G131" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H131" t="n">
         <v>15380</v>
@@ -4197,7 +4197,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>4.24365043640137</v>
+        <v>4.24365091323853</v>
       </c>
       <c r="H132" t="n">
         <v>3060</v>
@@ -4226,7 +4226,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G133" t="n">
-        <v>4.32667922973633</v>
+        <v>4.32667875289917</v>
       </c>
       <c r="H133" t="n">
         <v>10570</v>
@@ -4255,7 +4255,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G134" t="n">
-        <v>4.37741804122925</v>
+        <v>4.37741851806641</v>
       </c>
       <c r="H134" t="n">
         <v>1511</v>
@@ -4284,7 +4284,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G135" t="n">
-        <v>4.37280511856079</v>
+        <v>4.37280559539795</v>
       </c>
       <c r="H135" t="n">
         <v>4000</v>
@@ -4313,7 +4313,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G136" t="n">
-        <v>4.42354488372803</v>
+        <v>4.42354536056519</v>
       </c>
       <c r="H136" t="n">
         <v>520</v>
@@ -4342,7 +4342,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G137" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H137" t="n">
         <v>3650</v>
@@ -4371,7 +4371,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G138" t="n">
-        <v>4.28516530990601</v>
+        <v>4.28516483306885</v>
       </c>
       <c r="H138" t="n">
         <v>7384</v>
@@ -4400,7 +4400,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G139" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H139" t="n">
         <v>2000</v>
@@ -4429,7 +4429,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G140" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G143" t="n">
-        <v>4.2067494392395</v>
+        <v>4.20674991607666</v>
       </c>
       <c r="H143" t="n">
         <v>17151</v>
@@ -4545,7 +4545,7 @@
         <v>4.5</v>
       </c>
       <c r="G144" t="n">
-        <v>4.15139770507812</v>
+        <v>4.15139818191528</v>
       </c>
       <c r="H144" t="n">
         <v>12389</v>
@@ -4574,7 +4574,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G145" t="n">
-        <v>4.05453157424927</v>
+        <v>4.05453205108643</v>
       </c>
       <c r="H145" t="n">
         <v>90396</v>
@@ -4603,7 +4603,7 @@
         <v>4.25</v>
       </c>
       <c r="G146" t="n">
-        <v>3.92076444625854</v>
+        <v>3.92076468467712</v>
       </c>
       <c r="H146" t="n">
         <v>15623</v>
@@ -4661,7 +4661,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766568183899</v>
       </c>
       <c r="H148" t="n">
         <v>2849</v>
@@ -4690,7 +4690,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G149" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766568183899</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>4.1052713394165</v>
+        <v>4.10527086257935</v>
       </c>
       <c r="H151" t="n">
         <v>124</v>
@@ -4806,7 +4806,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G153" t="n">
-        <v>3.98534250259399</v>
+        <v>3.98534202575684</v>
       </c>
       <c r="H153" t="n">
         <v>8687</v>
@@ -4835,7 +4835,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G154" t="n">
-        <v>3.92999005317688</v>
+        <v>3.9299898147583</v>
       </c>
       <c r="H154" t="n">
         <v>5428</v>
@@ -4893,7 +4893,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>4.05914449691772</v>
+        <v>4.05914497375488</v>
       </c>
       <c r="H156" t="n">
         <v>120</v>
@@ -4922,7 +4922,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>3.9668915271759</v>
+        <v>3.96689128875732</v>
       </c>
       <c r="H157" t="n">
         <v>90</v>
@@ -4980,7 +4980,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G159" t="n">
-        <v>3.82851123809814</v>
+        <v>3.82851147651672</v>
       </c>
       <c r="H159" t="n">
         <v>11901</v>
@@ -5009,7 +5009,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G160" t="n">
-        <v>3.91153907775879</v>
+        <v>3.91153883934021</v>
       </c>
       <c r="H160" t="n">
         <v>4000</v>
@@ -5038,7 +5038,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G161" t="n">
-        <v>3.9668915271759</v>
+        <v>3.96689128875732</v>
       </c>
       <c r="H161" t="n">
         <v>1000</v>
@@ -5096,7 +5096,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G163" t="n">
-        <v>3.82851123809814</v>
+        <v>3.82851147651672</v>
       </c>
       <c r="H163" t="n">
         <v>5720</v>
@@ -5154,7 +5154,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G165" t="n">
-        <v>3.85618758201599</v>
+        <v>3.85618710517883</v>
       </c>
       <c r="H165" t="n">
         <v>450</v>
@@ -5183,7 +5183,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G166" t="n">
-        <v>3.84696197509766</v>
+        <v>3.84696221351624</v>
       </c>
       <c r="H166" t="n">
         <v>612</v>
@@ -5241,7 +5241,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G168" t="n">
-        <v>3.98534250259399</v>
+        <v>3.98534202575684</v>
       </c>
       <c r="H168" t="n">
         <v>5404</v>
@@ -5270,7 +5270,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>3.925377368927</v>
+        <v>3.92537713050842</v>
       </c>
       <c r="H169" t="n">
         <v>2375</v>
@@ -5299,7 +5299,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G170" t="n">
-        <v>3.92999005317688</v>
+        <v>3.9299898147583</v>
       </c>
       <c r="H170" t="n">
         <v>10150</v>
@@ -5386,7 +5386,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G173" t="n">
-        <v>4.05453157424927</v>
+        <v>4.05453205108643</v>
       </c>
       <c r="H173" t="n">
         <v>6047</v>
@@ -5473,7 +5473,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G176" t="n">
-        <v>3.95305323600769</v>
+        <v>3.95305299758911</v>
       </c>
       <c r="H176" t="n">
         <v>1056</v>
@@ -5502,7 +5502,7 @@
         <v>4.25</v>
       </c>
       <c r="G177" t="n">
-        <v>3.92076444625854</v>
+        <v>3.92076468467712</v>
       </c>
       <c r="H177" t="n">
         <v>3092</v>
@@ -5531,7 +5531,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>3.88386297225952</v>
+        <v>3.88386344909668</v>
       </c>
       <c r="H178" t="n">
         <v>5254</v>
@@ -5589,7 +5589,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G180" t="n">
-        <v>3.82851123809814</v>
+        <v>3.82851147651672</v>
       </c>
       <c r="H180" t="n">
         <v>6092</v>
@@ -5647,7 +5647,7 @@
         <v>4.25</v>
       </c>
       <c r="G182" t="n">
-        <v>3.92076444625854</v>
+        <v>3.92076468467712</v>
       </c>
       <c r="H182" t="n">
         <v>4226</v>
@@ -5676,7 +5676,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G183" t="n">
-        <v>3.88386297225952</v>
+        <v>3.88386344909668</v>
       </c>
       <c r="H183" t="n">
         <v>11079</v>
@@ -5850,7 +5850,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G189" t="n">
-        <v>4.00840520858765</v>
+        <v>4.00840473175049</v>
       </c>
       <c r="H189" t="n">
         <v>3667</v>
@@ -5879,7 +5879,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>3.88386297225952</v>
+        <v>3.88386344909668</v>
       </c>
       <c r="H190" t="n">
         <v>1237</v>
@@ -5937,7 +5937,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766568183899</v>
       </c>
       <c r="H192" t="n">
         <v>3183</v>
@@ -5966,7 +5966,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G193" t="n">
-        <v>4.01301765441895</v>
+        <v>4.0130181312561</v>
       </c>
       <c r="H193" t="n">
         <v>82</v>
@@ -6024,7 +6024,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>3.99456715583801</v>
+        <v>3.99456691741943</v>
       </c>
       <c r="H195" t="n">
         <v>131</v>
@@ -6053,7 +6053,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G196" t="n">
-        <v>3.86541223526001</v>
+        <v>3.86541247367859</v>
       </c>
       <c r="H196" t="n">
         <v>5890</v>
@@ -6082,7 +6082,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G197" t="n">
-        <v>3.94844102859497</v>
+        <v>3.94844055175781</v>
       </c>
       <c r="H197" t="n">
         <v>2149</v>
@@ -6111,7 +6111,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G198" t="n">
-        <v>3.86080026626587</v>
+        <v>3.86080002784729</v>
       </c>
       <c r="H198" t="n">
         <v>3433</v>
@@ -6140,7 +6140,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G199" t="n">
-        <v>3.92999005317688</v>
+        <v>3.9299898147583</v>
       </c>
       <c r="H199" t="n">
         <v>2982</v>
@@ -6169,7 +6169,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>3.99917936325073</v>
+        <v>3.99917984008789</v>
       </c>
       <c r="H200" t="n">
         <v>155</v>
@@ -6227,7 +6227,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G202" t="n">
-        <v>4.05914449691772</v>
+        <v>4.05914497375488</v>
       </c>
       <c r="H202" t="n">
         <v>7141</v>
@@ -6285,7 +6285,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G204" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766568183899</v>
       </c>
       <c r="H204" t="n">
         <v>5370</v>
@@ -6343,7 +6343,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G206" t="n">
-        <v>3.94844102859497</v>
+        <v>3.94844055175781</v>
       </c>
       <c r="H206" t="n">
         <v>5295</v>
@@ -6401,7 +6401,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>3.90231370925903</v>
+        <v>3.90231394767761</v>
       </c>
       <c r="H208" t="n">
         <v>1430</v>
@@ -6488,7 +6488,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G211" t="n">
-        <v>3.94844102859497</v>
+        <v>3.94844055175781</v>
       </c>
       <c r="H211" t="n">
         <v>5037</v>
@@ -6517,7 +6517,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G212" t="n">
-        <v>3.87002515792847</v>
+        <v>3.87002539634705</v>
       </c>
       <c r="H212" t="n">
         <v>3149</v>
@@ -6546,7 +6546,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>3.88386297225952</v>
+        <v>3.88386344909668</v>
       </c>
       <c r="H213" t="n">
         <v>1793</v>
@@ -6575,7 +6575,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G214" t="n">
-        <v>3.88386297225952</v>
+        <v>3.88386344909668</v>
       </c>
       <c r="H214" t="n">
         <v>63</v>
@@ -6633,7 +6633,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>3.94382786750793</v>
+        <v>3.94382834434509</v>
       </c>
       <c r="H216" t="n">
         <v>1</v>
@@ -6691,7 +6691,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G218" t="n">
-        <v>3.81928610801697</v>
+        <v>3.81928586959839</v>
       </c>
       <c r="H218" t="n">
         <v>120</v>
@@ -6720,7 +6720,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G219" t="n">
-        <v>3.82851123809814</v>
+        <v>3.82851147651672</v>
       </c>
       <c r="H219" t="n">
         <v>650</v>
@@ -6749,7 +6749,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>3.82851123809814</v>
+        <v>3.82851147651672</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G222" t="n">
-        <v>3.82851123809814</v>
+        <v>3.82851147651672</v>
       </c>
       <c r="H222" t="n">
         <v>400</v>
@@ -6865,7 +6865,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G224" t="n">
-        <v>4.1052713394165</v>
+        <v>4.10527086257935</v>
       </c>
       <c r="H224" t="n">
         <v>7165</v>
@@ -6894,7 +6894,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>4.01301765441895</v>
+        <v>4.0130181312561</v>
       </c>
       <c r="H225" t="n">
         <v>1000</v>
@@ -6923,7 +6923,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G226" t="n">
-        <v>4.24365043640137</v>
+        <v>4.24365091323853</v>
       </c>
       <c r="H226" t="n">
         <v>14277</v>
@@ -6952,7 +6952,7 @@
         <v>4.5</v>
       </c>
       <c r="G227" t="n">
-        <v>4.15139770507812</v>
+        <v>4.15139818191528</v>
       </c>
       <c r="H227" t="n">
         <v>5590</v>
@@ -6981,7 +6981,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G228" t="n">
-        <v>4.14217233657837</v>
+        <v>4.14217185974121</v>
       </c>
       <c r="H228" t="n">
         <v>6907</v>
@@ -7126,7 +7126,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G233" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H233" t="n">
         <v>12462</v>
@@ -7155,7 +7155,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H234" t="n">
         <v>15005</v>
@@ -7184,7 +7184,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G235" t="n">
-        <v>4.37280511856079</v>
+        <v>4.37280559539795</v>
       </c>
       <c r="H235" t="n">
         <v>17132</v>
@@ -7242,7 +7242,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G237" t="n">
-        <v>4.47428417205811</v>
+        <v>4.47428464889526</v>
       </c>
       <c r="H237" t="n">
         <v>567</v>
@@ -7271,7 +7271,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G238" t="n">
-        <v>4.42815828323364</v>
+        <v>4.42815780639648</v>
       </c>
       <c r="H238" t="n">
         <v>2197</v>
@@ -7300,7 +7300,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G239" t="n">
-        <v>4.46505975723267</v>
+        <v>4.46505928039551</v>
       </c>
       <c r="H239" t="n">
         <v>1590</v>
@@ -7329,7 +7329,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G240" t="n">
-        <v>4.42354488372803</v>
+        <v>4.42354536056519</v>
       </c>
       <c r="H240" t="n">
         <v>3500</v>
@@ -7358,7 +7358,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G241" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H241" t="n">
         <v>1200</v>
@@ -7387,7 +7387,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>4.42354488372803</v>
+        <v>4.42354536056519</v>
       </c>
       <c r="H242" t="n">
         <v>9000</v>
@@ -7416,7 +7416,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G243" t="n">
-        <v>4.50196075439453</v>
+        <v>4.50196027755737</v>
       </c>
       <c r="H243" t="n">
         <v>668</v>
@@ -7445,7 +7445,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G244" t="n">
-        <v>4.50196075439453</v>
+        <v>4.50196027755737</v>
       </c>
       <c r="H244" t="n">
         <v>32</v>
@@ -7474,7 +7474,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G245" t="n">
-        <v>4.50196075439453</v>
+        <v>4.50196027755737</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -7503,7 +7503,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G246" t="n">
-        <v>4.3543553352356</v>
+        <v>4.35435485839844</v>
       </c>
       <c r="H246" t="n">
         <v>2400</v>
@@ -7532,7 +7532,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G247" t="n">
-        <v>4.42815828323364</v>
+        <v>4.42815780639648</v>
       </c>
       <c r="H247" t="n">
         <v>1851</v>
@@ -7561,7 +7561,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G248" t="n">
-        <v>4.42815828323364</v>
+        <v>4.42815780639648</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G249" t="n">
-        <v>4.40970706939697</v>
+        <v>4.40970754623413</v>
       </c>
       <c r="H249" t="n">
         <v>6200</v>
@@ -7619,7 +7619,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G250" t="n">
-        <v>4.37280511856079</v>
+        <v>4.37280559539795</v>
       </c>
       <c r="H250" t="n">
         <v>241</v>
@@ -7648,7 +7648,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G251" t="n">
-        <v>4.3543553352356</v>
+        <v>4.35435485839844</v>
       </c>
       <c r="H251" t="n">
         <v>1595</v>
@@ -7677,7 +7677,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G252" t="n">
-        <v>4.2621021270752</v>
+        <v>4.26210165023804</v>
       </c>
       <c r="H252" t="n">
         <v>330</v>
@@ -7706,7 +7706,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G253" t="n">
-        <v>4.50196075439453</v>
+        <v>4.50196027755737</v>
       </c>
       <c r="H253" t="n">
         <v>1449</v>
@@ -7735,7 +7735,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>4.53886127471924</v>
+        <v>4.5388617515564</v>
       </c>
       <c r="H254" t="n">
         <v>12150</v>
@@ -7764,7 +7764,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G255" t="n">
-        <v>4.55731248855591</v>
+        <v>4.55731201171875</v>
       </c>
       <c r="H255" t="n">
         <v>4318</v>
@@ -7793,7 +7793,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G256" t="n">
-        <v>4.52041101455688</v>
+        <v>4.52041149139404</v>
       </c>
       <c r="H256" t="n">
         <v>9927</v>
@@ -7822,7 +7822,7 @@
         <v>5</v>
       </c>
       <c r="G257" t="n">
-        <v>4.61266374588013</v>
+        <v>4.61266422271729</v>
       </c>
       <c r="H257" t="n">
         <v>5177</v>
@@ -7851,7 +7851,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G258" t="n">
-        <v>4.51118516921997</v>
+        <v>4.51118564605713</v>
       </c>
       <c r="H258" t="n">
         <v>22611</v>
@@ -7880,7 +7880,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G259" t="n">
-        <v>4.42815828323364</v>
+        <v>4.42815780639648</v>
       </c>
       <c r="H259" t="n">
         <v>350</v>
@@ -7909,7 +7909,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>4.42815828323364</v>
+        <v>4.42815780639648</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G262" t="n">
-        <v>4.74181842803955</v>
+        <v>4.74181890487671</v>
       </c>
       <c r="H262" t="n">
         <v>8453</v>
@@ -8170,7 +8170,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G269" t="n">
-        <v>4.90787506103516</v>
+        <v>4.907874584198</v>
       </c>
       <c r="H269" t="n">
         <v>54096</v>
@@ -8286,7 +8286,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G273" t="n">
-        <v>4.99090242385864</v>
+        <v>4.9909029006958</v>
       </c>
       <c r="H273" t="n">
         <v>2440</v>
@@ -8315,7 +8315,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G274" t="n">
-        <v>4.99090242385864</v>
+        <v>4.9909029006958</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -8344,7 +8344,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G275" t="n">
-        <v>4.99090242385864</v>
+        <v>4.9909029006958</v>
       </c>
       <c r="H275" t="n">
         <v>6023</v>
@@ -8373,7 +8373,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H276" t="n">
         <v>5852</v>
@@ -8431,7 +8431,7 @@
         <v>5.5</v>
       </c>
       <c r="G278" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H278" t="n">
         <v>3731</v>
@@ -8460,7 +8460,7 @@
         <v>5.5</v>
       </c>
       <c r="G279" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H279" t="n">
         <v>5517</v>
@@ -8518,7 +8518,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G281" t="n">
-        <v>5.15695905685425</v>
+        <v>5.15695858001709</v>
       </c>
       <c r="H281" t="n">
         <v>13832</v>
@@ -8547,7 +8547,7 @@
         <v>5.5</v>
       </c>
       <c r="G282" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H282" t="n">
         <v>6695</v>
@@ -8576,7 +8576,7 @@
         <v>5.5</v>
       </c>
       <c r="G283" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H283" t="n">
         <v>5105</v>
@@ -8634,7 +8634,7 @@
         <v>5.5</v>
       </c>
       <c r="G285" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H285" t="n">
         <v>3111</v>
@@ -8692,7 +8692,7 @@
         <v>5.5</v>
       </c>
       <c r="G287" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H287" t="n">
         <v>5370</v>
@@ -8721,7 +8721,7 @@
         <v>5.5</v>
       </c>
       <c r="G288" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H288" t="n">
         <v>1000</v>
@@ -8808,7 +8808,7 @@
         <v>5.5</v>
       </c>
       <c r="G291" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H291" t="n">
         <v>4850</v>
@@ -8866,7 +8866,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G293" t="n">
-        <v>5.15695905685425</v>
+        <v>5.15695858001709</v>
       </c>
       <c r="H293" t="n">
         <v>10</v>
@@ -8895,7 +8895,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G294" t="n">
-        <v>5.11083173751831</v>
+        <v>5.11083221435547</v>
       </c>
       <c r="H294" t="n">
         <v>27739</v>
@@ -8953,7 +8953,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G296" t="n">
-        <v>4.90787506103516</v>
+        <v>4.907874584198</v>
       </c>
       <c r="H296" t="n">
         <v>14673</v>
@@ -8982,7 +8982,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G297" t="n">
-        <v>4.98167705535889</v>
+        <v>4.98167753219604</v>
       </c>
       <c r="H297" t="n">
         <v>83453</v>
@@ -9069,7 +9069,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G300" t="n">
-        <v>4.95400142669678</v>
+        <v>4.95400094985962</v>
       </c>
       <c r="H300" t="n">
         <v>25268</v>
@@ -9127,7 +9127,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G302" t="n">
-        <v>4.94477653503418</v>
+        <v>4.94477605819702</v>
       </c>
       <c r="H302" t="n">
         <v>8210</v>
@@ -9243,7 +9243,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G306" t="n">
-        <v>4.94477653503418</v>
+        <v>4.94477605819702</v>
       </c>
       <c r="H306" t="n">
         <v>69945</v>
@@ -9301,7 +9301,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>4.76949501037598</v>
+        <v>4.76949453353882</v>
       </c>
       <c r="H308" t="n">
         <v>7904</v>
@@ -9417,7 +9417,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G312" t="n">
-        <v>4.76949501037598</v>
+        <v>4.76949453353882</v>
       </c>
       <c r="H312" t="n">
         <v>4994</v>
@@ -9591,7 +9591,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G318" t="n">
-        <v>4.87097406387329</v>
+        <v>4.87097358703613</v>
       </c>
       <c r="H318" t="n">
         <v>7990</v>
@@ -9707,7 +9707,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G322" t="n">
-        <v>4.87097406387329</v>
+        <v>4.87097358703613</v>
       </c>
       <c r="H322" t="n">
         <v>10071</v>
@@ -9736,7 +9736,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G323" t="n">
-        <v>4.94477653503418</v>
+        <v>4.94477605819702</v>
       </c>
       <c r="H323" t="n">
         <v>1845</v>
@@ -9765,7 +9765,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G324" t="n">
-        <v>5.04625415802002</v>
+        <v>5.04625463485718</v>
       </c>
       <c r="H324" t="n">
         <v>3919</v>
@@ -9910,7 +9910,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G329" t="n">
-        <v>4.79717063903809</v>
+        <v>4.79717111587524</v>
       </c>
       <c r="H329" t="n">
         <v>5909</v>
@@ -9939,7 +9939,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>4.79717063903809</v>
+        <v>4.79717111587524</v>
       </c>
       <c r="H330" t="n">
         <v>445</v>
@@ -9968,7 +9968,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G331" t="n">
-        <v>4.99090242385864</v>
+        <v>4.9909029006958</v>
       </c>
       <c r="H331" t="n">
         <v>1655</v>
@@ -9997,7 +9997,7 @@
         <v>5.5</v>
       </c>
       <c r="G332" t="n">
-        <v>5.07393074035645</v>
+        <v>5.0739312171936</v>
       </c>
       <c r="H332" t="n">
         <v>10755</v>
@@ -10026,7 +10026,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G333" t="n">
-        <v>4.98167705535889</v>
+        <v>4.98167753219604</v>
       </c>
       <c r="H333" t="n">
         <v>54722</v>
@@ -10084,7 +10084,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G335" t="n">
-        <v>4.98167705535889</v>
+        <v>4.98167753219604</v>
       </c>
       <c r="H335" t="n">
         <v>34644</v>
@@ -10142,7 +10142,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G337" t="n">
-        <v>4.91709995269775</v>
+        <v>4.9170994758606</v>
       </c>
       <c r="H337" t="n">
         <v>5020</v>
@@ -10171,7 +10171,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>4.98167705535889</v>
+        <v>4.98167753219604</v>
       </c>
       <c r="H338" t="n">
         <v>3600</v>
@@ -10200,7 +10200,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G339" t="n">
-        <v>4.98167705535889</v>
+        <v>4.98167753219604</v>
       </c>
       <c r="H339" t="n">
         <v>700</v>
@@ -10229,7 +10229,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G340" t="n">
-        <v>4.90787506103516</v>
+        <v>4.907874584198</v>
       </c>
       <c r="H340" t="n">
         <v>9032</v>
@@ -10345,7 +10345,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G344" t="n">
-        <v>4.98167705535889</v>
+        <v>4.98167753219604</v>
       </c>
       <c r="H344" t="n">
         <v>8710</v>
@@ -10403,7 +10403,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G346" t="n">
-        <v>4.83407258987427</v>
+        <v>4.83407211303711</v>
       </c>
       <c r="H346" t="n">
         <v>2525</v>
@@ -10490,7 +10490,7 @@
         <v>5</v>
       </c>
       <c r="G349" t="n">
-        <v>4.61266374588013</v>
+        <v>4.61266422271729</v>
       </c>
       <c r="H349" t="n">
         <v>8051</v>
@@ -10519,7 +10519,7 @@
         <v>5</v>
       </c>
       <c r="G350" t="n">
-        <v>4.61266374588013</v>
+        <v>4.61266422271729</v>
       </c>
       <c r="H350" t="n">
         <v>5297</v>
@@ -10635,7 +10635,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G354" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H354" t="n">
         <v>1901</v>
@@ -10664,7 +10664,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H355" t="n">
         <v>7480</v>
@@ -10693,7 +10693,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G356" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H356" t="n">
         <v>7610</v>
@@ -10722,7 +10722,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G357" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H357" t="n">
         <v>1202</v>
@@ -10896,7 +10896,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G363" t="n">
-        <v>4.83407258987427</v>
+        <v>4.83407211303711</v>
       </c>
       <c r="H363" t="n">
         <v>1304</v>
@@ -10925,7 +10925,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G364" t="n">
-        <v>4.83407258987427</v>
+        <v>4.83407211303711</v>
       </c>
       <c r="H364" t="n">
         <v>15936</v>
@@ -10954,7 +10954,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G365" t="n">
-        <v>4.94477653503418</v>
+        <v>4.94477605819702</v>
       </c>
       <c r="H365" t="n">
         <v>3500</v>
@@ -11157,7 +11157,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G372" t="n">
-        <v>5.42449378967285</v>
+        <v>5.42449331283569</v>
       </c>
       <c r="H372" t="n">
         <v>16849</v>
@@ -11186,7 +11186,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G373" t="n">
-        <v>5.35069036483765</v>
+        <v>5.3506908416748</v>
       </c>
       <c r="H373" t="n">
         <v>5008</v>
@@ -11244,7 +11244,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G375" t="n">
-        <v>5.42449378967285</v>
+        <v>5.42449331283569</v>
       </c>
       <c r="H375" t="n">
         <v>7922</v>
@@ -11273,7 +11273,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>5.35069036483765</v>
+        <v>5.3506908416748</v>
       </c>
       <c r="H376" t="n">
         <v>1774</v>
@@ -11302,7 +11302,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>5.35069036483765</v>
+        <v>5.3506908416748</v>
       </c>
       <c r="H377" t="n">
         <v>2594</v>
@@ -11418,7 +11418,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>5.24876928329468</v>
+        <v>5.24876976013184</v>
       </c>
       <c r="H381" t="n">
         <v>20743</v>
@@ -11476,7 +11476,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G383" t="n">
-        <v>5.34249687194824</v>
+        <v>5.3424973487854</v>
       </c>
       <c r="H383" t="n">
         <v>7621</v>
@@ -11505,7 +11505,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G384" t="n">
-        <v>5.47371673583984</v>
+        <v>5.473717212677</v>
       </c>
       <c r="H384" t="n">
         <v>4634</v>
@@ -11563,7 +11563,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G386" t="n">
-        <v>5.60493612289429</v>
+        <v>5.60493564605713</v>
       </c>
       <c r="H386" t="n">
         <v>24572</v>
@@ -11592,7 +11592,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G387" t="n">
-        <v>5.66117286682129</v>
+        <v>5.66117238998413</v>
       </c>
       <c r="H387" t="n">
         <v>23023</v>
@@ -11621,7 +11621,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G388" t="n">
-        <v>5.529953956604</v>
+        <v>5.52995347976685</v>
       </c>
       <c r="H388" t="n">
         <v>9781</v>
@@ -11650,7 +11650,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G389" t="n">
-        <v>5.54869890213013</v>
+        <v>5.54869937896729</v>
       </c>
       <c r="H389" t="n">
         <v>8766</v>
@@ -11679,7 +11679,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H390" t="n">
         <v>24702</v>
@@ -11708,7 +11708,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G391" t="n">
-        <v>5.24876928329468</v>
+        <v>5.24876976013184</v>
       </c>
       <c r="H391" t="n">
         <v>7298</v>
@@ -11737,7 +11737,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G392" t="n">
-        <v>5.24876928329468</v>
+        <v>5.24876976013184</v>
       </c>
       <c r="H392" t="n">
         <v>2740</v>
@@ -11766,7 +11766,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G393" t="n">
-        <v>5.24876928329468</v>
+        <v>5.24876976013184</v>
       </c>
       <c r="H393" t="n">
         <v>16929</v>
@@ -11795,7 +11795,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G394" t="n">
-        <v>5.32375144958496</v>
+        <v>5.32375192642212</v>
       </c>
       <c r="H394" t="n">
         <v>680</v>
@@ -11824,7 +11824,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G395" t="n">
-        <v>5.54869890213013</v>
+        <v>5.54869937896729</v>
       </c>
       <c r="H395" t="n">
         <v>4979</v>
@@ -11882,7 +11882,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G397" t="n">
-        <v>5.47371673583984</v>
+        <v>5.473717212677</v>
       </c>
       <c r="H397" t="n">
         <v>2362</v>
@@ -11940,7 +11940,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G399" t="n">
-        <v>5.51120853424072</v>
+        <v>5.51120805740356</v>
       </c>
       <c r="H399" t="n">
         <v>550</v>
@@ -11998,7 +11998,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G401" t="n">
-        <v>5.529953956604</v>
+        <v>5.52995347976685</v>
       </c>
       <c r="H401" t="n">
         <v>9050</v>
@@ -12027,7 +12027,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>5.529953956604</v>
+        <v>5.52995347976685</v>
       </c>
       <c r="H402" t="n">
         <v>1661</v>
@@ -12085,7 +12085,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G404" t="n">
-        <v>5.51120853424072</v>
+        <v>5.51120805740356</v>
       </c>
       <c r="H404" t="n">
         <v>1070</v>
@@ -12114,7 +12114,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H405" t="n">
         <v>1418</v>
@@ -12288,7 +12288,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H411" t="n">
         <v>200</v>
@@ -12404,7 +12404,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H415" t="n">
         <v>100</v>
@@ -12433,7 +12433,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G416" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H416" t="n">
         <v>45</v>
@@ -12491,7 +12491,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G418" t="n">
-        <v>5.54869890213013</v>
+        <v>5.54869937896729</v>
       </c>
       <c r="H418" t="n">
         <v>1000</v>
@@ -12520,7 +12520,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G419" t="n">
-        <v>5.47371673583984</v>
+        <v>5.473717212677</v>
       </c>
       <c r="H419" t="n">
         <v>560</v>
@@ -12549,7 +12549,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G420" t="n">
-        <v>5.47371673583984</v>
+        <v>5.473717212677</v>
       </c>
       <c r="H420" t="n">
         <v>10242</v>
@@ -12607,7 +12607,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G422" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H422" t="n">
         <v>18970</v>
@@ -12636,7 +12636,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G423" t="n">
-        <v>5.529953956604</v>
+        <v>5.52995347976685</v>
       </c>
       <c r="H423" t="n">
         <v>1350</v>
@@ -12665,7 +12665,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G424" t="n">
-        <v>5.4549708366394</v>
+        <v>5.45497131347656</v>
       </c>
       <c r="H424" t="n">
         <v>8384</v>
@@ -12694,7 +12694,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G425" t="n">
-        <v>5.529953956604</v>
+        <v>5.52995347976685</v>
       </c>
       <c r="H425" t="n">
         <v>18369</v>
@@ -12752,7 +12752,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G427" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H427" t="n">
         <v>4203</v>
@@ -12781,7 +12781,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G428" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H428" t="n">
         <v>760</v>
@@ -12839,7 +12839,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G430" t="n">
-        <v>5.34249687194824</v>
+        <v>5.3424973487854</v>
       </c>
       <c r="H430" t="n">
         <v>3980</v>
@@ -12868,7 +12868,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G431" t="n">
-        <v>5.34249687194824</v>
+        <v>5.3424973487854</v>
       </c>
       <c r="H431" t="n">
         <v>2611</v>
@@ -12955,7 +12955,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G434" t="n">
-        <v>5.47371673583984</v>
+        <v>5.473717212677</v>
       </c>
       <c r="H434" t="n">
         <v>170</v>
@@ -12984,7 +12984,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G435" t="n">
-        <v>5.34249687194824</v>
+        <v>5.3424973487854</v>
       </c>
       <c r="H435" t="n">
         <v>868</v>
@@ -13013,7 +13013,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G436" t="n">
-        <v>5.34249687194824</v>
+        <v>5.3424973487854</v>
       </c>
       <c r="H436" t="n">
         <v>3947</v>
@@ -13042,7 +13042,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H437" t="n">
         <v>7332</v>
@@ -13071,7 +13071,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H438" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G442" t="n">
-        <v>5.34249687194824</v>
+        <v>5.3424973487854</v>
       </c>
       <c r="H442" t="n">
         <v>2261</v>
@@ -13245,7 +13245,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H444" t="n">
         <v>10</v>
@@ -13332,7 +13332,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G447" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H447" t="n">
         <v>20</v>
@@ -13361,7 +13361,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G448" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H448" t="n">
         <v>2255</v>
@@ -13390,7 +13390,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G449" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H449" t="n">
         <v>300</v>
@@ -13448,7 +13448,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G451" t="n">
-        <v>5.32375144958496</v>
+        <v>5.32375192642212</v>
       </c>
       <c r="H451" t="n">
         <v>924</v>
@@ -13477,7 +13477,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G452" t="n">
-        <v>5.32375144958496</v>
+        <v>5.32375192642212</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G453" t="n">
-        <v>5.32375144958496</v>
+        <v>5.32375192642212</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13593,7 +13593,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G456" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H456" t="n">
         <v>20122</v>
@@ -13622,7 +13622,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G457" t="n">
-        <v>5.47371673583984</v>
+        <v>5.473717212677</v>
       </c>
       <c r="H457" t="n">
         <v>3375</v>
@@ -13738,7 +13738,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G461" t="n">
-        <v>5.529953956604</v>
+        <v>5.52995347976685</v>
       </c>
       <c r="H461" t="n">
         <v>10854</v>
@@ -13767,7 +13767,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G462" t="n">
-        <v>5.54869890213013</v>
+        <v>5.54869937896729</v>
       </c>
       <c r="H462" t="n">
         <v>3576</v>
@@ -13796,7 +13796,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G463" t="n">
-        <v>5.529953956604</v>
+        <v>5.52995347976685</v>
       </c>
       <c r="H463" t="n">
         <v>3785</v>
@@ -13825,7 +13825,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G464" t="n">
-        <v>5.54869890213013</v>
+        <v>5.54869937896729</v>
       </c>
       <c r="H464" t="n">
         <v>1167</v>
@@ -13854,7 +13854,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G465" t="n">
-        <v>5.54869890213013</v>
+        <v>5.54869937896729</v>
       </c>
       <c r="H465" t="n">
         <v>2604</v>
@@ -13912,7 +13912,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G467" t="n">
-        <v>5.34249687194824</v>
+        <v>5.3424973487854</v>
       </c>
       <c r="H467" t="n">
         <v>3558</v>
@@ -13999,7 +13999,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G470" t="n">
-        <v>5.24876928329468</v>
+        <v>5.24876976013184</v>
       </c>
       <c r="H470" t="n">
         <v>2437</v>
@@ -14115,7 +14115,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G474" t="n">
-        <v>5.17378664016724</v>
+        <v>5.17378711700439</v>
       </c>
       <c r="H474" t="n">
         <v>3332</v>
@@ -14144,7 +14144,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G475" t="n">
-        <v>5.09880447387695</v>
+        <v>5.09880495071411</v>
       </c>
       <c r="H475" t="n">
         <v>5512</v>
@@ -14173,7 +14173,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G476" t="n">
-        <v>5.02382278442383</v>
+        <v>5.02382230758667</v>
       </c>
       <c r="H476" t="n">
         <v>311</v>
@@ -14318,7 +14318,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H481" t="n">
         <v>16552</v>
@@ -14347,7 +14347,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G482" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H482" t="n">
         <v>1000</v>
@@ -14376,7 +14376,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G483" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14405,7 +14405,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G484" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H484" t="n">
         <v>250</v>
@@ -14463,7 +14463,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G486" t="n">
-        <v>4.66765594482422</v>
+        <v>4.66765546798706</v>
       </c>
       <c r="H486" t="n">
         <v>8004</v>
@@ -14492,7 +14492,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G487" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H487" t="n">
         <v>1050</v>
@@ -14521,7 +14521,7 @@
         <v>5</v>
       </c>
       <c r="G488" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H488" t="n">
         <v>400</v>
@@ -14550,7 +14550,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G489" t="n">
-        <v>4.66765594482422</v>
+        <v>4.66765546798706</v>
       </c>
       <c r="H489" t="n">
         <v>49</v>
@@ -14579,7 +14579,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>4.64891004562378</v>
+        <v>4.64891052246094</v>
       </c>
       <c r="H490" t="n">
         <v>2650</v>
@@ -14666,7 +14666,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G493" t="n">
-        <v>4.56455421447754</v>
+        <v>4.5645546913147</v>
       </c>
       <c r="H493" t="n">
         <v>1016</v>
@@ -14695,7 +14695,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G494" t="n">
-        <v>4.64891004562378</v>
+        <v>4.64891052246094</v>
       </c>
       <c r="H494" t="n">
         <v>21434</v>
@@ -14724,7 +14724,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G495" t="n">
-        <v>4.65828323364258</v>
+        <v>4.65828275680542</v>
       </c>
       <c r="H495" t="n">
         <v>32639</v>
@@ -14753,7 +14753,7 @@
         <v>5</v>
       </c>
       <c r="G496" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H496" t="n">
         <v>7653</v>
@@ -14782,7 +14782,7 @@
         <v>5</v>
       </c>
       <c r="G497" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H497" t="n">
         <v>37466</v>
@@ -14840,7 +14840,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G499" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H499" t="n">
         <v>12994</v>
@@ -14898,7 +14898,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>4.83636569976807</v>
+        <v>4.83636617660522</v>
       </c>
       <c r="H501" t="n">
         <v>9387</v>
@@ -14956,7 +14956,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G503" t="n">
-        <v>4.87385702133179</v>
+        <v>4.87385749816895</v>
       </c>
       <c r="H503" t="n">
         <v>15019</v>
@@ -15014,7 +15014,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G505" t="n">
-        <v>4.85511112213135</v>
+        <v>4.85511159896851</v>
       </c>
       <c r="H505" t="n">
         <v>1553</v>
@@ -15043,7 +15043,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G506" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H506" t="n">
         <v>2350</v>
@@ -15072,7 +15072,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G509" t="n">
-        <v>4.85511112213135</v>
+        <v>4.85511159896851</v>
       </c>
       <c r="H509" t="n">
         <v>1200</v>
@@ -15159,7 +15159,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G510" t="n">
-        <v>4.91134881973267</v>
+        <v>4.91134834289551</v>
       </c>
       <c r="H510" t="n">
         <v>2290</v>
@@ -15188,7 +15188,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G511" t="n">
-        <v>5.02382278442383</v>
+        <v>5.02382230758667</v>
       </c>
       <c r="H511" t="n">
         <v>4402</v>
@@ -15217,7 +15217,7 @@
         <v>5.5</v>
       </c>
       <c r="G512" t="n">
-        <v>5.15504169464111</v>
+        <v>5.15504121780396</v>
       </c>
       <c r="H512" t="n">
         <v>4203</v>
@@ -15275,7 +15275,7 @@
         <v>5.5</v>
       </c>
       <c r="G514" t="n">
-        <v>5.15504169464111</v>
+        <v>5.15504121780396</v>
       </c>
       <c r="H514" t="n">
         <v>1884</v>
@@ -15304,7 +15304,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G515" t="n">
-        <v>5.00507688522339</v>
+        <v>5.00507640838623</v>
       </c>
       <c r="H515" t="n">
         <v>632</v>
@@ -15333,7 +15333,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G516" t="n">
-        <v>5.00507688522339</v>
+        <v>5.00507640838623</v>
       </c>
       <c r="H516" t="n">
         <v>0</v>
@@ -15362,7 +15362,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G517" t="n">
-        <v>5.06131315231323</v>
+        <v>5.06131362915039</v>
       </c>
       <c r="H517" t="n">
         <v>3072</v>
@@ -15391,7 +15391,7 @@
         <v>5.5</v>
       </c>
       <c r="G518" t="n">
-        <v>5.15504169464111</v>
+        <v>5.15504121780396</v>
       </c>
       <c r="H518" t="n">
         <v>6482</v>
@@ -15449,7 +15449,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G520" t="n">
-        <v>5.02382278442383</v>
+        <v>5.02382230758667</v>
       </c>
       <c r="H520" t="n">
         <v>1669</v>
@@ -15507,7 +15507,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G522" t="n">
-        <v>4.91134881973267</v>
+        <v>4.91134834289551</v>
       </c>
       <c r="H522" t="n">
         <v>551</v>
@@ -15536,7 +15536,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G523" t="n">
-        <v>4.96758556365967</v>
+        <v>4.96758508682251</v>
       </c>
       <c r="H523" t="n">
         <v>560</v>
@@ -15565,7 +15565,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G524" t="n">
-        <v>5.09880447387695</v>
+        <v>5.09880495071411</v>
       </c>
       <c r="H524" t="n">
         <v>1651</v>
@@ -15594,7 +15594,7 @@
         <v>5.5</v>
       </c>
       <c r="G525" t="n">
-        <v>5.15504169464111</v>
+        <v>5.15504121780396</v>
       </c>
       <c r="H525" t="n">
         <v>3840</v>
@@ -15623,7 +15623,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G526" t="n">
-        <v>5.09880447387695</v>
+        <v>5.09880495071411</v>
       </c>
       <c r="H526" t="n">
         <v>2500</v>
@@ -15652,7 +15652,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G527" t="n">
-        <v>4.91134881973267</v>
+        <v>4.91134834289551</v>
       </c>
       <c r="H527" t="n">
         <v>4746</v>
@@ -15681,7 +15681,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G528" t="n">
-        <v>4.91134881973267</v>
+        <v>4.91134834289551</v>
       </c>
       <c r="H528" t="n">
         <v>524</v>
@@ -15710,7 +15710,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G529" t="n">
-        <v>4.87385702133179</v>
+        <v>4.87385749816895</v>
       </c>
       <c r="H529" t="n">
         <v>22898</v>
@@ -15739,7 +15739,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G530" t="n">
-        <v>4.85511112213135</v>
+        <v>4.85511159896851</v>
       </c>
       <c r="H530" t="n">
         <v>7425</v>
@@ -15768,7 +15768,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G531" t="n">
-        <v>4.85511112213135</v>
+        <v>4.85511159896851</v>
       </c>
       <c r="H531" t="n">
         <v>1488</v>
@@ -15797,7 +15797,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G532" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H532" t="n">
         <v>121</v>
@@ -15855,7 +15855,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G534" t="n">
-        <v>4.87385702133179</v>
+        <v>4.87385749816895</v>
       </c>
       <c r="H534" t="n">
         <v>2718</v>
@@ -15884,7 +15884,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>4.87385702133179</v>
+        <v>4.87385749816895</v>
       </c>
       <c r="H535" t="n">
         <v>12616</v>
@@ -15913,7 +15913,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G536" t="n">
-        <v>4.85511112213135</v>
+        <v>4.85511159896851</v>
       </c>
       <c r="H536" t="n">
         <v>23217</v>
@@ -15942,7 +15942,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G537" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H537" t="n">
         <v>5650</v>
@@ -16000,7 +16000,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G539" t="n">
-        <v>4.85511112213135</v>
+        <v>4.85511159896851</v>
       </c>
       <c r="H539" t="n">
         <v>21211</v>
@@ -16029,7 +16029,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G540" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H540" t="n">
         <v>250</v>
@@ -16058,7 +16058,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G541" t="n">
-        <v>4.87385702133179</v>
+        <v>4.87385749816895</v>
       </c>
       <c r="H541" t="n">
         <v>1794</v>
@@ -16116,7 +16116,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G543" t="n">
-        <v>4.87385702133179</v>
+        <v>4.87385749816895</v>
       </c>
       <c r="H543" t="n">
         <v>4438</v>
@@ -16174,7 +16174,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G545" t="n">
-        <v>4.85511112213135</v>
+        <v>4.85511159896851</v>
       </c>
       <c r="H545" t="n">
         <v>550</v>
@@ -16203,7 +16203,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G546" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H546" t="n">
         <v>3803</v>
@@ -16232,7 +16232,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G547" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G548" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H548" t="n">
         <v>0</v>
@@ -16290,7 +16290,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G549" t="n">
-        <v>4.7426381111145</v>
+        <v>4.74263763427734</v>
       </c>
       <c r="H549" t="n">
         <v>400</v>
@@ -16348,7 +16348,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G551" t="n">
-        <v>4.66765594482422</v>
+        <v>4.66765546798706</v>
       </c>
       <c r="H551" t="n">
         <v>33872</v>
@@ -16377,7 +16377,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H552" t="n">
         <v>2770</v>
@@ -16406,7 +16406,7 @@
         <v>5</v>
       </c>
       <c r="G553" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H553" t="n">
         <v>200</v>
@@ -16435,7 +16435,7 @@
         <v>5</v>
       </c>
       <c r="G554" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H554" t="n">
         <v>1284</v>
@@ -16464,7 +16464,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H555" t="n">
         <v>1730</v>
@@ -16522,7 +16522,7 @@
         <v>5</v>
       </c>
       <c r="G557" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H557" t="n">
         <v>5070</v>
@@ -16551,7 +16551,7 @@
         <v>5</v>
       </c>
       <c r="G558" t="n">
-        <v>4.68640089035034</v>
+        <v>4.6864013671875</v>
       </c>
       <c r="H558" t="n">
         <v>497</v>
@@ -16580,7 +16580,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G559" t="n">
-        <v>4.6301646232605</v>
+        <v>4.63016414642334</v>
       </c>
       <c r="H559" t="n">
         <v>465</v>
@@ -16609,7 +16609,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>4.59267330169678</v>
+        <v>4.59267282485962</v>
       </c>
       <c r="H560" t="n">
         <v>2062</v>
@@ -16638,7 +16638,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G561" t="n">
-        <v>4.59267330169678</v>
+        <v>4.59267282485962</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G563" t="n">
-        <v>4.83636569976807</v>
+        <v>4.83636617660522</v>
       </c>
       <c r="H563" t="n">
         <v>5514</v>
@@ -16725,7 +16725,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G564" t="n">
-        <v>4.98633146286011</v>
+        <v>4.98633098602295</v>
       </c>
       <c r="H564" t="n">
         <v>4495</v>
@@ -16754,7 +16754,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>5.06131315231323</v>
+        <v>5.06131362915039</v>
       </c>
       <c r="H565" t="n">
         <v>5184</v>
@@ -16783,7 +16783,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G566" t="n">
-        <v>5.06131315231323</v>
+        <v>5.06131362915039</v>
       </c>
       <c r="H566" t="n">
         <v>7208</v>
@@ -16812,7 +16812,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>5.09880447387695</v>
+        <v>5.09880495071411</v>
       </c>
       <c r="H567" t="n">
         <v>17491</v>
@@ -16957,7 +16957,7 @@
         <v>4.25</v>
       </c>
       <c r="G572" t="n">
-        <v>3.98344087600708</v>
+        <v>3.98344135284424</v>
       </c>
       <c r="H572" t="n">
         <v>9140</v>
@@ -16986,7 +16986,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G573" t="n">
-        <v>3.96469521522522</v>
+        <v>3.9646954536438</v>
       </c>
       <c r="H573" t="n">
         <v>1226</v>
@@ -17073,7 +17073,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>4.04905128479004</v>
+        <v>4.04905080795288</v>
       </c>
       <c r="H576" t="n">
         <v>6405</v>
@@ -17102,7 +17102,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G577" t="n">
-        <v>4.04905128479004</v>
+        <v>4.04905080795288</v>
       </c>
       <c r="H577" t="n">
         <v>5942</v>
@@ -17131,7 +17131,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G578" t="n">
-        <v>3.96469521522522</v>
+        <v>3.9646954536438</v>
       </c>
       <c r="H578" t="n">
         <v>2445</v>
@@ -17189,7 +17189,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G580" t="n">
-        <v>3.94594955444336</v>
+        <v>3.94594979286194</v>
       </c>
       <c r="H580" t="n">
         <v>8147</v>
@@ -17305,7 +17305,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>3.94594955444336</v>
+        <v>3.94594979286194</v>
       </c>
       <c r="H584" t="n">
         <v>3049</v>
@@ -17334,7 +17334,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G585" t="n">
-        <v>4.00218629837036</v>
+        <v>4.00218677520752</v>
       </c>
       <c r="H585" t="n">
         <v>1475</v>
@@ -17363,7 +17363,7 @@
         <v>4.25</v>
       </c>
       <c r="G586" t="n">
-        <v>3.98344087600708</v>
+        <v>3.98344135284424</v>
       </c>
       <c r="H586" t="n">
         <v>2353</v>
@@ -17392,7 +17392,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G587" t="n">
-        <v>3.9272038936615</v>
+        <v>3.92720437049866</v>
       </c>
       <c r="H587" t="n">
         <v>1105</v>
@@ -17566,7 +17566,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G593" t="n">
-        <v>4.03967809677124</v>
+        <v>4.03967761993408</v>
       </c>
       <c r="H593" t="n">
         <v>12527</v>
@@ -17595,7 +17595,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G594" t="n">
-        <v>4.00218629837036</v>
+        <v>4.00218677520752</v>
       </c>
       <c r="H594" t="n">
         <v>22055</v>
@@ -17682,7 +17682,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G597" t="n">
-        <v>4.06779623031616</v>
+        <v>4.06779670715332</v>
       </c>
       <c r="H597" t="n">
         <v>2200</v>
@@ -17711,7 +17711,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G598" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H598" t="n">
         <v>5102</v>
@@ -17740,7 +17740,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G599" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H599" t="n">
         <v>4178</v>
@@ -17769,7 +17769,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G600" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H600" t="n">
         <v>2406</v>
@@ -17827,7 +17827,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G602" t="n">
-        <v>4.04905128479004</v>
+        <v>4.04905080795288</v>
       </c>
       <c r="H602" t="n">
         <v>150</v>
@@ -17856,7 +17856,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G603" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H603" t="n">
         <v>5008</v>
@@ -17885,7 +17885,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G604" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H604" t="n">
         <v>7230</v>
@@ -17972,7 +17972,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G607" t="n">
-        <v>4.13340616226196</v>
+        <v>4.1334056854248</v>
       </c>
       <c r="H607" t="n">
         <v>55370</v>
@@ -18030,7 +18030,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G609" t="n">
-        <v>4.00218629837036</v>
+        <v>4.00218677520752</v>
       </c>
       <c r="H609" t="n">
         <v>1958</v>
@@ -18059,7 +18059,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G610" t="n">
-        <v>4.00218629837036</v>
+        <v>4.00218677520752</v>
       </c>
       <c r="H610" t="n">
         <v>2262</v>
@@ -18117,7 +18117,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>4.09591484069824</v>
+        <v>4.09591436386108</v>
       </c>
       <c r="H612" t="n">
         <v>401</v>
@@ -18146,7 +18146,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G613" t="n">
-        <v>4.09591484069824</v>
+        <v>4.09591436386108</v>
       </c>
       <c r="H613" t="n">
         <v>0</v>
@@ -18175,7 +18175,7 @@
         <v>4.25</v>
       </c>
       <c r="G614" t="n">
-        <v>3.98344087600708</v>
+        <v>3.98344135284424</v>
       </c>
       <c r="H614" t="n">
         <v>2924</v>
@@ -18204,7 +18204,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G615" t="n">
-        <v>4.03967809677124</v>
+        <v>4.03967761993408</v>
       </c>
       <c r="H615" t="n">
         <v>320</v>
@@ -18233,7 +18233,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G616" t="n">
-        <v>3.9272038936615</v>
+        <v>3.92720437049866</v>
       </c>
       <c r="H616" t="n">
         <v>3977</v>
@@ -18523,7 +18523,7 @@
         <v>4</v>
       </c>
       <c r="G626" t="n">
-        <v>3.74912095069885</v>
+        <v>3.74912118911743</v>
       </c>
       <c r="H626" t="n">
         <v>4138</v>
@@ -18552,7 +18552,7 @@
         <v>4</v>
       </c>
       <c r="G627" t="n">
-        <v>3.74912095069885</v>
+        <v>3.74912118911743</v>
       </c>
       <c r="H627" t="n">
         <v>3430</v>
@@ -18610,7 +18610,7 @@
         <v>4</v>
       </c>
       <c r="G629" t="n">
-        <v>3.74912095069885</v>
+        <v>3.74912118911743</v>
       </c>
       <c r="H629" t="n">
         <v>1000</v>
@@ -18639,7 +18639,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G630" t="n">
-        <v>3.68351149559021</v>
+        <v>3.68351125717163</v>
       </c>
       <c r="H630" t="n">
         <v>9933</v>
@@ -18755,7 +18755,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G634" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H634" t="n">
         <v>3900</v>
@@ -18784,7 +18784,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G635" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H635" t="n">
         <v>6237</v>
@@ -18813,7 +18813,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G636" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H636" t="n">
         <v>7752</v>
@@ -18842,7 +18842,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G637" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H637" t="n">
         <v>1500</v>
@@ -18871,7 +18871,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G638" t="n">
-        <v>3.71341037750244</v>
+        <v>3.71341013908386</v>
       </c>
       <c r="H638" t="n">
         <v>8760</v>
@@ -18900,7 +18900,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G639" t="n">
-        <v>3.71341037750244</v>
+        <v>3.71341013908386</v>
       </c>
       <c r="H639" t="n">
         <v>0</v>
@@ -18929,7 +18929,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G640" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H640" t="n">
         <v>1052</v>
@@ -18958,7 +18958,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G641" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H641" t="n">
         <v>10</v>
@@ -18987,7 +18987,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G642" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H642" t="n">
         <v>90</v>
@@ -19103,7 +19103,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G646" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H646" t="n">
         <v>13400</v>
@@ -19190,7 +19190,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G649" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H649" t="n">
         <v>4153</v>
@@ -19248,7 +19248,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G651" t="n">
-        <v>3.65583801269531</v>
+        <v>3.65583825111389</v>
       </c>
       <c r="H651" t="n">
         <v>900</v>
@@ -19277,7 +19277,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>3.65583801269531</v>
+        <v>3.65583825111389</v>
       </c>
       <c r="H652" t="n">
         <v>10</v>
@@ -19335,7 +19335,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G654" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H654" t="n">
         <v>3015</v>
@@ -19393,7 +19393,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G656" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H656" t="n">
         <v>3182</v>
@@ -19422,7 +19422,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H657" t="n">
         <v>1517</v>
@@ -19480,7 +19480,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G659" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H659" t="n">
         <v>100</v>
@@ -19509,7 +19509,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G660" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H660" t="n">
         <v>299</v>
@@ -19538,7 +19538,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G661" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H661" t="n">
         <v>1404</v>
@@ -19567,7 +19567,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G662" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H662" t="n">
         <v>0</v>
@@ -19625,7 +19625,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G664" t="n">
-        <v>3.72300601005554</v>
+        <v>3.72300577163696</v>
       </c>
       <c r="H664" t="n">
         <v>800</v>
@@ -19712,7 +19712,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>4.12601184844971</v>
+        <v>4.12601137161255</v>
       </c>
       <c r="H667" t="n">
         <v>45390</v>
@@ -19770,7 +19770,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G669" t="n">
-        <v>4.12601184844971</v>
+        <v>4.12601137161255</v>
       </c>
       <c r="H669" t="n">
         <v>8487</v>
@@ -19799,7 +19799,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G670" t="n">
-        <v>4.12601184844971</v>
+        <v>4.12601137161255</v>
       </c>
       <c r="H670" t="n">
         <v>2970</v>
@@ -19973,7 +19973,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G676" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H676" t="n">
         <v>1500</v>
@@ -20089,7 +20089,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G680" t="n">
-        <v>4.02046203613281</v>
+        <v>4.02046251296997</v>
       </c>
       <c r="H680" t="n">
         <v>1420</v>
@@ -20118,7 +20118,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G681" t="n">
-        <v>3.99167609214783</v>
+        <v>3.99167633056641</v>
       </c>
       <c r="H681" t="n">
         <v>1555</v>
@@ -20176,7 +20176,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G683" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H683" t="n">
         <v>10</v>
@@ -20205,7 +20205,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H684" t="n">
         <v>9595</v>
@@ -20292,7 +20292,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G687" t="n">
-        <v>3.99167609214783</v>
+        <v>3.99167633056641</v>
       </c>
       <c r="H687" t="n">
         <v>750</v>
@@ -20321,7 +20321,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G688" t="n">
-        <v>3.99167609214783</v>
+        <v>3.99167633056641</v>
       </c>
       <c r="H688" t="n">
         <v>0</v>
@@ -20350,7 +20350,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G689" t="n">
-        <v>3.98208093643188</v>
+        <v>3.98208069801331</v>
       </c>
       <c r="H689" t="n">
         <v>150</v>
@@ -20379,7 +20379,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>4.03965282440186</v>
+        <v>4.03965330123901</v>
       </c>
       <c r="H690" t="n">
         <v>1160</v>
@@ -20408,7 +20408,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>4.03965282440186</v>
+        <v>4.03965330123901</v>
       </c>
       <c r="H691" t="n">
         <v>10</v>
@@ -20437,7 +20437,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H692" t="n">
         <v>11</v>
@@ -20466,7 +20466,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G693" t="n">
-        <v>4.03965282440186</v>
+        <v>4.03965330123901</v>
       </c>
       <c r="H693" t="n">
         <v>1069</v>
@@ -20524,7 +20524,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G695" t="n">
-        <v>3.98208093643188</v>
+        <v>3.98208069801331</v>
       </c>
       <c r="H695" t="n">
         <v>1981</v>
@@ -20553,7 +20553,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>3.98208093643188</v>
+        <v>3.98208069801331</v>
       </c>
       <c r="H696" t="n">
         <v>0</v>
@@ -20582,7 +20582,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>3.98208093643188</v>
+        <v>3.98208069801331</v>
       </c>
       <c r="H697" t="n">
         <v>120</v>
@@ -20611,7 +20611,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G698" t="n">
-        <v>4.02046203613281</v>
+        <v>4.02046251296997</v>
       </c>
       <c r="H698" t="n">
         <v>245</v>
@@ -20669,7 +20669,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G700" t="n">
-        <v>3.9436993598938</v>
+        <v>3.94369959831238</v>
       </c>
       <c r="H700" t="n">
         <v>210</v>
@@ -20698,7 +20698,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G701" t="n">
-        <v>3.9436993598938</v>
+        <v>3.94369959831238</v>
       </c>
       <c r="H701" t="n">
         <v>280</v>
@@ -20930,7 +20930,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G709" t="n">
-        <v>3.87653160095215</v>
+        <v>3.87653183937073</v>
       </c>
       <c r="H709" t="n">
         <v>1788</v>
@@ -21017,7 +21017,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G712" t="n">
-        <v>3.93410396575928</v>
+        <v>3.9341037273407</v>
       </c>
       <c r="H712" t="n">
         <v>3931</v>
@@ -21046,7 +21046,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G713" t="n">
-        <v>3.84774589538574</v>
+        <v>3.84774565696716</v>
       </c>
       <c r="H713" t="n">
         <v>5760</v>
@@ -21075,7 +21075,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G714" t="n">
-        <v>3.79017353057861</v>
+        <v>3.79017329216003</v>
       </c>
       <c r="H714" t="n">
         <v>185</v>
@@ -21104,7 +21104,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G715" t="n">
-        <v>3.77098274230957</v>
+        <v>3.77098250389099</v>
       </c>
       <c r="H715" t="n">
         <v>540</v>
@@ -21133,7 +21133,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G716" t="n">
-        <v>3.75179195404053</v>
+        <v>3.75179171562195</v>
       </c>
       <c r="H716" t="n">
         <v>330</v>
@@ -21162,7 +21162,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G717" t="n">
-        <v>3.75179195404053</v>
+        <v>3.75179171562195</v>
       </c>
       <c r="H717" t="n">
         <v>0</v>
@@ -21191,7 +21191,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G718" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H718" t="n">
         <v>20488</v>
@@ -21249,7 +21249,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G720" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H720" t="n">
         <v>1602</v>
@@ -21336,7 +21336,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>3.91491341590881</v>
+        <v>3.91491317749023</v>
       </c>
       <c r="H723" t="n">
         <v>750</v>
@@ -21365,7 +21365,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G724" t="n">
-        <v>4.21236991882324</v>
+        <v>4.21236944198608</v>
       </c>
       <c r="H724" t="n">
         <v>46988</v>
@@ -21423,7 +21423,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G726" t="n">
-        <v>4.21236991882324</v>
+        <v>4.21236944198608</v>
       </c>
       <c r="H726" t="n">
         <v>70435</v>
@@ -21481,7 +21481,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G728" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H728" t="n">
         <v>172</v>
@@ -21597,7 +21597,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G732" t="n">
-        <v>4.18358373641968</v>
+        <v>4.18358421325684</v>
       </c>
       <c r="H732" t="n">
         <v>1320</v>
@@ -21742,7 +21742,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G737" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H737" t="n">
         <v>1637</v>
@@ -21771,7 +21771,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G738" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H738" t="n">
         <v>75279</v>
@@ -21800,7 +21800,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G739" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H739" t="n">
         <v>0</v>
@@ -21829,7 +21829,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G740" t="n">
-        <v>3.99167609214783</v>
+        <v>3.99167633056641</v>
       </c>
       <c r="H740" t="n">
         <v>7953</v>
@@ -21974,7 +21974,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G745" t="n">
-        <v>3.93410396575928</v>
+        <v>3.9341037273407</v>
       </c>
       <c r="H745" t="n">
         <v>81270</v>
@@ -22003,7 +22003,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G746" t="n">
-        <v>3.93410396575928</v>
+        <v>3.9341037273407</v>
       </c>
       <c r="H746" t="n">
         <v>3945</v>
@@ -22032,7 +22032,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>3.91491341590881</v>
+        <v>3.91491317749023</v>
       </c>
       <c r="H747" t="n">
         <v>196255</v>
@@ -22119,7 +22119,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G750" t="n">
-        <v>4.0588436126709</v>
+        <v>4.05884408950806</v>
       </c>
       <c r="H750" t="n">
         <v>1996</v>
@@ -22148,7 +22148,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G751" t="n">
-        <v>3.98208093643188</v>
+        <v>3.98208069801331</v>
       </c>
       <c r="H751" t="n">
         <v>7044</v>
@@ -22206,7 +22206,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G753" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H753" t="n">
         <v>7875</v>
@@ -22235,7 +22235,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>4.03965282440186</v>
+        <v>4.03965330123901</v>
       </c>
       <c r="H754" t="n">
         <v>498</v>
@@ -22264,7 +22264,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G755" t="n">
-        <v>3.91491341590881</v>
+        <v>3.91491317749023</v>
       </c>
       <c r="H755" t="n">
         <v>21081</v>
@@ -22641,7 +22641,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>3.63664722442627</v>
+        <v>3.63664746284485</v>
       </c>
       <c r="H768" t="n">
         <v>8155</v>
@@ -22670,7 +22670,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G769" t="n">
-        <v>3.61745643615723</v>
+        <v>3.61745667457581</v>
       </c>
       <c r="H769" t="n">
         <v>19701</v>
@@ -22786,7 +22786,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G773" t="n">
-        <v>3.61745643615723</v>
+        <v>3.61745667457581</v>
       </c>
       <c r="H773" t="n">
         <v>16809</v>
@@ -22902,7 +22902,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>3.63664722442627</v>
+        <v>3.63664746284485</v>
       </c>
       <c r="H777" t="n">
         <v>23488</v>
@@ -22931,7 +22931,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G778" t="n">
-        <v>3.63664722442627</v>
+        <v>3.63664746284485</v>
       </c>
       <c r="H778" t="n">
         <v>5020</v>
@@ -23105,7 +23105,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G784" t="n">
-        <v>3.40635848045349</v>
+        <v>3.40635824203491</v>
       </c>
       <c r="H784" t="n">
         <v>13684</v>
@@ -23192,7 +23192,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H787" t="n">
         <v>1420</v>
@@ -23221,7 +23221,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G788" t="n">
-        <v>3.65583801269531</v>
+        <v>3.65583825111389</v>
       </c>
       <c r="H788" t="n">
         <v>1250</v>
@@ -23627,7 +23627,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G802" t="n">
-        <v>3.53109836578369</v>
+        <v>3.53109812736511</v>
       </c>
       <c r="H802" t="n">
         <v>18225</v>
@@ -23772,7 +23772,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G807" t="n">
-        <v>3.53109836578369</v>
+        <v>3.53109812736511</v>
       </c>
       <c r="H807" t="n">
         <v>6020</v>
@@ -23801,7 +23801,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>3.55988430976868</v>
+        <v>3.55988454818726</v>
       </c>
       <c r="H808" t="n">
         <v>5589</v>
@@ -23859,7 +23859,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G810" t="n">
-        <v>3.60786104202271</v>
+        <v>3.60786128044128</v>
       </c>
       <c r="H810" t="n">
         <v>35932</v>
@@ -23888,7 +23888,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G811" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H811" t="n">
         <v>3848</v>
@@ -23917,7 +23917,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G812" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H812" t="n">
         <v>10695</v>
@@ -23946,7 +23946,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G813" t="n">
-        <v>3.71341037750244</v>
+        <v>3.71341013908386</v>
       </c>
       <c r="H813" t="n">
         <v>3973</v>
@@ -23975,7 +23975,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G814" t="n">
-        <v>3.79017353057861</v>
+        <v>3.79017329216003</v>
       </c>
       <c r="H814" t="n">
         <v>8700</v>
@@ -24004,7 +24004,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G815" t="n">
-        <v>3.75179195404053</v>
+        <v>3.75179171562195</v>
       </c>
       <c r="H815" t="n">
         <v>4141</v>
@@ -24091,7 +24091,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>3.91491341590881</v>
+        <v>3.91491317749023</v>
       </c>
       <c r="H818" t="n">
         <v>4284</v>
@@ -24120,7 +24120,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G819" t="n">
-        <v>4.25075149536133</v>
+        <v>4.25075101852417</v>
       </c>
       <c r="H819" t="n">
         <v>51273</v>
@@ -24236,7 +24236,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G823" t="n">
-        <v>4.25075149536133</v>
+        <v>4.25075101852417</v>
       </c>
       <c r="H823" t="n">
         <v>21761</v>
@@ -24265,7 +24265,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G824" t="n">
-        <v>4.29872798919678</v>
+        <v>4.29872846603394</v>
       </c>
       <c r="H824" t="n">
         <v>12287</v>
@@ -24352,7 +24352,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G827" t="n">
-        <v>4.26994228363037</v>
+        <v>4.26994180679321</v>
       </c>
       <c r="H827" t="n">
         <v>3147</v>
@@ -24613,7 +24613,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G836" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H836" t="n">
         <v>440</v>
@@ -24642,7 +24642,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G837" t="n">
-        <v>4.12601184844971</v>
+        <v>4.12601137161255</v>
       </c>
       <c r="H837" t="n">
         <v>1700</v>
@@ -24874,7 +24874,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G845" t="n">
-        <v>4.12601184844971</v>
+        <v>4.12601137161255</v>
       </c>
       <c r="H845" t="n">
         <v>1616</v>
@@ -24903,7 +24903,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G846" t="n">
-        <v>4.12601184844971</v>
+        <v>4.12601137161255</v>
       </c>
       <c r="H846" t="n">
         <v>0</v>
@@ -25193,7 +25193,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G856" t="n">
-        <v>4.21236991882324</v>
+        <v>4.21236944198608</v>
       </c>
       <c r="H856" t="n">
         <v>12800</v>
@@ -25251,7 +25251,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G858" t="n">
-        <v>4.02046203613281</v>
+        <v>4.02046251296997</v>
       </c>
       <c r="H858" t="n">
         <v>3537</v>
@@ -25309,7 +25309,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G860" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H860" t="n">
         <v>2994</v>
@@ -25338,7 +25338,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G861" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H861" t="n">
         <v>280</v>
@@ -25657,7 +25657,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G872" t="n">
-        <v>3.91491341590881</v>
+        <v>3.91491317749023</v>
       </c>
       <c r="H872" t="n">
         <v>1409</v>
@@ -25686,7 +25686,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G873" t="n">
-        <v>3.91491341590881</v>
+        <v>3.91491317749023</v>
       </c>
       <c r="H873" t="n">
         <v>4382</v>
@@ -25831,7 +25831,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G878" t="n">
-        <v>3.97248554229736</v>
+        <v>3.97248530387878</v>
       </c>
       <c r="H878" t="n">
         <v>850</v>
@@ -25860,7 +25860,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G879" t="n">
-        <v>3.9436993598938</v>
+        <v>3.94369959831238</v>
       </c>
       <c r="H879" t="n">
         <v>3403</v>
@@ -25889,7 +25889,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G880" t="n">
-        <v>3.99167609214783</v>
+        <v>3.99167633056641</v>
       </c>
       <c r="H880" t="n">
         <v>17094</v>
@@ -25918,7 +25918,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G881" t="n">
-        <v>3.97248554229736</v>
+        <v>3.97248530387878</v>
       </c>
       <c r="H881" t="n">
         <v>7211</v>
@@ -26005,7 +26005,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G884" t="n">
-        <v>3.98208093643188</v>
+        <v>3.98208069801331</v>
       </c>
       <c r="H884" t="n">
         <v>2973</v>
@@ -36770,6 +36770,35 @@
         <v>1061</v>
       </c>
       <c r="I1255" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1256" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1256" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="D1256" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="E1256" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="F1256" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="G1256" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="H1256" t="n">
+        <v>3612</v>
+      </c>
+      <c r="I1256" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RFG.MI.xlsx
+++ b/data/RFG.MI.xlsx
@@ -456,7 +456,7 @@
         <v>5.0789999961853</v>
       </c>
       <c r="G3" t="n">
-        <v>4.60962152481079</v>
+        <v>4.60962104797363</v>
       </c>
       <c r="H3" t="n">
         <v>253124</v>
@@ -485,7 +485,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G4" t="n">
-        <v>4.40178489685059</v>
+        <v>4.40178442001343</v>
       </c>
       <c r="H4" t="n">
         <v>167566</v>
@@ -543,7 +543,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>4.26564693450928</v>
+        <v>4.26564645767212</v>
       </c>
       <c r="H6" t="n">
         <v>157332</v>
@@ -572,7 +572,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>4.35640525817871</v>
+        <v>4.35640573501587</v>
       </c>
       <c r="H7" t="n">
         <v>53988</v>
@@ -601,7 +601,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G8" t="n">
-        <v>4.22934293746948</v>
+        <v>4.22934341430664</v>
       </c>
       <c r="H8" t="n">
         <v>147200</v>
@@ -630,7 +630,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G9" t="n">
-        <v>4.07505321502686</v>
+        <v>4.07505369186401</v>
       </c>
       <c r="H9" t="n">
         <v>88738</v>
@@ -804,7 +804,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G15" t="n">
-        <v>4.26564693450928</v>
+        <v>4.26564645767212</v>
       </c>
       <c r="H15" t="n">
         <v>56165</v>
@@ -862,7 +862,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G17" t="n">
-        <v>4.26564693450928</v>
+        <v>4.26564645767212</v>
       </c>
       <c r="H17" t="n">
         <v>15689</v>
@@ -891,7 +891,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G18" t="n">
-        <v>4.32463932037354</v>
+        <v>4.32463979721069</v>
       </c>
       <c r="H18" t="n">
         <v>32335</v>
@@ -920,7 +920,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G19" t="n">
-        <v>4.4471640586853</v>
+        <v>4.44716358184814</v>
       </c>
       <c r="H19" t="n">
         <v>155415</v>
@@ -978,7 +978,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G21" t="n">
-        <v>4.60145330429077</v>
+        <v>4.60145282745361</v>
       </c>
       <c r="H21" t="n">
         <v>46761</v>
@@ -1065,7 +1065,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G24" t="n">
-        <v>4.8283486366272</v>
+        <v>4.82834911346436</v>
       </c>
       <c r="H24" t="n">
         <v>64828</v>
@@ -1094,7 +1094,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>4.84650087356567</v>
+        <v>4.84650039672852</v>
       </c>
       <c r="H25" t="n">
         <v>24608</v>
@@ -1123,7 +1123,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G26" t="n">
-        <v>4.84650087356567</v>
+        <v>4.84650039672852</v>
       </c>
       <c r="H26" t="n">
         <v>84199</v>
@@ -1152,7 +1152,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>4.95541143417358</v>
+        <v>4.95541095733643</v>
       </c>
       <c r="H27" t="n">
         <v>26232</v>
@@ -1210,7 +1210,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>5.20045804977417</v>
+        <v>5.20045852661133</v>
       </c>
       <c r="H29" t="n">
         <v>89716</v>
@@ -1268,7 +1268,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G31" t="n">
-        <v>5.5271897315979</v>
+        <v>5.52718925476074</v>
       </c>
       <c r="H31" t="n">
         <v>27209</v>
@@ -1355,7 +1355,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G34" t="n">
-        <v>5.48180961608887</v>
+        <v>5.48181009292603</v>
       </c>
       <c r="H34" t="n">
         <v>30948</v>
@@ -1413,7 +1413,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G36" t="n">
-        <v>5.33659648895264</v>
+        <v>5.33659601211548</v>
       </c>
       <c r="H36" t="n">
         <v>16617</v>
@@ -1442,7 +1442,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>5.25491380691528</v>
+        <v>5.25491428375244</v>
       </c>
       <c r="H37" t="n">
         <v>23662</v>
@@ -1500,7 +1500,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G39" t="n">
-        <v>5.36382341384888</v>
+        <v>5.36382389068604</v>
       </c>
       <c r="H39" t="n">
         <v>8885</v>
@@ -1529,7 +1529,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G40" t="n">
-        <v>5.30936861038208</v>
+        <v>5.30936908721924</v>
       </c>
       <c r="H40" t="n">
         <v>10863</v>
@@ -1587,7 +1587,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>5.38197469711304</v>
+        <v>5.3819751739502</v>
       </c>
       <c r="H42" t="n">
         <v>10599</v>
@@ -1616,7 +1616,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G43" t="n">
-        <v>5.42735433578491</v>
+        <v>5.42735481262207</v>
       </c>
       <c r="H43" t="n">
         <v>24833</v>
@@ -1674,7 +1674,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G45" t="n">
-        <v>5.35474824905396</v>
+        <v>5.3547477722168</v>
       </c>
       <c r="H45" t="n">
         <v>29347</v>
@@ -1761,7 +1761,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G48" t="n">
-        <v>5.10969972610474</v>
+        <v>5.10970020294189</v>
       </c>
       <c r="H48" t="n">
         <v>75369</v>
@@ -1790,7 +1790,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>5.10062456130981</v>
+        <v>5.10062408447266</v>
       </c>
       <c r="H49" t="n">
         <v>37488</v>
@@ -1848,7 +1848,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G51" t="n">
-        <v>5.20045804977417</v>
+        <v>5.20045852661133</v>
       </c>
       <c r="H51" t="n">
         <v>11633</v>
@@ -1877,7 +1877,7 @@
         <v>5.5</v>
       </c>
       <c r="G52" t="n">
-        <v>4.99171495437622</v>
+        <v>4.9917140007019</v>
       </c>
       <c r="H52" t="n">
         <v>31337</v>
@@ -1993,7 +1993,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G56" t="n">
-        <v>4.94633483886719</v>
+        <v>4.94633531570435</v>
       </c>
       <c r="H56" t="n">
         <v>4077</v>
@@ -2022,7 +2022,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G57" t="n">
-        <v>4.85557651519775</v>
+        <v>4.8555760383606</v>
       </c>
       <c r="H57" t="n">
         <v>32462</v>
@@ -2109,7 +2109,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G60" t="n">
-        <v>5.01894187927246</v>
+        <v>5.01894235610962</v>
       </c>
       <c r="H60" t="n">
         <v>23167</v>
@@ -2167,7 +2167,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G62" t="n">
-        <v>4.83742427825928</v>
+        <v>4.83742475509644</v>
       </c>
       <c r="H62" t="n">
         <v>13006</v>
@@ -2225,7 +2225,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G64" t="n">
-        <v>4.85557651519775</v>
+        <v>4.8555760383606</v>
       </c>
       <c r="H64" t="n">
         <v>15055</v>
@@ -2283,7 +2283,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G66" t="n">
-        <v>4.63775682449341</v>
+        <v>4.63775634765625</v>
       </c>
       <c r="H66" t="n">
         <v>9021</v>
@@ -2457,7 +2457,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G72" t="n">
-        <v>4.7738938331604</v>
+        <v>4.77389430999756</v>
       </c>
       <c r="H72" t="n">
         <v>8024</v>
@@ -2486,7 +2486,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G73" t="n">
-        <v>4.84650087356567</v>
+        <v>4.84650039672852</v>
       </c>
       <c r="H73" t="n">
         <v>6837</v>
@@ -2515,7 +2515,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G74" t="n">
-        <v>4.78296995162964</v>
+        <v>4.78296947479248</v>
       </c>
       <c r="H74" t="n">
         <v>4082</v>
@@ -2573,7 +2573,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>4.5197696685791</v>
+        <v>4.51977014541626</v>
       </c>
       <c r="H76" t="n">
         <v>20769</v>
@@ -2602,7 +2602,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G77" t="n">
-        <v>4.13858509063721</v>
+        <v>4.13858461380005</v>
       </c>
       <c r="H77" t="n">
         <v>29751</v>
@@ -2660,7 +2660,7 @@
         <v>4.5</v>
       </c>
       <c r="G79" t="n">
-        <v>4.08413028717041</v>
+        <v>4.08412981033325</v>
       </c>
       <c r="H79" t="n">
         <v>23806</v>
@@ -2689,7 +2689,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G80" t="n">
-        <v>4.32917737960815</v>
+        <v>4.32917785644531</v>
       </c>
       <c r="H80" t="n">
         <v>11441</v>
@@ -2776,7 +2776,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G83" t="n">
-        <v>3.9933717250824</v>
+        <v>3.99337196350098</v>
       </c>
       <c r="H83" t="n">
         <v>14139</v>
@@ -2892,7 +2892,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G87" t="n">
-        <v>4.21119117736816</v>
+        <v>4.21119165420532</v>
       </c>
       <c r="H87" t="n">
         <v>12593</v>
@@ -3037,7 +3037,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G92" t="n">
-        <v>4.53338384628296</v>
+        <v>4.53338432312012</v>
       </c>
       <c r="H92" t="n">
         <v>1969</v>
@@ -3124,7 +3124,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>4.5197696685791</v>
+        <v>4.51977014541626</v>
       </c>
       <c r="H95" t="n">
         <v>243259</v>
@@ -3153,7 +3153,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>4.5197696685791</v>
+        <v>4.51977014541626</v>
       </c>
       <c r="H96" t="n">
         <v>4515</v>
@@ -3182,7 +3182,7 @@
         <v>4.95499992370605</v>
       </c>
       <c r="G97" t="n">
-        <v>4.49708080291748</v>
+        <v>4.49708032608032</v>
       </c>
       <c r="H97" t="n">
         <v>8314</v>
@@ -3298,7 +3298,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G101" t="n">
-        <v>4.35640525817871</v>
+        <v>4.35640573501587</v>
       </c>
       <c r="H101" t="n">
         <v>2000</v>
@@ -3327,7 +3327,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G102" t="n">
-        <v>4.35640525817871</v>
+        <v>4.35640573501587</v>
       </c>
       <c r="H102" t="n">
         <v>1155</v>
@@ -3356,7 +3356,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G103" t="n">
-        <v>4.34732913970947</v>
+        <v>4.34732961654663</v>
       </c>
       <c r="H103" t="n">
         <v>12517</v>
@@ -3385,7 +3385,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G104" t="n">
-        <v>4.27472305297852</v>
+        <v>4.27472257614136</v>
       </c>
       <c r="H104" t="n">
         <v>501</v>
@@ -3414,7 +3414,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G105" t="n">
-        <v>4.36548137664795</v>
+        <v>4.36548089981079</v>
       </c>
       <c r="H105" t="n">
         <v>618</v>
@@ -3501,7 +3501,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>4.34732913970947</v>
+        <v>4.34732961654663</v>
       </c>
       <c r="H108" t="n">
         <v>5476</v>
@@ -3530,7 +3530,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G109" t="n">
-        <v>4.40632200241089</v>
+        <v>4.40632247924805</v>
       </c>
       <c r="H109" t="n">
         <v>2660</v>
@@ -3559,7 +3559,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>4.4471640586853</v>
+        <v>4.44716358184814</v>
       </c>
       <c r="H110" t="n">
         <v>197</v>
@@ -3588,7 +3588,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G111" t="n">
-        <v>4.43808794021606</v>
+        <v>4.43808746337891</v>
       </c>
       <c r="H111" t="n">
         <v>941</v>
@@ -3704,7 +3704,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G115" t="n">
-        <v>4.27472305297852</v>
+        <v>4.27472257614136</v>
       </c>
       <c r="H115" t="n">
         <v>3033</v>
@@ -3733,7 +3733,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G116" t="n">
-        <v>4.29287385940552</v>
+        <v>4.29287433624268</v>
       </c>
       <c r="H116" t="n">
         <v>5190</v>
@@ -3762,7 +3762,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G117" t="n">
-        <v>4.18396377563477</v>
+        <v>4.18396425247192</v>
       </c>
       <c r="H117" t="n">
         <v>3181</v>
@@ -3791,7 +3791,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G118" t="n">
-        <v>4.2429575920105</v>
+        <v>4.24295663833618</v>
       </c>
       <c r="H118" t="n">
         <v>50</v>
@@ -3849,7 +3849,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G120" t="n">
-        <v>3.88446116447449</v>
+        <v>3.88446092605591</v>
       </c>
       <c r="H120" t="n">
         <v>37503</v>
@@ -3878,7 +3878,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G121" t="n">
-        <v>3.81639242172241</v>
+        <v>3.81639266014099</v>
       </c>
       <c r="H121" t="n">
         <v>9794</v>
@@ -3907,7 +3907,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>3.89807486534119</v>
+        <v>3.89807462692261</v>
       </c>
       <c r="H122" t="n">
         <v>1318</v>
@@ -3936,7 +3936,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G123" t="n">
-        <v>3.88446116447449</v>
+        <v>3.88446092605591</v>
       </c>
       <c r="H123" t="n">
         <v>3695</v>
@@ -3965,7 +3965,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G124" t="n">
-        <v>3.88446116447449</v>
+        <v>3.88446092605591</v>
       </c>
       <c r="H124" t="n">
         <v>7707</v>
@@ -4052,7 +4052,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G127" t="n">
-        <v>4.21597528457642</v>
+        <v>4.21597480773926</v>
       </c>
       <c r="H127" t="n">
         <v>26910</v>
@@ -4081,7 +4081,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G128" t="n">
-        <v>4.2990026473999</v>
+        <v>4.29900312423706</v>
       </c>
       <c r="H128" t="n">
         <v>9321</v>
@@ -4197,7 +4197,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>4.24365091323853</v>
+        <v>4.24365139007568</v>
       </c>
       <c r="H132" t="n">
         <v>3060</v>
@@ -4255,7 +4255,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G134" t="n">
-        <v>4.37741851806641</v>
+        <v>4.37741804122925</v>
       </c>
       <c r="H134" t="n">
         <v>1511</v>
@@ -4458,7 +4458,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>4.24826383590698</v>
+        <v>4.24826335906982</v>
       </c>
       <c r="H141" t="n">
         <v>1470</v>
@@ -4516,7 +4516,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G143" t="n">
-        <v>4.20674991607666</v>
+        <v>4.2067494392395</v>
       </c>
       <c r="H143" t="n">
         <v>17151</v>
@@ -4545,7 +4545,7 @@
         <v>4.5</v>
       </c>
       <c r="G144" t="n">
-        <v>4.15139818191528</v>
+        <v>4.15139770507812</v>
       </c>
       <c r="H144" t="n">
         <v>12389</v>
@@ -4574,7 +4574,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G145" t="n">
-        <v>4.05453205108643</v>
+        <v>4.05453252792358</v>
       </c>
       <c r="H145" t="n">
         <v>90396</v>
@@ -4632,7 +4632,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>3.89770126342773</v>
+        <v>3.89770102500916</v>
       </c>
       <c r="H147" t="n">
         <v>8340</v>
@@ -4661,7 +4661,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95766568183899</v>
+        <v>3.95766592025757</v>
       </c>
       <c r="H148" t="n">
         <v>2849</v>
@@ -4690,7 +4690,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G149" t="n">
-        <v>3.95766568183899</v>
+        <v>3.95766592025757</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G150" t="n">
-        <v>4.04069375991821</v>
+        <v>4.04069423675537</v>
       </c>
       <c r="H150" t="n">
         <v>36</v>
@@ -4748,7 +4748,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>4.10527086257935</v>
+        <v>4.1052713394165</v>
       </c>
       <c r="H151" t="n">
         <v>124</v>
@@ -4835,7 +4835,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G154" t="n">
-        <v>3.9299898147583</v>
+        <v>3.92999005317688</v>
       </c>
       <c r="H154" t="n">
         <v>5428</v>
@@ -4980,7 +4980,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G159" t="n">
-        <v>3.82851147651672</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H159" t="n">
         <v>11901</v>
@@ -5096,7 +5096,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G163" t="n">
-        <v>3.82851147651672</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H163" t="n">
         <v>5720</v>
@@ -5125,7 +5125,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G164" t="n">
-        <v>3.8377366065979</v>
+        <v>3.83773636817932</v>
       </c>
       <c r="H164" t="n">
         <v>2438</v>
@@ -5212,7 +5212,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>3.89770126342773</v>
+        <v>3.89770102500916</v>
       </c>
       <c r="H167" t="n">
         <v>205</v>
@@ -5270,7 +5270,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>3.92537713050842</v>
+        <v>3.925377368927</v>
       </c>
       <c r="H169" t="n">
         <v>2375</v>
@@ -5299,7 +5299,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G170" t="n">
-        <v>3.9299898147583</v>
+        <v>3.92999005317688</v>
       </c>
       <c r="H170" t="n">
         <v>10150</v>
@@ -5386,7 +5386,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G173" t="n">
-        <v>4.05453205108643</v>
+        <v>4.05453252792358</v>
       </c>
       <c r="H173" t="n">
         <v>6047</v>
@@ -5473,7 +5473,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G176" t="n">
-        <v>3.95305299758911</v>
+        <v>3.95305275917053</v>
       </c>
       <c r="H176" t="n">
         <v>1056</v>
@@ -5531,7 +5531,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>3.88386344909668</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H178" t="n">
         <v>5254</v>
@@ -5589,7 +5589,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G180" t="n">
-        <v>3.82851147651672</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H180" t="n">
         <v>6092</v>
@@ -5618,7 +5618,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G181" t="n">
-        <v>3.8377366065979</v>
+        <v>3.83773636817932</v>
       </c>
       <c r="H181" t="n">
         <v>5582</v>
@@ -5676,7 +5676,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G183" t="n">
-        <v>3.88386344909668</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H183" t="n">
         <v>11079</v>
@@ -5821,7 +5821,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G188" t="n">
-        <v>3.93921494483948</v>
+        <v>3.93921542167664</v>
       </c>
       <c r="H188" t="n">
         <v>2507</v>
@@ -5879,7 +5879,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>3.88386344909668</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H190" t="n">
         <v>1237</v>
@@ -5937,7 +5937,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>3.95766568183899</v>
+        <v>3.95766592025757</v>
       </c>
       <c r="H192" t="n">
         <v>3183</v>
@@ -6024,7 +6024,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>3.99456691741943</v>
+        <v>3.99456715583801</v>
       </c>
       <c r="H195" t="n">
         <v>131</v>
@@ -6053,7 +6053,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G196" t="n">
-        <v>3.86541247367859</v>
+        <v>3.86541271209717</v>
       </c>
       <c r="H196" t="n">
         <v>5890</v>
@@ -6082,7 +6082,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G197" t="n">
-        <v>3.94844055175781</v>
+        <v>3.94844031333923</v>
       </c>
       <c r="H197" t="n">
         <v>2149</v>
@@ -6140,7 +6140,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G199" t="n">
-        <v>3.9299898147583</v>
+        <v>3.92999005317688</v>
       </c>
       <c r="H199" t="n">
         <v>2982</v>
@@ -6285,7 +6285,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G204" t="n">
-        <v>3.95766568183899</v>
+        <v>3.95766592025757</v>
       </c>
       <c r="H204" t="n">
         <v>5370</v>
@@ -6343,7 +6343,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G206" t="n">
-        <v>3.94844055175781</v>
+        <v>3.94844031333923</v>
       </c>
       <c r="H206" t="n">
         <v>5295</v>
@@ -6401,7 +6401,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>3.90231394767761</v>
+        <v>3.90231370925903</v>
       </c>
       <c r="H208" t="n">
         <v>1430</v>
@@ -6488,7 +6488,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G211" t="n">
-        <v>3.94844055175781</v>
+        <v>3.94844031333923</v>
       </c>
       <c r="H211" t="n">
         <v>5037</v>
@@ -6517,7 +6517,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G212" t="n">
-        <v>3.87002539634705</v>
+        <v>3.87002563476562</v>
       </c>
       <c r="H212" t="n">
         <v>3149</v>
@@ -6546,7 +6546,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>3.88386344909668</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H213" t="n">
         <v>1793</v>
@@ -6575,7 +6575,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G214" t="n">
-        <v>3.88386344909668</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H214" t="n">
         <v>63</v>
@@ -6633,7 +6633,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>3.94382834434509</v>
+        <v>3.94382762908936</v>
       </c>
       <c r="H216" t="n">
         <v>1</v>
@@ -6720,7 +6720,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G219" t="n">
-        <v>3.82851147651672</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H219" t="n">
         <v>650</v>
@@ -6749,7 +6749,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>3.82851147651672</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G222" t="n">
-        <v>3.82851147651672</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H222" t="n">
         <v>400</v>
@@ -6836,7 +6836,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G223" t="n">
-        <v>4.04069375991821</v>
+        <v>4.04069423675537</v>
       </c>
       <c r="H223" t="n">
         <v>36447</v>
@@ -6865,7 +6865,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G224" t="n">
-        <v>4.10527086257935</v>
+        <v>4.1052713394165</v>
       </c>
       <c r="H224" t="n">
         <v>7165</v>
@@ -6923,7 +6923,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G226" t="n">
-        <v>4.24365091323853</v>
+        <v>4.24365139007568</v>
       </c>
       <c r="H226" t="n">
         <v>14277</v>
@@ -6952,7 +6952,7 @@
         <v>4.5</v>
       </c>
       <c r="G227" t="n">
-        <v>4.15139818191528</v>
+        <v>4.15139770507812</v>
       </c>
       <c r="H227" t="n">
         <v>5590</v>
@@ -7097,7 +7097,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G232" t="n">
-        <v>4.21597528457642</v>
+        <v>4.21597480773926</v>
       </c>
       <c r="H232" t="n">
         <v>7962</v>
@@ -7213,7 +7213,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>4.45583343505859</v>
+        <v>4.45583391189575</v>
       </c>
       <c r="H236" t="n">
         <v>4300</v>
@@ -7242,7 +7242,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G237" t="n">
-        <v>4.47428464889526</v>
+        <v>4.47428417205811</v>
       </c>
       <c r="H237" t="n">
         <v>567</v>
@@ -7677,7 +7677,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G252" t="n">
-        <v>4.26210165023804</v>
+        <v>4.26210117340088</v>
       </c>
       <c r="H252" t="n">
         <v>330</v>
@@ -7793,7 +7793,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G256" t="n">
-        <v>4.52041149139404</v>
+        <v>4.52041101455688</v>
       </c>
       <c r="H256" t="n">
         <v>9927</v>
@@ -7851,7 +7851,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G258" t="n">
-        <v>4.51118564605713</v>
+        <v>4.51118516921997</v>
       </c>
       <c r="H258" t="n">
         <v>22611</v>
@@ -8025,7 +8025,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G264" t="n">
-        <v>4.88019847869873</v>
+        <v>4.88019895553589</v>
       </c>
       <c r="H264" t="n">
         <v>69249</v>
@@ -8141,7 +8141,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G268" t="n">
-        <v>5.02780389785767</v>
+        <v>5.02780437469482</v>
       </c>
       <c r="H268" t="n">
         <v>4916</v>
@@ -8170,7 +8170,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G269" t="n">
-        <v>4.907874584198</v>
+        <v>4.90787506103516</v>
       </c>
       <c r="H269" t="n">
         <v>54096</v>
@@ -8199,7 +8199,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G270" t="n">
-        <v>4.93555068969727</v>
+        <v>4.93555021286011</v>
       </c>
       <c r="H270" t="n">
         <v>78819</v>
@@ -8286,7 +8286,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G273" t="n">
-        <v>4.9909029006958</v>
+        <v>4.99090242385864</v>
       </c>
       <c r="H273" t="n">
         <v>2440</v>
@@ -8315,7 +8315,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G274" t="n">
-        <v>4.9909029006958</v>
+        <v>4.99090242385864</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -8344,7 +8344,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G275" t="n">
-        <v>4.9909029006958</v>
+        <v>4.99090242385864</v>
       </c>
       <c r="H275" t="n">
         <v>6023</v>
@@ -8373,7 +8373,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>5.01857900619507</v>
+        <v>5.01857852935791</v>
       </c>
       <c r="H276" t="n">
         <v>5852</v>
@@ -8431,7 +8431,7 @@
         <v>5.5</v>
       </c>
       <c r="G278" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H278" t="n">
         <v>3731</v>
@@ -8460,7 +8460,7 @@
         <v>5.5</v>
       </c>
       <c r="G279" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H279" t="n">
         <v>5517</v>
@@ -8547,7 +8547,7 @@
         <v>5.5</v>
       </c>
       <c r="G282" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H282" t="n">
         <v>6695</v>
@@ -8576,7 +8576,7 @@
         <v>5.5</v>
       </c>
       <c r="G283" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H283" t="n">
         <v>5105</v>
@@ -8634,7 +8634,7 @@
         <v>5.5</v>
       </c>
       <c r="G285" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H285" t="n">
         <v>3111</v>
@@ -8663,7 +8663,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G286" t="n">
-        <v>5.0923810005188</v>
+        <v>5.09238195419312</v>
       </c>
       <c r="H286" t="n">
         <v>233</v>
@@ -8692,7 +8692,7 @@
         <v>5.5</v>
       </c>
       <c r="G287" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H287" t="n">
         <v>5370</v>
@@ -8721,7 +8721,7 @@
         <v>5.5</v>
       </c>
       <c r="G288" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H288" t="n">
         <v>1000</v>
@@ -8808,7 +8808,7 @@
         <v>5.5</v>
       </c>
       <c r="G291" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H291" t="n">
         <v>4850</v>
@@ -8895,7 +8895,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G294" t="n">
-        <v>5.11083221435547</v>
+        <v>5.11083173751831</v>
       </c>
       <c r="H294" t="n">
         <v>27739</v>
@@ -8953,7 +8953,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G296" t="n">
-        <v>4.907874584198</v>
+        <v>4.90787506103516</v>
       </c>
       <c r="H296" t="n">
         <v>14673</v>
@@ -9011,7 +9011,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G298" t="n">
-        <v>5.06470537185669</v>
+        <v>5.06470489501953</v>
       </c>
       <c r="H298" t="n">
         <v>39937</v>
@@ -9040,7 +9040,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>4.93555068969727</v>
+        <v>4.93555021286011</v>
       </c>
       <c r="H299" t="n">
         <v>1763</v>
@@ -9069,7 +9069,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G300" t="n">
-        <v>4.95400094985962</v>
+        <v>4.95400142669678</v>
       </c>
       <c r="H300" t="n">
         <v>25268</v>
@@ -9127,7 +9127,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G302" t="n">
-        <v>4.94477605819702</v>
+        <v>4.94477558135986</v>
       </c>
       <c r="H302" t="n">
         <v>8210</v>
@@ -9156,7 +9156,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G303" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H303" t="n">
         <v>700</v>
@@ -9185,7 +9185,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G304" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H304" t="n">
         <v>3145</v>
@@ -9243,7 +9243,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G306" t="n">
-        <v>4.94477605819702</v>
+        <v>4.94477558135986</v>
       </c>
       <c r="H306" t="n">
         <v>69945</v>
@@ -9272,7 +9272,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G307" t="n">
-        <v>4.93555068969727</v>
+        <v>4.93555021286011</v>
       </c>
       <c r="H307" t="n">
         <v>1214</v>
@@ -9301,7 +9301,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>4.76949453353882</v>
+        <v>4.76949501037598</v>
       </c>
       <c r="H308" t="n">
         <v>7904</v>
@@ -9359,7 +9359,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G310" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H310" t="n">
         <v>1967</v>
@@ -9388,7 +9388,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G311" t="n">
-        <v>4.81562089920044</v>
+        <v>4.8156213760376</v>
       </c>
       <c r="H311" t="n">
         <v>3343</v>
@@ -9417,7 +9417,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G312" t="n">
-        <v>4.76949453353882</v>
+        <v>4.76949501037598</v>
       </c>
       <c r="H312" t="n">
         <v>4994</v>
@@ -9562,7 +9562,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G317" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H317" t="n">
         <v>31544</v>
@@ -9591,7 +9591,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G318" t="n">
-        <v>4.87097358703613</v>
+        <v>4.87097311019897</v>
       </c>
       <c r="H318" t="n">
         <v>7990</v>
@@ -9620,7 +9620,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G319" t="n">
-        <v>5.06470537185669</v>
+        <v>5.06470489501953</v>
       </c>
       <c r="H319" t="n">
         <v>4244</v>
@@ -9649,7 +9649,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>4.88019847869873</v>
+        <v>4.88019895553589</v>
       </c>
       <c r="H320" t="n">
         <v>6441</v>
@@ -9707,7 +9707,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G322" t="n">
-        <v>4.87097358703613</v>
+        <v>4.87097311019897</v>
       </c>
       <c r="H322" t="n">
         <v>10071</v>
@@ -9736,7 +9736,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G323" t="n">
-        <v>4.94477605819702</v>
+        <v>4.94477558135986</v>
       </c>
       <c r="H323" t="n">
         <v>1845</v>
@@ -9852,7 +9852,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G327" t="n">
-        <v>4.81562089920044</v>
+        <v>4.8156213760376</v>
       </c>
       <c r="H327" t="n">
         <v>123</v>
@@ -9910,7 +9910,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G329" t="n">
-        <v>4.79717111587524</v>
+        <v>4.79717063903809</v>
       </c>
       <c r="H329" t="n">
         <v>5909</v>
@@ -9939,7 +9939,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>4.79717111587524</v>
+        <v>4.79717063903809</v>
       </c>
       <c r="H330" t="n">
         <v>445</v>
@@ -9968,7 +9968,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G331" t="n">
-        <v>4.9909029006958</v>
+        <v>4.99090242385864</v>
       </c>
       <c r="H331" t="n">
         <v>1655</v>
@@ -9997,7 +9997,7 @@
         <v>5.5</v>
       </c>
       <c r="G332" t="n">
-        <v>5.0739312171936</v>
+        <v>5.07393074035645</v>
       </c>
       <c r="H332" t="n">
         <v>10755</v>
@@ -10055,7 +10055,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G334" t="n">
-        <v>5.10160684585571</v>
+        <v>5.10160732269287</v>
       </c>
       <c r="H334" t="n">
         <v>10899</v>
@@ -10113,7 +10113,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G336" t="n">
-        <v>5.06470537185669</v>
+        <v>5.06470489501953</v>
       </c>
       <c r="H336" t="n">
         <v>610</v>
@@ -10142,7 +10142,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G337" t="n">
-        <v>4.9170994758606</v>
+        <v>4.91709995269775</v>
       </c>
       <c r="H337" t="n">
         <v>5020</v>
@@ -10229,7 +10229,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G340" t="n">
-        <v>4.907874584198</v>
+        <v>4.90787506103516</v>
       </c>
       <c r="H340" t="n">
         <v>9032</v>
@@ -10258,7 +10258,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G341" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H341" t="n">
         <v>6351</v>
@@ -10287,7 +10287,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G342" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H342" t="n">
         <v>1223</v>
@@ -10316,7 +10316,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G343" t="n">
-        <v>4.93555068969727</v>
+        <v>4.93555021286011</v>
       </c>
       <c r="H343" t="n">
         <v>1750</v>
@@ -10374,7 +10374,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G345" t="n">
-        <v>4.86174821853638</v>
+        <v>4.86174774169922</v>
       </c>
       <c r="H345" t="n">
         <v>3141</v>
@@ -10461,7 +10461,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G348" t="n">
-        <v>4.52963590621948</v>
+        <v>4.52963638305664</v>
       </c>
       <c r="H348" t="n">
         <v>9810</v>
@@ -10606,7 +10606,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G353" t="n">
-        <v>4.88019847869873</v>
+        <v>4.88019895553589</v>
       </c>
       <c r="H353" t="n">
         <v>1026</v>
@@ -10635,7 +10635,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G354" t="n">
-        <v>5.01857900619507</v>
+        <v>5.01857852935791</v>
       </c>
       <c r="H354" t="n">
         <v>1901</v>
@@ -10664,7 +10664,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>5.01857900619507</v>
+        <v>5.01857852935791</v>
       </c>
       <c r="H355" t="n">
         <v>7480</v>
@@ -10693,7 +10693,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G356" t="n">
-        <v>5.01857900619507</v>
+        <v>5.01857852935791</v>
       </c>
       <c r="H356" t="n">
         <v>7610</v>
@@ -10722,7 +10722,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G357" t="n">
-        <v>5.01857900619507</v>
+        <v>5.01857852935791</v>
       </c>
       <c r="H357" t="n">
         <v>1202</v>
@@ -10954,7 +10954,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G365" t="n">
-        <v>4.94477605819702</v>
+        <v>4.94477558135986</v>
       </c>
       <c r="H365" t="n">
         <v>3500</v>
@@ -11070,7 +11070,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G369" t="n">
-        <v>5.0923810005188</v>
+        <v>5.09238195419312</v>
       </c>
       <c r="H369" t="n">
         <v>37466</v>
@@ -11099,7 +11099,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G370" t="n">
-        <v>5.20308542251587</v>
+        <v>5.20308494567871</v>
       </c>
       <c r="H370" t="n">
         <v>5557</v>
@@ -11128,7 +11128,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G371" t="n">
-        <v>5.33224010467529</v>
+        <v>5.33224058151245</v>
       </c>
       <c r="H371" t="n">
         <v>27751</v>
@@ -11331,7 +11331,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G378" t="n">
-        <v>5.25843667984009</v>
+        <v>5.25843715667725</v>
       </c>
       <c r="H378" t="n">
         <v>4491</v>
@@ -11360,7 +11360,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G379" t="n">
-        <v>5.25843667984009</v>
+        <v>5.25843715667725</v>
       </c>
       <c r="H379" t="n">
         <v>270</v>
@@ -11418,7 +11418,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>5.24876976013184</v>
+        <v>5.24876928329468</v>
       </c>
       <c r="H381" t="n">
         <v>20743</v>
@@ -11505,7 +11505,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G384" t="n">
-        <v>5.473717212677</v>
+        <v>5.47371673583984</v>
       </c>
       <c r="H384" t="n">
         <v>4634</v>
@@ -11563,7 +11563,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G386" t="n">
-        <v>5.60493564605713</v>
+        <v>5.60493612289429</v>
       </c>
       <c r="H386" t="n">
         <v>24572</v>
@@ -11592,7 +11592,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G387" t="n">
-        <v>5.66117238998413</v>
+        <v>5.66117286682129</v>
       </c>
       <c r="H387" t="n">
         <v>23023</v>
@@ -11679,7 +11679,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H390" t="n">
         <v>24702</v>
@@ -11708,7 +11708,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G391" t="n">
-        <v>5.24876976013184</v>
+        <v>5.24876928329468</v>
       </c>
       <c r="H391" t="n">
         <v>7298</v>
@@ -11737,7 +11737,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G392" t="n">
-        <v>5.24876976013184</v>
+        <v>5.24876928329468</v>
       </c>
       <c r="H392" t="n">
         <v>2740</v>
@@ -11766,7 +11766,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G393" t="n">
-        <v>5.24876976013184</v>
+        <v>5.24876928329468</v>
       </c>
       <c r="H393" t="n">
         <v>16929</v>
@@ -11795,7 +11795,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G394" t="n">
-        <v>5.32375192642212</v>
+        <v>5.32375144958496</v>
       </c>
       <c r="H394" t="n">
         <v>680</v>
@@ -11882,7 +11882,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G397" t="n">
-        <v>5.473717212677</v>
+        <v>5.47371673583984</v>
       </c>
       <c r="H397" t="n">
         <v>2362</v>
@@ -11911,7 +11911,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>5.58619022369385</v>
+        <v>5.58619070053101</v>
       </c>
       <c r="H398" t="n">
         <v>3700</v>
@@ -12056,7 +12056,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G403" t="n">
-        <v>5.58619022369385</v>
+        <v>5.58619070053101</v>
       </c>
       <c r="H403" t="n">
         <v>430</v>
@@ -12114,7 +12114,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H405" t="n">
         <v>1418</v>
@@ -12288,7 +12288,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H411" t="n">
         <v>200</v>
@@ -12404,7 +12404,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H415" t="n">
         <v>100</v>
@@ -12433,7 +12433,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G416" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H416" t="n">
         <v>45</v>
@@ -12520,7 +12520,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G419" t="n">
-        <v>5.473717212677</v>
+        <v>5.47371673583984</v>
       </c>
       <c r="H419" t="n">
         <v>560</v>
@@ -12549,7 +12549,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G420" t="n">
-        <v>5.473717212677</v>
+        <v>5.47371673583984</v>
       </c>
       <c r="H420" t="n">
         <v>10242</v>
@@ -12607,7 +12607,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G422" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H422" t="n">
         <v>18970</v>
@@ -12665,7 +12665,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G424" t="n">
-        <v>5.45497131347656</v>
+        <v>5.4549708366394</v>
       </c>
       <c r="H424" t="n">
         <v>8384</v>
@@ -12752,7 +12752,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G427" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H427" t="n">
         <v>4203</v>
@@ -12781,7 +12781,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G428" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H428" t="n">
         <v>760</v>
@@ -12955,7 +12955,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G434" t="n">
-        <v>5.473717212677</v>
+        <v>5.47371673583984</v>
       </c>
       <c r="H434" t="n">
         <v>170</v>
@@ -13042,7 +13042,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H437" t="n">
         <v>7332</v>
@@ -13071,7 +13071,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H438" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H444" t="n">
         <v>10</v>
@@ -13332,7 +13332,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G447" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H447" t="n">
         <v>20</v>
@@ -13361,7 +13361,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G448" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H448" t="n">
         <v>2255</v>
@@ -13390,7 +13390,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G449" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H449" t="n">
         <v>300</v>
@@ -13448,7 +13448,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G451" t="n">
-        <v>5.32375192642212</v>
+        <v>5.32375144958496</v>
       </c>
       <c r="H451" t="n">
         <v>924</v>
@@ -13477,7 +13477,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G452" t="n">
-        <v>5.32375192642212</v>
+        <v>5.32375144958496</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G453" t="n">
-        <v>5.32375192642212</v>
+        <v>5.32375144958496</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13593,7 +13593,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G456" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H456" t="n">
         <v>20122</v>
@@ -13622,7 +13622,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G457" t="n">
-        <v>5.473717212677</v>
+        <v>5.47371673583984</v>
       </c>
       <c r="H457" t="n">
         <v>3375</v>
@@ -13999,7 +13999,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G470" t="n">
-        <v>5.24876976013184</v>
+        <v>5.24876928329468</v>
       </c>
       <c r="H470" t="n">
         <v>2437</v>
@@ -14173,7 +14173,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G476" t="n">
-        <v>5.02382230758667</v>
+        <v>5.02382278442383</v>
       </c>
       <c r="H476" t="n">
         <v>311</v>
@@ -14202,7 +14202,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G477" t="n">
-        <v>4.93009424209595</v>
+        <v>4.93009471893311</v>
       </c>
       <c r="H477" t="n">
         <v>5511</v>
@@ -14289,7 +14289,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G480" t="n">
-        <v>4.7988748550415</v>
+        <v>4.79887437820435</v>
       </c>
       <c r="H480" t="n">
         <v>900</v>
@@ -14318,7 +14318,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H481" t="n">
         <v>16552</v>
@@ -14347,7 +14347,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G482" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H482" t="n">
         <v>1000</v>
@@ -14376,7 +14376,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G483" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14405,7 +14405,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G484" t="n">
-        <v>4.78012895584106</v>
+        <v>4.78012943267822</v>
       </c>
       <c r="H484" t="n">
         <v>250</v>
@@ -14492,7 +14492,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G487" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H487" t="n">
         <v>1050</v>
@@ -14579,7 +14579,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>4.64891052246094</v>
+        <v>4.64891004562378</v>
       </c>
       <c r="H490" t="n">
         <v>2650</v>
@@ -14666,7 +14666,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G493" t="n">
-        <v>4.5645546913147</v>
+        <v>4.56455421447754</v>
       </c>
       <c r="H493" t="n">
         <v>1016</v>
@@ -14695,7 +14695,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G494" t="n">
-        <v>4.64891052246094</v>
+        <v>4.64891004562378</v>
       </c>
       <c r="H494" t="n">
         <v>21434</v>
@@ -14811,7 +14811,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G498" t="n">
-        <v>4.6770281791687</v>
+        <v>4.67702865600586</v>
       </c>
       <c r="H498" t="n">
         <v>3536</v>
@@ -14840,7 +14840,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G499" t="n">
-        <v>4.78012895584106</v>
+        <v>4.78012943267822</v>
       </c>
       <c r="H499" t="n">
         <v>12994</v>
@@ -14898,7 +14898,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>4.83636617660522</v>
+        <v>4.83636569976807</v>
       </c>
       <c r="H501" t="n">
         <v>9387</v>
@@ -14956,7 +14956,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G503" t="n">
-        <v>4.87385749816895</v>
+        <v>4.87385654449463</v>
       </c>
       <c r="H503" t="n">
         <v>15019</v>
@@ -15043,7 +15043,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G506" t="n">
-        <v>4.78012895584106</v>
+        <v>4.78012943267822</v>
       </c>
       <c r="H506" t="n">
         <v>2350</v>
@@ -15072,7 +15072,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>4.78012895584106</v>
+        <v>4.78012943267822</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -15101,7 +15101,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G508" t="n">
-        <v>4.7988748550415</v>
+        <v>4.79887437820435</v>
       </c>
       <c r="H508" t="n">
         <v>80250</v>
@@ -15188,7 +15188,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G511" t="n">
-        <v>5.02382230758667</v>
+        <v>5.02382278442383</v>
       </c>
       <c r="H511" t="n">
         <v>4402</v>
@@ -15217,7 +15217,7 @@
         <v>5.5</v>
       </c>
       <c r="G512" t="n">
-        <v>5.15504121780396</v>
+        <v>5.15504169464111</v>
       </c>
       <c r="H512" t="n">
         <v>4203</v>
@@ -15275,7 +15275,7 @@
         <v>5.5</v>
       </c>
       <c r="G514" t="n">
-        <v>5.15504121780396</v>
+        <v>5.15504169464111</v>
       </c>
       <c r="H514" t="n">
         <v>1884</v>
@@ -15304,7 +15304,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G515" t="n">
-        <v>5.00507640838623</v>
+        <v>5.00507688522339</v>
       </c>
       <c r="H515" t="n">
         <v>632</v>
@@ -15333,7 +15333,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G516" t="n">
-        <v>5.00507640838623</v>
+        <v>5.00507688522339</v>
       </c>
       <c r="H516" t="n">
         <v>0</v>
@@ -15391,7 +15391,7 @@
         <v>5.5</v>
       </c>
       <c r="G518" t="n">
-        <v>5.15504121780396</v>
+        <v>5.15504169464111</v>
       </c>
       <c r="H518" t="n">
         <v>6482</v>
@@ -15449,7 +15449,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G520" t="n">
-        <v>5.02382230758667</v>
+        <v>5.02382278442383</v>
       </c>
       <c r="H520" t="n">
         <v>1669</v>
@@ -15536,7 +15536,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G523" t="n">
-        <v>4.96758508682251</v>
+        <v>4.96758556365967</v>
       </c>
       <c r="H523" t="n">
         <v>560</v>
@@ -15594,7 +15594,7 @@
         <v>5.5</v>
       </c>
       <c r="G525" t="n">
-        <v>5.15504121780396</v>
+        <v>5.15504169464111</v>
       </c>
       <c r="H525" t="n">
         <v>3840</v>
@@ -15710,7 +15710,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G529" t="n">
-        <v>4.87385749816895</v>
+        <v>4.87385654449463</v>
       </c>
       <c r="H529" t="n">
         <v>22898</v>
@@ -15797,7 +15797,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G532" t="n">
-        <v>4.78012895584106</v>
+        <v>4.78012943267822</v>
       </c>
       <c r="H532" t="n">
         <v>121</v>
@@ -15855,7 +15855,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G534" t="n">
-        <v>4.87385749816895</v>
+        <v>4.87385654449463</v>
       </c>
       <c r="H534" t="n">
         <v>2718</v>
@@ -15884,7 +15884,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>4.87385749816895</v>
+        <v>4.87385654449463</v>
       </c>
       <c r="H535" t="n">
         <v>12616</v>
@@ -15942,7 +15942,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G537" t="n">
-        <v>4.78012895584106</v>
+        <v>4.78012943267822</v>
       </c>
       <c r="H537" t="n">
         <v>5650</v>
@@ -15971,7 +15971,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G538" t="n">
-        <v>4.7988748550415</v>
+        <v>4.79887437820435</v>
       </c>
       <c r="H538" t="n">
         <v>11050</v>
@@ -16029,7 +16029,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G540" t="n">
-        <v>4.78012895584106</v>
+        <v>4.78012943267822</v>
       </c>
       <c r="H540" t="n">
         <v>250</v>
@@ -16058,7 +16058,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G541" t="n">
-        <v>4.87385749816895</v>
+        <v>4.87385654449463</v>
       </c>
       <c r="H541" t="n">
         <v>1794</v>
@@ -16087,7 +16087,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G542" t="n">
-        <v>4.93009424209595</v>
+        <v>4.93009471893311</v>
       </c>
       <c r="H542" t="n">
         <v>2795</v>
@@ -16116,7 +16116,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G543" t="n">
-        <v>4.87385749816895</v>
+        <v>4.87385654449463</v>
       </c>
       <c r="H543" t="n">
         <v>4438</v>
@@ -16145,7 +16145,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G544" t="n">
-        <v>4.7988748550415</v>
+        <v>4.79887437820435</v>
       </c>
       <c r="H544" t="n">
         <v>1500</v>
@@ -16203,7 +16203,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G546" t="n">
-        <v>4.78012895584106</v>
+        <v>4.78012943267822</v>
       </c>
       <c r="H546" t="n">
         <v>3803</v>
@@ -16232,7 +16232,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G547" t="n">
-        <v>4.78012895584106</v>
+        <v>4.78012943267822</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G548" t="n">
-        <v>4.78012895584106</v>
+        <v>4.78012943267822</v>
       </c>
       <c r="H548" t="n">
         <v>0</v>
@@ -16290,7 +16290,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G549" t="n">
-        <v>4.74263763427734</v>
+        <v>4.7426381111145</v>
       </c>
       <c r="H549" t="n">
         <v>400</v>
@@ -16377,7 +16377,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H552" t="n">
         <v>2770</v>
@@ -16464,7 +16464,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H555" t="n">
         <v>1730</v>
@@ -16609,7 +16609,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>4.59267282485962</v>
+        <v>4.59267330169678</v>
       </c>
       <c r="H560" t="n">
         <v>2062</v>
@@ -16638,7 +16638,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G561" t="n">
-        <v>4.59267282485962</v>
+        <v>4.59267330169678</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -16667,7 +16667,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G562" t="n">
-        <v>4.7988748550415</v>
+        <v>4.79887437820435</v>
       </c>
       <c r="H562" t="n">
         <v>5341</v>
@@ -16696,7 +16696,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G563" t="n">
-        <v>4.83636617660522</v>
+        <v>4.83636569976807</v>
       </c>
       <c r="H563" t="n">
         <v>5514</v>
@@ -16725,7 +16725,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G564" t="n">
-        <v>4.98633098602295</v>
+        <v>4.98633146286011</v>
       </c>
       <c r="H564" t="n">
         <v>4495</v>
@@ -16957,7 +16957,7 @@
         <v>4.25</v>
       </c>
       <c r="G572" t="n">
-        <v>3.98344135284424</v>
+        <v>3.9834406375885</v>
       </c>
       <c r="H572" t="n">
         <v>9140</v>
@@ -17334,7 +17334,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G585" t="n">
-        <v>4.00218677520752</v>
+        <v>4.00218629837036</v>
       </c>
       <c r="H585" t="n">
         <v>1475</v>
@@ -17363,7 +17363,7 @@
         <v>4.25</v>
       </c>
       <c r="G586" t="n">
-        <v>3.98344135284424</v>
+        <v>3.9834406375885</v>
       </c>
       <c r="H586" t="n">
         <v>2353</v>
@@ -17392,7 +17392,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G587" t="n">
-        <v>3.92720437049866</v>
+        <v>3.92720413208008</v>
       </c>
       <c r="H587" t="n">
         <v>1105</v>
@@ -17566,7 +17566,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G593" t="n">
-        <v>4.03967761993408</v>
+        <v>4.03967809677124</v>
       </c>
       <c r="H593" t="n">
         <v>12527</v>
@@ -17595,7 +17595,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G594" t="n">
-        <v>4.00218677520752</v>
+        <v>4.00218629837036</v>
       </c>
       <c r="H594" t="n">
         <v>22055</v>
@@ -17682,7 +17682,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G597" t="n">
-        <v>4.06779670715332</v>
+        <v>4.06779623031616</v>
       </c>
       <c r="H597" t="n">
         <v>2200</v>
@@ -17711,7 +17711,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G598" t="n">
-        <v>4.10528802871704</v>
+        <v>4.10528755187988</v>
       </c>
       <c r="H598" t="n">
         <v>5102</v>
@@ -17740,7 +17740,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G599" t="n">
-        <v>4.10528802871704</v>
+        <v>4.10528755187988</v>
       </c>
       <c r="H599" t="n">
         <v>4178</v>
@@ -17769,7 +17769,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G600" t="n">
-        <v>4.10528802871704</v>
+        <v>4.10528755187988</v>
       </c>
       <c r="H600" t="n">
         <v>2406</v>
@@ -17856,7 +17856,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G603" t="n">
-        <v>4.10528802871704</v>
+        <v>4.10528755187988</v>
       </c>
       <c r="H603" t="n">
         <v>5008</v>
@@ -17885,7 +17885,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G604" t="n">
-        <v>4.10528802871704</v>
+        <v>4.10528755187988</v>
       </c>
       <c r="H604" t="n">
         <v>7230</v>
@@ -17972,7 +17972,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G607" t="n">
-        <v>4.1334056854248</v>
+        <v>4.13340616226196</v>
       </c>
       <c r="H607" t="n">
         <v>55370</v>
@@ -18001,7 +18001,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G608" t="n">
-        <v>4.12403297424316</v>
+        <v>4.12403345108032</v>
       </c>
       <c r="H608" t="n">
         <v>2894</v>
@@ -18030,7 +18030,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G609" t="n">
-        <v>4.00218677520752</v>
+        <v>4.00218629837036</v>
       </c>
       <c r="H609" t="n">
         <v>1958</v>
@@ -18059,7 +18059,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G610" t="n">
-        <v>4.00218677520752</v>
+        <v>4.00218629837036</v>
       </c>
       <c r="H610" t="n">
         <v>2262</v>
@@ -18088,7 +18088,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G611" t="n">
-        <v>4.05842351913452</v>
+        <v>4.05842399597168</v>
       </c>
       <c r="H611" t="n">
         <v>2515</v>
@@ -18117,7 +18117,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>4.09591436386108</v>
+        <v>4.09591484069824</v>
       </c>
       <c r="H612" t="n">
         <v>401</v>
@@ -18146,7 +18146,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G613" t="n">
-        <v>4.09591436386108</v>
+        <v>4.09591484069824</v>
       </c>
       <c r="H613" t="n">
         <v>0</v>
@@ -18175,7 +18175,7 @@
         <v>4.25</v>
       </c>
       <c r="G614" t="n">
-        <v>3.98344135284424</v>
+        <v>3.9834406375885</v>
       </c>
       <c r="H614" t="n">
         <v>2924</v>
@@ -18204,7 +18204,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G615" t="n">
-        <v>4.03967761993408</v>
+        <v>4.03967809677124</v>
       </c>
       <c r="H615" t="n">
         <v>320</v>
@@ -18233,7 +18233,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G616" t="n">
-        <v>3.92720437049866</v>
+        <v>3.92720413208008</v>
       </c>
       <c r="H616" t="n">
         <v>3977</v>
@@ -18262,7 +18262,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G617" t="n">
-        <v>3.87096738815308</v>
+        <v>3.87096762657166</v>
       </c>
       <c r="H617" t="n">
         <v>5257</v>
@@ -18639,7 +18639,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G630" t="n">
-        <v>3.68351125717163</v>
+        <v>3.68351149559021</v>
       </c>
       <c r="H630" t="n">
         <v>9933</v>
@@ -18668,7 +18668,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G631" t="n">
-        <v>3.66476583480835</v>
+        <v>3.66476607322693</v>
       </c>
       <c r="H631" t="n">
         <v>2461</v>
@@ -18697,7 +18697,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G632" t="n">
-        <v>3.64602017402649</v>
+        <v>3.64602041244507</v>
       </c>
       <c r="H632" t="n">
         <v>3650</v>
@@ -18755,7 +18755,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G634" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H634" t="n">
         <v>3900</v>
@@ -18784,7 +18784,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G635" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H635" t="n">
         <v>6237</v>
@@ -18813,7 +18813,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G636" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H636" t="n">
         <v>7752</v>
@@ -18842,7 +18842,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G637" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H637" t="n">
         <v>1500</v>
@@ -18871,7 +18871,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G638" t="n">
-        <v>3.71341013908386</v>
+        <v>3.71341037750244</v>
       </c>
       <c r="H638" t="n">
         <v>8760</v>
@@ -18900,7 +18900,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G639" t="n">
-        <v>3.71341013908386</v>
+        <v>3.71341037750244</v>
       </c>
       <c r="H639" t="n">
         <v>0</v>
@@ -18929,7 +18929,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G640" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H640" t="n">
         <v>1052</v>
@@ -18958,7 +18958,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G641" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H641" t="n">
         <v>10</v>
@@ -18987,7 +18987,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G642" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H642" t="n">
         <v>90</v>
@@ -19103,7 +19103,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G646" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H646" t="n">
         <v>13400</v>
@@ -19190,7 +19190,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G649" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H649" t="n">
         <v>4153</v>
@@ -19248,7 +19248,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G651" t="n">
-        <v>3.65583825111389</v>
+        <v>3.65583801269531</v>
       </c>
       <c r="H651" t="n">
         <v>900</v>
@@ -19277,7 +19277,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>3.65583825111389</v>
+        <v>3.65583801269531</v>
       </c>
       <c r="H652" t="n">
         <v>10</v>
@@ -19335,7 +19335,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G654" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H654" t="n">
         <v>3015</v>
@@ -19393,7 +19393,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G656" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H656" t="n">
         <v>3182</v>
@@ -19422,7 +19422,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H657" t="n">
         <v>1517</v>
@@ -19480,7 +19480,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G659" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H659" t="n">
         <v>100</v>
@@ -19509,7 +19509,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G660" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H660" t="n">
         <v>299</v>
@@ -19538,7 +19538,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G661" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H661" t="n">
         <v>1404</v>
@@ -19567,7 +19567,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G662" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H662" t="n">
         <v>0</v>
@@ -19625,7 +19625,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G664" t="n">
-        <v>3.72300577163696</v>
+        <v>3.72300601005554</v>
       </c>
       <c r="H664" t="n">
         <v>800</v>
@@ -19712,7 +19712,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>4.12601137161255</v>
+        <v>4.12601184844971</v>
       </c>
       <c r="H667" t="n">
         <v>45390</v>
@@ -19770,7 +19770,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G669" t="n">
-        <v>4.12601137161255</v>
+        <v>4.12601184844971</v>
       </c>
       <c r="H669" t="n">
         <v>8487</v>
@@ -19799,7 +19799,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G670" t="n">
-        <v>4.12601137161255</v>
+        <v>4.12601184844971</v>
       </c>
       <c r="H670" t="n">
         <v>2970</v>
@@ -19973,7 +19973,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G676" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H676" t="n">
         <v>1500</v>
@@ -20089,7 +20089,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G680" t="n">
-        <v>4.02046251296997</v>
+        <v>4.02046203613281</v>
       </c>
       <c r="H680" t="n">
         <v>1420</v>
@@ -20118,7 +20118,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G681" t="n">
-        <v>3.99167633056641</v>
+        <v>3.99167609214783</v>
       </c>
       <c r="H681" t="n">
         <v>1555</v>
@@ -20176,7 +20176,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G683" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H683" t="n">
         <v>10</v>
@@ -20205,7 +20205,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H684" t="n">
         <v>9595</v>
@@ -20292,7 +20292,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G687" t="n">
-        <v>3.99167633056641</v>
+        <v>3.99167609214783</v>
       </c>
       <c r="H687" t="n">
         <v>750</v>
@@ -20321,7 +20321,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G688" t="n">
-        <v>3.99167633056641</v>
+        <v>3.99167609214783</v>
       </c>
       <c r="H688" t="n">
         <v>0</v>
@@ -20350,7 +20350,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G689" t="n">
-        <v>3.98208069801331</v>
+        <v>3.98208093643188</v>
       </c>
       <c r="H689" t="n">
         <v>150</v>
@@ -20379,7 +20379,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>4.03965330123901</v>
+        <v>4.03965282440186</v>
       </c>
       <c r="H690" t="n">
         <v>1160</v>
@@ -20408,7 +20408,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>4.03965330123901</v>
+        <v>4.03965282440186</v>
       </c>
       <c r="H691" t="n">
         <v>10</v>
@@ -20437,7 +20437,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H692" t="n">
         <v>11</v>
@@ -20466,7 +20466,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G693" t="n">
-        <v>4.03965330123901</v>
+        <v>4.03965282440186</v>
       </c>
       <c r="H693" t="n">
         <v>1069</v>
@@ -20524,7 +20524,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G695" t="n">
-        <v>3.98208069801331</v>
+        <v>3.98208093643188</v>
       </c>
       <c r="H695" t="n">
         <v>1981</v>
@@ -20553,7 +20553,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>3.98208069801331</v>
+        <v>3.98208093643188</v>
       </c>
       <c r="H696" t="n">
         <v>0</v>
@@ -20582,7 +20582,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>3.98208069801331</v>
+        <v>3.98208093643188</v>
       </c>
       <c r="H697" t="n">
         <v>120</v>
@@ -20611,7 +20611,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G698" t="n">
-        <v>4.02046251296997</v>
+        <v>4.02046203613281</v>
       </c>
       <c r="H698" t="n">
         <v>245</v>
@@ -20669,7 +20669,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G700" t="n">
-        <v>3.94369959831238</v>
+        <v>3.9436993598938</v>
       </c>
       <c r="H700" t="n">
         <v>210</v>
@@ -20698,7 +20698,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G701" t="n">
-        <v>3.94369959831238</v>
+        <v>3.9436993598938</v>
       </c>
       <c r="H701" t="n">
         <v>280</v>
@@ -20930,7 +20930,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G709" t="n">
-        <v>3.87653183937073</v>
+        <v>3.87653160095215</v>
       </c>
       <c r="H709" t="n">
         <v>1788</v>
@@ -21017,7 +21017,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G712" t="n">
-        <v>3.9341037273407</v>
+        <v>3.93410396575928</v>
       </c>
       <c r="H712" t="n">
         <v>3931</v>
@@ -21046,7 +21046,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G713" t="n">
-        <v>3.84774565696716</v>
+        <v>3.84774589538574</v>
       </c>
       <c r="H713" t="n">
         <v>5760</v>
@@ -21075,7 +21075,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G714" t="n">
-        <v>3.79017329216003</v>
+        <v>3.79017353057861</v>
       </c>
       <c r="H714" t="n">
         <v>185</v>
@@ -21104,7 +21104,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G715" t="n">
-        <v>3.77098250389099</v>
+        <v>3.77098274230957</v>
       </c>
       <c r="H715" t="n">
         <v>540</v>
@@ -21133,7 +21133,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G716" t="n">
-        <v>3.75179171562195</v>
+        <v>3.75179195404053</v>
       </c>
       <c r="H716" t="n">
         <v>330</v>
@@ -21162,7 +21162,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G717" t="n">
-        <v>3.75179171562195</v>
+        <v>3.75179195404053</v>
       </c>
       <c r="H717" t="n">
         <v>0</v>
@@ -21191,7 +21191,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G718" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H718" t="n">
         <v>20488</v>
@@ -21249,7 +21249,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G720" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H720" t="n">
         <v>1602</v>
@@ -21336,7 +21336,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>3.91491317749023</v>
+        <v>3.91491341590881</v>
       </c>
       <c r="H723" t="n">
         <v>750</v>
@@ -21365,7 +21365,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G724" t="n">
-        <v>4.21236944198608</v>
+        <v>4.21236991882324</v>
       </c>
       <c r="H724" t="n">
         <v>46988</v>
@@ -21423,7 +21423,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G726" t="n">
-        <v>4.21236944198608</v>
+        <v>4.21236991882324</v>
       </c>
       <c r="H726" t="n">
         <v>70435</v>
@@ -21481,7 +21481,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G728" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H728" t="n">
         <v>172</v>
@@ -21597,7 +21597,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G732" t="n">
-        <v>4.18358421325684</v>
+        <v>4.18358373641968</v>
       </c>
       <c r="H732" t="n">
         <v>1320</v>
@@ -21742,7 +21742,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G737" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H737" t="n">
         <v>1637</v>
@@ -21771,7 +21771,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G738" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H738" t="n">
         <v>75279</v>
@@ -21800,7 +21800,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G739" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H739" t="n">
         <v>0</v>
@@ -21829,7 +21829,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G740" t="n">
-        <v>3.99167633056641</v>
+        <v>3.99167609214783</v>
       </c>
       <c r="H740" t="n">
         <v>7953</v>
@@ -21974,7 +21974,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G745" t="n">
-        <v>3.9341037273407</v>
+        <v>3.93410396575928</v>
       </c>
       <c r="H745" t="n">
         <v>81270</v>
@@ -22003,7 +22003,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G746" t="n">
-        <v>3.9341037273407</v>
+        <v>3.93410396575928</v>
       </c>
       <c r="H746" t="n">
         <v>3945</v>
@@ -22032,7 +22032,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>3.91491317749023</v>
+        <v>3.91491341590881</v>
       </c>
       <c r="H747" t="n">
         <v>196255</v>
@@ -22119,7 +22119,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G750" t="n">
-        <v>4.05884408950806</v>
+        <v>4.0588436126709</v>
       </c>
       <c r="H750" t="n">
         <v>1996</v>
@@ -22148,7 +22148,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G751" t="n">
-        <v>3.98208069801331</v>
+        <v>3.98208093643188</v>
       </c>
       <c r="H751" t="n">
         <v>7044</v>
@@ -22206,7 +22206,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G753" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H753" t="n">
         <v>7875</v>
@@ -22235,7 +22235,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>4.03965330123901</v>
+        <v>4.03965282440186</v>
       </c>
       <c r="H754" t="n">
         <v>498</v>
@@ -22264,7 +22264,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G755" t="n">
-        <v>3.91491317749023</v>
+        <v>3.91491341590881</v>
       </c>
       <c r="H755" t="n">
         <v>21081</v>
@@ -22641,7 +22641,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>3.63664746284485</v>
+        <v>3.63664722442627</v>
       </c>
       <c r="H768" t="n">
         <v>8155</v>
@@ -22670,7 +22670,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G769" t="n">
-        <v>3.61745667457581</v>
+        <v>3.61745643615723</v>
       </c>
       <c r="H769" t="n">
         <v>19701</v>
@@ -22786,7 +22786,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G773" t="n">
-        <v>3.61745667457581</v>
+        <v>3.61745643615723</v>
       </c>
       <c r="H773" t="n">
         <v>16809</v>
@@ -22902,7 +22902,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>3.63664746284485</v>
+        <v>3.63664722442627</v>
       </c>
       <c r="H777" t="n">
         <v>23488</v>
@@ -22931,7 +22931,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G778" t="n">
-        <v>3.63664746284485</v>
+        <v>3.63664722442627</v>
       </c>
       <c r="H778" t="n">
         <v>5020</v>
@@ -23105,7 +23105,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G784" t="n">
-        <v>3.40635824203491</v>
+        <v>3.40635848045349</v>
       </c>
       <c r="H784" t="n">
         <v>13684</v>
@@ -23192,7 +23192,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H787" t="n">
         <v>1420</v>
@@ -23221,7 +23221,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G788" t="n">
-        <v>3.65583825111389</v>
+        <v>3.65583801269531</v>
       </c>
       <c r="H788" t="n">
         <v>1250</v>
@@ -23627,7 +23627,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G802" t="n">
-        <v>3.53109812736511</v>
+        <v>3.53109836578369</v>
       </c>
       <c r="H802" t="n">
         <v>18225</v>
@@ -23772,7 +23772,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G807" t="n">
-        <v>3.53109812736511</v>
+        <v>3.53109836578369</v>
       </c>
       <c r="H807" t="n">
         <v>6020</v>
@@ -23801,7 +23801,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>3.55988454818726</v>
+        <v>3.55988430976868</v>
       </c>
       <c r="H808" t="n">
         <v>5589</v>
@@ -23859,7 +23859,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G810" t="n">
-        <v>3.60786128044128</v>
+        <v>3.60786104202271</v>
       </c>
       <c r="H810" t="n">
         <v>35932</v>
@@ -23888,7 +23888,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G811" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H811" t="n">
         <v>3848</v>
@@ -23917,7 +23917,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G812" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H812" t="n">
         <v>10695</v>
@@ -23946,7 +23946,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G813" t="n">
-        <v>3.71341013908386</v>
+        <v>3.71341037750244</v>
       </c>
       <c r="H813" t="n">
         <v>3973</v>
@@ -23975,7 +23975,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G814" t="n">
-        <v>3.79017329216003</v>
+        <v>3.79017353057861</v>
       </c>
       <c r="H814" t="n">
         <v>8700</v>
@@ -24004,7 +24004,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G815" t="n">
-        <v>3.75179171562195</v>
+        <v>3.75179195404053</v>
       </c>
       <c r="H815" t="n">
         <v>4141</v>
@@ -24091,7 +24091,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>3.91491317749023</v>
+        <v>3.91491341590881</v>
       </c>
       <c r="H818" t="n">
         <v>4284</v>
@@ -24120,7 +24120,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G819" t="n">
-        <v>4.25075101852417</v>
+        <v>4.25075149536133</v>
       </c>
       <c r="H819" t="n">
         <v>51273</v>
@@ -24236,7 +24236,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G823" t="n">
-        <v>4.25075101852417</v>
+        <v>4.25075149536133</v>
       </c>
       <c r="H823" t="n">
         <v>21761</v>
@@ -24265,7 +24265,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G824" t="n">
-        <v>4.29872846603394</v>
+        <v>4.29872798919678</v>
       </c>
       <c r="H824" t="n">
         <v>12287</v>
@@ -24352,7 +24352,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G827" t="n">
-        <v>4.26994180679321</v>
+        <v>4.26994228363037</v>
       </c>
       <c r="H827" t="n">
         <v>3147</v>
@@ -24613,7 +24613,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G836" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H836" t="n">
         <v>440</v>
@@ -24642,7 +24642,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G837" t="n">
-        <v>4.12601137161255</v>
+        <v>4.12601184844971</v>
       </c>
       <c r="H837" t="n">
         <v>1700</v>
@@ -24874,7 +24874,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G845" t="n">
-        <v>4.12601137161255</v>
+        <v>4.12601184844971</v>
       </c>
       <c r="H845" t="n">
         <v>1616</v>
@@ -24903,7 +24903,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G846" t="n">
-        <v>4.12601137161255</v>
+        <v>4.12601184844971</v>
       </c>
       <c r="H846" t="n">
         <v>0</v>
@@ -25193,7 +25193,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G856" t="n">
-        <v>4.21236944198608</v>
+        <v>4.21236991882324</v>
       </c>
       <c r="H856" t="n">
         <v>12800</v>
@@ -25251,7 +25251,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G858" t="n">
-        <v>4.02046251296997</v>
+        <v>4.02046203613281</v>
       </c>
       <c r="H858" t="n">
         <v>3537</v>
@@ -25309,7 +25309,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G860" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H860" t="n">
         <v>2994</v>
@@ -25338,7 +25338,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G861" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H861" t="n">
         <v>280</v>
@@ -25657,7 +25657,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G872" t="n">
-        <v>3.91491317749023</v>
+        <v>3.91491341590881</v>
       </c>
       <c r="H872" t="n">
         <v>1409</v>
@@ -25686,7 +25686,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G873" t="n">
-        <v>3.91491317749023</v>
+        <v>3.91491341590881</v>
       </c>
       <c r="H873" t="n">
         <v>4382</v>
@@ -25831,7 +25831,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G878" t="n">
-        <v>3.97248530387878</v>
+        <v>3.97248554229736</v>
       </c>
       <c r="H878" t="n">
         <v>850</v>
@@ -25860,7 +25860,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G879" t="n">
-        <v>3.94369959831238</v>
+        <v>3.9436993598938</v>
       </c>
       <c r="H879" t="n">
         <v>3403</v>
@@ -25889,7 +25889,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G880" t="n">
-        <v>3.99167633056641</v>
+        <v>3.99167609214783</v>
       </c>
       <c r="H880" t="n">
         <v>17094</v>
@@ -25918,7 +25918,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G881" t="n">
-        <v>3.97248530387878</v>
+        <v>3.97248554229736</v>
       </c>
       <c r="H881" t="n">
         <v>7211</v>
@@ -26005,7 +26005,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G884" t="n">
-        <v>3.98208069801331</v>
+        <v>3.98208093643188</v>
       </c>
       <c r="H884" t="n">
         <v>2973</v>
@@ -36799,6 +36799,35 @@
         <v>3612</v>
       </c>
       <c r="I1256" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1257" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1257" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="D1257" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="E1257" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="F1257" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="G1257" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="H1257" t="n">
+        <v>1260</v>
+      </c>
+      <c r="I1257" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RFG.MI.xlsx
+++ b/data/RFG.MI.xlsx
@@ -427,7 +427,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2" t="n">
-        <v>4.62868022918701</v>
+        <v>4.62868070602417</v>
       </c>
       <c r="H2" t="n">
         <v>355635</v>
@@ -485,7 +485,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G4" t="n">
-        <v>4.40178442001343</v>
+        <v>4.40178394317627</v>
       </c>
       <c r="H4" t="n">
         <v>167566</v>
@@ -514,7 +514,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G5" t="n">
-        <v>4.30648803710938</v>
+        <v>4.30648756027222</v>
       </c>
       <c r="H5" t="n">
         <v>223483</v>
@@ -572,7 +572,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>4.35640573501587</v>
+        <v>4.35640525817871</v>
       </c>
       <c r="H7" t="n">
         <v>53988</v>
@@ -630,7 +630,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G9" t="n">
-        <v>4.07505369186401</v>
+        <v>4.07505416870117</v>
       </c>
       <c r="H9" t="n">
         <v>88738</v>
@@ -688,7 +688,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G11" t="n">
-        <v>4.17488813400269</v>
+        <v>4.17488861083984</v>
       </c>
       <c r="H11" t="n">
         <v>49843</v>
@@ -746,7 +746,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>4.17488813400269</v>
+        <v>4.17488861083984</v>
       </c>
       <c r="H13" t="n">
         <v>29293</v>
@@ -891,7 +891,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G18" t="n">
-        <v>4.32463979721069</v>
+        <v>4.32463932037354</v>
       </c>
       <c r="H18" t="n">
         <v>32335</v>
@@ -1036,7 +1036,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G23" t="n">
-        <v>4.75574207305908</v>
+        <v>4.75574159622192</v>
       </c>
       <c r="H23" t="n">
         <v>42090</v>
@@ -1065,7 +1065,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G24" t="n">
-        <v>4.82834911346436</v>
+        <v>4.82834959030151</v>
       </c>
       <c r="H24" t="n">
         <v>64828</v>
@@ -1094,7 +1094,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>4.84650039672852</v>
+        <v>4.84650087356567</v>
       </c>
       <c r="H25" t="n">
         <v>24608</v>
@@ -1123,7 +1123,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G26" t="n">
-        <v>4.84650039672852</v>
+        <v>4.84650087356567</v>
       </c>
       <c r="H26" t="n">
         <v>84199</v>
@@ -1152,7 +1152,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>4.95541095733643</v>
+        <v>4.95541048049927</v>
       </c>
       <c r="H27" t="n">
         <v>26232</v>
@@ -1297,7 +1297,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G32" t="n">
-        <v>5.43643045425415</v>
+        <v>5.43642997741699</v>
       </c>
       <c r="H32" t="n">
         <v>36811</v>
@@ -1326,7 +1326,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G33" t="n">
-        <v>5.43643045425415</v>
+        <v>5.43642997741699</v>
       </c>
       <c r="H33" t="n">
         <v>30706</v>
@@ -1413,7 +1413,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G36" t="n">
-        <v>5.33659601211548</v>
+        <v>5.33659648895264</v>
       </c>
       <c r="H36" t="n">
         <v>16617</v>
@@ -1442,7 +1442,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>5.25491428375244</v>
+        <v>5.25491333007812</v>
       </c>
       <c r="H37" t="n">
         <v>23662</v>
@@ -1471,7 +1471,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G38" t="n">
-        <v>5.31844472885132</v>
+        <v>5.31844520568848</v>
       </c>
       <c r="H38" t="n">
         <v>24272</v>
@@ -1500,7 +1500,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G39" t="n">
-        <v>5.36382389068604</v>
+        <v>5.36382341384888</v>
       </c>
       <c r="H39" t="n">
         <v>8885</v>
@@ -1529,7 +1529,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G40" t="n">
-        <v>5.30936908721924</v>
+        <v>5.30936813354492</v>
       </c>
       <c r="H40" t="n">
         <v>10863</v>
@@ -1587,7 +1587,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>5.3819751739502</v>
+        <v>5.38197565078735</v>
       </c>
       <c r="H42" t="n">
         <v>10599</v>
@@ -1616,7 +1616,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G43" t="n">
-        <v>5.42735481262207</v>
+        <v>5.42735433578491</v>
       </c>
       <c r="H43" t="n">
         <v>24833</v>
@@ -1645,7 +1645,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G44" t="n">
-        <v>5.32751989364624</v>
+        <v>5.3275203704834</v>
       </c>
       <c r="H44" t="n">
         <v>29103</v>
@@ -1732,7 +1732,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>5.26398992538452</v>
+        <v>5.26398944854736</v>
       </c>
       <c r="H47" t="n">
         <v>26913</v>
@@ -1906,7 +1906,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G53" t="n">
-        <v>5.03709363937378</v>
+        <v>5.03709411621094</v>
       </c>
       <c r="H53" t="n">
         <v>29429</v>
@@ -1964,7 +1964,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G55" t="n">
-        <v>5.0552453994751</v>
+        <v>5.05524444580078</v>
       </c>
       <c r="H55" t="n">
         <v>23049</v>
@@ -1993,7 +1993,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G56" t="n">
-        <v>4.94633531570435</v>
+        <v>4.94633483886719</v>
       </c>
       <c r="H56" t="n">
         <v>4077</v>
@@ -2051,7 +2051,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G58" t="n">
-        <v>4.86465215682983</v>
+        <v>4.86465167999268</v>
       </c>
       <c r="H58" t="n">
         <v>10871</v>
@@ -2080,7 +2080,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G59" t="n">
-        <v>4.87372779846191</v>
+        <v>4.87372827529907</v>
       </c>
       <c r="H59" t="n">
         <v>60004</v>
@@ -2138,7 +2138,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G61" t="n">
-        <v>4.92818355560303</v>
+        <v>4.92818307876587</v>
       </c>
       <c r="H61" t="n">
         <v>10150</v>
@@ -2167,7 +2167,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G62" t="n">
-        <v>4.83742475509644</v>
+        <v>4.83742523193359</v>
       </c>
       <c r="H62" t="n">
         <v>13006</v>
@@ -2283,7 +2283,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G66" t="n">
-        <v>4.63775634765625</v>
+        <v>4.63775682449341</v>
       </c>
       <c r="H66" t="n">
         <v>9021</v>
@@ -2370,7 +2370,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>4.87372779846191</v>
+        <v>4.87372827529907</v>
       </c>
       <c r="H69" t="n">
         <v>20469</v>
@@ -2486,7 +2486,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G73" t="n">
-        <v>4.84650039672852</v>
+        <v>4.84650087356567</v>
       </c>
       <c r="H73" t="n">
         <v>6837</v>
@@ -2515,7 +2515,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G74" t="n">
-        <v>4.78296947479248</v>
+        <v>4.78296995162964</v>
       </c>
       <c r="H74" t="n">
         <v>4082</v>
@@ -2573,7 +2573,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>4.51977014541626</v>
+        <v>4.51977062225342</v>
       </c>
       <c r="H76" t="n">
         <v>20769</v>
@@ -2631,7 +2631,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G78" t="n">
-        <v>4.13404655456543</v>
+        <v>4.13404703140259</v>
       </c>
       <c r="H78" t="n">
         <v>12171</v>
@@ -2747,7 +2747,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G82" t="n">
-        <v>4.02059888839722</v>
+        <v>4.02059841156006</v>
       </c>
       <c r="H82" t="n">
         <v>47987</v>
@@ -2776,7 +2776,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G83" t="n">
-        <v>3.99337196350098</v>
+        <v>3.99337124824524</v>
       </c>
       <c r="H83" t="n">
         <v>14139</v>
@@ -2805,7 +2805,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G84" t="n">
-        <v>4.01152324676514</v>
+        <v>4.01152276992798</v>
       </c>
       <c r="H84" t="n">
         <v>13008</v>
@@ -2834,7 +2834,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>4.03421306610107</v>
+        <v>4.03421258926392</v>
       </c>
       <c r="H85" t="n">
         <v>9318</v>
@@ -2892,7 +2892,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G87" t="n">
-        <v>4.21119165420532</v>
+        <v>4.21119117736816</v>
       </c>
       <c r="H87" t="n">
         <v>12593</v>
@@ -2921,7 +2921,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G88" t="n">
-        <v>4.47892904281616</v>
+        <v>4.47892951965332</v>
       </c>
       <c r="H88" t="n">
         <v>20559</v>
@@ -3008,7 +3008,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G91" t="n">
-        <v>4.48346662521362</v>
+        <v>4.48346710205078</v>
       </c>
       <c r="H91" t="n">
         <v>5261</v>
@@ -3037,7 +3037,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G92" t="n">
-        <v>4.53338432312012</v>
+        <v>4.53338384628296</v>
       </c>
       <c r="H92" t="n">
         <v>1969</v>
@@ -3095,7 +3095,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G94" t="n">
-        <v>4.50615644454956</v>
+        <v>4.50615692138672</v>
       </c>
       <c r="H94" t="n">
         <v>2116</v>
@@ -3124,7 +3124,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>4.51977014541626</v>
+        <v>4.51977062225342</v>
       </c>
       <c r="H95" t="n">
         <v>243259</v>
@@ -3153,7 +3153,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>4.51977014541626</v>
+        <v>4.51977062225342</v>
       </c>
       <c r="H96" t="n">
         <v>4515</v>
@@ -3211,7 +3211,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G98" t="n">
-        <v>4.41086053848267</v>
+        <v>4.41086006164551</v>
       </c>
       <c r="H98" t="n">
         <v>2735</v>
@@ -3298,7 +3298,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G101" t="n">
-        <v>4.35640573501587</v>
+        <v>4.35640525817871</v>
       </c>
       <c r="H101" t="n">
         <v>2000</v>
@@ -3327,7 +3327,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G102" t="n">
-        <v>4.35640573501587</v>
+        <v>4.35640525817871</v>
       </c>
       <c r="H102" t="n">
         <v>1155</v>
@@ -3356,7 +3356,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G103" t="n">
-        <v>4.34732961654663</v>
+        <v>4.34732913970947</v>
       </c>
       <c r="H103" t="n">
         <v>12517</v>
@@ -3443,7 +3443,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G106" t="n">
-        <v>4.42901182174683</v>
+        <v>4.42901229858398</v>
       </c>
       <c r="H106" t="n">
         <v>317</v>
@@ -3501,7 +3501,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>4.34732961654663</v>
+        <v>4.34732913970947</v>
       </c>
       <c r="H108" t="n">
         <v>5476</v>
@@ -3530,7 +3530,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G109" t="n">
-        <v>4.40632247924805</v>
+        <v>4.40632200241089</v>
       </c>
       <c r="H109" t="n">
         <v>2660</v>
@@ -3588,7 +3588,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G111" t="n">
-        <v>4.43808746337891</v>
+        <v>4.43808794021606</v>
       </c>
       <c r="H111" t="n">
         <v>941</v>
@@ -3617,7 +3617,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G112" t="n">
-        <v>4.33825397491455</v>
+        <v>4.33825349807739</v>
       </c>
       <c r="H112" t="n">
         <v>5545</v>
@@ -3675,7 +3675,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G114" t="n">
-        <v>4.46531534194946</v>
+        <v>4.4653148651123</v>
       </c>
       <c r="H114" t="n">
         <v>2900</v>
@@ -3733,7 +3733,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G116" t="n">
-        <v>4.29287433624268</v>
+        <v>4.29287385940552</v>
       </c>
       <c r="H116" t="n">
         <v>5190</v>
@@ -3820,7 +3820,7 @@
         <v>4.75</v>
       </c>
       <c r="G119" t="n">
-        <v>4.31102609634399</v>
+        <v>4.31102561950684</v>
       </c>
       <c r="H119" t="n">
         <v>635</v>
@@ -3849,7 +3849,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G120" t="n">
-        <v>3.88446092605591</v>
+        <v>3.88446187973022</v>
       </c>
       <c r="H120" t="n">
         <v>37503</v>
@@ -3878,7 +3878,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G121" t="n">
-        <v>3.81639266014099</v>
+        <v>3.81639242172241</v>
       </c>
       <c r="H121" t="n">
         <v>9794</v>
@@ -3907,7 +3907,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>3.89807462692261</v>
+        <v>3.89807510375977</v>
       </c>
       <c r="H122" t="n">
         <v>1318</v>
@@ -3936,7 +3936,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G123" t="n">
-        <v>3.88446092605591</v>
+        <v>3.88446187973022</v>
       </c>
       <c r="H123" t="n">
         <v>3695</v>
@@ -3965,7 +3965,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G124" t="n">
-        <v>3.88446092605591</v>
+        <v>3.88446187973022</v>
       </c>
       <c r="H124" t="n">
         <v>7707</v>
@@ -4052,7 +4052,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G127" t="n">
-        <v>4.21597480773926</v>
+        <v>4.21597528457642</v>
       </c>
       <c r="H127" t="n">
         <v>26910</v>
@@ -4081,7 +4081,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G128" t="n">
-        <v>4.29900312423706</v>
+        <v>4.2990026473999</v>
       </c>
       <c r="H128" t="n">
         <v>9321</v>
@@ -4168,7 +4168,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G131" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H131" t="n">
         <v>15380</v>
@@ -4197,7 +4197,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G132" t="n">
-        <v>4.24365139007568</v>
+        <v>4.24365091323853</v>
       </c>
       <c r="H132" t="n">
         <v>3060</v>
@@ -4226,7 +4226,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G133" t="n">
-        <v>4.32667875289917</v>
+        <v>4.32667922973633</v>
       </c>
       <c r="H133" t="n">
         <v>10570</v>
@@ -4284,7 +4284,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G135" t="n">
-        <v>4.37280559539795</v>
+        <v>4.37280607223511</v>
       </c>
       <c r="H135" t="n">
         <v>4000</v>
@@ -4342,7 +4342,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G137" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H137" t="n">
         <v>3650</v>
@@ -4371,7 +4371,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G138" t="n">
-        <v>4.28516483306885</v>
+        <v>4.28516530990601</v>
       </c>
       <c r="H138" t="n">
         <v>7384</v>
@@ -4400,7 +4400,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G139" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H139" t="n">
         <v>2000</v>
@@ -4429,7 +4429,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G140" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>4.24826335906982</v>
+        <v>4.24826431274414</v>
       </c>
       <c r="H141" t="n">
         <v>1470</v>
@@ -4516,7 +4516,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G143" t="n">
-        <v>4.2067494392395</v>
+        <v>4.20674991607666</v>
       </c>
       <c r="H143" t="n">
         <v>17151</v>
@@ -4574,7 +4574,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G145" t="n">
-        <v>4.05453252792358</v>
+        <v>4.05453205108643</v>
       </c>
       <c r="H145" t="n">
         <v>90396</v>
@@ -4632,7 +4632,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>3.89770102500916</v>
+        <v>3.89770126342773</v>
       </c>
       <c r="H147" t="n">
         <v>8340</v>
@@ -4661,7 +4661,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766615867615</v>
       </c>
       <c r="H148" t="n">
         <v>2849</v>
@@ -4690,7 +4690,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G149" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766615867615</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G150" t="n">
-        <v>4.04069423675537</v>
+        <v>4.04069375991821</v>
       </c>
       <c r="H150" t="n">
         <v>36</v>
@@ -4748,7 +4748,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>4.1052713394165</v>
+        <v>4.10527086257935</v>
       </c>
       <c r="H151" t="n">
         <v>124</v>
@@ -4806,7 +4806,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G153" t="n">
-        <v>3.98534202575684</v>
+        <v>3.98534250259399</v>
       </c>
       <c r="H153" t="n">
         <v>8687</v>
@@ -4835,7 +4835,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G154" t="n">
-        <v>3.92999005317688</v>
+        <v>3.9299898147583</v>
       </c>
       <c r="H154" t="n">
         <v>5428</v>
@@ -4893,7 +4893,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G156" t="n">
-        <v>4.05914497375488</v>
+        <v>4.05914449691772</v>
       </c>
       <c r="H156" t="n">
         <v>120</v>
@@ -4980,7 +4980,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G159" t="n">
-        <v>3.82851123809814</v>
+        <v>3.82851147651672</v>
       </c>
       <c r="H159" t="n">
         <v>11901</v>
@@ -5096,7 +5096,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G163" t="n">
-        <v>3.82851123809814</v>
+        <v>3.82851147651672</v>
       </c>
       <c r="H163" t="n">
         <v>5720</v>
@@ -5125,7 +5125,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G164" t="n">
-        <v>3.83773636817932</v>
+        <v>3.8377366065979</v>
       </c>
       <c r="H164" t="n">
         <v>2438</v>
@@ -5212,7 +5212,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>3.89770102500916</v>
+        <v>3.89770126342773</v>
       </c>
       <c r="H167" t="n">
         <v>205</v>
@@ -5241,7 +5241,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G168" t="n">
-        <v>3.98534202575684</v>
+        <v>3.98534250259399</v>
       </c>
       <c r="H168" t="n">
         <v>5404</v>
@@ -5270,7 +5270,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>3.925377368927</v>
+        <v>3.92537713050842</v>
       </c>
       <c r="H169" t="n">
         <v>2375</v>
@@ -5299,7 +5299,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G170" t="n">
-        <v>3.92999005317688</v>
+        <v>3.9299898147583</v>
       </c>
       <c r="H170" t="n">
         <v>10150</v>
@@ -5386,7 +5386,7 @@
         <v>4.39499998092651</v>
       </c>
       <c r="G173" t="n">
-        <v>4.05453252792358</v>
+        <v>4.05453205108643</v>
       </c>
       <c r="H173" t="n">
         <v>6047</v>
@@ -5473,7 +5473,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G176" t="n">
-        <v>3.95305275917053</v>
+        <v>3.95305299758911</v>
       </c>
       <c r="H176" t="n">
         <v>1056</v>
@@ -5531,7 +5531,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>3.8838632106781</v>
+        <v>3.88386297225952</v>
       </c>
       <c r="H178" t="n">
         <v>5254</v>
@@ -5589,7 +5589,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G180" t="n">
-        <v>3.82851123809814</v>
+        <v>3.82851147651672</v>
       </c>
       <c r="H180" t="n">
         <v>6092</v>
@@ -5618,7 +5618,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G181" t="n">
-        <v>3.83773636817932</v>
+        <v>3.8377366065979</v>
       </c>
       <c r="H181" t="n">
         <v>5582</v>
@@ -5676,7 +5676,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G183" t="n">
-        <v>3.8838632106781</v>
+        <v>3.88386297225952</v>
       </c>
       <c r="H183" t="n">
         <v>11079</v>
@@ -5879,7 +5879,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>3.8838632106781</v>
+        <v>3.88386297225952</v>
       </c>
       <c r="H190" t="n">
         <v>1237</v>
@@ -5937,7 +5937,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766615867615</v>
       </c>
       <c r="H192" t="n">
         <v>3183</v>
@@ -5966,7 +5966,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G193" t="n">
-        <v>4.0130181312561</v>
+        <v>4.01301765441895</v>
       </c>
       <c r="H193" t="n">
         <v>82</v>
@@ -5995,7 +5995,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G194" t="n">
-        <v>4.00379228591919</v>
+        <v>4.00379276275635</v>
       </c>
       <c r="H194" t="n">
         <v>1199</v>
@@ -6024,7 +6024,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>3.99456715583801</v>
+        <v>3.99456739425659</v>
       </c>
       <c r="H195" t="n">
         <v>131</v>
@@ -6053,7 +6053,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G196" t="n">
-        <v>3.86541271209717</v>
+        <v>3.86541247367859</v>
       </c>
       <c r="H196" t="n">
         <v>5890</v>
@@ -6082,7 +6082,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G197" t="n">
-        <v>3.94844031333923</v>
+        <v>3.94844055175781</v>
       </c>
       <c r="H197" t="n">
         <v>2149</v>
@@ -6140,7 +6140,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G199" t="n">
-        <v>3.92999005317688</v>
+        <v>3.9299898147583</v>
       </c>
       <c r="H199" t="n">
         <v>2982</v>
@@ -6227,7 +6227,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G202" t="n">
-        <v>4.05914497375488</v>
+        <v>4.05914449691772</v>
       </c>
       <c r="H202" t="n">
         <v>7141</v>
@@ -6285,7 +6285,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G204" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766615867615</v>
       </c>
       <c r="H204" t="n">
         <v>5370</v>
@@ -6314,7 +6314,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G205" t="n">
-        <v>3.87925052642822</v>
+        <v>3.87925100326538</v>
       </c>
       <c r="H205" t="n">
         <v>3705</v>
@@ -6343,7 +6343,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G206" t="n">
-        <v>3.94844031333923</v>
+        <v>3.94844055175781</v>
       </c>
       <c r="H206" t="n">
         <v>5295</v>
@@ -6401,7 +6401,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>3.90231370925903</v>
+        <v>3.90231418609619</v>
       </c>
       <c r="H208" t="n">
         <v>1430</v>
@@ -6488,7 +6488,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G211" t="n">
-        <v>3.94844031333923</v>
+        <v>3.94844055175781</v>
       </c>
       <c r="H211" t="n">
         <v>5037</v>
@@ -6517,7 +6517,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G212" t="n">
-        <v>3.87002563476562</v>
+        <v>3.87002539634705</v>
       </c>
       <c r="H212" t="n">
         <v>3149</v>
@@ -6546,7 +6546,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>3.8838632106781</v>
+        <v>3.88386297225952</v>
       </c>
       <c r="H213" t="n">
         <v>1793</v>
@@ -6575,7 +6575,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G214" t="n">
-        <v>3.8838632106781</v>
+        <v>3.88386297225952</v>
       </c>
       <c r="H214" t="n">
         <v>63</v>
@@ -6633,7 +6633,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>3.94382762908936</v>
+        <v>3.94382834434509</v>
       </c>
       <c r="H216" t="n">
         <v>1</v>
@@ -6720,7 +6720,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G219" t="n">
-        <v>3.82851123809814</v>
+        <v>3.82851147651672</v>
       </c>
       <c r="H219" t="n">
         <v>650</v>
@@ -6749,7 +6749,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>3.82851123809814</v>
+        <v>3.82851147651672</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G221" t="n">
-        <v>3.79161024093628</v>
+        <v>3.7916100025177</v>
       </c>
       <c r="H221" t="n">
         <v>3006</v>
@@ -6807,7 +6807,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G222" t="n">
-        <v>3.82851123809814</v>
+        <v>3.82851147651672</v>
       </c>
       <c r="H222" t="n">
         <v>400</v>
@@ -6836,7 +6836,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G223" t="n">
-        <v>4.04069423675537</v>
+        <v>4.04069375991821</v>
       </c>
       <c r="H223" t="n">
         <v>36447</v>
@@ -6865,7 +6865,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G224" t="n">
-        <v>4.1052713394165</v>
+        <v>4.10527086257935</v>
       </c>
       <c r="H224" t="n">
         <v>7165</v>
@@ -6894,7 +6894,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>4.0130181312561</v>
+        <v>4.01301765441895</v>
       </c>
       <c r="H225" t="n">
         <v>1000</v>
@@ -6923,7 +6923,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G226" t="n">
-        <v>4.24365139007568</v>
+        <v>4.24365091323853</v>
       </c>
       <c r="H226" t="n">
         <v>14277</v>
@@ -6981,7 +6981,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G228" t="n">
-        <v>4.14217185974121</v>
+        <v>4.14217233657837</v>
       </c>
       <c r="H228" t="n">
         <v>6907</v>
@@ -7097,7 +7097,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G232" t="n">
-        <v>4.21597480773926</v>
+        <v>4.21597528457642</v>
       </c>
       <c r="H232" t="n">
         <v>7962</v>
@@ -7126,7 +7126,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G233" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H233" t="n">
         <v>12462</v>
@@ -7155,7 +7155,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H234" t="n">
         <v>15005</v>
@@ -7184,7 +7184,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G235" t="n">
-        <v>4.37280559539795</v>
+        <v>4.37280607223511</v>
       </c>
       <c r="H235" t="n">
         <v>17132</v>
@@ -7213,7 +7213,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>4.45583391189575</v>
+        <v>4.45583343505859</v>
       </c>
       <c r="H236" t="n">
         <v>4300</v>
@@ -7242,7 +7242,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G237" t="n">
-        <v>4.47428417205811</v>
+        <v>4.47428464889526</v>
       </c>
       <c r="H237" t="n">
         <v>567</v>
@@ -7300,7 +7300,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G239" t="n">
-        <v>4.46505928039551</v>
+        <v>4.46505880355835</v>
       </c>
       <c r="H239" t="n">
         <v>1590</v>
@@ -7358,7 +7358,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G241" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H241" t="n">
         <v>1200</v>
@@ -7503,7 +7503,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G246" t="n">
-        <v>4.35435485839844</v>
+        <v>4.35435438156128</v>
       </c>
       <c r="H246" t="n">
         <v>2400</v>
@@ -7619,7 +7619,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G250" t="n">
-        <v>4.37280559539795</v>
+        <v>4.37280607223511</v>
       </c>
       <c r="H250" t="n">
         <v>241</v>
@@ -7648,7 +7648,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G251" t="n">
-        <v>4.35435485839844</v>
+        <v>4.35435438156128</v>
       </c>
       <c r="H251" t="n">
         <v>1595</v>
@@ -7677,7 +7677,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G252" t="n">
-        <v>4.26210117340088</v>
+        <v>4.26210165023804</v>
       </c>
       <c r="H252" t="n">
         <v>330</v>
@@ -7793,7 +7793,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G256" t="n">
-        <v>4.52041101455688</v>
+        <v>4.52041149139404</v>
       </c>
       <c r="H256" t="n">
         <v>9927</v>
@@ -7851,7 +7851,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G258" t="n">
-        <v>4.51118516921997</v>
+        <v>4.51118564605713</v>
       </c>
       <c r="H258" t="n">
         <v>22611</v>
@@ -7967,7 +7967,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G262" t="n">
-        <v>4.74181890487671</v>
+        <v>4.74181842803955</v>
       </c>
       <c r="H262" t="n">
         <v>8453</v>
@@ -7996,7 +7996,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G263" t="n">
-        <v>4.89864921569824</v>
+        <v>4.8986496925354</v>
       </c>
       <c r="H263" t="n">
         <v>29512</v>
@@ -8025,7 +8025,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G264" t="n">
-        <v>4.88019895553589</v>
+        <v>4.88019847869873</v>
       </c>
       <c r="H264" t="n">
         <v>69249</v>
@@ -8141,7 +8141,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G268" t="n">
-        <v>5.02780437469482</v>
+        <v>5.02780342102051</v>
       </c>
       <c r="H268" t="n">
         <v>4916</v>
@@ -8170,7 +8170,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G269" t="n">
-        <v>4.90787506103516</v>
+        <v>4.907874584198</v>
       </c>
       <c r="H269" t="n">
         <v>54096</v>
@@ -8199,7 +8199,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G270" t="n">
-        <v>4.93555021286011</v>
+        <v>4.93555068969727</v>
       </c>
       <c r="H270" t="n">
         <v>78819</v>
@@ -8228,7 +8228,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G271" t="n">
-        <v>4.89864921569824</v>
+        <v>4.8986496925354</v>
       </c>
       <c r="H271" t="n">
         <v>10062</v>
@@ -8663,7 +8663,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G286" t="n">
-        <v>5.09238195419312</v>
+        <v>5.0923810005188</v>
       </c>
       <c r="H286" t="n">
         <v>233</v>
@@ -8750,7 +8750,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>5.14773321151733</v>
+        <v>5.14773368835449</v>
       </c>
       <c r="H289" t="n">
         <v>160</v>
@@ -8837,7 +8837,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G292" t="n">
-        <v>5.14773321151733</v>
+        <v>5.14773368835449</v>
       </c>
       <c r="H292" t="n">
         <v>14959</v>
@@ -8953,7 +8953,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G296" t="n">
-        <v>4.90787506103516</v>
+        <v>4.907874584198</v>
       </c>
       <c r="H296" t="n">
         <v>14673</v>
@@ -9011,7 +9011,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G298" t="n">
-        <v>5.06470489501953</v>
+        <v>5.06470537185669</v>
       </c>
       <c r="H298" t="n">
         <v>39937</v>
@@ -9040,7 +9040,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>4.93555021286011</v>
+        <v>4.93555068969727</v>
       </c>
       <c r="H299" t="n">
         <v>1763</v>
@@ -9098,7 +9098,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G301" t="n">
-        <v>4.89864921569824</v>
+        <v>4.8986496925354</v>
       </c>
       <c r="H301" t="n">
         <v>49432</v>
@@ -9127,7 +9127,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G302" t="n">
-        <v>4.94477558135986</v>
+        <v>4.94477605819702</v>
       </c>
       <c r="H302" t="n">
         <v>8210</v>
@@ -9156,7 +9156,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G303" t="n">
-        <v>4.92632532119751</v>
+        <v>4.92632579803467</v>
       </c>
       <c r="H303" t="n">
         <v>700</v>
@@ -9185,7 +9185,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G304" t="n">
-        <v>4.92632532119751</v>
+        <v>4.92632579803467</v>
       </c>
       <c r="H304" t="n">
         <v>3145</v>
@@ -9243,7 +9243,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G306" t="n">
-        <v>4.94477558135986</v>
+        <v>4.94477605819702</v>
       </c>
       <c r="H306" t="n">
         <v>69945</v>
@@ -9272,7 +9272,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G307" t="n">
-        <v>4.93555021286011</v>
+        <v>4.93555068969727</v>
       </c>
       <c r="H307" t="n">
         <v>1214</v>
@@ -9301,7 +9301,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>4.76949501037598</v>
+        <v>4.76949453353882</v>
       </c>
       <c r="H308" t="n">
         <v>7904</v>
@@ -9330,7 +9330,7 @@
         <v>5.25</v>
       </c>
       <c r="G309" t="n">
-        <v>4.84329748153687</v>
+        <v>4.84329700469971</v>
       </c>
       <c r="H309" t="n">
         <v>995</v>
@@ -9359,7 +9359,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G310" t="n">
-        <v>4.92632532119751</v>
+        <v>4.92632579803467</v>
       </c>
       <c r="H310" t="n">
         <v>1967</v>
@@ -9388,7 +9388,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G311" t="n">
-        <v>4.8156213760376</v>
+        <v>4.81562089920044</v>
       </c>
       <c r="H311" t="n">
         <v>3343</v>
@@ -9417,7 +9417,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G312" t="n">
-        <v>4.76949501037598</v>
+        <v>4.76949453353882</v>
       </c>
       <c r="H312" t="n">
         <v>4994</v>
@@ -9533,7 +9533,7 @@
         <v>5.25</v>
       </c>
       <c r="G316" t="n">
-        <v>4.84329748153687</v>
+        <v>4.84329700469971</v>
       </c>
       <c r="H316" t="n">
         <v>16</v>
@@ -9562,7 +9562,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G317" t="n">
-        <v>4.92632532119751</v>
+        <v>4.92632579803467</v>
       </c>
       <c r="H317" t="n">
         <v>31544</v>
@@ -9591,7 +9591,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G318" t="n">
-        <v>4.87097311019897</v>
+        <v>4.87097358703613</v>
       </c>
       <c r="H318" t="n">
         <v>7990</v>
@@ -9620,7 +9620,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G319" t="n">
-        <v>5.06470489501953</v>
+        <v>5.06470537185669</v>
       </c>
       <c r="H319" t="n">
         <v>4244</v>
@@ -9649,7 +9649,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>4.88019895553589</v>
+        <v>4.88019847869873</v>
       </c>
       <c r="H320" t="n">
         <v>6441</v>
@@ -9707,7 +9707,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G322" t="n">
-        <v>4.87097311019897</v>
+        <v>4.87097358703613</v>
       </c>
       <c r="H322" t="n">
         <v>10071</v>
@@ -9736,7 +9736,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G323" t="n">
-        <v>4.94477558135986</v>
+        <v>4.94477605819702</v>
       </c>
       <c r="H323" t="n">
         <v>1845</v>
@@ -9765,7 +9765,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G324" t="n">
-        <v>5.04625463485718</v>
+        <v>5.04625415802002</v>
       </c>
       <c r="H324" t="n">
         <v>3919</v>
@@ -9852,7 +9852,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G327" t="n">
-        <v>4.8156213760376</v>
+        <v>4.81562089920044</v>
       </c>
       <c r="H327" t="n">
         <v>123</v>
@@ -9910,7 +9910,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G329" t="n">
-        <v>4.79717063903809</v>
+        <v>4.79717111587524</v>
       </c>
       <c r="H329" t="n">
         <v>5909</v>
@@ -9939,7 +9939,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>4.79717063903809</v>
+        <v>4.79717111587524</v>
       </c>
       <c r="H330" t="n">
         <v>445</v>
@@ -10113,7 +10113,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G336" t="n">
-        <v>5.06470489501953</v>
+        <v>5.06470537185669</v>
       </c>
       <c r="H336" t="n">
         <v>610</v>
@@ -10229,7 +10229,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G340" t="n">
-        <v>4.90787506103516</v>
+        <v>4.907874584198</v>
       </c>
       <c r="H340" t="n">
         <v>9032</v>
@@ -10258,7 +10258,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G341" t="n">
-        <v>4.92632532119751</v>
+        <v>4.92632579803467</v>
       </c>
       <c r="H341" t="n">
         <v>6351</v>
@@ -10287,7 +10287,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G342" t="n">
-        <v>4.92632532119751</v>
+        <v>4.92632579803467</v>
       </c>
       <c r="H342" t="n">
         <v>1223</v>
@@ -10316,7 +10316,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G343" t="n">
-        <v>4.93555021286011</v>
+        <v>4.93555068969727</v>
       </c>
       <c r="H343" t="n">
         <v>1750</v>
@@ -10374,7 +10374,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G345" t="n">
-        <v>4.86174774169922</v>
+        <v>4.86174869537354</v>
       </c>
       <c r="H345" t="n">
         <v>3141</v>
@@ -10432,7 +10432,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G347" t="n">
-        <v>4.70491743087769</v>
+        <v>4.70491695404053</v>
       </c>
       <c r="H347" t="n">
         <v>10502</v>
@@ -10461,7 +10461,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G348" t="n">
-        <v>4.52963638305664</v>
+        <v>4.52963590621948</v>
       </c>
       <c r="H348" t="n">
         <v>9810</v>
@@ -10577,7 +10577,7 @@
         <v>5.25</v>
       </c>
       <c r="G352" t="n">
-        <v>4.84329748153687</v>
+        <v>4.84329700469971</v>
       </c>
       <c r="H352" t="n">
         <v>15431</v>
@@ -10606,7 +10606,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G353" t="n">
-        <v>4.88019895553589</v>
+        <v>4.88019847869873</v>
       </c>
       <c r="H353" t="n">
         <v>1026</v>
@@ -10954,7 +10954,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G365" t="n">
-        <v>4.94477558135986</v>
+        <v>4.94477605819702</v>
       </c>
       <c r="H365" t="n">
         <v>3500</v>
@@ -11041,7 +11041,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G368" t="n">
-        <v>5.14773321151733</v>
+        <v>5.14773368835449</v>
       </c>
       <c r="H368" t="n">
         <v>5393</v>
@@ -11070,7 +11070,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G369" t="n">
-        <v>5.09238195419312</v>
+        <v>5.0923810005188</v>
       </c>
       <c r="H369" t="n">
         <v>37466</v>
@@ -11099,7 +11099,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G370" t="n">
-        <v>5.20308494567871</v>
+        <v>5.20308542251587</v>
       </c>
       <c r="H370" t="n">
         <v>5557</v>
@@ -11128,7 +11128,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G371" t="n">
-        <v>5.33224058151245</v>
+        <v>5.33224010467529</v>
       </c>
       <c r="H371" t="n">
         <v>27751</v>
@@ -11215,7 +11215,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G374" t="n">
-        <v>5.2768874168396</v>
+        <v>5.27688789367676</v>
       </c>
       <c r="H374" t="n">
         <v>2643</v>
@@ -11331,7 +11331,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G378" t="n">
-        <v>5.25843715667725</v>
+        <v>5.25843667984009</v>
       </c>
       <c r="H378" t="n">
         <v>4491</v>
@@ -11360,7 +11360,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G379" t="n">
-        <v>5.25843715667725</v>
+        <v>5.25843667984009</v>
       </c>
       <c r="H379" t="n">
         <v>270</v>
@@ -11389,7 +11389,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G380" t="n">
-        <v>5.2768874168396</v>
+        <v>5.27688789367676</v>
       </c>
       <c r="H380" t="n">
         <v>43761</v>
@@ -11418,7 +11418,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>5.24876928329468</v>
+        <v>5.24876976013184</v>
       </c>
       <c r="H381" t="n">
         <v>20743</v>
@@ -11505,7 +11505,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G384" t="n">
-        <v>5.47371673583984</v>
+        <v>5.473717212677</v>
       </c>
       <c r="H384" t="n">
         <v>4634</v>
@@ -11563,7 +11563,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G386" t="n">
-        <v>5.60493612289429</v>
+        <v>5.60493564605713</v>
       </c>
       <c r="H386" t="n">
         <v>24572</v>
@@ -11592,7 +11592,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G387" t="n">
-        <v>5.66117286682129</v>
+        <v>5.66117238998413</v>
       </c>
       <c r="H387" t="n">
         <v>23023</v>
@@ -11679,7 +11679,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H390" t="n">
         <v>24702</v>
@@ -11708,7 +11708,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G391" t="n">
-        <v>5.24876928329468</v>
+        <v>5.24876976013184</v>
       </c>
       <c r="H391" t="n">
         <v>7298</v>
@@ -11737,7 +11737,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G392" t="n">
-        <v>5.24876928329468</v>
+        <v>5.24876976013184</v>
       </c>
       <c r="H392" t="n">
         <v>2740</v>
@@ -11766,7 +11766,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G393" t="n">
-        <v>5.24876928329468</v>
+        <v>5.24876976013184</v>
       </c>
       <c r="H393" t="n">
         <v>16929</v>
@@ -11795,7 +11795,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G394" t="n">
-        <v>5.32375144958496</v>
+        <v>5.32375192642212</v>
       </c>
       <c r="H394" t="n">
         <v>680</v>
@@ -11882,7 +11882,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G397" t="n">
-        <v>5.47371673583984</v>
+        <v>5.473717212677</v>
       </c>
       <c r="H397" t="n">
         <v>2362</v>
@@ -11911,7 +11911,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>5.58619070053101</v>
+        <v>5.58619022369385</v>
       </c>
       <c r="H398" t="n">
         <v>3700</v>
@@ -12056,7 +12056,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G403" t="n">
-        <v>5.58619070053101</v>
+        <v>5.58619022369385</v>
       </c>
       <c r="H403" t="n">
         <v>430</v>
@@ -12114,7 +12114,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H405" t="n">
         <v>1418</v>
@@ -12288,7 +12288,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H411" t="n">
         <v>200</v>
@@ -12404,7 +12404,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H415" t="n">
         <v>100</v>
@@ -12433,7 +12433,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G416" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H416" t="n">
         <v>45</v>
@@ -12520,7 +12520,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G419" t="n">
-        <v>5.47371673583984</v>
+        <v>5.473717212677</v>
       </c>
       <c r="H419" t="n">
         <v>560</v>
@@ -12549,7 +12549,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G420" t="n">
-        <v>5.47371673583984</v>
+        <v>5.473717212677</v>
       </c>
       <c r="H420" t="n">
         <v>10242</v>
@@ -12607,7 +12607,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G422" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H422" t="n">
         <v>18970</v>
@@ -12665,7 +12665,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G424" t="n">
-        <v>5.4549708366394</v>
+        <v>5.45497131347656</v>
       </c>
       <c r="H424" t="n">
         <v>8384</v>
@@ -12752,7 +12752,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G427" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H427" t="n">
         <v>4203</v>
@@ -12781,7 +12781,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G428" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H428" t="n">
         <v>760</v>
@@ -12955,7 +12955,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G434" t="n">
-        <v>5.47371673583984</v>
+        <v>5.473717212677</v>
       </c>
       <c r="H434" t="n">
         <v>170</v>
@@ -13042,7 +13042,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H437" t="n">
         <v>7332</v>
@@ -13071,7 +13071,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H438" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H444" t="n">
         <v>10</v>
@@ -13332,7 +13332,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G447" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H447" t="n">
         <v>20</v>
@@ -13361,7 +13361,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G448" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H448" t="n">
         <v>2255</v>
@@ -13390,7 +13390,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G449" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H449" t="n">
         <v>300</v>
@@ -13448,7 +13448,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G451" t="n">
-        <v>5.32375144958496</v>
+        <v>5.32375192642212</v>
       </c>
       <c r="H451" t="n">
         <v>924</v>
@@ -13477,7 +13477,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G452" t="n">
-        <v>5.32375144958496</v>
+        <v>5.32375192642212</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G453" t="n">
-        <v>5.32375144958496</v>
+        <v>5.32375192642212</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13593,7 +13593,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G456" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H456" t="n">
         <v>20122</v>
@@ -13622,7 +13622,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G457" t="n">
-        <v>5.47371673583984</v>
+        <v>5.473717212677</v>
       </c>
       <c r="H457" t="n">
         <v>3375</v>
@@ -13999,7 +13999,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G470" t="n">
-        <v>5.24876928329468</v>
+        <v>5.24876976013184</v>
       </c>
       <c r="H470" t="n">
         <v>2437</v>
@@ -14173,7 +14173,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G476" t="n">
-        <v>5.02382278442383</v>
+        <v>5.02382230758667</v>
       </c>
       <c r="H476" t="n">
         <v>311</v>
@@ -14202,7 +14202,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G477" t="n">
-        <v>4.93009471893311</v>
+        <v>4.93009424209595</v>
       </c>
       <c r="H477" t="n">
         <v>5511</v>
@@ -14289,7 +14289,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G480" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H480" t="n">
         <v>900</v>
@@ -14318,7 +14318,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H481" t="n">
         <v>16552</v>
@@ -14347,7 +14347,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G482" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H482" t="n">
         <v>1000</v>
@@ -14376,7 +14376,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G483" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14405,7 +14405,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G484" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H484" t="n">
         <v>250</v>
@@ -14492,7 +14492,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G487" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H487" t="n">
         <v>1050</v>
@@ -14579,7 +14579,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>4.64891004562378</v>
+        <v>4.64891052246094</v>
       </c>
       <c r="H490" t="n">
         <v>2650</v>
@@ -14666,7 +14666,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G493" t="n">
-        <v>4.56455421447754</v>
+        <v>4.5645546913147</v>
       </c>
       <c r="H493" t="n">
         <v>1016</v>
@@ -14695,7 +14695,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G494" t="n">
-        <v>4.64891004562378</v>
+        <v>4.64891052246094</v>
       </c>
       <c r="H494" t="n">
         <v>21434</v>
@@ -14811,7 +14811,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G498" t="n">
-        <v>4.67702865600586</v>
+        <v>4.6770281791687</v>
       </c>
       <c r="H498" t="n">
         <v>3536</v>
@@ -14840,7 +14840,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G499" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H499" t="n">
         <v>12994</v>
@@ -14898,7 +14898,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>4.83636569976807</v>
+        <v>4.83636617660522</v>
       </c>
       <c r="H501" t="n">
         <v>9387</v>
@@ -14956,7 +14956,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G503" t="n">
-        <v>4.87385654449463</v>
+        <v>4.87385749816895</v>
       </c>
       <c r="H503" t="n">
         <v>15019</v>
@@ -15043,7 +15043,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G506" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H506" t="n">
         <v>2350</v>
@@ -15072,7 +15072,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -15101,7 +15101,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G508" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H508" t="n">
         <v>80250</v>
@@ -15188,7 +15188,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G511" t="n">
-        <v>5.02382278442383</v>
+        <v>5.02382230758667</v>
       </c>
       <c r="H511" t="n">
         <v>4402</v>
@@ -15217,7 +15217,7 @@
         <v>5.5</v>
       </c>
       <c r="G512" t="n">
-        <v>5.15504169464111</v>
+        <v>5.15504121780396</v>
       </c>
       <c r="H512" t="n">
         <v>4203</v>
@@ -15275,7 +15275,7 @@
         <v>5.5</v>
       </c>
       <c r="G514" t="n">
-        <v>5.15504169464111</v>
+        <v>5.15504121780396</v>
       </c>
       <c r="H514" t="n">
         <v>1884</v>
@@ -15304,7 +15304,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G515" t="n">
-        <v>5.00507688522339</v>
+        <v>5.00507640838623</v>
       </c>
       <c r="H515" t="n">
         <v>632</v>
@@ -15333,7 +15333,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G516" t="n">
-        <v>5.00507688522339</v>
+        <v>5.00507640838623</v>
       </c>
       <c r="H516" t="n">
         <v>0</v>
@@ -15391,7 +15391,7 @@
         <v>5.5</v>
       </c>
       <c r="G518" t="n">
-        <v>5.15504169464111</v>
+        <v>5.15504121780396</v>
       </c>
       <c r="H518" t="n">
         <v>6482</v>
@@ -15449,7 +15449,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G520" t="n">
-        <v>5.02382278442383</v>
+        <v>5.02382230758667</v>
       </c>
       <c r="H520" t="n">
         <v>1669</v>
@@ -15536,7 +15536,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G523" t="n">
-        <v>4.96758556365967</v>
+        <v>4.96758508682251</v>
       </c>
       <c r="H523" t="n">
         <v>560</v>
@@ -15594,7 +15594,7 @@
         <v>5.5</v>
       </c>
       <c r="G525" t="n">
-        <v>5.15504169464111</v>
+        <v>5.15504121780396</v>
       </c>
       <c r="H525" t="n">
         <v>3840</v>
@@ -15710,7 +15710,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G529" t="n">
-        <v>4.87385654449463</v>
+        <v>4.87385749816895</v>
       </c>
       <c r="H529" t="n">
         <v>22898</v>
@@ -15797,7 +15797,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G532" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H532" t="n">
         <v>121</v>
@@ -15855,7 +15855,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G534" t="n">
-        <v>4.87385654449463</v>
+        <v>4.87385749816895</v>
       </c>
       <c r="H534" t="n">
         <v>2718</v>
@@ -15884,7 +15884,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>4.87385654449463</v>
+        <v>4.87385749816895</v>
       </c>
       <c r="H535" t="n">
         <v>12616</v>
@@ -15942,7 +15942,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G537" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H537" t="n">
         <v>5650</v>
@@ -15971,7 +15971,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G538" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H538" t="n">
         <v>11050</v>
@@ -16029,7 +16029,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G540" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H540" t="n">
         <v>250</v>
@@ -16058,7 +16058,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G541" t="n">
-        <v>4.87385654449463</v>
+        <v>4.87385749816895</v>
       </c>
       <c r="H541" t="n">
         <v>1794</v>
@@ -16087,7 +16087,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G542" t="n">
-        <v>4.93009471893311</v>
+        <v>4.93009424209595</v>
       </c>
       <c r="H542" t="n">
         <v>2795</v>
@@ -16116,7 +16116,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G543" t="n">
-        <v>4.87385654449463</v>
+        <v>4.87385749816895</v>
       </c>
       <c r="H543" t="n">
         <v>4438</v>
@@ -16145,7 +16145,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G544" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H544" t="n">
         <v>1500</v>
@@ -16203,7 +16203,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G546" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H546" t="n">
         <v>3803</v>
@@ -16232,7 +16232,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G547" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G548" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H548" t="n">
         <v>0</v>
@@ -16290,7 +16290,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G549" t="n">
-        <v>4.7426381111145</v>
+        <v>4.74263763427734</v>
       </c>
       <c r="H549" t="n">
         <v>400</v>
@@ -16377,7 +16377,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H552" t="n">
         <v>2770</v>
@@ -16464,7 +16464,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H555" t="n">
         <v>1730</v>
@@ -16609,7 +16609,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>4.59267330169678</v>
+        <v>4.59267282485962</v>
       </c>
       <c r="H560" t="n">
         <v>2062</v>
@@ -16638,7 +16638,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G561" t="n">
-        <v>4.59267330169678</v>
+        <v>4.59267282485962</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -16667,7 +16667,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G562" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H562" t="n">
         <v>5341</v>
@@ -16696,7 +16696,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G563" t="n">
-        <v>4.83636569976807</v>
+        <v>4.83636617660522</v>
       </c>
       <c r="H563" t="n">
         <v>5514</v>
@@ -16725,7 +16725,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G564" t="n">
-        <v>4.98633146286011</v>
+        <v>4.98633098602295</v>
       </c>
       <c r="H564" t="n">
         <v>4495</v>
@@ -16957,7 +16957,7 @@
         <v>4.25</v>
       </c>
       <c r="G572" t="n">
-        <v>3.9834406375885</v>
+        <v>3.98344135284424</v>
       </c>
       <c r="H572" t="n">
         <v>9140</v>
@@ -17334,7 +17334,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G585" t="n">
-        <v>4.00218629837036</v>
+        <v>4.00218677520752</v>
       </c>
       <c r="H585" t="n">
         <v>1475</v>
@@ -17363,7 +17363,7 @@
         <v>4.25</v>
       </c>
       <c r="G586" t="n">
-        <v>3.9834406375885</v>
+        <v>3.98344135284424</v>
       </c>
       <c r="H586" t="n">
         <v>2353</v>
@@ -17392,7 +17392,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G587" t="n">
-        <v>3.92720413208008</v>
+        <v>3.92720437049866</v>
       </c>
       <c r="H587" t="n">
         <v>1105</v>
@@ -17566,7 +17566,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G593" t="n">
-        <v>4.03967809677124</v>
+        <v>4.03967761993408</v>
       </c>
       <c r="H593" t="n">
         <v>12527</v>
@@ -17595,7 +17595,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G594" t="n">
-        <v>4.00218629837036</v>
+        <v>4.00218677520752</v>
       </c>
       <c r="H594" t="n">
         <v>22055</v>
@@ -17682,7 +17682,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G597" t="n">
-        <v>4.06779623031616</v>
+        <v>4.06779670715332</v>
       </c>
       <c r="H597" t="n">
         <v>2200</v>
@@ -17711,7 +17711,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G598" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H598" t="n">
         <v>5102</v>
@@ -17740,7 +17740,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G599" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H599" t="n">
         <v>4178</v>
@@ -17769,7 +17769,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G600" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H600" t="n">
         <v>2406</v>
@@ -17856,7 +17856,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G603" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H603" t="n">
         <v>5008</v>
@@ -17885,7 +17885,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G604" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H604" t="n">
         <v>7230</v>
@@ -17972,7 +17972,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G607" t="n">
-        <v>4.13340616226196</v>
+        <v>4.1334056854248</v>
       </c>
       <c r="H607" t="n">
         <v>55370</v>
@@ -18001,7 +18001,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G608" t="n">
-        <v>4.12403345108032</v>
+        <v>4.12403297424316</v>
       </c>
       <c r="H608" t="n">
         <v>2894</v>
@@ -18030,7 +18030,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G609" t="n">
-        <v>4.00218629837036</v>
+        <v>4.00218677520752</v>
       </c>
       <c r="H609" t="n">
         <v>1958</v>
@@ -18059,7 +18059,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G610" t="n">
-        <v>4.00218629837036</v>
+        <v>4.00218677520752</v>
       </c>
       <c r="H610" t="n">
         <v>2262</v>
@@ -18088,7 +18088,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G611" t="n">
-        <v>4.05842399597168</v>
+        <v>4.05842351913452</v>
       </c>
       <c r="H611" t="n">
         <v>2515</v>
@@ -18117,7 +18117,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>4.09591484069824</v>
+        <v>4.09591436386108</v>
       </c>
       <c r="H612" t="n">
         <v>401</v>
@@ -18146,7 +18146,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G613" t="n">
-        <v>4.09591484069824</v>
+        <v>4.09591436386108</v>
       </c>
       <c r="H613" t="n">
         <v>0</v>
@@ -18175,7 +18175,7 @@
         <v>4.25</v>
       </c>
       <c r="G614" t="n">
-        <v>3.9834406375885</v>
+        <v>3.98344135284424</v>
       </c>
       <c r="H614" t="n">
         <v>2924</v>
@@ -18204,7 +18204,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G615" t="n">
-        <v>4.03967809677124</v>
+        <v>4.03967761993408</v>
       </c>
       <c r="H615" t="n">
         <v>320</v>
@@ -18233,7 +18233,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G616" t="n">
-        <v>3.92720413208008</v>
+        <v>3.92720437049866</v>
       </c>
       <c r="H616" t="n">
         <v>3977</v>
@@ -18262,7 +18262,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G617" t="n">
-        <v>3.87096762657166</v>
+        <v>3.87096738815308</v>
       </c>
       <c r="H617" t="n">
         <v>5257</v>
@@ -18639,7 +18639,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G630" t="n">
-        <v>3.68351149559021</v>
+        <v>3.68351125717163</v>
       </c>
       <c r="H630" t="n">
         <v>9933</v>
@@ -18668,7 +18668,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G631" t="n">
-        <v>3.66476607322693</v>
+        <v>3.66476583480835</v>
       </c>
       <c r="H631" t="n">
         <v>2461</v>
@@ -18697,7 +18697,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G632" t="n">
-        <v>3.64602041244507</v>
+        <v>3.64602017402649</v>
       </c>
       <c r="H632" t="n">
         <v>3650</v>
@@ -18755,7 +18755,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G634" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H634" t="n">
         <v>3900</v>
@@ -18784,7 +18784,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G635" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H635" t="n">
         <v>6237</v>
@@ -18813,7 +18813,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G636" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H636" t="n">
         <v>7752</v>
@@ -18842,7 +18842,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G637" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H637" t="n">
         <v>1500</v>
@@ -18871,7 +18871,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G638" t="n">
-        <v>3.71341037750244</v>
+        <v>3.71341013908386</v>
       </c>
       <c r="H638" t="n">
         <v>8760</v>
@@ -18900,7 +18900,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G639" t="n">
-        <v>3.71341037750244</v>
+        <v>3.71341013908386</v>
       </c>
       <c r="H639" t="n">
         <v>0</v>
@@ -18929,7 +18929,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G640" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H640" t="n">
         <v>1052</v>
@@ -18958,7 +18958,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G641" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H641" t="n">
         <v>10</v>
@@ -18987,7 +18987,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G642" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H642" t="n">
         <v>90</v>
@@ -19103,7 +19103,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G646" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H646" t="n">
         <v>13400</v>
@@ -19190,7 +19190,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G649" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H649" t="n">
         <v>4153</v>
@@ -19248,7 +19248,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G651" t="n">
-        <v>3.65583801269531</v>
+        <v>3.65583825111389</v>
       </c>
       <c r="H651" t="n">
         <v>900</v>
@@ -19277,7 +19277,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>3.65583801269531</v>
+        <v>3.65583825111389</v>
       </c>
       <c r="H652" t="n">
         <v>10</v>
@@ -19335,7 +19335,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G654" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H654" t="n">
         <v>3015</v>
@@ -19393,7 +19393,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G656" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H656" t="n">
         <v>3182</v>
@@ -19422,7 +19422,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H657" t="n">
         <v>1517</v>
@@ -19480,7 +19480,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G659" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H659" t="n">
         <v>100</v>
@@ -19509,7 +19509,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G660" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H660" t="n">
         <v>299</v>
@@ -19538,7 +19538,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G661" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H661" t="n">
         <v>1404</v>
@@ -19567,7 +19567,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G662" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H662" t="n">
         <v>0</v>
@@ -19625,7 +19625,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G664" t="n">
-        <v>3.72300601005554</v>
+        <v>3.72300577163696</v>
       </c>
       <c r="H664" t="n">
         <v>800</v>
@@ -19712,7 +19712,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>4.12601184844971</v>
+        <v>4.12601137161255</v>
       </c>
       <c r="H667" t="n">
         <v>45390</v>
@@ -19770,7 +19770,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G669" t="n">
-        <v>4.12601184844971</v>
+        <v>4.12601137161255</v>
       </c>
       <c r="H669" t="n">
         <v>8487</v>
@@ -19799,7 +19799,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G670" t="n">
-        <v>4.12601184844971</v>
+        <v>4.12601137161255</v>
       </c>
       <c r="H670" t="n">
         <v>2970</v>
@@ -19973,7 +19973,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G676" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H676" t="n">
         <v>1500</v>
@@ -20089,7 +20089,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G680" t="n">
-        <v>4.02046203613281</v>
+        <v>4.02046251296997</v>
       </c>
       <c r="H680" t="n">
         <v>1420</v>
@@ -20118,7 +20118,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G681" t="n">
-        <v>3.99167609214783</v>
+        <v>3.99167633056641</v>
       </c>
       <c r="H681" t="n">
         <v>1555</v>
@@ -20176,7 +20176,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G683" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H683" t="n">
         <v>10</v>
@@ -20205,7 +20205,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H684" t="n">
         <v>9595</v>
@@ -20292,7 +20292,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G687" t="n">
-        <v>3.99167609214783</v>
+        <v>3.99167633056641</v>
       </c>
       <c r="H687" t="n">
         <v>750</v>
@@ -20321,7 +20321,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G688" t="n">
-        <v>3.99167609214783</v>
+        <v>3.99167633056641</v>
       </c>
       <c r="H688" t="n">
         <v>0</v>
@@ -20350,7 +20350,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G689" t="n">
-        <v>3.98208093643188</v>
+        <v>3.98208069801331</v>
       </c>
       <c r="H689" t="n">
         <v>150</v>
@@ -20379,7 +20379,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>4.03965282440186</v>
+        <v>4.03965330123901</v>
       </c>
       <c r="H690" t="n">
         <v>1160</v>
@@ -20408,7 +20408,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>4.03965282440186</v>
+        <v>4.03965330123901</v>
       </c>
       <c r="H691" t="n">
         <v>10</v>
@@ -20437,7 +20437,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H692" t="n">
         <v>11</v>
@@ -20466,7 +20466,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G693" t="n">
-        <v>4.03965282440186</v>
+        <v>4.03965330123901</v>
       </c>
       <c r="H693" t="n">
         <v>1069</v>
@@ -20524,7 +20524,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G695" t="n">
-        <v>3.98208093643188</v>
+        <v>3.98208069801331</v>
       </c>
       <c r="H695" t="n">
         <v>1981</v>
@@ -20553,7 +20553,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>3.98208093643188</v>
+        <v>3.98208069801331</v>
       </c>
       <c r="H696" t="n">
         <v>0</v>
@@ -20582,7 +20582,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>3.98208093643188</v>
+        <v>3.98208069801331</v>
       </c>
       <c r="H697" t="n">
         <v>120</v>
@@ -20611,7 +20611,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G698" t="n">
-        <v>4.02046203613281</v>
+        <v>4.02046251296997</v>
       </c>
       <c r="H698" t="n">
         <v>245</v>
@@ -20669,7 +20669,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G700" t="n">
-        <v>3.9436993598938</v>
+        <v>3.94369959831238</v>
       </c>
       <c r="H700" t="n">
         <v>210</v>
@@ -20698,7 +20698,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G701" t="n">
-        <v>3.9436993598938</v>
+        <v>3.94369959831238</v>
       </c>
       <c r="H701" t="n">
         <v>280</v>
@@ -20930,7 +20930,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G709" t="n">
-        <v>3.87653160095215</v>
+        <v>3.87653183937073</v>
       </c>
       <c r="H709" t="n">
         <v>1788</v>
@@ -21017,7 +21017,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G712" t="n">
-        <v>3.93410396575928</v>
+        <v>3.9341037273407</v>
       </c>
       <c r="H712" t="n">
         <v>3931</v>
@@ -21046,7 +21046,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G713" t="n">
-        <v>3.84774589538574</v>
+        <v>3.84774565696716</v>
       </c>
       <c r="H713" t="n">
         <v>5760</v>
@@ -21075,7 +21075,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G714" t="n">
-        <v>3.79017353057861</v>
+        <v>3.79017329216003</v>
       </c>
       <c r="H714" t="n">
         <v>185</v>
@@ -21104,7 +21104,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G715" t="n">
-        <v>3.77098274230957</v>
+        <v>3.77098250389099</v>
       </c>
       <c r="H715" t="n">
         <v>540</v>
@@ -21133,7 +21133,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G716" t="n">
-        <v>3.75179195404053</v>
+        <v>3.75179171562195</v>
       </c>
       <c r="H716" t="n">
         <v>330</v>
@@ -21162,7 +21162,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G717" t="n">
-        <v>3.75179195404053</v>
+        <v>3.75179171562195</v>
       </c>
       <c r="H717" t="n">
         <v>0</v>
@@ -21191,7 +21191,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G718" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H718" t="n">
         <v>20488</v>
@@ -21249,7 +21249,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G720" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H720" t="n">
         <v>1602</v>
@@ -21336,7 +21336,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>3.91491341590881</v>
+        <v>3.91491317749023</v>
       </c>
       <c r="H723" t="n">
         <v>750</v>
@@ -21365,7 +21365,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G724" t="n">
-        <v>4.21236991882324</v>
+        <v>4.21236944198608</v>
       </c>
       <c r="H724" t="n">
         <v>46988</v>
@@ -21423,7 +21423,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G726" t="n">
-        <v>4.21236991882324</v>
+        <v>4.21236944198608</v>
       </c>
       <c r="H726" t="n">
         <v>70435</v>
@@ -21481,7 +21481,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G728" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H728" t="n">
         <v>172</v>
@@ -21597,7 +21597,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G732" t="n">
-        <v>4.18358373641968</v>
+        <v>4.18358421325684</v>
       </c>
       <c r="H732" t="n">
         <v>1320</v>
@@ -21742,7 +21742,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G737" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H737" t="n">
         <v>1637</v>
@@ -21771,7 +21771,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G738" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H738" t="n">
         <v>75279</v>
@@ -21800,7 +21800,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G739" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H739" t="n">
         <v>0</v>
@@ -21829,7 +21829,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G740" t="n">
-        <v>3.99167609214783</v>
+        <v>3.99167633056641</v>
       </c>
       <c r="H740" t="n">
         <v>7953</v>
@@ -21974,7 +21974,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G745" t="n">
-        <v>3.93410396575928</v>
+        <v>3.9341037273407</v>
       </c>
       <c r="H745" t="n">
         <v>81270</v>
@@ -22003,7 +22003,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G746" t="n">
-        <v>3.93410396575928</v>
+        <v>3.9341037273407</v>
       </c>
       <c r="H746" t="n">
         <v>3945</v>
@@ -22032,7 +22032,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>3.91491341590881</v>
+        <v>3.91491317749023</v>
       </c>
       <c r="H747" t="n">
         <v>196255</v>
@@ -22119,7 +22119,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G750" t="n">
-        <v>4.0588436126709</v>
+        <v>4.05884408950806</v>
       </c>
       <c r="H750" t="n">
         <v>1996</v>
@@ -22148,7 +22148,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G751" t="n">
-        <v>3.98208093643188</v>
+        <v>3.98208069801331</v>
       </c>
       <c r="H751" t="n">
         <v>7044</v>
@@ -22206,7 +22206,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G753" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H753" t="n">
         <v>7875</v>
@@ -22235,7 +22235,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>4.03965282440186</v>
+        <v>4.03965330123901</v>
       </c>
       <c r="H754" t="n">
         <v>498</v>
@@ -22264,7 +22264,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G755" t="n">
-        <v>3.91491341590881</v>
+        <v>3.91491317749023</v>
       </c>
       <c r="H755" t="n">
         <v>21081</v>
@@ -22641,7 +22641,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>3.63664722442627</v>
+        <v>3.63664746284485</v>
       </c>
       <c r="H768" t="n">
         <v>8155</v>
@@ -22670,7 +22670,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G769" t="n">
-        <v>3.61745643615723</v>
+        <v>3.61745667457581</v>
       </c>
       <c r="H769" t="n">
         <v>19701</v>
@@ -22786,7 +22786,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G773" t="n">
-        <v>3.61745643615723</v>
+        <v>3.61745667457581</v>
       </c>
       <c r="H773" t="n">
         <v>16809</v>
@@ -22902,7 +22902,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>3.63664722442627</v>
+        <v>3.63664746284485</v>
       </c>
       <c r="H777" t="n">
         <v>23488</v>
@@ -22931,7 +22931,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G778" t="n">
-        <v>3.63664722442627</v>
+        <v>3.63664746284485</v>
       </c>
       <c r="H778" t="n">
         <v>5020</v>
@@ -23105,7 +23105,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G784" t="n">
-        <v>3.40635848045349</v>
+        <v>3.40635824203491</v>
       </c>
       <c r="H784" t="n">
         <v>13684</v>
@@ -23192,7 +23192,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H787" t="n">
         <v>1420</v>
@@ -23221,7 +23221,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G788" t="n">
-        <v>3.65583801269531</v>
+        <v>3.65583825111389</v>
       </c>
       <c r="H788" t="n">
         <v>1250</v>
@@ -23627,7 +23627,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G802" t="n">
-        <v>3.53109836578369</v>
+        <v>3.53109812736511</v>
       </c>
       <c r="H802" t="n">
         <v>18225</v>
@@ -23772,7 +23772,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G807" t="n">
-        <v>3.53109836578369</v>
+        <v>3.53109812736511</v>
       </c>
       <c r="H807" t="n">
         <v>6020</v>
@@ -23801,7 +23801,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>3.55988430976868</v>
+        <v>3.55988454818726</v>
       </c>
       <c r="H808" t="n">
         <v>5589</v>
@@ -23859,7 +23859,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G810" t="n">
-        <v>3.60786104202271</v>
+        <v>3.60786128044128</v>
       </c>
       <c r="H810" t="n">
         <v>35932</v>
@@ -23888,7 +23888,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G811" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H811" t="n">
         <v>3848</v>
@@ -23917,7 +23917,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G812" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H812" t="n">
         <v>10695</v>
@@ -23946,7 +23946,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G813" t="n">
-        <v>3.71341037750244</v>
+        <v>3.71341013908386</v>
       </c>
       <c r="H813" t="n">
         <v>3973</v>
@@ -23975,7 +23975,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G814" t="n">
-        <v>3.79017353057861</v>
+        <v>3.79017329216003</v>
       </c>
       <c r="H814" t="n">
         <v>8700</v>
@@ -24004,7 +24004,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G815" t="n">
-        <v>3.75179195404053</v>
+        <v>3.75179171562195</v>
       </c>
       <c r="H815" t="n">
         <v>4141</v>
@@ -24091,7 +24091,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>3.91491341590881</v>
+        <v>3.91491317749023</v>
       </c>
       <c r="H818" t="n">
         <v>4284</v>
@@ -24120,7 +24120,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G819" t="n">
-        <v>4.25075149536133</v>
+        <v>4.25075101852417</v>
       </c>
       <c r="H819" t="n">
         <v>51273</v>
@@ -24236,7 +24236,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G823" t="n">
-        <v>4.25075149536133</v>
+        <v>4.25075101852417</v>
       </c>
       <c r="H823" t="n">
         <v>21761</v>
@@ -24265,7 +24265,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G824" t="n">
-        <v>4.29872798919678</v>
+        <v>4.29872846603394</v>
       </c>
       <c r="H824" t="n">
         <v>12287</v>
@@ -24352,7 +24352,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G827" t="n">
-        <v>4.26994228363037</v>
+        <v>4.26994180679321</v>
       </c>
       <c r="H827" t="n">
         <v>3147</v>
@@ -24613,7 +24613,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G836" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H836" t="n">
         <v>440</v>
@@ -24642,7 +24642,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G837" t="n">
-        <v>4.12601184844971</v>
+        <v>4.12601137161255</v>
       </c>
       <c r="H837" t="n">
         <v>1700</v>
@@ -24874,7 +24874,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G845" t="n">
-        <v>4.12601184844971</v>
+        <v>4.12601137161255</v>
       </c>
       <c r="H845" t="n">
         <v>1616</v>
@@ -24903,7 +24903,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G846" t="n">
-        <v>4.12601184844971</v>
+        <v>4.12601137161255</v>
       </c>
       <c r="H846" t="n">
         <v>0</v>
@@ -25193,7 +25193,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G856" t="n">
-        <v>4.21236991882324</v>
+        <v>4.21236944198608</v>
       </c>
       <c r="H856" t="n">
         <v>12800</v>
@@ -25251,7 +25251,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G858" t="n">
-        <v>4.02046203613281</v>
+        <v>4.02046251296997</v>
       </c>
       <c r="H858" t="n">
         <v>3537</v>
@@ -25309,7 +25309,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G860" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H860" t="n">
         <v>2994</v>
@@ -25338,7 +25338,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G861" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H861" t="n">
         <v>280</v>
@@ -25657,7 +25657,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G872" t="n">
-        <v>3.91491341590881</v>
+        <v>3.91491317749023</v>
       </c>
       <c r="H872" t="n">
         <v>1409</v>
@@ -25686,7 +25686,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G873" t="n">
-        <v>3.91491341590881</v>
+        <v>3.91491317749023</v>
       </c>
       <c r="H873" t="n">
         <v>4382</v>
@@ -25831,7 +25831,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G878" t="n">
-        <v>3.97248554229736</v>
+        <v>3.97248530387878</v>
       </c>
       <c r="H878" t="n">
         <v>850</v>
@@ -25860,7 +25860,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G879" t="n">
-        <v>3.9436993598938</v>
+        <v>3.94369959831238</v>
       </c>
       <c r="H879" t="n">
         <v>3403</v>
@@ -25889,7 +25889,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G880" t="n">
-        <v>3.99167609214783</v>
+        <v>3.99167633056641</v>
       </c>
       <c r="H880" t="n">
         <v>17094</v>
@@ -25918,7 +25918,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G881" t="n">
-        <v>3.97248554229736</v>
+        <v>3.97248530387878</v>
       </c>
       <c r="H881" t="n">
         <v>7211</v>
@@ -26005,7 +26005,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G884" t="n">
-        <v>3.98208093643188</v>
+        <v>3.98208069801331</v>
       </c>
       <c r="H884" t="n">
         <v>2973</v>
@@ -36813,7 +36813,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="D1257" t="n">
-        <v>5.09999990463257</v>
+        <v>5.11999988555908</v>
       </c>
       <c r="E1257" t="n">
         <v>5.05999994277954</v>
@@ -36828,6 +36828,35 @@
         <v>1260</v>
       </c>
       <c r="I1257" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1258" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1258" t="n">
+        <v>5.15999984741211</v>
+      </c>
+      <c r="D1258" t="n">
+        <v>5.15999984741211</v>
+      </c>
+      <c r="E1258" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="F1258" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="G1258" t="n">
+        <v>5.03999996185303</v>
+      </c>
+      <c r="H1258" t="n">
+        <v>84038</v>
+      </c>
+      <c r="I1258" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RFG.MI.xlsx
+++ b/data/RFG.MI.xlsx
@@ -427,7 +427,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2" t="n">
-        <v>4.62868070602417</v>
+        <v>4.62868022918701</v>
       </c>
       <c r="H2" t="n">
         <v>355635</v>
@@ -514,7 +514,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G5" t="n">
-        <v>4.30648756027222</v>
+        <v>4.30648803710938</v>
       </c>
       <c r="H5" t="n">
         <v>223483</v>
@@ -659,7 +659,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G10" t="n">
-        <v>4.17035007476807</v>
+        <v>4.17034959793091</v>
       </c>
       <c r="H10" t="n">
         <v>39798</v>
@@ -688,7 +688,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G11" t="n">
-        <v>4.17488861083984</v>
+        <v>4.17488813400269</v>
       </c>
       <c r="H11" t="n">
         <v>49843</v>
@@ -717,7 +717,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G12" t="n">
-        <v>4.18850183486938</v>
+        <v>4.18850231170654</v>
       </c>
       <c r="H12" t="n">
         <v>43700</v>
@@ -746,7 +746,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>4.17488861083984</v>
+        <v>4.17488813400269</v>
       </c>
       <c r="H13" t="n">
         <v>29293</v>
@@ -775,7 +775,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>4.193039894104</v>
+        <v>4.19304037094116</v>
       </c>
       <c r="H14" t="n">
         <v>6960</v>
@@ -833,7 +833,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G16" t="n">
-        <v>4.29741239547729</v>
+        <v>4.29741191864014</v>
       </c>
       <c r="H16" t="n">
         <v>16165</v>
@@ -891,7 +891,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G18" t="n">
-        <v>4.32463932037354</v>
+        <v>4.32463979721069</v>
       </c>
       <c r="H18" t="n">
         <v>32335</v>
@@ -920,7 +920,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G19" t="n">
-        <v>4.44716358184814</v>
+        <v>4.4471640586853</v>
       </c>
       <c r="H19" t="n">
         <v>155415</v>
@@ -949,7 +949,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G20" t="n">
-        <v>4.41993570327759</v>
+        <v>4.41993618011475</v>
       </c>
       <c r="H20" t="n">
         <v>14288</v>
@@ -1065,7 +1065,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G24" t="n">
-        <v>4.82834959030151</v>
+        <v>4.82834911346436</v>
       </c>
       <c r="H24" t="n">
         <v>64828</v>
@@ -1094,7 +1094,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G25" t="n">
-        <v>4.84650087356567</v>
+        <v>4.84650039672852</v>
       </c>
       <c r="H25" t="n">
         <v>24608</v>
@@ -1123,7 +1123,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G26" t="n">
-        <v>4.84650087356567</v>
+        <v>4.84650039672852</v>
       </c>
       <c r="H26" t="n">
         <v>84199</v>
@@ -1152,7 +1152,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>4.95541048049927</v>
+        <v>4.95541095733643</v>
       </c>
       <c r="H27" t="n">
         <v>26232</v>
@@ -1297,7 +1297,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G32" t="n">
-        <v>5.43642997741699</v>
+        <v>5.43643045425415</v>
       </c>
       <c r="H32" t="n">
         <v>36811</v>
@@ -1326,7 +1326,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G33" t="n">
-        <v>5.43642997741699</v>
+        <v>5.43643045425415</v>
       </c>
       <c r="H33" t="n">
         <v>30706</v>
@@ -1413,7 +1413,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G36" t="n">
-        <v>5.33659648895264</v>
+        <v>5.33659601211548</v>
       </c>
       <c r="H36" t="n">
         <v>16617</v>
@@ -1442,7 +1442,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>5.25491333007812</v>
+        <v>5.25491380691528</v>
       </c>
       <c r="H37" t="n">
         <v>23662</v>
@@ -1471,7 +1471,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G38" t="n">
-        <v>5.31844520568848</v>
+        <v>5.31844472885132</v>
       </c>
       <c r="H38" t="n">
         <v>24272</v>
@@ -1500,7 +1500,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G39" t="n">
-        <v>5.36382341384888</v>
+        <v>5.36382389068604</v>
       </c>
       <c r="H39" t="n">
         <v>8885</v>
@@ -1558,7 +1558,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G41" t="n">
-        <v>5.39105129241943</v>
+        <v>5.39105176925659</v>
       </c>
       <c r="H41" t="n">
         <v>11791</v>
@@ -1616,7 +1616,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G43" t="n">
-        <v>5.42735433578491</v>
+        <v>5.42735481262207</v>
       </c>
       <c r="H43" t="n">
         <v>24833</v>
@@ -1674,7 +1674,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G45" t="n">
-        <v>5.3547477722168</v>
+        <v>5.35474729537964</v>
       </c>
       <c r="H45" t="n">
         <v>29347</v>
@@ -1732,7 +1732,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>5.26398944854736</v>
+        <v>5.26398992538452</v>
       </c>
       <c r="H47" t="n">
         <v>26913</v>
@@ -1761,7 +1761,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G48" t="n">
-        <v>5.10970020294189</v>
+        <v>5.10969972610474</v>
       </c>
       <c r="H48" t="n">
         <v>75369</v>
@@ -1790,7 +1790,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>5.10062408447266</v>
+        <v>5.1006236076355</v>
       </c>
       <c r="H49" t="n">
         <v>37488</v>
@@ -1906,7 +1906,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G53" t="n">
-        <v>5.03709411621094</v>
+        <v>5.03709363937378</v>
       </c>
       <c r="H53" t="n">
         <v>29429</v>
@@ -1964,7 +1964,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G55" t="n">
-        <v>5.05524444580078</v>
+        <v>5.05524492263794</v>
       </c>
       <c r="H55" t="n">
         <v>23049</v>
@@ -2051,7 +2051,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G58" t="n">
-        <v>4.86465167999268</v>
+        <v>4.86465215682983</v>
       </c>
       <c r="H58" t="n">
         <v>10871</v>
@@ -2080,7 +2080,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G59" t="n">
-        <v>4.87372827529907</v>
+        <v>4.87372779846191</v>
       </c>
       <c r="H59" t="n">
         <v>60004</v>
@@ -2138,7 +2138,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G61" t="n">
-        <v>4.92818307876587</v>
+        <v>4.92818355560303</v>
       </c>
       <c r="H61" t="n">
         <v>10150</v>
@@ -2167,7 +2167,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G62" t="n">
-        <v>4.83742523193359</v>
+        <v>4.83742475509644</v>
       </c>
       <c r="H62" t="n">
         <v>13006</v>
@@ -2254,7 +2254,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G65" t="n">
-        <v>4.68313550949097</v>
+        <v>4.68313598632812</v>
       </c>
       <c r="H65" t="n">
         <v>14192</v>
@@ -2283,7 +2283,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G66" t="n">
-        <v>4.63775682449341</v>
+        <v>4.63775587081909</v>
       </c>
       <c r="H66" t="n">
         <v>9021</v>
@@ -2341,7 +2341,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G68" t="n">
-        <v>4.67405986785889</v>
+        <v>4.67406034469604</v>
       </c>
       <c r="H68" t="n">
         <v>26836</v>
@@ -2370,7 +2370,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>4.87372827529907</v>
+        <v>4.87372779846191</v>
       </c>
       <c r="H69" t="n">
         <v>20469</v>
@@ -2399,7 +2399,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G70" t="n">
-        <v>4.93725967407227</v>
+        <v>4.93725919723511</v>
       </c>
       <c r="H70" t="n">
         <v>2829</v>
@@ -2428,7 +2428,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G71" t="n">
-        <v>4.68313550949097</v>
+        <v>4.68313598632812</v>
       </c>
       <c r="H71" t="n">
         <v>21164</v>
@@ -2457,7 +2457,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G72" t="n">
-        <v>4.77389430999756</v>
+        <v>4.77389478683472</v>
       </c>
       <c r="H72" t="n">
         <v>8024</v>
@@ -2486,7 +2486,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G73" t="n">
-        <v>4.84650087356567</v>
+        <v>4.84650039672852</v>
       </c>
       <c r="H73" t="n">
         <v>6837</v>
@@ -2631,7 +2631,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G78" t="n">
-        <v>4.13404703140259</v>
+        <v>4.13404655456543</v>
       </c>
       <c r="H78" t="n">
         <v>12171</v>
@@ -2660,7 +2660,7 @@
         <v>4.5</v>
       </c>
       <c r="G79" t="n">
-        <v>4.08412981033325</v>
+        <v>4.08413028717041</v>
       </c>
       <c r="H79" t="n">
         <v>23806</v>
@@ -2776,7 +2776,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G83" t="n">
-        <v>3.99337124824524</v>
+        <v>3.99337148666382</v>
       </c>
       <c r="H83" t="n">
         <v>14139</v>
@@ -2805,7 +2805,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G84" t="n">
-        <v>4.01152276992798</v>
+        <v>4.01152324676514</v>
       </c>
       <c r="H84" t="n">
         <v>13008</v>
@@ -2834,7 +2834,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>4.03421258926392</v>
+        <v>4.03421306610107</v>
       </c>
       <c r="H85" t="n">
         <v>9318</v>
@@ -2863,7 +2863,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>4.15673637390137</v>
+        <v>4.15673589706421</v>
       </c>
       <c r="H86" t="n">
         <v>20105</v>
@@ -2892,7 +2892,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G87" t="n">
-        <v>4.21119117736816</v>
+        <v>4.21119165420532</v>
       </c>
       <c r="H87" t="n">
         <v>12593</v>
@@ -2921,7 +2921,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G88" t="n">
-        <v>4.47892951965332</v>
+        <v>4.47892904281616</v>
       </c>
       <c r="H88" t="n">
         <v>20559</v>
@@ -2979,7 +2979,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G90" t="n">
-        <v>4.68313550949097</v>
+        <v>4.68313598632812</v>
       </c>
       <c r="H90" t="n">
         <v>7231</v>
@@ -3037,7 +3037,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G92" t="n">
-        <v>4.53338384628296</v>
+        <v>4.53338432312012</v>
       </c>
       <c r="H92" t="n">
         <v>1969</v>
@@ -3095,7 +3095,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G94" t="n">
-        <v>4.50615692138672</v>
+        <v>4.50615644454956</v>
       </c>
       <c r="H94" t="n">
         <v>2116</v>
@@ -3182,7 +3182,7 @@
         <v>4.95499992370605</v>
       </c>
       <c r="G97" t="n">
-        <v>4.49708032608032</v>
+        <v>4.49708080291748</v>
       </c>
       <c r="H97" t="n">
         <v>8314</v>
@@ -3211,7 +3211,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G98" t="n">
-        <v>4.41086006164551</v>
+        <v>4.41085958480835</v>
       </c>
       <c r="H98" t="n">
         <v>2735</v>
@@ -3414,7 +3414,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G105" t="n">
-        <v>4.36548089981079</v>
+        <v>4.36548042297363</v>
       </c>
       <c r="H105" t="n">
         <v>618</v>
@@ -3443,7 +3443,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G106" t="n">
-        <v>4.42901229858398</v>
+        <v>4.42901277542114</v>
       </c>
       <c r="H106" t="n">
         <v>317</v>
@@ -3559,7 +3559,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>4.44716358184814</v>
+        <v>4.4471640586853</v>
       </c>
       <c r="H110" t="n">
         <v>197</v>
@@ -3617,7 +3617,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G112" t="n">
-        <v>4.33825349807739</v>
+        <v>4.33825397491455</v>
       </c>
       <c r="H112" t="n">
         <v>5545</v>
@@ -3675,7 +3675,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G114" t="n">
-        <v>4.4653148651123</v>
+        <v>4.46531534194946</v>
       </c>
       <c r="H114" t="n">
         <v>2900</v>
@@ -3791,7 +3791,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G118" t="n">
-        <v>4.24295663833618</v>
+        <v>4.2429575920105</v>
       </c>
       <c r="H118" t="n">
         <v>50</v>
@@ -3820,7 +3820,7 @@
         <v>4.75</v>
       </c>
       <c r="G119" t="n">
-        <v>4.31102561950684</v>
+        <v>4.31102609634399</v>
       </c>
       <c r="H119" t="n">
         <v>635</v>
@@ -3849,7 +3849,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G120" t="n">
-        <v>3.88446187973022</v>
+        <v>3.88446140289307</v>
       </c>
       <c r="H120" t="n">
         <v>37503</v>
@@ -3878,7 +3878,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G121" t="n">
-        <v>3.81639242172241</v>
+        <v>3.81639218330383</v>
       </c>
       <c r="H121" t="n">
         <v>9794</v>
@@ -3936,7 +3936,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G123" t="n">
-        <v>3.88446187973022</v>
+        <v>3.88446140289307</v>
       </c>
       <c r="H123" t="n">
         <v>3695</v>
@@ -3965,7 +3965,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G124" t="n">
-        <v>3.88446187973022</v>
+        <v>3.88446140289307</v>
       </c>
       <c r="H124" t="n">
         <v>7707</v>
@@ -4052,7 +4052,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G127" t="n">
-        <v>4.21597528457642</v>
+        <v>4.21597480773926</v>
       </c>
       <c r="H127" t="n">
         <v>26910</v>
@@ -4081,7 +4081,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G128" t="n">
-        <v>4.2990026473999</v>
+        <v>4.29900312423706</v>
       </c>
       <c r="H128" t="n">
         <v>9321</v>
@@ -4168,7 +4168,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G131" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H131" t="n">
         <v>15380</v>
@@ -4284,7 +4284,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G135" t="n">
-        <v>4.37280607223511</v>
+        <v>4.37280559539795</v>
       </c>
       <c r="H135" t="n">
         <v>4000</v>
@@ -4313,7 +4313,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G136" t="n">
-        <v>4.42354536056519</v>
+        <v>4.42354488372803</v>
       </c>
       <c r="H136" t="n">
         <v>520</v>
@@ -4342,7 +4342,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G137" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H137" t="n">
         <v>3650</v>
@@ -4371,7 +4371,7 @@
         <v>4.64499998092651</v>
       </c>
       <c r="G138" t="n">
-        <v>4.28516530990601</v>
+        <v>4.28516483306885</v>
       </c>
       <c r="H138" t="n">
         <v>7384</v>
@@ -4400,7 +4400,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G139" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H139" t="n">
         <v>2000</v>
@@ -4429,7 +4429,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G140" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>4.24826431274414</v>
+        <v>4.24826335906982</v>
       </c>
       <c r="H141" t="n">
         <v>1470</v>
@@ -4516,7 +4516,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G143" t="n">
-        <v>4.20674991607666</v>
+        <v>4.2067494392395</v>
       </c>
       <c r="H143" t="n">
         <v>17151</v>
@@ -4632,7 +4632,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>3.89770126342773</v>
+        <v>3.89770150184631</v>
       </c>
       <c r="H147" t="n">
         <v>8340</v>
@@ -4661,7 +4661,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95766615867615</v>
+        <v>3.95766592025757</v>
       </c>
       <c r="H148" t="n">
         <v>2849</v>
@@ -4690,7 +4690,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G149" t="n">
-        <v>3.95766615867615</v>
+        <v>3.95766592025757</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>4.10527086257935</v>
+        <v>4.1052713394165</v>
       </c>
       <c r="H151" t="n">
         <v>124</v>
@@ -4777,7 +4777,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G152" t="n">
-        <v>4.14678525924683</v>
+        <v>4.14678573608398</v>
       </c>
       <c r="H152" t="n">
         <v>2449</v>
@@ -4806,7 +4806,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G153" t="n">
-        <v>3.98534250259399</v>
+        <v>3.98534202575684</v>
       </c>
       <c r="H153" t="n">
         <v>8687</v>
@@ -4835,7 +4835,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G154" t="n">
-        <v>3.9299898147583</v>
+        <v>3.92999005317688</v>
       </c>
       <c r="H154" t="n">
         <v>5428</v>
@@ -4980,7 +4980,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G159" t="n">
-        <v>3.82851147651672</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H159" t="n">
         <v>11901</v>
@@ -5096,7 +5096,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G163" t="n">
-        <v>3.82851147651672</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H163" t="n">
         <v>5720</v>
@@ -5125,7 +5125,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G164" t="n">
-        <v>3.8377366065979</v>
+        <v>3.83773636817932</v>
       </c>
       <c r="H164" t="n">
         <v>2438</v>
@@ -5212,7 +5212,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>3.89770126342773</v>
+        <v>3.89770150184631</v>
       </c>
       <c r="H167" t="n">
         <v>205</v>
@@ -5241,7 +5241,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G168" t="n">
-        <v>3.98534250259399</v>
+        <v>3.98534202575684</v>
       </c>
       <c r="H168" t="n">
         <v>5404</v>
@@ -5270,7 +5270,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>3.92537713050842</v>
+        <v>3.925377368927</v>
       </c>
       <c r="H169" t="n">
         <v>2375</v>
@@ -5299,7 +5299,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G170" t="n">
-        <v>3.9299898147583</v>
+        <v>3.92999005317688</v>
       </c>
       <c r="H170" t="n">
         <v>10150</v>
@@ -5415,7 +5415,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G174" t="n">
-        <v>3.89308834075928</v>
+        <v>3.89308881759644</v>
       </c>
       <c r="H174" t="n">
         <v>3424</v>
@@ -5444,7 +5444,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G175" t="n">
-        <v>3.89308834075928</v>
+        <v>3.89308881759644</v>
       </c>
       <c r="H175" t="n">
         <v>470</v>
@@ -5473,7 +5473,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G176" t="n">
-        <v>3.95305299758911</v>
+        <v>3.95305323600769</v>
       </c>
       <c r="H176" t="n">
         <v>1056</v>
@@ -5531,7 +5531,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>3.88386297225952</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H178" t="n">
         <v>5254</v>
@@ -5589,7 +5589,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G180" t="n">
-        <v>3.82851147651672</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H180" t="n">
         <v>6092</v>
@@ -5618,7 +5618,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G181" t="n">
-        <v>3.8377366065979</v>
+        <v>3.83773636817932</v>
       </c>
       <c r="H181" t="n">
         <v>5582</v>
@@ -5676,7 +5676,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G183" t="n">
-        <v>3.88386297225952</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H183" t="n">
         <v>11079</v>
@@ -5763,7 +5763,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G186" t="n">
-        <v>3.89308834075928</v>
+        <v>3.89308881759644</v>
       </c>
       <c r="H186" t="n">
         <v>13086</v>
@@ -5821,7 +5821,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G188" t="n">
-        <v>3.93921542167664</v>
+        <v>3.93921494483948</v>
       </c>
       <c r="H188" t="n">
         <v>2507</v>
@@ -5850,7 +5850,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G189" t="n">
-        <v>4.00840473175049</v>
+        <v>4.00840520858765</v>
       </c>
       <c r="H189" t="n">
         <v>3667</v>
@@ -5879,7 +5879,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>3.88386297225952</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H190" t="n">
         <v>1237</v>
@@ -5937,7 +5937,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>3.95766615867615</v>
+        <v>3.95766592025757</v>
       </c>
       <c r="H192" t="n">
         <v>3183</v>
@@ -5966,7 +5966,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G193" t="n">
-        <v>4.01301765441895</v>
+        <v>4.0130181312561</v>
       </c>
       <c r="H193" t="n">
         <v>82</v>
@@ -5995,7 +5995,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G194" t="n">
-        <v>4.00379276275635</v>
+        <v>4.00379228591919</v>
       </c>
       <c r="H194" t="n">
         <v>1199</v>
@@ -6024,7 +6024,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>3.99456739425659</v>
+        <v>3.99456763267517</v>
       </c>
       <c r="H195" t="n">
         <v>131</v>
@@ -6053,7 +6053,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G196" t="n">
-        <v>3.86541247367859</v>
+        <v>3.86541223526001</v>
       </c>
       <c r="H196" t="n">
         <v>5890</v>
@@ -6082,7 +6082,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G197" t="n">
-        <v>3.94844055175781</v>
+        <v>3.94844079017639</v>
       </c>
       <c r="H197" t="n">
         <v>2149</v>
@@ -6140,7 +6140,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G199" t="n">
-        <v>3.9299898147583</v>
+        <v>3.92999005317688</v>
       </c>
       <c r="H199" t="n">
         <v>2982</v>
@@ -6198,7 +6198,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G201" t="n">
-        <v>3.89308834075928</v>
+        <v>3.89308881759644</v>
       </c>
       <c r="H201" t="n">
         <v>1122</v>
@@ -6285,7 +6285,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G204" t="n">
-        <v>3.95766615867615</v>
+        <v>3.95766592025757</v>
       </c>
       <c r="H204" t="n">
         <v>5370</v>
@@ -6314,7 +6314,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G205" t="n">
-        <v>3.87925100326538</v>
+        <v>3.87925052642822</v>
       </c>
       <c r="H205" t="n">
         <v>3705</v>
@@ -6343,7 +6343,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G206" t="n">
-        <v>3.94844055175781</v>
+        <v>3.94844079017639</v>
       </c>
       <c r="H206" t="n">
         <v>5295</v>
@@ -6401,7 +6401,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>3.90231418609619</v>
+        <v>3.90231370925903</v>
       </c>
       <c r="H208" t="n">
         <v>1430</v>
@@ -6430,7 +6430,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G209" t="n">
-        <v>3.89308834075928</v>
+        <v>3.89308881759644</v>
       </c>
       <c r="H209" t="n">
         <v>7711</v>
@@ -6488,7 +6488,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G211" t="n">
-        <v>3.94844055175781</v>
+        <v>3.94844079017639</v>
       </c>
       <c r="H211" t="n">
         <v>5037</v>
@@ -6517,7 +6517,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G212" t="n">
-        <v>3.87002539634705</v>
+        <v>3.87002563476562</v>
       </c>
       <c r="H212" t="n">
         <v>3149</v>
@@ -6546,7 +6546,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>3.88386297225952</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H213" t="n">
         <v>1793</v>
@@ -6575,7 +6575,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G214" t="n">
-        <v>3.88386297225952</v>
+        <v>3.8838632106781</v>
       </c>
       <c r="H214" t="n">
         <v>63</v>
@@ -6633,7 +6633,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>3.94382834434509</v>
+        <v>3.94382810592651</v>
       </c>
       <c r="H216" t="n">
         <v>1</v>
@@ -6720,7 +6720,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G219" t="n">
-        <v>3.82851147651672</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H219" t="n">
         <v>650</v>
@@ -6749,7 +6749,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>3.82851147651672</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G222" t="n">
-        <v>3.82851147651672</v>
+        <v>3.82851123809814</v>
       </c>
       <c r="H222" t="n">
         <v>400</v>
@@ -6865,7 +6865,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G224" t="n">
-        <v>4.10527086257935</v>
+        <v>4.1052713394165</v>
       </c>
       <c r="H224" t="n">
         <v>7165</v>
@@ -6894,7 +6894,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>4.01301765441895</v>
+        <v>4.0130181312561</v>
       </c>
       <c r="H225" t="n">
         <v>1000</v>
@@ -6981,7 +6981,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G228" t="n">
-        <v>4.14217233657837</v>
+        <v>4.14217185974121</v>
       </c>
       <c r="H228" t="n">
         <v>6907</v>
@@ -7097,7 +7097,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G232" t="n">
-        <v>4.21597528457642</v>
+        <v>4.21597480773926</v>
       </c>
       <c r="H232" t="n">
         <v>7962</v>
@@ -7126,7 +7126,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G233" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H233" t="n">
         <v>12462</v>
@@ -7155,7 +7155,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H234" t="n">
         <v>15005</v>
@@ -7184,7 +7184,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G235" t="n">
-        <v>4.37280607223511</v>
+        <v>4.37280559539795</v>
       </c>
       <c r="H235" t="n">
         <v>17132</v>
@@ -7213,7 +7213,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>4.45583343505859</v>
+        <v>4.45583391189575</v>
       </c>
       <c r="H236" t="n">
         <v>4300</v>
@@ -7242,7 +7242,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G237" t="n">
-        <v>4.47428464889526</v>
+        <v>4.47428369522095</v>
       </c>
       <c r="H237" t="n">
         <v>567</v>
@@ -7300,7 +7300,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G239" t="n">
-        <v>4.46505880355835</v>
+        <v>4.46505928039551</v>
       </c>
       <c r="H239" t="n">
         <v>1590</v>
@@ -7329,7 +7329,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G240" t="n">
-        <v>4.42354536056519</v>
+        <v>4.42354488372803</v>
       </c>
       <c r="H240" t="n">
         <v>3500</v>
@@ -7358,7 +7358,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G241" t="n">
-        <v>4.33590412139893</v>
+        <v>4.33590459823608</v>
       </c>
       <c r="H241" t="n">
         <v>1200</v>
@@ -7387,7 +7387,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>4.42354536056519</v>
+        <v>4.42354488372803</v>
       </c>
       <c r="H242" t="n">
         <v>9000</v>
@@ -7503,7 +7503,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G246" t="n">
-        <v>4.35435438156128</v>
+        <v>4.35435485839844</v>
       </c>
       <c r="H246" t="n">
         <v>2400</v>
@@ -7619,7 +7619,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G250" t="n">
-        <v>4.37280607223511</v>
+        <v>4.37280559539795</v>
       </c>
       <c r="H250" t="n">
         <v>241</v>
@@ -7648,7 +7648,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G251" t="n">
-        <v>4.35435438156128</v>
+        <v>4.35435485839844</v>
       </c>
       <c r="H251" t="n">
         <v>1595</v>
@@ -7764,7 +7764,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G255" t="n">
-        <v>4.55731201171875</v>
+        <v>4.55731248855591</v>
       </c>
       <c r="H255" t="n">
         <v>4318</v>
@@ -7793,7 +7793,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G256" t="n">
-        <v>4.52041149139404</v>
+        <v>4.52041101455688</v>
       </c>
       <c r="H256" t="n">
         <v>9927</v>
@@ -7851,7 +7851,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G258" t="n">
-        <v>4.51118564605713</v>
+        <v>4.51118516921997</v>
       </c>
       <c r="H258" t="n">
         <v>22611</v>
@@ -7967,7 +7967,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G262" t="n">
-        <v>4.74181842803955</v>
+        <v>4.74181890487671</v>
       </c>
       <c r="H262" t="n">
         <v>8453</v>
@@ -7996,7 +7996,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G263" t="n">
-        <v>4.8986496925354</v>
+        <v>4.89864921569824</v>
       </c>
       <c r="H263" t="n">
         <v>29512</v>
@@ -8025,7 +8025,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G264" t="n">
-        <v>4.88019847869873</v>
+        <v>4.88019895553589</v>
       </c>
       <c r="H264" t="n">
         <v>69249</v>
@@ -8054,7 +8054,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G265" t="n">
-        <v>4.88942432403564</v>
+        <v>4.8894248008728</v>
       </c>
       <c r="H265" t="n">
         <v>13281</v>
@@ -8083,7 +8083,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G266" t="n">
-        <v>4.88942432403564</v>
+        <v>4.8894248008728</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>4.88942432403564</v>
+        <v>4.8894248008728</v>
       </c>
       <c r="H267" t="n">
         <v>5927</v>
@@ -8141,7 +8141,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G268" t="n">
-        <v>5.02780342102051</v>
+        <v>5.02780389785767</v>
       </c>
       <c r="H268" t="n">
         <v>4916</v>
@@ -8170,7 +8170,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G269" t="n">
-        <v>4.907874584198</v>
+        <v>4.90787506103516</v>
       </c>
       <c r="H269" t="n">
         <v>54096</v>
@@ -8199,7 +8199,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G270" t="n">
-        <v>4.93555068969727</v>
+        <v>4.93555021286011</v>
       </c>
       <c r="H270" t="n">
         <v>78819</v>
@@ -8228,7 +8228,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G271" t="n">
-        <v>4.8986496925354</v>
+        <v>4.89864921569824</v>
       </c>
       <c r="H271" t="n">
         <v>10062</v>
@@ -8257,7 +8257,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G272" t="n">
-        <v>4.88942432403564</v>
+        <v>4.8894248008728</v>
       </c>
       <c r="H272" t="n">
         <v>12329</v>
@@ -8402,7 +8402,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G277" t="n">
-        <v>5.03702974319458</v>
+        <v>5.03702926635742</v>
       </c>
       <c r="H277" t="n">
         <v>22783</v>
@@ -8663,7 +8663,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G286" t="n">
-        <v>5.0923810005188</v>
+        <v>5.09238195419312</v>
       </c>
       <c r="H286" t="n">
         <v>233</v>
@@ -8750,7 +8750,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>5.14773368835449</v>
+        <v>5.14773321151733</v>
       </c>
       <c r="H289" t="n">
         <v>160</v>
@@ -8779,7 +8779,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G290" t="n">
-        <v>5.0831561088562</v>
+        <v>5.08315563201904</v>
       </c>
       <c r="H290" t="n">
         <v>100</v>
@@ -8837,7 +8837,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G292" t="n">
-        <v>5.14773368835449</v>
+        <v>5.14773321151733</v>
       </c>
       <c r="H292" t="n">
         <v>14959</v>
@@ -8953,7 +8953,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G296" t="n">
-        <v>4.907874584198</v>
+        <v>4.90787506103516</v>
       </c>
       <c r="H296" t="n">
         <v>14673</v>
@@ -9011,7 +9011,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G298" t="n">
-        <v>5.06470537185669</v>
+        <v>5.06470441818237</v>
       </c>
       <c r="H298" t="n">
         <v>39937</v>
@@ -9040,7 +9040,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>4.93555068969727</v>
+        <v>4.93555021286011</v>
       </c>
       <c r="H299" t="n">
         <v>1763</v>
@@ -9098,7 +9098,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G301" t="n">
-        <v>4.8986496925354</v>
+        <v>4.89864921569824</v>
       </c>
       <c r="H301" t="n">
         <v>49432</v>
@@ -9214,7 +9214,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G305" t="n">
-        <v>4.88942432403564</v>
+        <v>4.8894248008728</v>
       </c>
       <c r="H305" t="n">
         <v>9988</v>
@@ -9272,7 +9272,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G307" t="n">
-        <v>4.93555068969727</v>
+        <v>4.93555021286011</v>
       </c>
       <c r="H307" t="n">
         <v>1214</v>
@@ -9301,7 +9301,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>4.76949453353882</v>
+        <v>4.76949501037598</v>
       </c>
       <c r="H308" t="n">
         <v>7904</v>
@@ -9330,7 +9330,7 @@
         <v>5.25</v>
       </c>
       <c r="G309" t="n">
-        <v>4.84329700469971</v>
+        <v>4.84329748153687</v>
       </c>
       <c r="H309" t="n">
         <v>995</v>
@@ -9388,7 +9388,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G311" t="n">
-        <v>4.81562089920044</v>
+        <v>4.8156213760376</v>
       </c>
       <c r="H311" t="n">
         <v>3343</v>
@@ -9417,7 +9417,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G312" t="n">
-        <v>4.76949453353882</v>
+        <v>4.76949501037598</v>
       </c>
       <c r="H312" t="n">
         <v>4994</v>
@@ -9533,7 +9533,7 @@
         <v>5.25</v>
       </c>
       <c r="G316" t="n">
-        <v>4.84329700469971</v>
+        <v>4.84329748153687</v>
       </c>
       <c r="H316" t="n">
         <v>16</v>
@@ -9620,7 +9620,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G319" t="n">
-        <v>5.06470537185669</v>
+        <v>5.06470441818237</v>
       </c>
       <c r="H319" t="n">
         <v>4244</v>
@@ -9649,7 +9649,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>4.88019847869873</v>
+        <v>4.88019895553589</v>
       </c>
       <c r="H320" t="n">
         <v>6441</v>
@@ -9678,7 +9678,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>4.88942432403564</v>
+        <v>4.8894248008728</v>
       </c>
       <c r="H321" t="n">
         <v>34175</v>
@@ -9765,7 +9765,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G324" t="n">
-        <v>5.04625415802002</v>
+        <v>5.04625463485718</v>
       </c>
       <c r="H324" t="n">
         <v>3919</v>
@@ -9794,7 +9794,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G325" t="n">
-        <v>4.88942432403564</v>
+        <v>4.8894248008728</v>
       </c>
       <c r="H325" t="n">
         <v>2844</v>
@@ -9852,7 +9852,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G327" t="n">
-        <v>4.81562089920044</v>
+        <v>4.8156213760376</v>
       </c>
       <c r="H327" t="n">
         <v>123</v>
@@ -9910,7 +9910,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G329" t="n">
-        <v>4.79717111587524</v>
+        <v>4.79717016220093</v>
       </c>
       <c r="H329" t="n">
         <v>5909</v>
@@ -9939,7 +9939,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>4.79717111587524</v>
+        <v>4.79717016220093</v>
       </c>
       <c r="H330" t="n">
         <v>445</v>
@@ -10055,7 +10055,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G334" t="n">
-        <v>5.10160732269287</v>
+        <v>5.10160684585571</v>
       </c>
       <c r="H334" t="n">
         <v>10899</v>
@@ -10113,7 +10113,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G336" t="n">
-        <v>5.06470537185669</v>
+        <v>5.06470441818237</v>
       </c>
       <c r="H336" t="n">
         <v>610</v>
@@ -10229,7 +10229,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G340" t="n">
-        <v>4.907874584198</v>
+        <v>4.90787506103516</v>
       </c>
       <c r="H340" t="n">
         <v>9032</v>
@@ -10316,7 +10316,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G343" t="n">
-        <v>4.93555068969727</v>
+        <v>4.93555021286011</v>
       </c>
       <c r="H343" t="n">
         <v>1750</v>
@@ -10374,7 +10374,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G345" t="n">
-        <v>4.86174869537354</v>
+        <v>4.86174821853638</v>
       </c>
       <c r="H345" t="n">
         <v>3141</v>
@@ -10461,7 +10461,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G348" t="n">
-        <v>4.52963590621948</v>
+        <v>4.52963638305664</v>
       </c>
       <c r="H348" t="n">
         <v>9810</v>
@@ -10577,7 +10577,7 @@
         <v>5.25</v>
       </c>
       <c r="G352" t="n">
-        <v>4.84329700469971</v>
+        <v>4.84329748153687</v>
       </c>
       <c r="H352" t="n">
         <v>15431</v>
@@ -10606,7 +10606,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G353" t="n">
-        <v>4.88019847869873</v>
+        <v>4.88019895553589</v>
       </c>
       <c r="H353" t="n">
         <v>1026</v>
@@ -10751,7 +10751,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G358" t="n">
-        <v>5.03702974319458</v>
+        <v>5.03702926635742</v>
       </c>
       <c r="H358" t="n">
         <v>1175</v>
@@ -10780,7 +10780,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G359" t="n">
-        <v>4.88942432403564</v>
+        <v>4.8894248008728</v>
       </c>
       <c r="H359" t="n">
         <v>4186</v>
@@ -10809,7 +10809,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>4.88942432403564</v>
+        <v>4.8894248008728</v>
       </c>
       <c r="H360" t="n">
         <v>4150</v>
@@ -10838,7 +10838,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G361" t="n">
-        <v>4.88942432403564</v>
+        <v>4.8894248008728</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -11041,7 +11041,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G368" t="n">
-        <v>5.14773368835449</v>
+        <v>5.14773321151733</v>
       </c>
       <c r="H368" t="n">
         <v>5393</v>
@@ -11070,7 +11070,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G369" t="n">
-        <v>5.0923810005188</v>
+        <v>5.09238195419312</v>
       </c>
       <c r="H369" t="n">
         <v>37466</v>
@@ -11099,7 +11099,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G370" t="n">
-        <v>5.20308542251587</v>
+        <v>5.20308494567871</v>
       </c>
       <c r="H370" t="n">
         <v>5557</v>
@@ -11157,7 +11157,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G372" t="n">
-        <v>5.42449331283569</v>
+        <v>5.42449378967285</v>
       </c>
       <c r="H372" t="n">
         <v>16849</v>
@@ -11215,7 +11215,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G374" t="n">
-        <v>5.27688789367676</v>
+        <v>5.2768874168396</v>
       </c>
       <c r="H374" t="n">
         <v>2643</v>
@@ -11244,7 +11244,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G375" t="n">
-        <v>5.42449331283569</v>
+        <v>5.42449378967285</v>
       </c>
       <c r="H375" t="n">
         <v>7922</v>
@@ -11331,7 +11331,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G378" t="n">
-        <v>5.25843667984009</v>
+        <v>5.25843715667725</v>
       </c>
       <c r="H378" t="n">
         <v>4491</v>
@@ -11360,7 +11360,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G379" t="n">
-        <v>5.25843667984009</v>
+        <v>5.25843715667725</v>
       </c>
       <c r="H379" t="n">
         <v>270</v>
@@ -11389,7 +11389,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G380" t="n">
-        <v>5.27688789367676</v>
+        <v>5.2768874168396</v>
       </c>
       <c r="H380" t="n">
         <v>43761</v>
@@ -11418,7 +11418,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>5.24876976013184</v>
+        <v>5.24876928329468</v>
       </c>
       <c r="H381" t="n">
         <v>20743</v>
@@ -11505,7 +11505,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G384" t="n">
-        <v>5.473717212677</v>
+        <v>5.47371673583984</v>
       </c>
       <c r="H384" t="n">
         <v>4634</v>
@@ -11563,7 +11563,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G386" t="n">
-        <v>5.60493564605713</v>
+        <v>5.60493612289429</v>
       </c>
       <c r="H386" t="n">
         <v>24572</v>
@@ -11592,7 +11592,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G387" t="n">
-        <v>5.66117238998413</v>
+        <v>5.66117286682129</v>
       </c>
       <c r="H387" t="n">
         <v>23023</v>
@@ -11679,7 +11679,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H390" t="n">
         <v>24702</v>
@@ -11708,7 +11708,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G391" t="n">
-        <v>5.24876976013184</v>
+        <v>5.24876928329468</v>
       </c>
       <c r="H391" t="n">
         <v>7298</v>
@@ -11737,7 +11737,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G392" t="n">
-        <v>5.24876976013184</v>
+        <v>5.24876928329468</v>
       </c>
       <c r="H392" t="n">
         <v>2740</v>
@@ -11766,7 +11766,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G393" t="n">
-        <v>5.24876976013184</v>
+        <v>5.24876928329468</v>
       </c>
       <c r="H393" t="n">
         <v>16929</v>
@@ -11795,7 +11795,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G394" t="n">
-        <v>5.32375192642212</v>
+        <v>5.32375144958496</v>
       </c>
       <c r="H394" t="n">
         <v>680</v>
@@ -11882,7 +11882,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G397" t="n">
-        <v>5.473717212677</v>
+        <v>5.47371673583984</v>
       </c>
       <c r="H397" t="n">
         <v>2362</v>
@@ -11911,7 +11911,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>5.58619022369385</v>
+        <v>5.58619070053101</v>
       </c>
       <c r="H398" t="n">
         <v>3700</v>
@@ -12056,7 +12056,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G403" t="n">
-        <v>5.58619022369385</v>
+        <v>5.58619070053101</v>
       </c>
       <c r="H403" t="n">
         <v>430</v>
@@ -12114,7 +12114,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H405" t="n">
         <v>1418</v>
@@ -12288,7 +12288,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H411" t="n">
         <v>200</v>
@@ -12404,7 +12404,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H415" t="n">
         <v>100</v>
@@ -12433,7 +12433,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G416" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H416" t="n">
         <v>45</v>
@@ -12520,7 +12520,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G419" t="n">
-        <v>5.473717212677</v>
+        <v>5.47371673583984</v>
       </c>
       <c r="H419" t="n">
         <v>560</v>
@@ -12549,7 +12549,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G420" t="n">
-        <v>5.473717212677</v>
+        <v>5.47371673583984</v>
       </c>
       <c r="H420" t="n">
         <v>10242</v>
@@ -12607,7 +12607,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G422" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H422" t="n">
         <v>18970</v>
@@ -12665,7 +12665,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G424" t="n">
-        <v>5.45497131347656</v>
+        <v>5.4549708366394</v>
       </c>
       <c r="H424" t="n">
         <v>8384</v>
@@ -12752,7 +12752,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G427" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H427" t="n">
         <v>4203</v>
@@ -12781,7 +12781,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G428" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H428" t="n">
         <v>760</v>
@@ -12955,7 +12955,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G434" t="n">
-        <v>5.473717212677</v>
+        <v>5.47371673583984</v>
       </c>
       <c r="H434" t="n">
         <v>170</v>
@@ -13042,7 +13042,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H437" t="n">
         <v>7332</v>
@@ -13071,7 +13071,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H438" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H444" t="n">
         <v>10</v>
@@ -13332,7 +13332,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G447" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H447" t="n">
         <v>20</v>
@@ -13361,7 +13361,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G448" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H448" t="n">
         <v>2255</v>
@@ -13390,7 +13390,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G449" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H449" t="n">
         <v>300</v>
@@ -13448,7 +13448,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G451" t="n">
-        <v>5.32375192642212</v>
+        <v>5.32375144958496</v>
       </c>
       <c r="H451" t="n">
         <v>924</v>
@@ -13477,7 +13477,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G452" t="n">
-        <v>5.32375192642212</v>
+        <v>5.32375144958496</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G453" t="n">
-        <v>5.32375192642212</v>
+        <v>5.32375144958496</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13593,7 +13593,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G456" t="n">
-        <v>5.43622589111328</v>
+        <v>5.43622541427612</v>
       </c>
       <c r="H456" t="n">
         <v>20122</v>
@@ -13622,7 +13622,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G457" t="n">
-        <v>5.473717212677</v>
+        <v>5.47371673583984</v>
       </c>
       <c r="H457" t="n">
         <v>3375</v>
@@ -13999,7 +13999,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G470" t="n">
-        <v>5.24876976013184</v>
+        <v>5.24876928329468</v>
       </c>
       <c r="H470" t="n">
         <v>2437</v>
@@ -14173,7 +14173,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G476" t="n">
-        <v>5.02382230758667</v>
+        <v>5.02382278442383</v>
       </c>
       <c r="H476" t="n">
         <v>311</v>
@@ -14202,7 +14202,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G477" t="n">
-        <v>4.93009424209595</v>
+        <v>4.93009471893311</v>
       </c>
       <c r="H477" t="n">
         <v>5511</v>
@@ -14289,7 +14289,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G480" t="n">
-        <v>4.7988748550415</v>
+        <v>4.79887437820435</v>
       </c>
       <c r="H480" t="n">
         <v>900</v>
@@ -14318,7 +14318,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H481" t="n">
         <v>16552</v>
@@ -14347,7 +14347,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G482" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H482" t="n">
         <v>1000</v>
@@ -14376,7 +14376,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G483" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14405,7 +14405,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G484" t="n">
-        <v>4.78012895584106</v>
+        <v>4.78012943267822</v>
       </c>
       <c r="H484" t="n">
         <v>250</v>
@@ -14492,7 +14492,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G487" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H487" t="n">
         <v>1050</v>
@@ -14579,7 +14579,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>4.64891052246094</v>
+        <v>4.64891004562378</v>
       </c>
       <c r="H490" t="n">
         <v>2650</v>
@@ -14666,7 +14666,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G493" t="n">
-        <v>4.5645546913147</v>
+        <v>4.56455421447754</v>
       </c>
       <c r="H493" t="n">
         <v>1016</v>
@@ -14695,7 +14695,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G494" t="n">
-        <v>4.64891052246094</v>
+        <v>4.64891004562378</v>
       </c>
       <c r="H494" t="n">
         <v>21434</v>
@@ -14811,7 +14811,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G498" t="n">
-        <v>4.6770281791687</v>
+        <v>4.67702865600586</v>
       </c>
       <c r="H498" t="n">
         <v>3536</v>
@@ -14840,7 +14840,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G499" t="n">
-        <v>4.78012895584106</v>
+        <v>4.78012943267822</v>
       </c>
       <c r="H499" t="n">
         <v>12994</v>
@@ -14898,7 +14898,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>4.83636617660522</v>
+        <v>4.83636569976807</v>
       </c>
       <c r="H501" t="n">
         <v>9387</v>
@@ -14956,7 +14956,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G503" t="n">
-        <v>4.87385749816895</v>
+        <v>4.87385654449463</v>
       </c>
       <c r="H503" t="n">
         <v>15019</v>
@@ -15043,7 +15043,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G506" t="n">
-        <v>4.78012895584106</v>
+        <v>4.78012943267822</v>
       </c>
       <c r="H506" t="n">
         <v>2350</v>
@@ -15072,7 +15072,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>4.78012895584106</v>
+        <v>4.78012943267822</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -15101,7 +15101,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G508" t="n">
-        <v>4.7988748550415</v>
+        <v>4.79887437820435</v>
       </c>
       <c r="H508" t="n">
         <v>80250</v>
@@ -15188,7 +15188,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G511" t="n">
-        <v>5.02382230758667</v>
+        <v>5.02382278442383</v>
       </c>
       <c r="H511" t="n">
         <v>4402</v>
@@ -15217,7 +15217,7 @@
         <v>5.5</v>
       </c>
       <c r="G512" t="n">
-        <v>5.15504121780396</v>
+        <v>5.15504169464111</v>
       </c>
       <c r="H512" t="n">
         <v>4203</v>
@@ -15275,7 +15275,7 @@
         <v>5.5</v>
       </c>
       <c r="G514" t="n">
-        <v>5.15504121780396</v>
+        <v>5.15504169464111</v>
       </c>
       <c r="H514" t="n">
         <v>1884</v>
@@ -15304,7 +15304,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G515" t="n">
-        <v>5.00507640838623</v>
+        <v>5.00507688522339</v>
       </c>
       <c r="H515" t="n">
         <v>632</v>
@@ -15333,7 +15333,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G516" t="n">
-        <v>5.00507640838623</v>
+        <v>5.00507688522339</v>
       </c>
       <c r="H516" t="n">
         <v>0</v>
@@ -15391,7 +15391,7 @@
         <v>5.5</v>
       </c>
       <c r="G518" t="n">
-        <v>5.15504121780396</v>
+        <v>5.15504169464111</v>
       </c>
       <c r="H518" t="n">
         <v>6482</v>
@@ -15449,7 +15449,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G520" t="n">
-        <v>5.02382230758667</v>
+        <v>5.02382278442383</v>
       </c>
       <c r="H520" t="n">
         <v>1669</v>
@@ -15536,7 +15536,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G523" t="n">
-        <v>4.96758508682251</v>
+        <v>4.96758556365967</v>
       </c>
       <c r="H523" t="n">
         <v>560</v>
@@ -15594,7 +15594,7 @@
         <v>5.5</v>
       </c>
       <c r="G525" t="n">
-        <v>5.15504121780396</v>
+        <v>5.15504169464111</v>
       </c>
       <c r="H525" t="n">
         <v>3840</v>
@@ -15710,7 +15710,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G529" t="n">
-        <v>4.87385749816895</v>
+        <v>4.87385654449463</v>
       </c>
       <c r="H529" t="n">
         <v>22898</v>
@@ -15797,7 +15797,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G532" t="n">
-        <v>4.78012895584106</v>
+        <v>4.78012943267822</v>
       </c>
       <c r="H532" t="n">
         <v>121</v>
@@ -15855,7 +15855,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G534" t="n">
-        <v>4.87385749816895</v>
+        <v>4.87385654449463</v>
       </c>
       <c r="H534" t="n">
         <v>2718</v>
@@ -15884,7 +15884,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>4.87385749816895</v>
+        <v>4.87385654449463</v>
       </c>
       <c r="H535" t="n">
         <v>12616</v>
@@ -15942,7 +15942,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G537" t="n">
-        <v>4.78012895584106</v>
+        <v>4.78012943267822</v>
       </c>
       <c r="H537" t="n">
         <v>5650</v>
@@ -15971,7 +15971,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G538" t="n">
-        <v>4.7988748550415</v>
+        <v>4.79887437820435</v>
       </c>
       <c r="H538" t="n">
         <v>11050</v>
@@ -16029,7 +16029,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G540" t="n">
-        <v>4.78012895584106</v>
+        <v>4.78012943267822</v>
       </c>
       <c r="H540" t="n">
         <v>250</v>
@@ -16058,7 +16058,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G541" t="n">
-        <v>4.87385749816895</v>
+        <v>4.87385654449463</v>
       </c>
       <c r="H541" t="n">
         <v>1794</v>
@@ -16087,7 +16087,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G542" t="n">
-        <v>4.93009424209595</v>
+        <v>4.93009471893311</v>
       </c>
       <c r="H542" t="n">
         <v>2795</v>
@@ -16116,7 +16116,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G543" t="n">
-        <v>4.87385749816895</v>
+        <v>4.87385654449463</v>
       </c>
       <c r="H543" t="n">
         <v>4438</v>
@@ -16145,7 +16145,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G544" t="n">
-        <v>4.7988748550415</v>
+        <v>4.79887437820435</v>
       </c>
       <c r="H544" t="n">
         <v>1500</v>
@@ -16203,7 +16203,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G546" t="n">
-        <v>4.78012895584106</v>
+        <v>4.78012943267822</v>
       </c>
       <c r="H546" t="n">
         <v>3803</v>
@@ -16232,7 +16232,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G547" t="n">
-        <v>4.78012895584106</v>
+        <v>4.78012943267822</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G548" t="n">
-        <v>4.78012895584106</v>
+        <v>4.78012943267822</v>
       </c>
       <c r="H548" t="n">
         <v>0</v>
@@ -16290,7 +16290,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G549" t="n">
-        <v>4.74263763427734</v>
+        <v>4.7426381111145</v>
       </c>
       <c r="H549" t="n">
         <v>400</v>
@@ -16377,7 +16377,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H552" t="n">
         <v>2770</v>
@@ -16464,7 +16464,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>4.72389268875122</v>
+        <v>4.72389221191406</v>
       </c>
       <c r="H555" t="n">
         <v>1730</v>
@@ -16609,7 +16609,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>4.59267282485962</v>
+        <v>4.59267330169678</v>
       </c>
       <c r="H560" t="n">
         <v>2062</v>
@@ -16638,7 +16638,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G561" t="n">
-        <v>4.59267282485962</v>
+        <v>4.59267330169678</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -16667,7 +16667,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G562" t="n">
-        <v>4.7988748550415</v>
+        <v>4.79887437820435</v>
       </c>
       <c r="H562" t="n">
         <v>5341</v>
@@ -16696,7 +16696,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G563" t="n">
-        <v>4.83636617660522</v>
+        <v>4.83636569976807</v>
       </c>
       <c r="H563" t="n">
         <v>5514</v>
@@ -16725,7 +16725,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G564" t="n">
-        <v>4.98633098602295</v>
+        <v>4.98633146286011</v>
       </c>
       <c r="H564" t="n">
         <v>4495</v>
@@ -16957,7 +16957,7 @@
         <v>4.25</v>
       </c>
       <c r="G572" t="n">
-        <v>3.98344135284424</v>
+        <v>3.9834406375885</v>
       </c>
       <c r="H572" t="n">
         <v>9140</v>
@@ -17334,7 +17334,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G585" t="n">
-        <v>4.00218677520752</v>
+        <v>4.00218629837036</v>
       </c>
       <c r="H585" t="n">
         <v>1475</v>
@@ -17363,7 +17363,7 @@
         <v>4.25</v>
       </c>
       <c r="G586" t="n">
-        <v>3.98344135284424</v>
+        <v>3.9834406375885</v>
       </c>
       <c r="H586" t="n">
         <v>2353</v>
@@ -17392,7 +17392,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G587" t="n">
-        <v>3.92720437049866</v>
+        <v>3.92720413208008</v>
       </c>
       <c r="H587" t="n">
         <v>1105</v>
@@ -17566,7 +17566,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G593" t="n">
-        <v>4.03967761993408</v>
+        <v>4.03967809677124</v>
       </c>
       <c r="H593" t="n">
         <v>12527</v>
@@ -17595,7 +17595,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G594" t="n">
-        <v>4.00218677520752</v>
+        <v>4.00218629837036</v>
       </c>
       <c r="H594" t="n">
         <v>22055</v>
@@ -17682,7 +17682,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G597" t="n">
-        <v>4.06779670715332</v>
+        <v>4.06779623031616</v>
       </c>
       <c r="H597" t="n">
         <v>2200</v>
@@ -17711,7 +17711,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G598" t="n">
-        <v>4.10528802871704</v>
+        <v>4.10528755187988</v>
       </c>
       <c r="H598" t="n">
         <v>5102</v>
@@ -17740,7 +17740,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G599" t="n">
-        <v>4.10528802871704</v>
+        <v>4.10528755187988</v>
       </c>
       <c r="H599" t="n">
         <v>4178</v>
@@ -17769,7 +17769,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G600" t="n">
-        <v>4.10528802871704</v>
+        <v>4.10528755187988</v>
       </c>
       <c r="H600" t="n">
         <v>2406</v>
@@ -17856,7 +17856,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G603" t="n">
-        <v>4.10528802871704</v>
+        <v>4.10528755187988</v>
       </c>
       <c r="H603" t="n">
         <v>5008</v>
@@ -17885,7 +17885,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G604" t="n">
-        <v>4.10528802871704</v>
+        <v>4.10528755187988</v>
       </c>
       <c r="H604" t="n">
         <v>7230</v>
@@ -17972,7 +17972,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G607" t="n">
-        <v>4.1334056854248</v>
+        <v>4.13340616226196</v>
       </c>
       <c r="H607" t="n">
         <v>55370</v>
@@ -18001,7 +18001,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G608" t="n">
-        <v>4.12403297424316</v>
+        <v>4.12403345108032</v>
       </c>
       <c r="H608" t="n">
         <v>2894</v>
@@ -18030,7 +18030,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G609" t="n">
-        <v>4.00218677520752</v>
+        <v>4.00218629837036</v>
       </c>
       <c r="H609" t="n">
         <v>1958</v>
@@ -18059,7 +18059,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G610" t="n">
-        <v>4.00218677520752</v>
+        <v>4.00218629837036</v>
       </c>
       <c r="H610" t="n">
         <v>2262</v>
@@ -18088,7 +18088,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G611" t="n">
-        <v>4.05842351913452</v>
+        <v>4.05842399597168</v>
       </c>
       <c r="H611" t="n">
         <v>2515</v>
@@ -18117,7 +18117,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>4.09591436386108</v>
+        <v>4.09591484069824</v>
       </c>
       <c r="H612" t="n">
         <v>401</v>
@@ -18146,7 +18146,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G613" t="n">
-        <v>4.09591436386108</v>
+        <v>4.09591484069824</v>
       </c>
       <c r="H613" t="n">
         <v>0</v>
@@ -18175,7 +18175,7 @@
         <v>4.25</v>
       </c>
       <c r="G614" t="n">
-        <v>3.98344135284424</v>
+        <v>3.9834406375885</v>
       </c>
       <c r="H614" t="n">
         <v>2924</v>
@@ -18204,7 +18204,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G615" t="n">
-        <v>4.03967761993408</v>
+        <v>4.03967809677124</v>
       </c>
       <c r="H615" t="n">
         <v>320</v>
@@ -18233,7 +18233,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G616" t="n">
-        <v>3.92720437049866</v>
+        <v>3.92720413208008</v>
       </c>
       <c r="H616" t="n">
         <v>3977</v>
@@ -18262,7 +18262,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G617" t="n">
-        <v>3.87096738815308</v>
+        <v>3.87096762657166</v>
       </c>
       <c r="H617" t="n">
         <v>5257</v>
@@ -18639,7 +18639,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G630" t="n">
-        <v>3.68351125717163</v>
+        <v>3.68351149559021</v>
       </c>
       <c r="H630" t="n">
         <v>9933</v>
@@ -18668,7 +18668,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G631" t="n">
-        <v>3.66476583480835</v>
+        <v>3.66476607322693</v>
       </c>
       <c r="H631" t="n">
         <v>2461</v>
@@ -18697,7 +18697,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G632" t="n">
-        <v>3.64602017402649</v>
+        <v>3.64602041244507</v>
       </c>
       <c r="H632" t="n">
         <v>3650</v>
@@ -18755,7 +18755,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G634" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H634" t="n">
         <v>3900</v>
@@ -18784,7 +18784,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G635" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H635" t="n">
         <v>6237</v>
@@ -18813,7 +18813,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G636" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H636" t="n">
         <v>7752</v>
@@ -18842,7 +18842,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G637" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H637" t="n">
         <v>1500</v>
@@ -18871,7 +18871,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G638" t="n">
-        <v>3.71341013908386</v>
+        <v>3.71341037750244</v>
       </c>
       <c r="H638" t="n">
         <v>8760</v>
@@ -18900,7 +18900,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G639" t="n">
-        <v>3.71341013908386</v>
+        <v>3.71341037750244</v>
       </c>
       <c r="H639" t="n">
         <v>0</v>
@@ -18929,7 +18929,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G640" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H640" t="n">
         <v>1052</v>
@@ -18958,7 +18958,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G641" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H641" t="n">
         <v>10</v>
@@ -18987,7 +18987,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G642" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H642" t="n">
         <v>90</v>
@@ -19103,7 +19103,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G646" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H646" t="n">
         <v>13400</v>
@@ -19190,7 +19190,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G649" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H649" t="n">
         <v>4153</v>
@@ -19248,7 +19248,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G651" t="n">
-        <v>3.65583825111389</v>
+        <v>3.65583801269531</v>
       </c>
       <c r="H651" t="n">
         <v>900</v>
@@ -19277,7 +19277,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>3.65583825111389</v>
+        <v>3.65583801269531</v>
       </c>
       <c r="H652" t="n">
         <v>10</v>
@@ -19335,7 +19335,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G654" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H654" t="n">
         <v>3015</v>
@@ -19393,7 +19393,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G656" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H656" t="n">
         <v>3182</v>
@@ -19422,7 +19422,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H657" t="n">
         <v>1517</v>
@@ -19480,7 +19480,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G659" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H659" t="n">
         <v>100</v>
@@ -19509,7 +19509,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G660" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H660" t="n">
         <v>299</v>
@@ -19538,7 +19538,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G661" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H661" t="n">
         <v>1404</v>
@@ -19567,7 +19567,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G662" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H662" t="n">
         <v>0</v>
@@ -19625,7 +19625,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G664" t="n">
-        <v>3.72300577163696</v>
+        <v>3.72300601005554</v>
       </c>
       <c r="H664" t="n">
         <v>800</v>
@@ -19712,7 +19712,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>4.12601137161255</v>
+        <v>4.12601184844971</v>
       </c>
       <c r="H667" t="n">
         <v>45390</v>
@@ -19770,7 +19770,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G669" t="n">
-        <v>4.12601137161255</v>
+        <v>4.12601184844971</v>
       </c>
       <c r="H669" t="n">
         <v>8487</v>
@@ -19799,7 +19799,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G670" t="n">
-        <v>4.12601137161255</v>
+        <v>4.12601184844971</v>
       </c>
       <c r="H670" t="n">
         <v>2970</v>
@@ -19973,7 +19973,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G676" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H676" t="n">
         <v>1500</v>
@@ -20089,7 +20089,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G680" t="n">
-        <v>4.02046251296997</v>
+        <v>4.02046203613281</v>
       </c>
       <c r="H680" t="n">
         <v>1420</v>
@@ -20118,7 +20118,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G681" t="n">
-        <v>3.99167633056641</v>
+        <v>3.99167609214783</v>
       </c>
       <c r="H681" t="n">
         <v>1555</v>
@@ -20176,7 +20176,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G683" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H683" t="n">
         <v>10</v>
@@ -20205,7 +20205,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H684" t="n">
         <v>9595</v>
@@ -20292,7 +20292,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G687" t="n">
-        <v>3.99167633056641</v>
+        <v>3.99167609214783</v>
       </c>
       <c r="H687" t="n">
         <v>750</v>
@@ -20321,7 +20321,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G688" t="n">
-        <v>3.99167633056641</v>
+        <v>3.99167609214783</v>
       </c>
       <c r="H688" t="n">
         <v>0</v>
@@ -20350,7 +20350,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G689" t="n">
-        <v>3.98208069801331</v>
+        <v>3.98208093643188</v>
       </c>
       <c r="H689" t="n">
         <v>150</v>
@@ -20379,7 +20379,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>4.03965330123901</v>
+        <v>4.03965282440186</v>
       </c>
       <c r="H690" t="n">
         <v>1160</v>
@@ -20408,7 +20408,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>4.03965330123901</v>
+        <v>4.03965282440186</v>
       </c>
       <c r="H691" t="n">
         <v>10</v>
@@ -20437,7 +20437,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H692" t="n">
         <v>11</v>
@@ -20466,7 +20466,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G693" t="n">
-        <v>4.03965330123901</v>
+        <v>4.03965282440186</v>
       </c>
       <c r="H693" t="n">
         <v>1069</v>
@@ -20524,7 +20524,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G695" t="n">
-        <v>3.98208069801331</v>
+        <v>3.98208093643188</v>
       </c>
       <c r="H695" t="n">
         <v>1981</v>
@@ -20553,7 +20553,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>3.98208069801331</v>
+        <v>3.98208093643188</v>
       </c>
       <c r="H696" t="n">
         <v>0</v>
@@ -20582,7 +20582,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>3.98208069801331</v>
+        <v>3.98208093643188</v>
       </c>
       <c r="H697" t="n">
         <v>120</v>
@@ -20611,7 +20611,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G698" t="n">
-        <v>4.02046251296997</v>
+        <v>4.02046203613281</v>
       </c>
       <c r="H698" t="n">
         <v>245</v>
@@ -20669,7 +20669,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G700" t="n">
-        <v>3.94369959831238</v>
+        <v>3.9436993598938</v>
       </c>
       <c r="H700" t="n">
         <v>210</v>
@@ -20698,7 +20698,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G701" t="n">
-        <v>3.94369959831238</v>
+        <v>3.9436993598938</v>
       </c>
       <c r="H701" t="n">
         <v>280</v>
@@ -20930,7 +20930,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G709" t="n">
-        <v>3.87653183937073</v>
+        <v>3.87653160095215</v>
       </c>
       <c r="H709" t="n">
         <v>1788</v>
@@ -21017,7 +21017,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G712" t="n">
-        <v>3.9341037273407</v>
+        <v>3.93410396575928</v>
       </c>
       <c r="H712" t="n">
         <v>3931</v>
@@ -21046,7 +21046,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G713" t="n">
-        <v>3.84774565696716</v>
+        <v>3.84774589538574</v>
       </c>
       <c r="H713" t="n">
         <v>5760</v>
@@ -21075,7 +21075,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G714" t="n">
-        <v>3.79017329216003</v>
+        <v>3.79017353057861</v>
       </c>
       <c r="H714" t="n">
         <v>185</v>
@@ -21104,7 +21104,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G715" t="n">
-        <v>3.77098250389099</v>
+        <v>3.77098274230957</v>
       </c>
       <c r="H715" t="n">
         <v>540</v>
@@ -21133,7 +21133,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G716" t="n">
-        <v>3.75179171562195</v>
+        <v>3.75179195404053</v>
       </c>
       <c r="H716" t="n">
         <v>330</v>
@@ -21162,7 +21162,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G717" t="n">
-        <v>3.75179171562195</v>
+        <v>3.75179195404053</v>
       </c>
       <c r="H717" t="n">
         <v>0</v>
@@ -21191,7 +21191,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G718" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H718" t="n">
         <v>20488</v>
@@ -21249,7 +21249,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G720" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H720" t="n">
         <v>1602</v>
@@ -21336,7 +21336,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>3.91491317749023</v>
+        <v>3.91491341590881</v>
       </c>
       <c r="H723" t="n">
         <v>750</v>
@@ -21365,7 +21365,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G724" t="n">
-        <v>4.21236944198608</v>
+        <v>4.21236991882324</v>
       </c>
       <c r="H724" t="n">
         <v>46988</v>
@@ -21423,7 +21423,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G726" t="n">
-        <v>4.21236944198608</v>
+        <v>4.21236991882324</v>
       </c>
       <c r="H726" t="n">
         <v>70435</v>
@@ -21481,7 +21481,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G728" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H728" t="n">
         <v>172</v>
@@ -21597,7 +21597,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G732" t="n">
-        <v>4.18358421325684</v>
+        <v>4.18358373641968</v>
       </c>
       <c r="H732" t="n">
         <v>1320</v>
@@ -21742,7 +21742,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G737" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H737" t="n">
         <v>1637</v>
@@ -21771,7 +21771,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G738" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H738" t="n">
         <v>75279</v>
@@ -21800,7 +21800,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G739" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H739" t="n">
         <v>0</v>
@@ -21829,7 +21829,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G740" t="n">
-        <v>3.99167633056641</v>
+        <v>3.99167609214783</v>
       </c>
       <c r="H740" t="n">
         <v>7953</v>
@@ -21974,7 +21974,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G745" t="n">
-        <v>3.9341037273407</v>
+        <v>3.93410396575928</v>
       </c>
       <c r="H745" t="n">
         <v>81270</v>
@@ -22003,7 +22003,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G746" t="n">
-        <v>3.9341037273407</v>
+        <v>3.93410396575928</v>
       </c>
       <c r="H746" t="n">
         <v>3945</v>
@@ -22032,7 +22032,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>3.91491317749023</v>
+        <v>3.91491341590881</v>
       </c>
       <c r="H747" t="n">
         <v>196255</v>
@@ -22119,7 +22119,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G750" t="n">
-        <v>4.05884408950806</v>
+        <v>4.0588436126709</v>
       </c>
       <c r="H750" t="n">
         <v>1996</v>
@@ -22148,7 +22148,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G751" t="n">
-        <v>3.98208069801331</v>
+        <v>3.98208093643188</v>
       </c>
       <c r="H751" t="n">
         <v>7044</v>
@@ -22206,7 +22206,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G753" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H753" t="n">
         <v>7875</v>
@@ -22235,7 +22235,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>4.03965330123901</v>
+        <v>4.03965282440186</v>
       </c>
       <c r="H754" t="n">
         <v>498</v>
@@ -22264,7 +22264,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G755" t="n">
-        <v>3.91491317749023</v>
+        <v>3.91491341590881</v>
       </c>
       <c r="H755" t="n">
         <v>21081</v>
@@ -22641,7 +22641,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>3.63664746284485</v>
+        <v>3.63664722442627</v>
       </c>
       <c r="H768" t="n">
         <v>8155</v>
@@ -22670,7 +22670,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G769" t="n">
-        <v>3.61745667457581</v>
+        <v>3.61745643615723</v>
       </c>
       <c r="H769" t="n">
         <v>19701</v>
@@ -22786,7 +22786,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G773" t="n">
-        <v>3.61745667457581</v>
+        <v>3.61745643615723</v>
       </c>
       <c r="H773" t="n">
         <v>16809</v>
@@ -22902,7 +22902,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>3.63664746284485</v>
+        <v>3.63664722442627</v>
       </c>
       <c r="H777" t="n">
         <v>23488</v>
@@ -22931,7 +22931,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G778" t="n">
-        <v>3.63664746284485</v>
+        <v>3.63664722442627</v>
       </c>
       <c r="H778" t="n">
         <v>5020</v>
@@ -23105,7 +23105,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G784" t="n">
-        <v>3.40635824203491</v>
+        <v>3.40635848045349</v>
       </c>
       <c r="H784" t="n">
         <v>13684</v>
@@ -23192,7 +23192,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H787" t="n">
         <v>1420</v>
@@ -23221,7 +23221,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G788" t="n">
-        <v>3.65583825111389</v>
+        <v>3.65583801269531</v>
       </c>
       <c r="H788" t="n">
         <v>1250</v>
@@ -23627,7 +23627,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G802" t="n">
-        <v>3.53109812736511</v>
+        <v>3.53109836578369</v>
       </c>
       <c r="H802" t="n">
         <v>18225</v>
@@ -23772,7 +23772,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G807" t="n">
-        <v>3.53109812736511</v>
+        <v>3.53109836578369</v>
       </c>
       <c r="H807" t="n">
         <v>6020</v>
@@ -23801,7 +23801,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>3.55988454818726</v>
+        <v>3.55988430976868</v>
       </c>
       <c r="H808" t="n">
         <v>5589</v>
@@ -23859,7 +23859,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G810" t="n">
-        <v>3.60786128044128</v>
+        <v>3.60786104202271</v>
       </c>
       <c r="H810" t="n">
         <v>35932</v>
@@ -23888,7 +23888,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G811" t="n">
-        <v>3.68462419509888</v>
+        <v>3.6846239566803</v>
       </c>
       <c r="H811" t="n">
         <v>3848</v>
@@ -23917,7 +23917,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G812" t="n">
-        <v>3.67502880096436</v>
+        <v>3.67502856254578</v>
       </c>
       <c r="H812" t="n">
         <v>10695</v>
@@ -23946,7 +23946,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G813" t="n">
-        <v>3.71341013908386</v>
+        <v>3.71341037750244</v>
       </c>
       <c r="H813" t="n">
         <v>3973</v>
@@ -23975,7 +23975,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G814" t="n">
-        <v>3.79017329216003</v>
+        <v>3.79017353057861</v>
       </c>
       <c r="H814" t="n">
         <v>8700</v>
@@ -24004,7 +24004,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G815" t="n">
-        <v>3.75179171562195</v>
+        <v>3.75179195404053</v>
       </c>
       <c r="H815" t="n">
         <v>4141</v>
@@ -24091,7 +24091,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>3.91491317749023</v>
+        <v>3.91491341590881</v>
       </c>
       <c r="H818" t="n">
         <v>4284</v>
@@ -24120,7 +24120,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G819" t="n">
-        <v>4.25075101852417</v>
+        <v>4.25075149536133</v>
       </c>
       <c r="H819" t="n">
         <v>51273</v>
@@ -24236,7 +24236,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G823" t="n">
-        <v>4.25075101852417</v>
+        <v>4.25075149536133</v>
       </c>
       <c r="H823" t="n">
         <v>21761</v>
@@ -24265,7 +24265,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G824" t="n">
-        <v>4.29872846603394</v>
+        <v>4.29872798919678</v>
       </c>
       <c r="H824" t="n">
         <v>12287</v>
@@ -24352,7 +24352,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G827" t="n">
-        <v>4.26994180679321</v>
+        <v>4.26994228363037</v>
       </c>
       <c r="H827" t="n">
         <v>3147</v>
@@ -24613,7 +24613,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G836" t="n">
-        <v>4.09722566604614</v>
+        <v>4.09722518920898</v>
       </c>
       <c r="H836" t="n">
         <v>440</v>
@@ -24642,7 +24642,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G837" t="n">
-        <v>4.12601137161255</v>
+        <v>4.12601184844971</v>
       </c>
       <c r="H837" t="n">
         <v>1700</v>
@@ -24874,7 +24874,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G845" t="n">
-        <v>4.12601137161255</v>
+        <v>4.12601184844971</v>
       </c>
       <c r="H845" t="n">
         <v>1616</v>
@@ -24903,7 +24903,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G846" t="n">
-        <v>4.12601137161255</v>
+        <v>4.12601184844971</v>
       </c>
       <c r="H846" t="n">
         <v>0</v>
@@ -25193,7 +25193,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G856" t="n">
-        <v>4.21236944198608</v>
+        <v>4.21236991882324</v>
       </c>
       <c r="H856" t="n">
         <v>12800</v>
@@ -25251,7 +25251,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G858" t="n">
-        <v>4.02046251296997</v>
+        <v>4.02046203613281</v>
       </c>
       <c r="H858" t="n">
         <v>3537</v>
@@ -25309,7 +25309,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G860" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H860" t="n">
         <v>2994</v>
@@ -25338,7 +25338,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G861" t="n">
-        <v>4.01086664199829</v>
+        <v>4.01086711883545</v>
       </c>
       <c r="H861" t="n">
         <v>280</v>
@@ -25657,7 +25657,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G872" t="n">
-        <v>3.91491317749023</v>
+        <v>3.91491341590881</v>
       </c>
       <c r="H872" t="n">
         <v>1409</v>
@@ -25686,7 +25686,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G873" t="n">
-        <v>3.91491317749023</v>
+        <v>3.91491341590881</v>
       </c>
       <c r="H873" t="n">
         <v>4382</v>
@@ -25831,7 +25831,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G878" t="n">
-        <v>3.97248530387878</v>
+        <v>3.97248554229736</v>
       </c>
       <c r="H878" t="n">
         <v>850</v>
@@ -25860,7 +25860,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G879" t="n">
-        <v>3.94369959831238</v>
+        <v>3.9436993598938</v>
       </c>
       <c r="H879" t="n">
         <v>3403</v>
@@ -25889,7 +25889,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G880" t="n">
-        <v>3.99167633056641</v>
+        <v>3.99167609214783</v>
       </c>
       <c r="H880" t="n">
         <v>17094</v>
@@ -25918,7 +25918,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G881" t="n">
-        <v>3.97248530387878</v>
+        <v>3.97248554229736</v>
       </c>
       <c r="H881" t="n">
         <v>7211</v>
@@ -26005,7 +26005,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G884" t="n">
-        <v>3.98208069801331</v>
+        <v>3.98208093643188</v>
       </c>
       <c r="H884" t="n">
         <v>2973</v>
@@ -36857,6 +36857,35 @@
         <v>84038</v>
       </c>
       <c r="I1258" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1259" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1259" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="D1259" t="n">
+        <v>5.1399998664856</v>
+      </c>
+      <c r="E1259" t="n">
+        <v>5.01999998092651</v>
+      </c>
+      <c r="F1259" t="n">
+        <v>5.1399998664856</v>
+      </c>
+      <c r="G1259" t="n">
+        <v>5.1399998664856</v>
+      </c>
+      <c r="H1259" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I1259" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RFG.MI.xlsx
+++ b/data/RFG.MI.xlsx
@@ -485,7 +485,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G4" t="n">
-        <v>4.40178394317627</v>
+        <v>4.40178442001343</v>
       </c>
       <c r="H4" t="n">
         <v>167566</v>
@@ -514,7 +514,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G5" t="n">
-        <v>4.30648803710938</v>
+        <v>4.30648756027222</v>
       </c>
       <c r="H5" t="n">
         <v>223483</v>
@@ -572,7 +572,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>4.35640525817871</v>
+        <v>4.35640573501587</v>
       </c>
       <c r="H7" t="n">
         <v>53988</v>
@@ -601,7 +601,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G8" t="n">
-        <v>4.22934341430664</v>
+        <v>4.22934293746948</v>
       </c>
       <c r="H8" t="n">
         <v>147200</v>
@@ -630,7 +630,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G9" t="n">
-        <v>4.07505416870117</v>
+        <v>4.07505369186401</v>
       </c>
       <c r="H9" t="n">
         <v>88738</v>
@@ -659,7 +659,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G10" t="n">
-        <v>4.17034959793091</v>
+        <v>4.17035007476807</v>
       </c>
       <c r="H10" t="n">
         <v>39798</v>
@@ -717,7 +717,7 @@
         <v>4.61499977111816</v>
       </c>
       <c r="G12" t="n">
-        <v>4.18850231170654</v>
+        <v>4.18850183486938</v>
       </c>
       <c r="H12" t="n">
         <v>43700</v>
@@ -833,7 +833,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G16" t="n">
-        <v>4.29741191864014</v>
+        <v>4.29741287231445</v>
       </c>
       <c r="H16" t="n">
         <v>16165</v>
@@ -891,7 +891,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G18" t="n">
-        <v>4.32463979721069</v>
+        <v>4.32463932037354</v>
       </c>
       <c r="H18" t="n">
         <v>32335</v>
@@ -920,7 +920,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G19" t="n">
-        <v>4.4471640586853</v>
+        <v>4.44716358184814</v>
       </c>
       <c r="H19" t="n">
         <v>155415</v>
@@ -978,7 +978,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G21" t="n">
-        <v>4.60145282745361</v>
+        <v>4.60145330429077</v>
       </c>
       <c r="H21" t="n">
         <v>46761</v>
@@ -1036,7 +1036,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G23" t="n">
-        <v>4.75574159622192</v>
+        <v>4.75574254989624</v>
       </c>
       <c r="H23" t="n">
         <v>42090</v>
@@ -1152,7 +1152,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>4.95541095733643</v>
+        <v>4.95541048049927</v>
       </c>
       <c r="H27" t="n">
         <v>26232</v>
@@ -1181,7 +1181,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G28" t="n">
-        <v>5.00079011917114</v>
+        <v>5.0007905960083</v>
       </c>
       <c r="H28" t="n">
         <v>40759</v>
@@ -1210,7 +1210,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G29" t="n">
-        <v>5.20045852661133</v>
+        <v>5.20045804977417</v>
       </c>
       <c r="H29" t="n">
         <v>89716</v>
@@ -1239,7 +1239,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G30" t="n">
-        <v>5.47273397445679</v>
+        <v>5.47273445129395</v>
       </c>
       <c r="H30" t="n">
         <v>193631</v>
@@ -1355,7 +1355,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G34" t="n">
-        <v>5.48181009292603</v>
+        <v>5.48180961608887</v>
       </c>
       <c r="H34" t="n">
         <v>30948</v>
@@ -1413,7 +1413,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G36" t="n">
-        <v>5.33659601211548</v>
+        <v>5.33659696578979</v>
       </c>
       <c r="H36" t="n">
         <v>16617</v>
@@ -1442,7 +1442,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G37" t="n">
-        <v>5.25491380691528</v>
+        <v>5.25491428375244</v>
       </c>
       <c r="H37" t="n">
         <v>23662</v>
@@ -1529,7 +1529,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G40" t="n">
-        <v>5.30936813354492</v>
+        <v>5.30936861038208</v>
       </c>
       <c r="H40" t="n">
         <v>10863</v>
@@ -1558,7 +1558,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G41" t="n">
-        <v>5.39105176925659</v>
+        <v>5.39105129241943</v>
       </c>
       <c r="H41" t="n">
         <v>11791</v>
@@ -1616,7 +1616,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G43" t="n">
-        <v>5.42735481262207</v>
+        <v>5.42735433578491</v>
       </c>
       <c r="H43" t="n">
         <v>24833</v>
@@ -1674,7 +1674,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G45" t="n">
-        <v>5.35474729537964</v>
+        <v>5.35474824905396</v>
       </c>
       <c r="H45" t="n">
         <v>29347</v>
@@ -1703,7 +1703,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G46" t="n">
-        <v>5.34567165374756</v>
+        <v>5.3456711769104</v>
       </c>
       <c r="H46" t="n">
         <v>21861</v>
@@ -1761,7 +1761,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G48" t="n">
-        <v>5.10969972610474</v>
+        <v>5.10970067977905</v>
       </c>
       <c r="H48" t="n">
         <v>75369</v>
@@ -1790,7 +1790,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G49" t="n">
-        <v>5.1006236076355</v>
+        <v>5.10062408447266</v>
       </c>
       <c r="H49" t="n">
         <v>37488</v>
@@ -1848,7 +1848,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G51" t="n">
-        <v>5.20045852661133</v>
+        <v>5.20045804977417</v>
       </c>
       <c r="H51" t="n">
         <v>11633</v>
@@ -2022,7 +2022,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G57" t="n">
-        <v>4.8555760383606</v>
+        <v>4.85557651519775</v>
       </c>
       <c r="H57" t="n">
         <v>32462</v>
@@ -2051,7 +2051,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G58" t="n">
-        <v>4.86465215682983</v>
+        <v>4.86465263366699</v>
       </c>
       <c r="H58" t="n">
         <v>10871</v>
@@ -2080,7 +2080,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G59" t="n">
-        <v>4.87372779846191</v>
+        <v>4.87372827529907</v>
       </c>
       <c r="H59" t="n">
         <v>60004</v>
@@ -2109,7 +2109,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G60" t="n">
-        <v>5.01894235610962</v>
+        <v>5.01894187927246</v>
       </c>
       <c r="H60" t="n">
         <v>23167</v>
@@ -2138,7 +2138,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G61" t="n">
-        <v>4.92818355560303</v>
+        <v>4.92818260192871</v>
       </c>
       <c r="H61" t="n">
         <v>10150</v>
@@ -2167,7 +2167,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G62" t="n">
-        <v>4.83742475509644</v>
+        <v>4.83742523193359</v>
       </c>
       <c r="H62" t="n">
         <v>13006</v>
@@ -2225,7 +2225,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G64" t="n">
-        <v>4.8555760383606</v>
+        <v>4.85557651519775</v>
       </c>
       <c r="H64" t="n">
         <v>15055</v>
@@ -2254,7 +2254,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G65" t="n">
-        <v>4.68313598632812</v>
+        <v>4.68313550949097</v>
       </c>
       <c r="H65" t="n">
         <v>14192</v>
@@ -2283,7 +2283,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G66" t="n">
-        <v>4.63775587081909</v>
+        <v>4.63775634765625</v>
       </c>
       <c r="H66" t="n">
         <v>9021</v>
@@ -2341,7 +2341,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G68" t="n">
-        <v>4.67406034469604</v>
+        <v>4.67405986785889</v>
       </c>
       <c r="H68" t="n">
         <v>26836</v>
@@ -2370,7 +2370,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>4.87372779846191</v>
+        <v>4.87372827529907</v>
       </c>
       <c r="H69" t="n">
         <v>20469</v>
@@ -2399,7 +2399,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G70" t="n">
-        <v>4.93725919723511</v>
+        <v>4.93725967407227</v>
       </c>
       <c r="H70" t="n">
         <v>2829</v>
@@ -2428,7 +2428,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G71" t="n">
-        <v>4.68313598632812</v>
+        <v>4.68313550949097</v>
       </c>
       <c r="H71" t="n">
         <v>21164</v>
@@ -2457,7 +2457,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G72" t="n">
-        <v>4.77389478683472</v>
+        <v>4.77389430999756</v>
       </c>
       <c r="H72" t="n">
         <v>8024</v>
@@ -2573,7 +2573,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G76" t="n">
-        <v>4.51977062225342</v>
+        <v>4.51977014541626</v>
       </c>
       <c r="H76" t="n">
         <v>20769</v>
@@ -2602,7 +2602,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G77" t="n">
-        <v>4.13858461380005</v>
+        <v>4.13858509063721</v>
       </c>
       <c r="H77" t="n">
         <v>29751</v>
@@ -2660,7 +2660,7 @@
         <v>4.5</v>
       </c>
       <c r="G79" t="n">
-        <v>4.08413028717041</v>
+        <v>4.08412981033325</v>
       </c>
       <c r="H79" t="n">
         <v>23806</v>
@@ -2689,7 +2689,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G80" t="n">
-        <v>4.32917785644531</v>
+        <v>4.32917737960815</v>
       </c>
       <c r="H80" t="n">
         <v>11441</v>
@@ -2718,7 +2718,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G81" t="n">
-        <v>4.07051610946655</v>
+        <v>4.07051658630371</v>
       </c>
       <c r="H81" t="n">
         <v>26271</v>
@@ -2747,7 +2747,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G82" t="n">
-        <v>4.02059841156006</v>
+        <v>4.02059888839722</v>
       </c>
       <c r="H82" t="n">
         <v>47987</v>
@@ -2776,7 +2776,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G83" t="n">
-        <v>3.99337148666382</v>
+        <v>3.9933717250824</v>
       </c>
       <c r="H83" t="n">
         <v>14139</v>
@@ -2805,7 +2805,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G84" t="n">
-        <v>4.01152324676514</v>
+        <v>4.01152276992798</v>
       </c>
       <c r="H84" t="n">
         <v>13008</v>
@@ -2834,7 +2834,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G85" t="n">
-        <v>4.03421306610107</v>
+        <v>4.03421258926392</v>
       </c>
       <c r="H85" t="n">
         <v>9318</v>
@@ -2863,7 +2863,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G86" t="n">
-        <v>4.15673589706421</v>
+        <v>4.15673637390137</v>
       </c>
       <c r="H86" t="n">
         <v>20105</v>
@@ -2921,7 +2921,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G88" t="n">
-        <v>4.47892904281616</v>
+        <v>4.47892951965332</v>
       </c>
       <c r="H88" t="n">
         <v>20559</v>
@@ -2979,7 +2979,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G90" t="n">
-        <v>4.68313598632812</v>
+        <v>4.68313550949097</v>
       </c>
       <c r="H90" t="n">
         <v>7231</v>
@@ -3008,7 +3008,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G91" t="n">
-        <v>4.48346710205078</v>
+        <v>4.48346662521362</v>
       </c>
       <c r="H91" t="n">
         <v>5261</v>
@@ -3037,7 +3037,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G92" t="n">
-        <v>4.53338432312012</v>
+        <v>4.53338384628296</v>
       </c>
       <c r="H92" t="n">
         <v>1969</v>
@@ -3095,7 +3095,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G94" t="n">
-        <v>4.50615644454956</v>
+        <v>4.50615692138672</v>
       </c>
       <c r="H94" t="n">
         <v>2116</v>
@@ -3124,7 +3124,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G95" t="n">
-        <v>4.51977062225342</v>
+        <v>4.51977014541626</v>
       </c>
       <c r="H95" t="n">
         <v>243259</v>
@@ -3153,7 +3153,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>4.51977062225342</v>
+        <v>4.51977014541626</v>
       </c>
       <c r="H96" t="n">
         <v>4515</v>
@@ -3182,7 +3182,7 @@
         <v>4.95499992370605</v>
       </c>
       <c r="G97" t="n">
-        <v>4.49708080291748</v>
+        <v>4.49708032608032</v>
       </c>
       <c r="H97" t="n">
         <v>8314</v>
@@ -3211,7 +3211,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G98" t="n">
-        <v>4.41085958480835</v>
+        <v>4.41086006164551</v>
       </c>
       <c r="H98" t="n">
         <v>2735</v>
@@ -3240,7 +3240,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>4.50161838531494</v>
+        <v>4.50161933898926</v>
       </c>
       <c r="H99" t="n">
         <v>18031</v>
@@ -3298,7 +3298,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G101" t="n">
-        <v>4.35640525817871</v>
+        <v>4.35640573501587</v>
       </c>
       <c r="H101" t="n">
         <v>2000</v>
@@ -3327,7 +3327,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G102" t="n">
-        <v>4.35640525817871</v>
+        <v>4.35640573501587</v>
       </c>
       <c r="H102" t="n">
         <v>1155</v>
@@ -3356,7 +3356,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G103" t="n">
-        <v>4.34732913970947</v>
+        <v>4.34732866287231</v>
       </c>
       <c r="H103" t="n">
         <v>12517</v>
@@ -3414,7 +3414,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G105" t="n">
-        <v>4.36548042297363</v>
+        <v>4.36548089981079</v>
       </c>
       <c r="H105" t="n">
         <v>618</v>
@@ -3443,7 +3443,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G106" t="n">
-        <v>4.42901277542114</v>
+        <v>4.42901182174683</v>
       </c>
       <c r="H106" t="n">
         <v>317</v>
@@ -3501,7 +3501,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G108" t="n">
-        <v>4.34732913970947</v>
+        <v>4.34732866287231</v>
       </c>
       <c r="H108" t="n">
         <v>5476</v>
@@ -3530,7 +3530,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G109" t="n">
-        <v>4.40632200241089</v>
+        <v>4.40632247924805</v>
       </c>
       <c r="H109" t="n">
         <v>2660</v>
@@ -3559,7 +3559,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G110" t="n">
-        <v>4.4471640586853</v>
+        <v>4.44716358184814</v>
       </c>
       <c r="H110" t="n">
         <v>197</v>
@@ -3646,7 +3646,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G113" t="n">
-        <v>4.37455701828003</v>
+        <v>4.37455654144287</v>
       </c>
       <c r="H113" t="n">
         <v>38</v>
@@ -3733,7 +3733,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G116" t="n">
-        <v>4.29287385940552</v>
+        <v>4.29287433624268</v>
       </c>
       <c r="H116" t="n">
         <v>5190</v>
@@ -3762,7 +3762,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G117" t="n">
-        <v>4.18396425247192</v>
+        <v>4.18396377563477</v>
       </c>
       <c r="H117" t="n">
         <v>3181</v>
@@ -3791,7 +3791,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G118" t="n">
-        <v>4.2429575920105</v>
+        <v>4.24295711517334</v>
       </c>
       <c r="H118" t="n">
         <v>50</v>
@@ -3849,7 +3849,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G120" t="n">
-        <v>3.88446140289307</v>
+        <v>3.88446116447449</v>
       </c>
       <c r="H120" t="n">
         <v>37503</v>
@@ -3878,7 +3878,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G121" t="n">
-        <v>3.81639218330383</v>
+        <v>3.81639266014099</v>
       </c>
       <c r="H121" t="n">
         <v>9794</v>
@@ -3907,7 +3907,7 @@
         <v>4.29500007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>3.89807510375977</v>
+        <v>3.89807534217834</v>
       </c>
       <c r="H122" t="n">
         <v>1318</v>
@@ -3936,7 +3936,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G123" t="n">
-        <v>3.88446140289307</v>
+        <v>3.88446116447449</v>
       </c>
       <c r="H123" t="n">
         <v>3695</v>
@@ -3965,7 +3965,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G124" t="n">
-        <v>3.88446140289307</v>
+        <v>3.88446116447449</v>
       </c>
       <c r="H124" t="n">
         <v>7707</v>
@@ -3994,7 +3994,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G125" t="n">
-        <v>3.92076468467712</v>
+        <v>3.9207649230957</v>
       </c>
       <c r="H125" t="n">
         <v>16385</v>
@@ -4052,7 +4052,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G127" t="n">
-        <v>4.21597480773926</v>
+        <v>4.21597528457642</v>
       </c>
       <c r="H127" t="n">
         <v>26910</v>
@@ -4081,7 +4081,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G128" t="n">
-        <v>4.29900312423706</v>
+        <v>4.2990026473999</v>
       </c>
       <c r="H128" t="n">
         <v>9321</v>
@@ -4110,7 +4110,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G129" t="n">
-        <v>4.27132701873779</v>
+        <v>4.27132654190063</v>
       </c>
       <c r="H129" t="n">
         <v>2854</v>
@@ -4168,7 +4168,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G131" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H131" t="n">
         <v>15380</v>
@@ -4226,7 +4226,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G133" t="n">
-        <v>4.32667922973633</v>
+        <v>4.32667970657349</v>
       </c>
       <c r="H133" t="n">
         <v>10570</v>
@@ -4284,7 +4284,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G135" t="n">
-        <v>4.37280559539795</v>
+        <v>4.37280607223511</v>
       </c>
       <c r="H135" t="n">
         <v>4000</v>
@@ -4313,7 +4313,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G136" t="n">
-        <v>4.42354488372803</v>
+        <v>4.42354536056519</v>
       </c>
       <c r="H136" t="n">
         <v>520</v>
@@ -4342,7 +4342,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G137" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H137" t="n">
         <v>3650</v>
@@ -4400,7 +4400,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G139" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H139" t="n">
         <v>2000</v>
@@ -4429,7 +4429,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G140" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>4.60500001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>4.24826335906982</v>
+        <v>4.24826431274414</v>
       </c>
       <c r="H141" t="n">
         <v>1470</v>
@@ -4516,7 +4516,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G143" t="n">
-        <v>4.2067494392395</v>
+        <v>4.20674991607666</v>
       </c>
       <c r="H143" t="n">
         <v>17151</v>
@@ -4545,7 +4545,7 @@
         <v>4.5</v>
       </c>
       <c r="G144" t="n">
-        <v>4.15139770507812</v>
+        <v>4.15139818191528</v>
       </c>
       <c r="H144" t="n">
         <v>12389</v>
@@ -4603,7 +4603,7 @@
         <v>4.25</v>
       </c>
       <c r="G146" t="n">
-        <v>3.92076468467712</v>
+        <v>3.9207649230957</v>
       </c>
       <c r="H146" t="n">
         <v>15623</v>
@@ -4632,7 +4632,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G147" t="n">
-        <v>3.89770150184631</v>
+        <v>3.89770126342773</v>
       </c>
       <c r="H147" t="n">
         <v>8340</v>
@@ -4661,7 +4661,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G148" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766615867615</v>
       </c>
       <c r="H148" t="n">
         <v>2849</v>
@@ -4690,7 +4690,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G149" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766615867615</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G150" t="n">
-        <v>4.04069375991821</v>
+        <v>4.04069423675537</v>
       </c>
       <c r="H150" t="n">
         <v>36</v>
@@ -4748,7 +4748,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G151" t="n">
-        <v>4.1052713394165</v>
+        <v>4.10527086257935</v>
       </c>
       <c r="H151" t="n">
         <v>124</v>
@@ -4777,7 +4777,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G152" t="n">
-        <v>4.14678573608398</v>
+        <v>4.14678525924683</v>
       </c>
       <c r="H152" t="n">
         <v>2449</v>
@@ -4806,7 +4806,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G153" t="n">
-        <v>3.98534202575684</v>
+        <v>3.98534250259399</v>
       </c>
       <c r="H153" t="n">
         <v>8687</v>
@@ -4835,7 +4835,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G154" t="n">
-        <v>3.92999005317688</v>
+        <v>3.92999029159546</v>
       </c>
       <c r="H154" t="n">
         <v>5428</v>
@@ -4951,7 +4951,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G158" t="n">
-        <v>4.04991912841797</v>
+        <v>4.04991865158081</v>
       </c>
       <c r="H158" t="n">
         <v>5</v>
@@ -5067,7 +5067,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G162" t="n">
-        <v>3.88847589492798</v>
+        <v>3.88847613334656</v>
       </c>
       <c r="H162" t="n">
         <v>19019</v>
@@ -5125,7 +5125,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G164" t="n">
-        <v>3.83773636817932</v>
+        <v>3.83773684501648</v>
       </c>
       <c r="H164" t="n">
         <v>2438</v>
@@ -5154,7 +5154,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G165" t="n">
-        <v>3.85618710517883</v>
+        <v>3.85618734359741</v>
       </c>
       <c r="H165" t="n">
         <v>450</v>
@@ -5183,7 +5183,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G166" t="n">
-        <v>3.84696221351624</v>
+        <v>3.84696197509766</v>
       </c>
       <c r="H166" t="n">
         <v>612</v>
@@ -5212,7 +5212,7 @@
         <v>4.22499990463257</v>
       </c>
       <c r="G167" t="n">
-        <v>3.89770150184631</v>
+        <v>3.89770126342773</v>
       </c>
       <c r="H167" t="n">
         <v>205</v>
@@ -5241,7 +5241,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G168" t="n">
-        <v>3.98534202575684</v>
+        <v>3.98534250259399</v>
       </c>
       <c r="H168" t="n">
         <v>5404</v>
@@ -5270,7 +5270,7 @@
         <v>4.25500011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>3.925377368927</v>
+        <v>3.92537713050842</v>
       </c>
       <c r="H169" t="n">
         <v>2375</v>
@@ -5299,7 +5299,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G170" t="n">
-        <v>3.92999005317688</v>
+        <v>3.92999029159546</v>
       </c>
       <c r="H170" t="n">
         <v>10150</v>
@@ -5328,7 +5328,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G171" t="n">
-        <v>4.04991912841797</v>
+        <v>4.04991865158081</v>
       </c>
       <c r="H171" t="n">
         <v>2250</v>
@@ -5357,7 +5357,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G172" t="n">
-        <v>4.04991912841797</v>
+        <v>4.04991865158081</v>
       </c>
       <c r="H172" t="n">
         <v>520</v>
@@ -5415,7 +5415,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G174" t="n">
-        <v>3.89308881759644</v>
+        <v>3.89308857917786</v>
       </c>
       <c r="H174" t="n">
         <v>3424</v>
@@ -5444,7 +5444,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G175" t="n">
-        <v>3.89308881759644</v>
+        <v>3.89308857917786</v>
       </c>
       <c r="H175" t="n">
         <v>470</v>
@@ -5473,7 +5473,7 @@
         <v>4.28499984741211</v>
       </c>
       <c r="G176" t="n">
-        <v>3.95305323600769</v>
+        <v>3.95305299758911</v>
       </c>
       <c r="H176" t="n">
         <v>1056</v>
@@ -5502,7 +5502,7 @@
         <v>4.25</v>
       </c>
       <c r="G177" t="n">
-        <v>3.92076468467712</v>
+        <v>3.9207649230957</v>
       </c>
       <c r="H177" t="n">
         <v>3092</v>
@@ -5531,7 +5531,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>3.8838632106781</v>
+        <v>3.88386297225952</v>
       </c>
       <c r="H178" t="n">
         <v>5254</v>
@@ -5560,7 +5560,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G179" t="n">
-        <v>4.04991912841797</v>
+        <v>4.04991865158081</v>
       </c>
       <c r="H179" t="n">
         <v>3005</v>
@@ -5618,7 +5618,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G181" t="n">
-        <v>3.83773636817932</v>
+        <v>3.83773684501648</v>
       </c>
       <c r="H181" t="n">
         <v>5582</v>
@@ -5647,7 +5647,7 @@
         <v>4.25</v>
       </c>
       <c r="G182" t="n">
-        <v>3.92076468467712</v>
+        <v>3.9207649230957</v>
       </c>
       <c r="H182" t="n">
         <v>4226</v>
@@ -5676,7 +5676,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G183" t="n">
-        <v>3.8838632106781</v>
+        <v>3.88386297225952</v>
       </c>
       <c r="H183" t="n">
         <v>11079</v>
@@ -5705,7 +5705,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G184" t="n">
-        <v>3.87463784217834</v>
+        <v>3.87463760375977</v>
       </c>
       <c r="H184" t="n">
         <v>508</v>
@@ -5734,7 +5734,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G185" t="n">
-        <v>3.87463784217834</v>
+        <v>3.87463760375977</v>
       </c>
       <c r="H185" t="n">
         <v>4806</v>
@@ -5763,7 +5763,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G186" t="n">
-        <v>3.89308881759644</v>
+        <v>3.89308857917786</v>
       </c>
       <c r="H186" t="n">
         <v>13086</v>
@@ -5792,7 +5792,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G187" t="n">
-        <v>3.87463784217834</v>
+        <v>3.87463760375977</v>
       </c>
       <c r="H187" t="n">
         <v>1555</v>
@@ -5850,7 +5850,7 @@
         <v>4.34499979019165</v>
       </c>
       <c r="G189" t="n">
-        <v>4.00840520858765</v>
+        <v>4.00840473175049</v>
       </c>
       <c r="H189" t="n">
         <v>3667</v>
@@ -5879,7 +5879,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G190" t="n">
-        <v>3.8838632106781</v>
+        <v>3.88386297225952</v>
       </c>
       <c r="H190" t="n">
         <v>1237</v>
@@ -5908,7 +5908,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G191" t="n">
-        <v>3.87463784217834</v>
+        <v>3.87463760375977</v>
       </c>
       <c r="H191" t="n">
         <v>3347</v>
@@ -5937,7 +5937,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G192" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766615867615</v>
       </c>
       <c r="H192" t="n">
         <v>3183</v>
@@ -5966,7 +5966,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G193" t="n">
-        <v>4.0130181312561</v>
+        <v>4.01301765441895</v>
       </c>
       <c r="H193" t="n">
         <v>82</v>
@@ -5995,7 +5995,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G194" t="n">
-        <v>4.00379228591919</v>
+        <v>4.00379323959351</v>
       </c>
       <c r="H194" t="n">
         <v>1199</v>
@@ -6024,7 +6024,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G195" t="n">
-        <v>3.99456763267517</v>
+        <v>3.99456691741943</v>
       </c>
       <c r="H195" t="n">
         <v>131</v>
@@ -6053,7 +6053,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G196" t="n">
-        <v>3.86541223526001</v>
+        <v>3.86541271209717</v>
       </c>
       <c r="H196" t="n">
         <v>5890</v>
@@ -6082,7 +6082,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G197" t="n">
-        <v>3.94844079017639</v>
+        <v>3.94844055175781</v>
       </c>
       <c r="H197" t="n">
         <v>2149</v>
@@ -6140,7 +6140,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G199" t="n">
-        <v>3.92999005317688</v>
+        <v>3.92999029159546</v>
       </c>
       <c r="H199" t="n">
         <v>2982</v>
@@ -6169,7 +6169,7 @@
         <v>4.33500003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>3.99917984008789</v>
+        <v>3.99918031692505</v>
       </c>
       <c r="H200" t="n">
         <v>155</v>
@@ -6198,7 +6198,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G201" t="n">
-        <v>3.89308881759644</v>
+        <v>3.89308857917786</v>
       </c>
       <c r="H201" t="n">
         <v>1122</v>
@@ -6256,7 +6256,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G203" t="n">
-        <v>4.04991912841797</v>
+        <v>4.04991865158081</v>
       </c>
       <c r="H203" t="n">
         <v>24810</v>
@@ -6285,7 +6285,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G204" t="n">
-        <v>3.95766592025757</v>
+        <v>3.95766615867615</v>
       </c>
       <c r="H204" t="n">
         <v>5370</v>
@@ -6314,7 +6314,7 @@
         <v>4.20499992370605</v>
       </c>
       <c r="G205" t="n">
-        <v>3.87925052642822</v>
+        <v>3.8792507648468</v>
       </c>
       <c r="H205" t="n">
         <v>3705</v>
@@ -6343,7 +6343,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G206" t="n">
-        <v>3.94844079017639</v>
+        <v>3.94844055175781</v>
       </c>
       <c r="H206" t="n">
         <v>5295</v>
@@ -6372,7 +6372,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>3.87463784217834</v>
+        <v>3.87463760375977</v>
       </c>
       <c r="H207" t="n">
         <v>6451</v>
@@ -6401,7 +6401,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G208" t="n">
-        <v>3.90231370925903</v>
+        <v>3.90231394767761</v>
       </c>
       <c r="H208" t="n">
         <v>1430</v>
@@ -6430,7 +6430,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G209" t="n">
-        <v>3.89308881759644</v>
+        <v>3.89308857917786</v>
       </c>
       <c r="H209" t="n">
         <v>7711</v>
@@ -6459,7 +6459,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G210" t="n">
-        <v>3.90692663192749</v>
+        <v>3.90692639350891</v>
       </c>
       <c r="H210" t="n">
         <v>2126</v>
@@ -6488,7 +6488,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G211" t="n">
-        <v>3.94844079017639</v>
+        <v>3.94844055175781</v>
       </c>
       <c r="H211" t="n">
         <v>5037</v>
@@ -6517,7 +6517,7 @@
         <v>4.19500017166138</v>
       </c>
       <c r="G212" t="n">
-        <v>3.87002563476562</v>
+        <v>3.87002515792847</v>
       </c>
       <c r="H212" t="n">
         <v>3149</v>
@@ -6546,7 +6546,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>3.8838632106781</v>
+        <v>3.88386297225952</v>
       </c>
       <c r="H213" t="n">
         <v>1793</v>
@@ -6575,7 +6575,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G214" t="n">
-        <v>3.8838632106781</v>
+        <v>3.88386297225952</v>
       </c>
       <c r="H214" t="n">
         <v>63</v>
@@ -6604,7 +6604,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G215" t="n">
-        <v>3.87463784217834</v>
+        <v>3.87463760375977</v>
       </c>
       <c r="H215" t="n">
         <v>5793</v>
@@ -6633,7 +6633,7 @@
         <v>4.27500009536743</v>
       </c>
       <c r="G216" t="n">
-        <v>3.94382810592651</v>
+        <v>3.94382834434509</v>
       </c>
       <c r="H216" t="n">
         <v>1</v>
@@ -6662,7 +6662,7 @@
         <v>4.2350001335144</v>
       </c>
       <c r="G217" t="n">
-        <v>3.90692663192749</v>
+        <v>3.90692639350891</v>
       </c>
       <c r="H217" t="n">
         <v>601</v>
@@ -6691,7 +6691,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G218" t="n">
-        <v>3.81928586959839</v>
+        <v>3.81928610801697</v>
       </c>
       <c r="H218" t="n">
         <v>120</v>
@@ -6836,7 +6836,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G223" t="n">
-        <v>4.04069375991821</v>
+        <v>4.04069423675537</v>
       </c>
       <c r="H223" t="n">
         <v>36447</v>
@@ -6865,7 +6865,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G224" t="n">
-        <v>4.1052713394165</v>
+        <v>4.10527086257935</v>
       </c>
       <c r="H224" t="n">
         <v>7165</v>
@@ -6894,7 +6894,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>4.0130181312561</v>
+        <v>4.01301765441895</v>
       </c>
       <c r="H225" t="n">
         <v>1000</v>
@@ -6952,7 +6952,7 @@
         <v>4.5</v>
       </c>
       <c r="G227" t="n">
-        <v>4.15139770507812</v>
+        <v>4.15139818191528</v>
       </c>
       <c r="H227" t="n">
         <v>5590</v>
@@ -6981,7 +6981,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G228" t="n">
-        <v>4.14217185974121</v>
+        <v>4.14217233657837</v>
       </c>
       <c r="H228" t="n">
         <v>6907</v>
@@ -7097,7 +7097,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G232" t="n">
-        <v>4.21597480773926</v>
+        <v>4.21597528457642</v>
       </c>
       <c r="H232" t="n">
         <v>7962</v>
@@ -7126,7 +7126,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G233" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H233" t="n">
         <v>12462</v>
@@ -7155,7 +7155,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G234" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H234" t="n">
         <v>15005</v>
@@ -7184,7 +7184,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G235" t="n">
-        <v>4.37280559539795</v>
+        <v>4.37280607223511</v>
       </c>
       <c r="H235" t="n">
         <v>17132</v>
@@ -7213,7 +7213,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G236" t="n">
-        <v>4.45583391189575</v>
+        <v>4.45583343505859</v>
       </c>
       <c r="H236" t="n">
         <v>4300</v>
@@ -7242,7 +7242,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G237" t="n">
-        <v>4.47428369522095</v>
+        <v>4.47428464889526</v>
       </c>
       <c r="H237" t="n">
         <v>567</v>
@@ -7329,7 +7329,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G240" t="n">
-        <v>4.42354488372803</v>
+        <v>4.42354536056519</v>
       </c>
       <c r="H240" t="n">
         <v>3500</v>
@@ -7358,7 +7358,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G241" t="n">
-        <v>4.33590459823608</v>
+        <v>4.33590412139893</v>
       </c>
       <c r="H241" t="n">
         <v>1200</v>
@@ -7387,7 +7387,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>4.42354488372803</v>
+        <v>4.42354536056519</v>
       </c>
       <c r="H242" t="n">
         <v>9000</v>
@@ -7619,7 +7619,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G250" t="n">
-        <v>4.37280559539795</v>
+        <v>4.37280607223511</v>
       </c>
       <c r="H250" t="n">
         <v>241</v>
@@ -7677,7 +7677,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G252" t="n">
-        <v>4.26210165023804</v>
+        <v>4.2621021270752</v>
       </c>
       <c r="H252" t="n">
         <v>330</v>
@@ -7764,7 +7764,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G255" t="n">
-        <v>4.55731248855591</v>
+        <v>4.55731153488159</v>
       </c>
       <c r="H255" t="n">
         <v>4318</v>
@@ -7851,7 +7851,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G258" t="n">
-        <v>4.51118516921997</v>
+        <v>4.51118564605713</v>
       </c>
       <c r="H258" t="n">
         <v>22611</v>
@@ -7938,7 +7938,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G261" t="n">
-        <v>4.59882640838623</v>
+        <v>4.59882593154907</v>
       </c>
       <c r="H261" t="n">
         <v>4514</v>
@@ -7967,7 +7967,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G262" t="n">
-        <v>4.74181890487671</v>
+        <v>4.74181842803955</v>
       </c>
       <c r="H262" t="n">
         <v>8453</v>
@@ -8054,7 +8054,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G265" t="n">
-        <v>4.8894248008728</v>
+        <v>4.88942432403564</v>
       </c>
       <c r="H265" t="n">
         <v>13281</v>
@@ -8083,7 +8083,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G266" t="n">
-        <v>4.8894248008728</v>
+        <v>4.88942432403564</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G267" t="n">
-        <v>4.8894248008728</v>
+        <v>4.88942432403564</v>
       </c>
       <c r="H267" t="n">
         <v>5927</v>
@@ -8141,7 +8141,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G268" t="n">
-        <v>5.02780389785767</v>
+        <v>5.02780342102051</v>
       </c>
       <c r="H268" t="n">
         <v>4916</v>
@@ -8199,7 +8199,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G270" t="n">
-        <v>4.93555021286011</v>
+        <v>4.93555068969727</v>
       </c>
       <c r="H270" t="n">
         <v>78819</v>
@@ -8257,7 +8257,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G272" t="n">
-        <v>4.8894248008728</v>
+        <v>4.88942432403564</v>
       </c>
       <c r="H272" t="n">
         <v>12329</v>
@@ -8373,7 +8373,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H276" t="n">
         <v>5852</v>
@@ -8489,7 +8489,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G280" t="n">
-        <v>5.16618394851685</v>
+        <v>5.166184425354</v>
       </c>
       <c r="H280" t="n">
         <v>15005</v>
@@ -8663,7 +8663,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G286" t="n">
-        <v>5.09238195419312</v>
+        <v>5.0923810005188</v>
       </c>
       <c r="H286" t="n">
         <v>233</v>
@@ -8779,7 +8779,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G290" t="n">
-        <v>5.08315563201904</v>
+        <v>5.08315658569336</v>
       </c>
       <c r="H290" t="n">
         <v>100</v>
@@ -9011,7 +9011,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G298" t="n">
-        <v>5.06470441818237</v>
+        <v>5.06470489501953</v>
       </c>
       <c r="H298" t="n">
         <v>39937</v>
@@ -9040,7 +9040,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>4.93555021286011</v>
+        <v>4.93555068969727</v>
       </c>
       <c r="H299" t="n">
         <v>1763</v>
@@ -9156,7 +9156,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G303" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H303" t="n">
         <v>700</v>
@@ -9185,7 +9185,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G304" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H304" t="n">
         <v>3145</v>
@@ -9214,7 +9214,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G305" t="n">
-        <v>4.8894248008728</v>
+        <v>4.88942432403564</v>
       </c>
       <c r="H305" t="n">
         <v>9988</v>
@@ -9272,7 +9272,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G307" t="n">
-        <v>4.93555021286011</v>
+        <v>4.93555068969727</v>
       </c>
       <c r="H307" t="n">
         <v>1214</v>
@@ -9359,7 +9359,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G310" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H310" t="n">
         <v>1967</v>
@@ -9388,7 +9388,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G311" t="n">
-        <v>4.8156213760376</v>
+        <v>4.81562089920044</v>
       </c>
       <c r="H311" t="n">
         <v>3343</v>
@@ -9446,7 +9446,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G313" t="n">
-        <v>4.75104427337646</v>
+        <v>4.75104379653931</v>
       </c>
       <c r="H313" t="n">
         <v>3070</v>
@@ -9504,7 +9504,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>4.75104427337646</v>
+        <v>4.75104379653931</v>
       </c>
       <c r="H315" t="n">
         <v>278649</v>
@@ -9562,7 +9562,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G317" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H317" t="n">
         <v>31544</v>
@@ -9620,7 +9620,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G319" t="n">
-        <v>5.06470441818237</v>
+        <v>5.06470489501953</v>
       </c>
       <c r="H319" t="n">
         <v>4244</v>
@@ -9678,7 +9678,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G321" t="n">
-        <v>4.8894248008728</v>
+        <v>4.88942432403564</v>
       </c>
       <c r="H321" t="n">
         <v>34175</v>
@@ -9765,7 +9765,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G324" t="n">
-        <v>5.04625463485718</v>
+        <v>5.04625415802002</v>
       </c>
       <c r="H324" t="n">
         <v>3919</v>
@@ -9794,7 +9794,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G325" t="n">
-        <v>4.8894248008728</v>
+        <v>4.88942432403564</v>
       </c>
       <c r="H325" t="n">
         <v>2844</v>
@@ -9852,7 +9852,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G327" t="n">
-        <v>4.8156213760376</v>
+        <v>4.81562089920044</v>
       </c>
       <c r="H327" t="n">
         <v>123</v>
@@ -9910,7 +9910,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G329" t="n">
-        <v>4.79717016220093</v>
+        <v>4.79717111587524</v>
       </c>
       <c r="H329" t="n">
         <v>5909</v>
@@ -9939,7 +9939,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>4.79717016220093</v>
+        <v>4.79717111587524</v>
       </c>
       <c r="H330" t="n">
         <v>445</v>
@@ -10113,7 +10113,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G336" t="n">
-        <v>5.06470441818237</v>
+        <v>5.06470489501953</v>
       </c>
       <c r="H336" t="n">
         <v>610</v>
@@ -10142,7 +10142,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G337" t="n">
-        <v>4.91709995269775</v>
+        <v>4.91710042953491</v>
       </c>
       <c r="H337" t="n">
         <v>5020</v>
@@ -10258,7 +10258,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G341" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H341" t="n">
         <v>6351</v>
@@ -10287,7 +10287,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G342" t="n">
-        <v>4.92632579803467</v>
+        <v>4.92632532119751</v>
       </c>
       <c r="H342" t="n">
         <v>1223</v>
@@ -10316,7 +10316,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G343" t="n">
-        <v>4.93555021286011</v>
+        <v>4.93555068969727</v>
       </c>
       <c r="H343" t="n">
         <v>1750</v>
@@ -10374,7 +10374,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G345" t="n">
-        <v>4.86174821853638</v>
+        <v>4.86174869537354</v>
       </c>
       <c r="H345" t="n">
         <v>3141</v>
@@ -10461,7 +10461,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G348" t="n">
-        <v>4.52963638305664</v>
+        <v>4.52963590621948</v>
       </c>
       <c r="H348" t="n">
         <v>9810</v>
@@ -10548,7 +10548,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G351" t="n">
-        <v>4.75104427337646</v>
+        <v>4.75104379653931</v>
       </c>
       <c r="H351" t="n">
         <v>9088</v>
@@ -10635,7 +10635,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G354" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H354" t="n">
         <v>1901</v>
@@ -10664,7 +10664,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G355" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H355" t="n">
         <v>7480</v>
@@ -10693,7 +10693,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G356" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H356" t="n">
         <v>7610</v>
@@ -10722,7 +10722,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G357" t="n">
-        <v>5.01857852935791</v>
+        <v>5.01857900619507</v>
       </c>
       <c r="H357" t="n">
         <v>1202</v>
@@ -10780,7 +10780,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G359" t="n">
-        <v>4.8894248008728</v>
+        <v>4.88942432403564</v>
       </c>
       <c r="H359" t="n">
         <v>4186</v>
@@ -10809,7 +10809,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G360" t="n">
-        <v>4.8894248008728</v>
+        <v>4.88942432403564</v>
       </c>
       <c r="H360" t="n">
         <v>4150</v>
@@ -10838,7 +10838,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G361" t="n">
-        <v>4.8894248008728</v>
+        <v>4.88942432403564</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G366" t="n">
-        <v>5.05548000335693</v>
+        <v>5.05548048019409</v>
       </c>
       <c r="H366" t="n">
         <v>26294</v>
@@ -11070,7 +11070,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G369" t="n">
-        <v>5.09238195419312</v>
+        <v>5.0923810005188</v>
       </c>
       <c r="H369" t="n">
         <v>37466</v>
@@ -11099,7 +11099,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G370" t="n">
-        <v>5.20308494567871</v>
+        <v>5.20308542251587</v>
       </c>
       <c r="H370" t="n">
         <v>5557</v>
@@ -11215,7 +11215,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G374" t="n">
-        <v>5.2768874168396</v>
+        <v>5.27688789367676</v>
       </c>
       <c r="H374" t="n">
         <v>2643</v>
@@ -11331,7 +11331,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G378" t="n">
-        <v>5.25843715667725</v>
+        <v>5.25843667984009</v>
       </c>
       <c r="H378" t="n">
         <v>4491</v>
@@ -11360,7 +11360,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G379" t="n">
-        <v>5.25843715667725</v>
+        <v>5.25843667984009</v>
       </c>
       <c r="H379" t="n">
         <v>270</v>
@@ -11389,7 +11389,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G380" t="n">
-        <v>5.2768874168396</v>
+        <v>5.27688789367676</v>
       </c>
       <c r="H380" t="n">
         <v>43761</v>
@@ -11418,7 +11418,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G381" t="n">
-        <v>5.24876928329468</v>
+        <v>5.24876976013184</v>
       </c>
       <c r="H381" t="n">
         <v>20743</v>
@@ -11505,7 +11505,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G384" t="n">
-        <v>5.47371673583984</v>
+        <v>5.473717212677</v>
       </c>
       <c r="H384" t="n">
         <v>4634</v>
@@ -11563,7 +11563,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G386" t="n">
-        <v>5.60493612289429</v>
+        <v>5.60493564605713</v>
       </c>
       <c r="H386" t="n">
         <v>24572</v>
@@ -11592,7 +11592,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G387" t="n">
-        <v>5.66117286682129</v>
+        <v>5.66117238998413</v>
       </c>
       <c r="H387" t="n">
         <v>23023</v>
@@ -11679,7 +11679,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H390" t="n">
         <v>24702</v>
@@ -11708,7 +11708,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G391" t="n">
-        <v>5.24876928329468</v>
+        <v>5.24876976013184</v>
       </c>
       <c r="H391" t="n">
         <v>7298</v>
@@ -11737,7 +11737,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G392" t="n">
-        <v>5.24876928329468</v>
+        <v>5.24876976013184</v>
       </c>
       <c r="H392" t="n">
         <v>2740</v>
@@ -11766,7 +11766,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G393" t="n">
-        <v>5.24876928329468</v>
+        <v>5.24876976013184</v>
       </c>
       <c r="H393" t="n">
         <v>16929</v>
@@ -11795,7 +11795,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G394" t="n">
-        <v>5.32375144958496</v>
+        <v>5.32375192642212</v>
       </c>
       <c r="H394" t="n">
         <v>680</v>
@@ -11882,7 +11882,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G397" t="n">
-        <v>5.47371673583984</v>
+        <v>5.473717212677</v>
       </c>
       <c r="H397" t="n">
         <v>2362</v>
@@ -11911,7 +11911,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>5.58619070053101</v>
+        <v>5.58619022369385</v>
       </c>
       <c r="H398" t="n">
         <v>3700</v>
@@ -12056,7 +12056,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G403" t="n">
-        <v>5.58619070053101</v>
+        <v>5.58619022369385</v>
       </c>
       <c r="H403" t="n">
         <v>430</v>
@@ -12114,7 +12114,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G405" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H405" t="n">
         <v>1418</v>
@@ -12288,7 +12288,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G411" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H411" t="n">
         <v>200</v>
@@ -12404,7 +12404,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G415" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H415" t="n">
         <v>100</v>
@@ -12433,7 +12433,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G416" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H416" t="n">
         <v>45</v>
@@ -12520,7 +12520,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G419" t="n">
-        <v>5.47371673583984</v>
+        <v>5.473717212677</v>
       </c>
       <c r="H419" t="n">
         <v>560</v>
@@ -12549,7 +12549,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G420" t="n">
-        <v>5.47371673583984</v>
+        <v>5.473717212677</v>
       </c>
       <c r="H420" t="n">
         <v>10242</v>
@@ -12607,7 +12607,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G422" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H422" t="n">
         <v>18970</v>
@@ -12665,7 +12665,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G424" t="n">
-        <v>5.4549708366394</v>
+        <v>5.45497131347656</v>
       </c>
       <c r="H424" t="n">
         <v>8384</v>
@@ -12752,7 +12752,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G427" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H427" t="n">
         <v>4203</v>
@@ -12781,7 +12781,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G428" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H428" t="n">
         <v>760</v>
@@ -12955,7 +12955,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G434" t="n">
-        <v>5.47371673583984</v>
+        <v>5.473717212677</v>
       </c>
       <c r="H434" t="n">
         <v>170</v>
@@ -13042,7 +13042,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G437" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H437" t="n">
         <v>7332</v>
@@ -13071,7 +13071,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H438" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H444" t="n">
         <v>10</v>
@@ -13332,7 +13332,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G447" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H447" t="n">
         <v>20</v>
@@ -13361,7 +13361,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G448" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H448" t="n">
         <v>2255</v>
@@ -13390,7 +13390,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G449" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H449" t="n">
         <v>300</v>
@@ -13448,7 +13448,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G451" t="n">
-        <v>5.32375144958496</v>
+        <v>5.32375192642212</v>
       </c>
       <c r="H451" t="n">
         <v>924</v>
@@ -13477,7 +13477,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G452" t="n">
-        <v>5.32375144958496</v>
+        <v>5.32375192642212</v>
       </c>
       <c r="H452" t="n">
         <v>0</v>
@@ -13506,7 +13506,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G453" t="n">
-        <v>5.32375144958496</v>
+        <v>5.32375192642212</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13593,7 +13593,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G456" t="n">
-        <v>5.43622541427612</v>
+        <v>5.43622589111328</v>
       </c>
       <c r="H456" t="n">
         <v>20122</v>
@@ -13622,7 +13622,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G457" t="n">
-        <v>5.47371673583984</v>
+        <v>5.473717212677</v>
       </c>
       <c r="H457" t="n">
         <v>3375</v>
@@ -13999,7 +13999,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G470" t="n">
-        <v>5.24876928329468</v>
+        <v>5.24876976013184</v>
       </c>
       <c r="H470" t="n">
         <v>2437</v>
@@ -14173,7 +14173,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G476" t="n">
-        <v>5.02382278442383</v>
+        <v>5.02382230758667</v>
       </c>
       <c r="H476" t="n">
         <v>311</v>
@@ -14202,7 +14202,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G477" t="n">
-        <v>4.93009471893311</v>
+        <v>4.93009424209595</v>
       </c>
       <c r="H477" t="n">
         <v>5511</v>
@@ -14289,7 +14289,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G480" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H480" t="n">
         <v>900</v>
@@ -14318,7 +14318,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G481" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H481" t="n">
         <v>16552</v>
@@ -14347,7 +14347,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G482" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H482" t="n">
         <v>1000</v>
@@ -14376,7 +14376,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G483" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14405,7 +14405,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G484" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H484" t="n">
         <v>250</v>
@@ -14492,7 +14492,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G487" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H487" t="n">
         <v>1050</v>
@@ -14579,7 +14579,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G490" t="n">
-        <v>4.64891004562378</v>
+        <v>4.64891052246094</v>
       </c>
       <c r="H490" t="n">
         <v>2650</v>
@@ -14666,7 +14666,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G493" t="n">
-        <v>4.56455421447754</v>
+        <v>4.5645546913147</v>
       </c>
       <c r="H493" t="n">
         <v>1016</v>
@@ -14695,7 +14695,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G494" t="n">
-        <v>4.64891004562378</v>
+        <v>4.64891052246094</v>
       </c>
       <c r="H494" t="n">
         <v>21434</v>
@@ -14811,7 +14811,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G498" t="n">
-        <v>4.67702865600586</v>
+        <v>4.6770281791687</v>
       </c>
       <c r="H498" t="n">
         <v>3536</v>
@@ -14840,7 +14840,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G499" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H499" t="n">
         <v>12994</v>
@@ -14898,7 +14898,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G501" t="n">
-        <v>4.83636569976807</v>
+        <v>4.83636617660522</v>
       </c>
       <c r="H501" t="n">
         <v>9387</v>
@@ -14956,7 +14956,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G503" t="n">
-        <v>4.87385654449463</v>
+        <v>4.87385749816895</v>
       </c>
       <c r="H503" t="n">
         <v>15019</v>
@@ -15043,7 +15043,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G506" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H506" t="n">
         <v>2350</v>
@@ -15072,7 +15072,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G507" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H507" t="n">
         <v>0</v>
@@ -15101,7 +15101,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G508" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H508" t="n">
         <v>80250</v>
@@ -15188,7 +15188,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G511" t="n">
-        <v>5.02382278442383</v>
+        <v>5.02382230758667</v>
       </c>
       <c r="H511" t="n">
         <v>4402</v>
@@ -15217,7 +15217,7 @@
         <v>5.5</v>
       </c>
       <c r="G512" t="n">
-        <v>5.15504169464111</v>
+        <v>5.15504121780396</v>
       </c>
       <c r="H512" t="n">
         <v>4203</v>
@@ -15275,7 +15275,7 @@
         <v>5.5</v>
       </c>
       <c r="G514" t="n">
-        <v>5.15504169464111</v>
+        <v>5.15504121780396</v>
       </c>
       <c r="H514" t="n">
         <v>1884</v>
@@ -15304,7 +15304,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G515" t="n">
-        <v>5.00507688522339</v>
+        <v>5.00507640838623</v>
       </c>
       <c r="H515" t="n">
         <v>632</v>
@@ -15333,7 +15333,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G516" t="n">
-        <v>5.00507688522339</v>
+        <v>5.00507640838623</v>
       </c>
       <c r="H516" t="n">
         <v>0</v>
@@ -15391,7 +15391,7 @@
         <v>5.5</v>
       </c>
       <c r="G518" t="n">
-        <v>5.15504169464111</v>
+        <v>5.15504121780396</v>
       </c>
       <c r="H518" t="n">
         <v>6482</v>
@@ -15449,7 +15449,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G520" t="n">
-        <v>5.02382278442383</v>
+        <v>5.02382230758667</v>
       </c>
       <c r="H520" t="n">
         <v>1669</v>
@@ -15536,7 +15536,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G523" t="n">
-        <v>4.96758556365967</v>
+        <v>4.96758508682251</v>
       </c>
       <c r="H523" t="n">
         <v>560</v>
@@ -15594,7 +15594,7 @@
         <v>5.5</v>
       </c>
       <c r="G525" t="n">
-        <v>5.15504169464111</v>
+        <v>5.15504121780396</v>
       </c>
       <c r="H525" t="n">
         <v>3840</v>
@@ -15710,7 +15710,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G529" t="n">
-        <v>4.87385654449463</v>
+        <v>4.87385749816895</v>
       </c>
       <c r="H529" t="n">
         <v>22898</v>
@@ -15797,7 +15797,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G532" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H532" t="n">
         <v>121</v>
@@ -15855,7 +15855,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G534" t="n">
-        <v>4.87385654449463</v>
+        <v>4.87385749816895</v>
       </c>
       <c r="H534" t="n">
         <v>2718</v>
@@ -15884,7 +15884,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>4.87385654449463</v>
+        <v>4.87385749816895</v>
       </c>
       <c r="H535" t="n">
         <v>12616</v>
@@ -15942,7 +15942,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G537" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H537" t="n">
         <v>5650</v>
@@ -15971,7 +15971,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G538" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H538" t="n">
         <v>11050</v>
@@ -16029,7 +16029,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G540" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H540" t="n">
         <v>250</v>
@@ -16058,7 +16058,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G541" t="n">
-        <v>4.87385654449463</v>
+        <v>4.87385749816895</v>
       </c>
       <c r="H541" t="n">
         <v>1794</v>
@@ -16087,7 +16087,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G542" t="n">
-        <v>4.93009471893311</v>
+        <v>4.93009424209595</v>
       </c>
       <c r="H542" t="n">
         <v>2795</v>
@@ -16116,7 +16116,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G543" t="n">
-        <v>4.87385654449463</v>
+        <v>4.87385749816895</v>
       </c>
       <c r="H543" t="n">
         <v>4438</v>
@@ -16145,7 +16145,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G544" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H544" t="n">
         <v>1500</v>
@@ -16203,7 +16203,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G546" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H546" t="n">
         <v>3803</v>
@@ -16232,7 +16232,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G547" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H547" t="n">
         <v>0</v>
@@ -16261,7 +16261,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G548" t="n">
-        <v>4.78012943267822</v>
+        <v>4.78012895584106</v>
       </c>
       <c r="H548" t="n">
         <v>0</v>
@@ -16290,7 +16290,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G549" t="n">
-        <v>4.7426381111145</v>
+        <v>4.74263763427734</v>
       </c>
       <c r="H549" t="n">
         <v>400</v>
@@ -16377,7 +16377,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G552" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H552" t="n">
         <v>2770</v>
@@ -16464,7 +16464,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G555" t="n">
-        <v>4.72389221191406</v>
+        <v>4.72389268875122</v>
       </c>
       <c r="H555" t="n">
         <v>1730</v>
@@ -16609,7 +16609,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>4.59267330169678</v>
+        <v>4.59267282485962</v>
       </c>
       <c r="H560" t="n">
         <v>2062</v>
@@ -16638,7 +16638,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G561" t="n">
-        <v>4.59267330169678</v>
+        <v>4.59267282485962</v>
       </c>
       <c r="H561" t="n">
         <v>0</v>
@@ -16667,7 +16667,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G562" t="n">
-        <v>4.79887437820435</v>
+        <v>4.7988748550415</v>
       </c>
       <c r="H562" t="n">
         <v>5341</v>
@@ -16696,7 +16696,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G563" t="n">
-        <v>4.83636569976807</v>
+        <v>4.83636617660522</v>
       </c>
       <c r="H563" t="n">
         <v>5514</v>
@@ -16725,7 +16725,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G564" t="n">
-        <v>4.98633146286011</v>
+        <v>4.98633098602295</v>
       </c>
       <c r="H564" t="n">
         <v>4495</v>
@@ -16957,7 +16957,7 @@
         <v>4.25</v>
       </c>
       <c r="G572" t="n">
-        <v>3.9834406375885</v>
+        <v>3.98344135284424</v>
       </c>
       <c r="H572" t="n">
         <v>9140</v>
@@ -17334,7 +17334,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G585" t="n">
-        <v>4.00218629837036</v>
+        <v>4.00218677520752</v>
       </c>
       <c r="H585" t="n">
         <v>1475</v>
@@ -17363,7 +17363,7 @@
         <v>4.25</v>
       </c>
       <c r="G586" t="n">
-        <v>3.9834406375885</v>
+        <v>3.98344135284424</v>
       </c>
       <c r="H586" t="n">
         <v>2353</v>
@@ -17392,7 +17392,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G587" t="n">
-        <v>3.92720413208008</v>
+        <v>3.92720437049866</v>
       </c>
       <c r="H587" t="n">
         <v>1105</v>
@@ -17566,7 +17566,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G593" t="n">
-        <v>4.03967809677124</v>
+        <v>4.03967761993408</v>
       </c>
       <c r="H593" t="n">
         <v>12527</v>
@@ -17595,7 +17595,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G594" t="n">
-        <v>4.00218629837036</v>
+        <v>4.00218677520752</v>
       </c>
       <c r="H594" t="n">
         <v>22055</v>
@@ -17682,7 +17682,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G597" t="n">
-        <v>4.06779623031616</v>
+        <v>4.06779670715332</v>
       </c>
       <c r="H597" t="n">
         <v>2200</v>
@@ -17711,7 +17711,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G598" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H598" t="n">
         <v>5102</v>
@@ -17740,7 +17740,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G599" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H599" t="n">
         <v>4178</v>
@@ -17769,7 +17769,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G600" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H600" t="n">
         <v>2406</v>
@@ -17856,7 +17856,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G603" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H603" t="n">
         <v>5008</v>
@@ -17885,7 +17885,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G604" t="n">
-        <v>4.10528755187988</v>
+        <v>4.10528802871704</v>
       </c>
       <c r="H604" t="n">
         <v>7230</v>
@@ -17972,7 +17972,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G607" t="n">
-        <v>4.13340616226196</v>
+        <v>4.1334056854248</v>
       </c>
       <c r="H607" t="n">
         <v>55370</v>
@@ -18001,7 +18001,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G608" t="n">
-        <v>4.12403345108032</v>
+        <v>4.12403297424316</v>
       </c>
       <c r="H608" t="n">
         <v>2894</v>
@@ -18030,7 +18030,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G609" t="n">
-        <v>4.00218629837036</v>
+        <v>4.00218677520752</v>
       </c>
       <c r="H609" t="n">
         <v>1958</v>
@@ -18059,7 +18059,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G610" t="n">
-        <v>4.00218629837036</v>
+        <v>4.00218677520752</v>
       </c>
       <c r="H610" t="n">
         <v>2262</v>
@@ -18088,7 +18088,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G611" t="n">
-        <v>4.05842399597168</v>
+        <v>4.05842351913452</v>
       </c>
       <c r="H611" t="n">
         <v>2515</v>
@@ -18117,7 +18117,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>4.09591484069824</v>
+        <v>4.09591436386108</v>
       </c>
       <c r="H612" t="n">
         <v>401</v>
@@ -18146,7 +18146,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G613" t="n">
-        <v>4.09591484069824</v>
+        <v>4.09591436386108</v>
       </c>
       <c r="H613" t="n">
         <v>0</v>
@@ -18175,7 +18175,7 @@
         <v>4.25</v>
       </c>
       <c r="G614" t="n">
-        <v>3.9834406375885</v>
+        <v>3.98344135284424</v>
       </c>
       <c r="H614" t="n">
         <v>2924</v>
@@ -18204,7 +18204,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G615" t="n">
-        <v>4.03967809677124</v>
+        <v>4.03967761993408</v>
       </c>
       <c r="H615" t="n">
         <v>320</v>
@@ -18233,7 +18233,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G616" t="n">
-        <v>3.92720413208008</v>
+        <v>3.92720437049866</v>
       </c>
       <c r="H616" t="n">
         <v>3977</v>
@@ -18262,7 +18262,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G617" t="n">
-        <v>3.87096762657166</v>
+        <v>3.87096738815308</v>
       </c>
       <c r="H617" t="n">
         <v>5257</v>
@@ -18639,7 +18639,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G630" t="n">
-        <v>3.68351149559021</v>
+        <v>3.68351125717163</v>
       </c>
       <c r="H630" t="n">
         <v>9933</v>
@@ -18668,7 +18668,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G631" t="n">
-        <v>3.66476607322693</v>
+        <v>3.66476583480835</v>
       </c>
       <c r="H631" t="n">
         <v>2461</v>
@@ -18697,7 +18697,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G632" t="n">
-        <v>3.64602041244507</v>
+        <v>3.64602017402649</v>
       </c>
       <c r="H632" t="n">
         <v>3650</v>
@@ -18755,7 +18755,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G634" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H634" t="n">
         <v>3900</v>
@@ -18784,7 +18784,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G635" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H635" t="n">
         <v>6237</v>
@@ -18813,7 +18813,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G636" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H636" t="n">
         <v>7752</v>
@@ -18842,7 +18842,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G637" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H637" t="n">
         <v>1500</v>
@@ -18871,7 +18871,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G638" t="n">
-        <v>3.71341037750244</v>
+        <v>3.71341013908386</v>
       </c>
       <c r="H638" t="n">
         <v>8760</v>
@@ -18900,7 +18900,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G639" t="n">
-        <v>3.71341037750244</v>
+        <v>3.71341013908386</v>
       </c>
       <c r="H639" t="n">
         <v>0</v>
@@ -18929,7 +18929,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G640" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H640" t="n">
         <v>1052</v>
@@ -18958,7 +18958,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G641" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H641" t="n">
         <v>10</v>
@@ -18987,7 +18987,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G642" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H642" t="n">
         <v>90</v>
@@ -19103,7 +19103,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G646" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H646" t="n">
         <v>13400</v>
@@ -19190,7 +19190,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G649" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H649" t="n">
         <v>4153</v>
@@ -19248,7 +19248,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G651" t="n">
-        <v>3.65583801269531</v>
+        <v>3.65583825111389</v>
       </c>
       <c r="H651" t="n">
         <v>900</v>
@@ -19277,7 +19277,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G652" t="n">
-        <v>3.65583801269531</v>
+        <v>3.65583825111389</v>
       </c>
       <c r="H652" t="n">
         <v>10</v>
@@ -19335,7 +19335,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G654" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H654" t="n">
         <v>3015</v>
@@ -19393,7 +19393,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G656" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H656" t="n">
         <v>3182</v>
@@ -19422,7 +19422,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G657" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H657" t="n">
         <v>1517</v>
@@ -19480,7 +19480,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G659" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H659" t="n">
         <v>100</v>
@@ -19509,7 +19509,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G660" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H660" t="n">
         <v>299</v>
@@ -19538,7 +19538,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G661" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H661" t="n">
         <v>1404</v>
@@ -19567,7 +19567,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G662" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H662" t="n">
         <v>0</v>
@@ -19625,7 +19625,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G664" t="n">
-        <v>3.72300601005554</v>
+        <v>3.72300577163696</v>
       </c>
       <c r="H664" t="n">
         <v>800</v>
@@ -19712,7 +19712,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>4.12601184844971</v>
+        <v>4.12601137161255</v>
       </c>
       <c r="H667" t="n">
         <v>45390</v>
@@ -19770,7 +19770,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G669" t="n">
-        <v>4.12601184844971</v>
+        <v>4.12601137161255</v>
       </c>
       <c r="H669" t="n">
         <v>8487</v>
@@ -19799,7 +19799,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G670" t="n">
-        <v>4.12601184844971</v>
+        <v>4.12601137161255</v>
       </c>
       <c r="H670" t="n">
         <v>2970</v>
@@ -19973,7 +19973,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G676" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H676" t="n">
         <v>1500</v>
@@ -20089,7 +20089,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G680" t="n">
-        <v>4.02046203613281</v>
+        <v>4.02046251296997</v>
       </c>
       <c r="H680" t="n">
         <v>1420</v>
@@ -20118,7 +20118,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G681" t="n">
-        <v>3.99167609214783</v>
+        <v>3.99167633056641</v>
       </c>
       <c r="H681" t="n">
         <v>1555</v>
@@ -20176,7 +20176,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G683" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H683" t="n">
         <v>10</v>
@@ -20205,7 +20205,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G684" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H684" t="n">
         <v>9595</v>
@@ -20292,7 +20292,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G687" t="n">
-        <v>3.99167609214783</v>
+        <v>3.99167633056641</v>
       </c>
       <c r="H687" t="n">
         <v>750</v>
@@ -20321,7 +20321,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G688" t="n">
-        <v>3.99167609214783</v>
+        <v>3.99167633056641</v>
       </c>
       <c r="H688" t="n">
         <v>0</v>
@@ -20350,7 +20350,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G689" t="n">
-        <v>3.98208093643188</v>
+        <v>3.98208069801331</v>
       </c>
       <c r="H689" t="n">
         <v>150</v>
@@ -20379,7 +20379,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G690" t="n">
-        <v>4.03965282440186</v>
+        <v>4.03965330123901</v>
       </c>
       <c r="H690" t="n">
         <v>1160</v>
@@ -20408,7 +20408,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G691" t="n">
-        <v>4.03965282440186</v>
+        <v>4.03965330123901</v>
       </c>
       <c r="H691" t="n">
         <v>10</v>
@@ -20437,7 +20437,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G692" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H692" t="n">
         <v>11</v>
@@ -20466,7 +20466,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G693" t="n">
-        <v>4.03965282440186</v>
+        <v>4.03965330123901</v>
       </c>
       <c r="H693" t="n">
         <v>1069</v>
@@ -20524,7 +20524,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G695" t="n">
-        <v>3.98208093643188</v>
+        <v>3.98208069801331</v>
       </c>
       <c r="H695" t="n">
         <v>1981</v>
@@ -20553,7 +20553,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>3.98208093643188</v>
+        <v>3.98208069801331</v>
       </c>
       <c r="H696" t="n">
         <v>0</v>
@@ -20582,7 +20582,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G697" t="n">
-        <v>3.98208093643188</v>
+        <v>3.98208069801331</v>
       </c>
       <c r="H697" t="n">
         <v>120</v>
@@ -20611,7 +20611,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G698" t="n">
-        <v>4.02046203613281</v>
+        <v>4.02046251296997</v>
       </c>
       <c r="H698" t="n">
         <v>245</v>
@@ -20669,7 +20669,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G700" t="n">
-        <v>3.9436993598938</v>
+        <v>3.94369959831238</v>
       </c>
       <c r="H700" t="n">
         <v>210</v>
@@ -20698,7 +20698,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G701" t="n">
-        <v>3.9436993598938</v>
+        <v>3.94369959831238</v>
       </c>
       <c r="H701" t="n">
         <v>280</v>
@@ -20930,7 +20930,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G709" t="n">
-        <v>3.87653160095215</v>
+        <v>3.87653183937073</v>
       </c>
       <c r="H709" t="n">
         <v>1788</v>
@@ -21017,7 +21017,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G712" t="n">
-        <v>3.93410396575928</v>
+        <v>3.9341037273407</v>
       </c>
       <c r="H712" t="n">
         <v>3931</v>
@@ -21046,7 +21046,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G713" t="n">
-        <v>3.84774589538574</v>
+        <v>3.84774565696716</v>
       </c>
       <c r="H713" t="n">
         <v>5760</v>
@@ -21075,7 +21075,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G714" t="n">
-        <v>3.79017353057861</v>
+        <v>3.79017329216003</v>
       </c>
       <c r="H714" t="n">
         <v>185</v>
@@ -21104,7 +21104,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G715" t="n">
-        <v>3.77098274230957</v>
+        <v>3.77098250389099</v>
       </c>
       <c r="H715" t="n">
         <v>540</v>
@@ -21133,7 +21133,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G716" t="n">
-        <v>3.75179195404053</v>
+        <v>3.75179171562195</v>
       </c>
       <c r="H716" t="n">
         <v>330</v>
@@ -21162,7 +21162,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G717" t="n">
-        <v>3.75179195404053</v>
+        <v>3.75179171562195</v>
       </c>
       <c r="H717" t="n">
         <v>0</v>
@@ -21191,7 +21191,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G718" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H718" t="n">
         <v>20488</v>
@@ -21249,7 +21249,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G720" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H720" t="n">
         <v>1602</v>
@@ -21336,7 +21336,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G723" t="n">
-        <v>3.91491341590881</v>
+        <v>3.91491317749023</v>
       </c>
       <c r="H723" t="n">
         <v>750</v>
@@ -21365,7 +21365,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G724" t="n">
-        <v>4.21236991882324</v>
+        <v>4.21236944198608</v>
       </c>
       <c r="H724" t="n">
         <v>46988</v>
@@ -21423,7 +21423,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G726" t="n">
-        <v>4.21236991882324</v>
+        <v>4.21236944198608</v>
       </c>
       <c r="H726" t="n">
         <v>70435</v>
@@ -21481,7 +21481,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G728" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H728" t="n">
         <v>172</v>
@@ -21597,7 +21597,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G732" t="n">
-        <v>4.18358373641968</v>
+        <v>4.18358421325684</v>
       </c>
       <c r="H732" t="n">
         <v>1320</v>
@@ -21742,7 +21742,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G737" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H737" t="n">
         <v>1637</v>
@@ -21771,7 +21771,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G738" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H738" t="n">
         <v>75279</v>
@@ -21800,7 +21800,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G739" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H739" t="n">
         <v>0</v>
@@ -21829,7 +21829,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G740" t="n">
-        <v>3.99167609214783</v>
+        <v>3.99167633056641</v>
       </c>
       <c r="H740" t="n">
         <v>7953</v>
@@ -21974,7 +21974,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G745" t="n">
-        <v>3.93410396575928</v>
+        <v>3.9341037273407</v>
       </c>
       <c r="H745" t="n">
         <v>81270</v>
@@ -22003,7 +22003,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G746" t="n">
-        <v>3.93410396575928</v>
+        <v>3.9341037273407</v>
       </c>
       <c r="H746" t="n">
         <v>3945</v>
@@ -22032,7 +22032,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G747" t="n">
-        <v>3.91491341590881</v>
+        <v>3.91491317749023</v>
       </c>
       <c r="H747" t="n">
         <v>196255</v>
@@ -22119,7 +22119,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G750" t="n">
-        <v>4.0588436126709</v>
+        <v>4.05884408950806</v>
       </c>
       <c r="H750" t="n">
         <v>1996</v>
@@ -22148,7 +22148,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G751" t="n">
-        <v>3.98208093643188</v>
+        <v>3.98208069801331</v>
       </c>
       <c r="H751" t="n">
         <v>7044</v>
@@ -22206,7 +22206,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G753" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H753" t="n">
         <v>7875</v>
@@ -22235,7 +22235,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>4.03965282440186</v>
+        <v>4.03965330123901</v>
       </c>
       <c r="H754" t="n">
         <v>498</v>
@@ -22264,7 +22264,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G755" t="n">
-        <v>3.91491341590881</v>
+        <v>3.91491317749023</v>
       </c>
       <c r="H755" t="n">
         <v>21081</v>
@@ -22641,7 +22641,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>3.63664722442627</v>
+        <v>3.63664746284485</v>
       </c>
       <c r="H768" t="n">
         <v>8155</v>
@@ -22670,7 +22670,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G769" t="n">
-        <v>3.61745643615723</v>
+        <v>3.61745667457581</v>
       </c>
       <c r="H769" t="n">
         <v>19701</v>
@@ -22786,7 +22786,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G773" t="n">
-        <v>3.61745643615723</v>
+        <v>3.61745667457581</v>
       </c>
       <c r="H773" t="n">
         <v>16809</v>
@@ -22902,7 +22902,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>3.63664722442627</v>
+        <v>3.63664746284485</v>
       </c>
       <c r="H777" t="n">
         <v>23488</v>
@@ -22931,7 +22931,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G778" t="n">
-        <v>3.63664722442627</v>
+        <v>3.63664746284485</v>
       </c>
       <c r="H778" t="n">
         <v>5020</v>
@@ -23105,7 +23105,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G784" t="n">
-        <v>3.40635848045349</v>
+        <v>3.40635824203491</v>
       </c>
       <c r="H784" t="n">
         <v>13684</v>
@@ -23192,7 +23192,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H787" t="n">
         <v>1420</v>
@@ -23221,7 +23221,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G788" t="n">
-        <v>3.65583801269531</v>
+        <v>3.65583825111389</v>
       </c>
       <c r="H788" t="n">
         <v>1250</v>
@@ -23627,7 +23627,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G802" t="n">
-        <v>3.53109836578369</v>
+        <v>3.53109812736511</v>
       </c>
       <c r="H802" t="n">
         <v>18225</v>
@@ -23772,7 +23772,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G807" t="n">
-        <v>3.53109836578369</v>
+        <v>3.53109812736511</v>
       </c>
       <c r="H807" t="n">
         <v>6020</v>
@@ -23801,7 +23801,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G808" t="n">
-        <v>3.55988430976868</v>
+        <v>3.55988454818726</v>
       </c>
       <c r="H808" t="n">
         <v>5589</v>
@@ -23859,7 +23859,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G810" t="n">
-        <v>3.60786104202271</v>
+        <v>3.60786128044128</v>
       </c>
       <c r="H810" t="n">
         <v>35932</v>
@@ -23888,7 +23888,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G811" t="n">
-        <v>3.6846239566803</v>
+        <v>3.68462419509888</v>
       </c>
       <c r="H811" t="n">
         <v>3848</v>
@@ -23917,7 +23917,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G812" t="n">
-        <v>3.67502856254578</v>
+        <v>3.67502880096436</v>
       </c>
       <c r="H812" t="n">
         <v>10695</v>
@@ -23946,7 +23946,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G813" t="n">
-        <v>3.71341037750244</v>
+        <v>3.71341013908386</v>
       </c>
       <c r="H813" t="n">
         <v>3973</v>
@@ -23975,7 +23975,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G814" t="n">
-        <v>3.79017353057861</v>
+        <v>3.79017329216003</v>
       </c>
       <c r="H814" t="n">
         <v>8700</v>
@@ -24004,7 +24004,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G815" t="n">
-        <v>3.75179195404053</v>
+        <v>3.75179171562195</v>
       </c>
       <c r="H815" t="n">
         <v>4141</v>
@@ -24091,7 +24091,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G818" t="n">
-        <v>3.91491341590881</v>
+        <v>3.91491317749023</v>
       </c>
       <c r="H818" t="n">
         <v>4284</v>
@@ -24120,7 +24120,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G819" t="n">
-        <v>4.25075149536133</v>
+        <v>4.25075101852417</v>
       </c>
       <c r="H819" t="n">
         <v>51273</v>
@@ -24236,7 +24236,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G823" t="n">
-        <v>4.25075149536133</v>
+        <v>4.25075101852417</v>
       </c>
       <c r="H823" t="n">
         <v>21761</v>
@@ -24265,7 +24265,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G824" t="n">
-        <v>4.29872798919678</v>
+        <v>4.29872846603394</v>
       </c>
       <c r="H824" t="n">
         <v>12287</v>
@@ -24352,7 +24352,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G827" t="n">
-        <v>4.26994228363037</v>
+        <v>4.26994180679321</v>
       </c>
       <c r="H827" t="n">
         <v>3147</v>
@@ -24613,7 +24613,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G836" t="n">
-        <v>4.09722518920898</v>
+        <v>4.09722566604614</v>
       </c>
       <c r="H836" t="n">
         <v>440</v>
@@ -24642,7 +24642,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G837" t="n">
-        <v>4.12601184844971</v>
+        <v>4.12601137161255</v>
       </c>
       <c r="H837" t="n">
         <v>1700</v>
@@ -24874,7 +24874,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G845" t="n">
-        <v>4.12601184844971</v>
+        <v>4.12601137161255</v>
       </c>
       <c r="H845" t="n">
         <v>1616</v>
@@ -24903,7 +24903,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G846" t="n">
-        <v>4.12601184844971</v>
+        <v>4.12601137161255</v>
       </c>
       <c r="H846" t="n">
         <v>0</v>
@@ -25193,7 +25193,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G856" t="n">
-        <v>4.21236991882324</v>
+        <v>4.21236944198608</v>
       </c>
       <c r="H856" t="n">
         <v>12800</v>
@@ -25251,7 +25251,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G858" t="n">
-        <v>4.02046203613281</v>
+        <v>4.02046251296997</v>
       </c>
       <c r="H858" t="n">
         <v>3537</v>
@@ -25309,7 +25309,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G860" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H860" t="n">
         <v>2994</v>
@@ -25338,7 +25338,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G861" t="n">
-        <v>4.01086711883545</v>
+        <v>4.01086664199829</v>
       </c>
       <c r="H861" t="n">
         <v>280</v>
@@ -25657,7 +25657,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G872" t="n">
-        <v>3.91491341590881</v>
+        <v>3.91491317749023</v>
       </c>
       <c r="H872" t="n">
         <v>1409</v>
@@ -25686,7 +25686,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G873" t="n">
-        <v>3.91491341590881</v>
+        <v>3.91491317749023</v>
       </c>
       <c r="H873" t="n">
         <v>4382</v>
@@ -25831,7 +25831,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G878" t="n">
-        <v>3.97248554229736</v>
+        <v>3.97248530387878</v>
       </c>
       <c r="H878" t="n">
         <v>850</v>
@@ -25860,7 +25860,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G879" t="n">
-        <v>3.9436993598938</v>
+        <v>3.94369959831238</v>
       </c>
       <c r="H879" t="n">
         <v>3403</v>
@@ -25889,7 +25889,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G880" t="n">
-        <v>3.99167609214783</v>
+        <v>3.99167633056641</v>
       </c>
       <c r="H880" t="n">
         <v>17094</v>
@@ -25918,7 +25918,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G881" t="n">
-        <v>3.97248554229736</v>
+        <v>3.97248530387878</v>
       </c>
       <c r="H881" t="n">
         <v>7211</v>
@@ -26005,7 +26005,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G884" t="n">
-        <v>3.98208093643188</v>
+        <v>3.98208069801331</v>
       </c>
       <c r="H884" t="n">
         <v>2973</v>
@@ -36886,6 +36886,35 @@
         <v>1800</v>
       </c>
       <c r="I1259" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1260" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1260" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="D1260" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="E1260" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="F1260" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="G1260" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="H1260" t="n">
+        <v>405</v>
+      </c>
+      <c r="I1260" t="s">
         <v>9</v>
       </c>
     </row>
